--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217515945435</t>
+    <t xml:space="preserve">7.18217420578003</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051198959351</t>
+    <t xml:space="preserve">7.16394424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07279968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925912857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051151275635</t>
   </si>
   <si>
     <t xml:space="preserve">7.14207029342651</t>
@@ -68,43 +68,43 @@
     <t xml:space="preserve">6.96707344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03634357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96342754364014</t>
+    <t xml:space="preserve">7.03634262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717687606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96342849731445</t>
   </si>
   <si>
     <t xml:space="preserve">7.25144386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863174438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362955093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737840652466</t>
+    <t xml:space="preserve">7.27696466445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154825210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238107681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737888336182</t>
   </si>
   <si>
     <t xml:space="preserve">7.28790235519409</t>
@@ -113,34 +113,34 @@
     <t xml:space="preserve">7.28425550460815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43008661270142</t>
+    <t xml:space="preserve">7.4300856590271</t>
   </si>
   <si>
     <t xml:space="preserve">7.51029348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66341543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48842000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112726211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613088607788</t>
+    <t xml:space="preserve">7.66341590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154195785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3061318397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.6196665763855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54675245285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216886520386</t>
+    <t xml:space="preserve">7.54675149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216791152954</t>
   </si>
   <si>
     <t xml:space="preserve">7.25508975982666</t>
@@ -149,85 +149,85 @@
     <t xml:space="preserve">7.33529663085938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34987878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29883813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873470306396</t>
+    <t xml:space="preserve">7.3498797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29883909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873565673828</t>
   </si>
   <si>
     <t xml:space="preserve">7.24779748916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21498775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988508224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623918533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5248761177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3863377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320903778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9477858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278270721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424482345581</t>
+    <t xml:space="preserve">7.21498727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050664901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99624061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487707138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133460998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904062271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487173080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424434661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.14273262023926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24770355224609</t>
+    <t xml:space="preserve">8.24770259857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.18022155761719</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030385971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782915115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787796020508</t>
+    <t xml:space="preserve">7.88030433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787843704224</t>
   </si>
   <si>
     <t xml:space="preserve">7.68535995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64787006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527669906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8953013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276611328125</t>
+    <t xml:space="preserve">7.6478705406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98527526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276420593262</t>
   </si>
   <si>
     <t xml:space="preserve">8.0602560043335</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47264194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84003734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4398717880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990337371826</t>
+    <t xml:space="preserve">8.47264003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84003925323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">9.1324577331543</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">8.98249816894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92251586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99749374389648</t>
+    <t xml:space="preserve">8.92251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9974946975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252376556396</t>
+    <t xml:space="preserve">8.89252281188965</t>
   </si>
   <si>
     <t xml:space="preserve">8.66008853912354</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">8.69757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754398345947</t>
+    <t xml:space="preserve">8.59260654449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754302978516</t>
   </si>
   <si>
     <t xml:space="preserve">8.72756862640381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507621765137</t>
+    <t xml:space="preserve">8.70507526397705</t>
   </si>
   <si>
     <t xml:space="preserve">8.79505062103271</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007179260254</t>
+    <t xml:space="preserve">8.72007083892822</t>
   </si>
   <si>
     <t xml:space="preserve">8.6900806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36767101287842</t>
+    <t xml:space="preserve">8.60010433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266468048096</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">8.62259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5476188659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4126558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268333435059</t>
+    <t xml:space="preserve">8.61509990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54761791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268238067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.73506641387939</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">8.90002155303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67508316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51762771606445</t>
+    <t xml:space="preserve">8.67508411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51762676239014</t>
   </si>
   <si>
     <t xml:space="preserve">8.58510875701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3601713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31518363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766120910645</t>
+    <t xml:space="preserve">8.5101318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36017227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31518459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766025543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.3001880645752</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">8.20271492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45764446258545</t>
+    <t xml:space="preserve">8.45764350891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21021366119385</t>
+    <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.11273956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09024715423584</t>
+    <t xml:space="preserve">8.09024810791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.06775283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08274841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277305603027</t>
+    <t xml:space="preserve">8.08274745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277400970459</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777843475342</t>
@@ -467,97 +467,97 @@
     <t xml:space="preserve">8.00777053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76783609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82781934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282377243042</t>
+    <t xml:space="preserve">7.76783657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282424926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026485443115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776168823242</t>
+    <t xml:space="preserve">7.95528411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776073455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780498504639</t>
+    <t xml:space="preserve">7.93279075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780307769775</t>
   </si>
   <si>
     <t xml:space="preserve">7.92529296875</t>
   </si>
   <si>
+    <t xml:space="preserve">7.94778728485107</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.87280750274658</t>
   </si>
   <si>
     <t xml:space="preserve">7.91029644012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76033973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531761169434</t>
+    <t xml:space="preserve">7.76033782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531665802002</t>
   </si>
   <si>
     <t xml:space="preserve">8.09667873382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78823328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21234607696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678890228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55690002441406</t>
+    <t xml:space="preserve">7.78823280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69570064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967908859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534547805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112298965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690050125122</t>
   </si>
   <si>
     <t xml:space="preserve">7.51063299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147815704346</t>
+    <t xml:space="preserve">7.61858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147720336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.47978830337524</t>
@@ -566,79 +566,79 @@
     <t xml:space="preserve">7.32556629180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41810035705566</t>
+    <t xml:space="preserve">7.41809988021851</t>
   </si>
   <si>
     <t xml:space="preserve">7.38725519180298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254365921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507724761963</t>
+    <t xml:space="preserve">7.21760988235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387643814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507629394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929830551147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1713433265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218801498413</t>
+    <t xml:space="preserve">7.17134428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218944549561</t>
   </si>
   <si>
     <t xml:space="preserve">7.10965538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0788106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472208023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014442443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169992446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916538238525</t>
+    <t xml:space="preserve">7.14050006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.310142993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916585922241</t>
   </si>
   <si>
     <t xml:space="preserve">6.83205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92458772659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409915924072</t>
+    <t xml:space="preserve">6.92458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409868240356</t>
   </si>
   <si>
     <t xml:space="preserve">6.73952150344849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712131500244</t>
+    <t xml:space="preserve">6.86289882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712226867676</t>
   </si>
   <si>
     <t xml:space="preserve">6.78578758239746</t>
@@ -656,31 +656,31 @@
     <t xml:space="preserve">6.67783212661743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7086763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4773416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903150558472</t>
+    <t xml:space="preserve">6.70867681503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6315655708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903102874756</t>
   </si>
   <si>
     <t xml:space="preserve">6.61614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974184036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058700561523</t>
+    <t xml:space="preserve">6.52361011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974279403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058748245239</t>
   </si>
   <si>
     <t xml:space="preserve">6.32312059402466</t>
@@ -689,178 +689,178 @@
     <t xml:space="preserve">6.40023231506348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2614312171936</t>
+    <t xml:space="preserve">6.26143169403076</t>
   </si>
   <si>
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56987619400024</t>
+    <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565418243408</t>
+    <t xml:space="preserve">6.41565370559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81663227081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89374351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6469874382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036428451538</t>
+    <t xml:space="preserve">6.81663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89374303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77036619186401</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16889762878418</t>
+    <t xml:space="preserve">6.10720872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16889810562134</t>
   </si>
   <si>
     <t xml:space="preserve">6.09178686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30769824981689</t>
+    <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.246009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66240978240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649839401245</t>
+    <t xml:space="preserve">6.24600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66241025924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649791717529</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516466140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338691711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314340591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64106130599976</t>
+    <t xml:space="preserve">6.36938762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494337081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676519393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338787078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20115041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314245223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313108444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106178283691</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83309173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75307941436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73707628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72107362747192</t>
+    <t xml:space="preserve">7.08913230895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113809585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.833092212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88109970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8650975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75307893753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73707675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
     <t xml:space="preserve">6.48103618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54504585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76908206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81708955764771</t>
+    <t xml:space="preserve">6.54504632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76908254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81709003448486</t>
   </si>
   <si>
     <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706443786621</t>
+    <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305334091187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302822113037</t>
+    <t xml:space="preserve">6.62505865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302869796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.51304149627686</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">6.44903087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41702651977539</t>
+    <t xml:space="preserve">6.41702556610107</t>
   </si>
   <si>
     <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701324462891</t>
+    <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
     <t xml:space="preserve">6.22499513626099</t>
@@ -887,49 +887,49 @@
     <t xml:space="preserve">6.04896688461304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06496953964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697484970093</t>
+    <t xml:space="preserve">6.06496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.1609845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00095987319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95295143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01696157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92094659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76092100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74491834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68090772628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71291303634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82493162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293910980225</t>
+    <t xml:space="preserve">6.0009593963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95295190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895456314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92094707489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74491786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.680908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71291255950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494394302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293863296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.79292583465576</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24099779129028</t>
+    <t xml:space="preserve">6.24099731445312</t>
   </si>
   <si>
     <t xml:space="preserve">6.32101058959961</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">6.27300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20899200439453</t>
+    <t xml:space="preserve">6.20899295806885</t>
   </si>
   <si>
     <t xml:space="preserve">6.1769871711731</t>
@@ -962,40 +962,40 @@
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897920608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1449818611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25699996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93694925308228</t>
+    <t xml:space="preserve">6.12897968292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14498233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25700092315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93694877624512</t>
   </si>
   <si>
     <t xml:space="preserve">6.03296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887729644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290071487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55288743972778</t>
+    <t xml:space="preserve">5.61689805984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887777328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5528883934021</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50487995147705</t>
+    <t xml:space="preserve">5.50488042831421</t>
   </si>
   <si>
     <t xml:space="preserve">5.60089540481567</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">5.36085653305054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12081813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73675680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67274713516235</t>
+    <t xml:space="preserve">5.12081909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73675727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6727466583252</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24067735671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062664031982</t>
+    <t xml:space="preserve">4.24067783355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062616348267</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1606650352478</t>
+    <t xml:space="preserve">4.04864692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16066455841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065223693848</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13682126998901</t>
+    <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">5.40886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.32885217666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0088005065918</t>
+    <t xml:space="preserve">5.18482828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880002975464</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882610321045</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23283672332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47287511825562</t>
+    <t xml:space="preserve">5.23283576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47287464141846</t>
   </si>
   <si>
     <t xml:space="preserve">5.72891569137573</t>
@@ -1094,40 +1094,40 @@
     <t xml:space="preserve">5.77692317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6969108581543</t>
+    <t xml:space="preserve">5.69690990447998</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486715316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56889009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34485483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44087028503418</t>
+    <t xml:space="preserve">5.58489322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56888961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44086980819702</t>
   </si>
   <si>
     <t xml:space="preserve">5.37685918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26484107971191</t>
+    <t xml:space="preserve">5.26484155654907</t>
   </si>
   <si>
     <t xml:space="preserve">5.24883937835693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45687198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688526153564</t>
+    <t xml:space="preserve">5.45687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688478469849</t>
   </si>
   <si>
     <t xml:space="preserve">5.29684638977051</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49703788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7050724029541</t>
+    <t xml:space="preserve">6.28900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
     <t xml:space="preserve">6.67306709289551</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">6.91310501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24915885925293</t>
+    <t xml:space="preserve">7.24915933609009</t>
   </si>
   <si>
     <t xml:space="preserve">7.26516151428223</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">7.28116416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64922285079956</t>
+    <t xml:space="preserve">7.6492223739624</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60121536254883</t>
+    <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.52120161056519</t>
@@ -1181,46 +1181,46 @@
     <t xml:space="preserve">7.47319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44118881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40918445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50520038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716539382935</t>
+    <t xml:space="preserve">7.44118928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40918397903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3131685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716634750366</t>
   </si>
   <si>
     <t xml:space="preserve">7.74523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84125328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526390075684</t>
+    <t xml:space="preserve">7.84125232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526294708252</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">8.04128551483154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92126655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87325716018677</t>
+    <t xml:space="preserve">7.92126560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8732590675354</t>
   </si>
   <si>
     <t xml:space="preserve">7.95327138900757</t>
@@ -1247,43 +1247,43 @@
     <t xml:space="preserve">8.12129783630371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96927404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44134902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00144004821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04144668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143245697021</t>
+    <t xml:space="preserve">7.96927356719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28132343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44134998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00143814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8414134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9614315032959</t>
   </si>
   <si>
     <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48151683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72155380249023</t>
+    <t xml:space="preserve">9.48151588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72155284881592</t>
   </si>
   <si>
     <t xml:space="preserve">9.84157371520996</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">10.1616249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0816125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.121618270874</t>
+    <t xml:space="preserve">10.0816106796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1216173171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.2816429138184</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218088150024</t>
+    <t xml:space="preserve">11.3218097686768</t>
   </si>
   <si>
     <t xml:space="preserve">11.2017908096313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1217775344849</t>
+    <t xml:space="preserve">11.1217784881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617851257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8417339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8817405700684</t>
+    <t xml:space="preserve">11.1617832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8417329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881739616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818353652954</t>
@@ -1340,61 +1340,61 @@
     <t xml:space="preserve">11.0817708969116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.76171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017585754395</t>
+    <t xml:space="preserve">10.7617197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017576217651</t>
   </si>
   <si>
     <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.60169506073</t>
+    <t xml:space="preserve">10.6016941070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818040847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6965770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573705673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7011222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4937362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.037486076355</t>
+    <t xml:space="preserve">11.6965761184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7011213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4937353134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0374879837036</t>
   </si>
   <si>
     <t xml:space="preserve">10.1204414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1619186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9545316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4107818603516</t>
+    <t xml:space="preserve">10.161919593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95453262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4107828140259</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9914617538452</t>
+    <t xml:space="preserve">10.9914627075195</t>
   </si>
   <si>
     <t xml:space="preserve">10.7425994873047</t>
@@ -1403,52 +1403,52 @@
     <t xml:space="preserve">10.8255548477173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5766916275024</t>
+    <t xml:space="preserve">10.5766906738281</t>
   </si>
   <si>
     <t xml:space="preserve">10.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863492965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033967971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.452260017395</t>
+    <t xml:space="preserve">10.6181688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033958435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87157726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522581100464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7840757369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1158933639526</t>
+    <t xml:space="preserve">10.7840766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535213470459</t>
+    <t xml:space="preserve">10.5352144241333</t>
   </si>
   <si>
     <t xml:space="preserve">10.6596450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0329399108887</t>
+    <t xml:space="preserve">11.032940864563</t>
   </si>
   <si>
     <t xml:space="preserve">11.323281288147</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2403268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5721454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5306663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7795295715332</t>
+    <t xml:space="preserve">11.2403259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5721435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5306673049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7795305252075</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
@@ -1478,31 +1478,31 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5675973892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.816460609436</t>
+    <t xml:space="preserve">12.3187341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261201858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8164596557617</t>
   </si>
   <si>
     <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5630502700806</t>
+    <t xml:space="preserve">13.5630521774292</t>
   </si>
   <si>
     <t xml:space="preserve">13.8119134902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6460065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215740203857</t>
+    <t xml:space="preserve">13.6460056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215721130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141870498657</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0192995071411</t>
+    <t xml:space="preserve">14.0192985534668</t>
   </si>
   <si>
     <t xml:space="preserve">13.894868850708</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.609073638916</t>
+    <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846429824829</t>
@@ -1538,40 +1538,40 @@
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062356948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8210077285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988496780396</t>
+    <t xml:space="preserve">11.3647565841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8210067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988487243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6641902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74714756011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6136207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4808940887451</t>
+    <t xml:space="preserve">11.7380533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.747145652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.613621711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4808931350708</t>
   </si>
   <si>
     <t xml:space="preserve">11.0661220550537</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">10.7177133560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9665784835815</t>
+    <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
     <t xml:space="preserve">10.7343044281006</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504419326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168033599854</t>
+    <t xml:space="preserve">10.6679410934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168043136597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8006687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9002122879028</t>
+    <t xml:space="preserve">10.9002132415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172588348389</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.8338499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5849866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4003820419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4693689346313</t>
+    <t xml:space="preserve">10.5849857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693698883057</t>
   </si>
   <si>
     <t xml:space="preserve">11.331392288208</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">11.9005489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2454919815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109966278076</t>
+    <t xml:space="preserve">12.2454929351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109975814819</t>
   </si>
   <si>
     <t xml:space="preserve">12.2282457351685</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">12.1592569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4179639816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.193751335144</t>
+    <t xml:space="preserve">12.4179630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937503814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.021279335022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1420097351074</t>
+    <t xml:space="preserve">12.1420087814331</t>
   </si>
   <si>
     <t xml:space="preserve">11.88330078125</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106609344482</t>
+    <t xml:space="preserve">11.2106618881226</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">11.1589202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3831338882446</t>
+    <t xml:space="preserve">11.7625722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.831561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
     <t xml:space="preserve">11.9522895812988</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">11.7280778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5728521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7453241348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.69358253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8660545349121</t>
+    <t xml:space="preserve">11.5728530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7453231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6935834884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6763353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8660554885864</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9867839813232</t>
+    <t xml:space="preserve">11.9867849349976</t>
   </si>
   <si>
     <t xml:space="preserve">11.9177961349487</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075143814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0902671813965</t>
+    <t xml:space="preserve">11.9695386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350423812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
     <t xml:space="preserve">11.7970657348633</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">11.6073474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486385345459</t>
+    <t xml:space="preserve">11.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486394882202</t>
   </si>
   <si>
     <t xml:space="preserve">11.245156288147</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">11.3658866882324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5211114883423</t>
+    <t xml:space="preserve">11.521110534668</t>
   </si>
   <si>
     <t xml:space="preserve">11.5900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6418418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381898880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209436416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1244258880615</t>
+    <t xml:space="preserve">11.6418409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4348745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1071796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1244249343872</t>
   </si>
   <si>
     <t xml:space="preserve">11.1416730880737</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">10.969202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8829650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415061950684</t>
+    <t xml:space="preserve">10.8829660415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.641505241394</t>
   </si>
   <si>
     <t xml:space="preserve">10.1758317947388</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">10.5207748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3483028411865</t>
+    <t xml:space="preserve">10.3483037948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">10.193078994751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4862813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383586883545</t>
+    <t xml:space="preserve">10.4862804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312253952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383577346802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
@@ -1850,28 +1850,28 @@
     <t xml:space="preserve">11.4176273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8143129348755</t>
+    <t xml:space="preserve">11.8143119812012</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4697046279907</t>
+    <t xml:space="preserve">12.469705581665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007177352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869527816772</t>
+    <t xml:space="preserve">12.4007167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662233352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869518280029</t>
   </si>
   <si>
     <t xml:space="preserve">12.573187828064</t>
@@ -1880,94 +1880,94 @@
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521448135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386943817139</t>
+    <t xml:space="preserve">12.5214471817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386934280396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2799873352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4352121353149</t>
+    <t xml:space="preserve">12.2799854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4352111816406</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108297348022</t>
+    <t xml:space="preserve">11.7108306884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521217346191</t>
+    <t xml:space="preserve">11.4521226882935</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2796516418457</t>
+    <t xml:space="preserve">11.2796497344971</t>
   </si>
   <si>
     <t xml:space="preserve">11.3141450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9519538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0899314880371</t>
+    <t xml:space="preserve">10.9519548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0899324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7967300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657197952271</t>
+    <t xml:space="preserve">10.7967290878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657178878784</t>
   </si>
   <si>
     <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5725164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6070117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345388412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4517860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.469033241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380229949951</t>
+    <t xml:space="preserve">10.5725173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6070108413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4690341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380210876465</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2770614624023</t>
+    <t xml:space="preserve">10.277060508728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3850517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4930410385132</t>
+    <t xml:space="preserve">10.3850507736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4930419921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.043083190918</t>
+    <t xml:space="preserve">10.0430822372437</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509197235107</t>
+    <t xml:space="preserve">9.93509292602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.187068939209</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">9.97108840942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89909648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250844955444</t>
+    <t xml:space="preserve">9.89909553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95309066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">9.80910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2030,19 +2030,19 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.421049118042</t>
+    <t xml:space="preserve">10.4210481643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030504226685</t>
+    <t xml:space="preserve">10.4030494689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.3130578994751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950601577759</t>
+    <t xml:space="preserve">10.2950592041016</t>
   </si>
   <si>
     <t xml:space="preserve">10.3670530319214</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41313934326172</t>
+    <t xml:space="preserve">9.41314029693604</t>
   </si>
   <si>
     <t xml:space="preserve">9.17916107177734</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48513412475586</t>
+    <t xml:space="preserve">9.28715133666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37714385986328</t>
+    <t xml:space="preserve">9.37714290618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.35914516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32314777374268</t>
+    <t xml:space="preserve">9.32314872741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.25115489959717</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85519027709961</t>
+    <t xml:space="preserve">8.87318992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.97218132019043</t>
@@ -2117,10 +2117,10 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4772253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62121200561523</t>
+    <t xml:space="preserve">8.47722625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62121295928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.63921070098877</t>
@@ -2132,25 +2132,25 @@
     <t xml:space="preserve">8.72920227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60321426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9012770652771</t>
+    <t xml:space="preserve">8.60321521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90127754211426</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04526519775391</t>
+    <t xml:space="preserve">8.04526424407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.05426406860352</t>
@@ -2162,43 +2162,43 @@
     <t xml:space="preserve">7.96427249908447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91027784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81128644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227914810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927671432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79328775405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64930152893066</t>
+    <t xml:space="preserve">7.91027736663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81128692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828449249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.793288230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64930200576782</t>
   </si>
   <si>
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130235671997</t>
+    <t xml:space="preserve">7.63130283355713</t>
   </si>
   <si>
     <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19934225082397</t>
+    <t xml:space="preserve">7.19934272766113</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">6.69538831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74038410186768</t>
+    <t xml:space="preserve">6.74038362503052</t>
   </si>
   <si>
     <t xml:space="preserve">6.77638101577759</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">7.19034290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16334581375122</t>
+    <t xml:space="preserve">7.16334533691406</t>
   </si>
   <si>
     <t xml:space="preserve">7.10935068130493</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42432165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51431369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631452560425</t>
+    <t xml:space="preserve">7.4243221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5143141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631547927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.30733203887939</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28933429718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28033542633057</t>
+    <t xml:space="preserve">7.28933477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28033494949341</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434646606445</t>
+    <t xml:space="preserve">7.15434598922729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136041641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05535554885864</t>
+    <t xml:space="preserve">7.00136089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0553560256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
@@ -2285,19 +2285,19 @@
     <t xml:space="preserve">7.68529796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99127006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9462742805481</t>
+    <t xml:space="preserve">7.99126958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627380371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024459838867</t>
+    <t xml:space="preserve">8.27024364471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.37823486328125</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">8.55821895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75619983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66620826721191</t>
+    <t xml:space="preserve">8.75619888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66620922088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56721878051758</t>
+    <t xml:space="preserve">8.56721782684326</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923503875732</t>
+    <t xml:space="preserve">8.36923599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19824981689453</t>
+    <t xml:space="preserve">8.19825077056885</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11725902557373</t>
+    <t xml:space="preserve">8.11725997924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922660827637</t>
+    <t xml:space="preserve">8.45922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170127868652</t>
+    <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8350105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6370286941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.90700340271</t>
+    <t xml:space="preserve">10.8350114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6370277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9070043563843</t>
   </si>
   <si>
     <t xml:space="preserve">10.6010313034058</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550264358521</t>
+    <t xml:space="preserve">10.6550273895264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730241775513</t>
+    <t xml:space="preserve">10.6730251312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">11.4649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669706344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3389654159546</t>
+    <t xml:space="preserve">11.2669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3389644622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5009498596191</t>
+    <t xml:space="preserve">11.5009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">11.9689064025879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709255218506</t>
+    <t xml:space="preserve">11.7709245681763</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249197006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349281311035</t>
+    <t xml:space="preserve">11.7349290847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578472137451</t>
+    <t xml:space="preserve">11.3578481674194</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514036178589</t>
+    <t xml:space="preserve">11.4514045715332</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2081546783447</t>
+    <t xml:space="preserve">11.208155632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443441390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688810348511</t>
+    <t xml:space="preserve">11.8443450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688819885254</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940357208252</t>
+    <t xml:space="preserve">11.9940366744995</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133646011353</t>
+    <t xml:space="preserve">11.7133655548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2531,10 +2531,7 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806921005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4139814376831</t>
+    <t xml:space="preserve">11.4139804840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2549,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823841094971</t>
+    <t xml:space="preserve">11.5823850631714</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2561,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624383926392</t>
+    <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.919189453125</t>
+    <t xml:space="preserve">11.9191904067993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2576,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5449619293213</t>
+    <t xml:space="preserve">11.544960975647</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2585,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.058464050293</t>
+    <t xml:space="preserve">11.0584630966187</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2594,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771751403809</t>
+    <t xml:space="preserve">11.0771760940552</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2603,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842355728149</t>
+    <t xml:space="preserve">10.6842346191406</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2612,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222755432129</t>
+    <t xml:space="preserve">10.4784088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222745895386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287181854248</t>
+    <t xml:space="preserve">10.3287172317505</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977376937866</t>
+    <t xml:space="preserve">10.1977367401123</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3108,6 +3105,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -16750,7 +16750,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16776,7 +16776,7 @@
         <v>10.5</v>
       </c>
       <c r="G513" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16802,7 +16802,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G514" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16828,7 +16828,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16854,7 +16854,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G516" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16906,7 +16906,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17062,7 +17062,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17088,7 +17088,7 @@
         <v>10.5</v>
       </c>
       <c r="G525" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17114,7 +17114,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G526" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17712,7 +17712,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G549" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17842,7 +17842,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G554" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17868,7 +17868,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17946,7 +17946,7 @@
         <v>10.5</v>
       </c>
       <c r="G558" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17972,7 +17972,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18024,7 +18024,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18050,7 +18050,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G562" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18076,7 +18076,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G563" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18102,7 +18102,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18154,7 +18154,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G566" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18206,7 +18206,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18336,7 +18336,7 @@
         <v>10.5</v>
       </c>
       <c r="G573" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18388,7 +18388,7 @@
         <v>10.5</v>
       </c>
       <c r="G575" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18414,7 +18414,7 @@
         <v>10.5</v>
       </c>
       <c r="G576" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18440,7 +18440,7 @@
         <v>10.5</v>
       </c>
       <c r="G577" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18986,7 +18986,7 @@
         <v>10.5</v>
       </c>
       <c r="G598" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19012,7 +19012,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19038,7 +19038,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G600" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19064,7 +19064,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19090,7 +19090,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G602" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19116,7 +19116,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19142,7 +19142,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19168,7 +19168,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19194,7 +19194,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G606" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19220,7 +19220,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G607" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19246,7 +19246,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19272,7 +19272,7 @@
         <v>10.5</v>
       </c>
       <c r="G609" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19298,7 +19298,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19324,7 +19324,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G611" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19376,7 +19376,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19402,7 +19402,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19480,7 +19480,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19506,7 +19506,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19688,7 +19688,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19714,7 +19714,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19740,7 +19740,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G627" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19766,7 +19766,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19792,7 +19792,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20078,7 +20078,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G640" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20156,7 +20156,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -59884,7 +59884,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59936,7 +59936,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60040,7 +60040,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60066,7 +60066,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60092,7 +60092,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60118,7 +60118,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60170,7 +60170,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60274,7 +60274,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60300,7 +60300,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60326,7 +60326,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60352,7 +60352,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60456,7 +60456,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60482,7 +60482,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60508,7 +60508,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60534,7 +60534,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60560,7 +60560,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60664,7 +60664,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60794,7 +60794,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60820,7 +60820,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60846,7 +60846,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60898,7 +60898,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60924,7 +60924,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60976,7 +60976,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61002,7 +61002,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61028,7 +61028,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61054,7 +61054,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61106,7 +61106,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61158,7 +61158,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61184,7 +61184,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61236,7 +61236,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61262,7 +61262,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61288,7 +61288,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61340,7 +61340,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61366,7 +61366,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61418,7 +61418,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61574,7 +61574,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61678,7 +61678,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61704,7 +61704,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61860,7 +61860,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61886,7 +61886,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61912,7 +61912,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61938,7 +61938,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61964,7 +61964,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61990,7 +61990,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62016,7 +62016,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62042,7 +62042,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62068,7 +62068,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62094,7 +62094,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62120,7 +62120,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62146,7 +62146,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62172,7 +62172,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62198,7 +62198,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62224,7 +62224,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62250,7 +62250,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62276,7 +62276,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62302,7 +62302,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62328,7 +62328,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62354,7 +62354,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62380,7 +62380,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62406,7 +62406,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62432,7 +62432,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62458,7 +62458,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62484,7 +62484,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62510,7 +62510,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62536,7 +62536,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62562,7 +62562,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62588,7 +62588,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62614,7 +62614,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62640,7 +62640,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62666,7 +62666,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62692,7 +62692,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62718,7 +62718,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62744,7 +62744,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62770,7 +62770,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62796,7 +62796,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62822,7 +62822,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62848,7 +62848,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62874,7 +62874,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62900,7 +62900,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62926,7 +62926,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62952,7 +62952,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62978,7 +62978,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63004,7 +63004,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63030,7 +63030,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63056,7 +63056,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63082,7 +63082,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63108,7 +63108,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63134,7 +63134,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63160,7 +63160,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63186,7 +63186,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63212,7 +63212,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63238,7 +63238,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63264,7 +63264,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63290,7 +63290,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63316,7 +63316,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63342,7 +63342,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63368,7 +63368,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63394,7 +63394,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63420,7 +63420,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63446,7 +63446,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63472,7 +63472,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63498,7 +63498,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63524,7 +63524,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63550,7 +63550,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63576,7 +63576,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63602,7 +63602,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63628,7 +63628,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63654,7 +63654,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63680,7 +63680,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63706,7 +63706,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63732,7 +63732,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63758,7 +63758,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63784,7 +63784,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63810,7 +63810,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63836,7 +63836,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63862,7 +63862,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63888,7 +63888,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63914,7 +63914,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63940,7 +63940,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63966,7 +63966,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63992,7 +63992,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64018,7 +64018,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64044,7 +64044,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64070,7 +64070,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64096,7 +64096,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64122,7 +64122,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64148,7 +64148,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64174,7 +64174,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64200,7 +64200,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64226,7 +64226,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64252,7 +64252,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64278,7 +64278,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64304,7 +64304,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64330,7 +64330,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64356,7 +64356,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64382,7 +64382,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64408,7 +64408,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64434,7 +64434,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64460,7 +64460,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64486,7 +64486,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64512,7 +64512,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64538,7 +64538,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64564,7 +64564,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64590,7 +64590,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64616,7 +64616,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64642,7 +64642,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64668,7 +64668,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64694,7 +64694,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64720,7 +64720,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64746,7 +64746,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64772,7 +64772,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64798,7 +64798,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64824,7 +64824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64850,7 +64850,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64876,7 +64876,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64902,7 +64902,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64928,7 +64928,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64954,7 +64954,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64980,7 +64980,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65006,7 +65006,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65032,7 +65032,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65058,7 +65058,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65084,7 +65084,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65110,7 +65110,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65136,7 +65136,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65162,7 +65162,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65188,7 +65188,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65214,7 +65214,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65240,7 +65240,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65266,7 +65266,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65292,7 +65292,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65318,7 +65318,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65344,7 +65344,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65370,7 +65370,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65396,7 +65396,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65422,7 +65422,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65448,7 +65448,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65474,7 +65474,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65500,7 +65500,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65526,7 +65526,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65552,7 +65552,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65578,7 +65578,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65604,7 +65604,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65630,7 +65630,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65656,7 +65656,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65682,7 +65682,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65708,7 +65708,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65734,7 +65734,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65760,7 +65760,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65786,7 +65786,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65812,7 +65812,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65838,7 +65838,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65864,7 +65864,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65890,7 +65890,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65916,7 +65916,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65942,7 +65942,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65968,7 +65968,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65994,7 +65994,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66020,7 +66020,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66046,7 +66046,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66072,7 +66072,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66098,7 +66098,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66124,7 +66124,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66150,7 +66150,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66176,7 +66176,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66202,7 +66202,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66228,7 +66228,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66254,7 +66254,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66280,7 +66280,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66306,7 +66306,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66332,7 +66332,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66358,7 +66358,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66384,7 +66384,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66410,7 +66410,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66436,7 +66436,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66462,7 +66462,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66488,7 +66488,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66514,7 +66514,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66540,7 +66540,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66566,7 +66566,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66592,7 +66592,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66618,7 +66618,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66644,7 +66644,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66670,7 +66670,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66696,7 +66696,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66722,7 +66722,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66748,7 +66748,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66774,7 +66774,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66800,7 +66800,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66826,7 +66826,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66852,7 +66852,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66878,7 +66878,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66904,7 +66904,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66930,7 +66930,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66956,7 +66956,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66982,7 +66982,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67008,7 +67008,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67034,7 +67034,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67060,7 +67060,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67086,7 +67086,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67112,7 +67112,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67138,7 +67138,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67164,7 +67164,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67190,7 +67190,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67216,7 +67216,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67242,7 +67242,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67268,7 +67268,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67294,7 +67294,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67320,7 +67320,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67346,7 +67346,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67372,7 +67372,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67398,7 +67398,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67424,7 +67424,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67450,7 +67450,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67476,7 +67476,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67502,7 +67502,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67528,7 +67528,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67554,7 +67554,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67580,7 +67580,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67606,7 +67606,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67632,7 +67632,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67658,7 +67658,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67684,7 +67684,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67710,7 +67710,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67736,7 +67736,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67762,7 +67762,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67788,7 +67788,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67814,7 +67814,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67840,7 +67840,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67866,7 +67866,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67892,7 +67892,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67918,7 +67918,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67944,7 +67944,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67970,7 +67970,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67996,7 +67996,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68022,7 +68022,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68048,7 +68048,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68074,7 +68074,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68082,7 +68082,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496412037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>58155</v>
@@ -68091,7 +68091,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="D2487" t="n">
-        <v>17.5599994659424</v>
+        <v>17.4599990844727</v>
       </c>
       <c r="E2487" t="n">
         <v>18.2000007629395</v>
@@ -68100,9 +68100,35 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493518519</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>55856</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>18.0599994659424</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>17.4799995422363</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>17.4799995422363</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="G2488" t="s">
         <v>1031</v>
       </c>
-      <c r="H2487" t="s">
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="1034">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217420578003</t>
+    <t xml:space="preserve">7.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07279968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10925912857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061637878418</t>
+    <t xml:space="preserve">7.16394472122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061590194702</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14207029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717687606812</t>
+    <t xml:space="preserve">7.14207077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0071759223938</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696466445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446142196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154825210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863126754761</t>
+    <t xml:space="preserve">7.2514443397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446332931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2915472984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863079071045</t>
   </si>
   <si>
     <t xml:space="preserve">7.26238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40821266174316</t>
+    <t xml:space="preserve">7.40821170806885</t>
   </si>
   <si>
     <t xml:space="preserve">7.39362859725952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43737888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790235519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4300856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029348373413</t>
+    <t xml:space="preserve">7.43737840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.284255027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029396057129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154195785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3061318397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6196665763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216791152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508975982666</t>
+    <t xml:space="preserve">7.64154100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30612993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675245285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
   </si>
   <si>
     <t xml:space="preserve">7.33529663085938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3498797416687</t>
+    <t xml:space="preserve">7.34987926483154</t>
   </si>
   <si>
     <t xml:space="preserve">7.29883909225464</t>
@@ -158,112 +158,112 @@
     <t xml:space="preserve">7.25873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24779748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769500732422</t>
+    <t xml:space="preserve">7.2477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498537063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2076940536499</t>
   </si>
   <si>
     <t xml:space="preserve">6.99988603591919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99624061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904062271118</t>
+    <t xml:space="preserve">7.0217604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133413314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320951461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72903966903687</t>
   </si>
   <si>
     <t xml:space="preserve">7.87487173080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528594970703</t>
+    <t xml:space="preserve">7.94778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528499603271</t>
   </si>
   <si>
     <t xml:space="preserve">8.12278366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98424434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18022155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774494171143</t>
+    <t xml:space="preserve">7.98424530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1802225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774589538574</t>
   </si>
   <si>
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030433654785</t>
+    <t xml:space="preserve">7.88030529022217</t>
   </si>
   <si>
     <t xml:space="preserve">7.79782772064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61787843704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6478705406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276420593262</t>
+    <t xml:space="preserve">7.61787700653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.985276222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276515960693</t>
   </si>
   <si>
     <t xml:space="preserve">8.0602560043335</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47264003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84003925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240749359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1324577331543</t>
+    <t xml:space="preserve">8.47264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43987274169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990528106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245677947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.98249816894531</t>
@@ -302,49 +302,49 @@
     <t xml:space="preserve">8.9974946975708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
+    <t xml:space="preserve">9.10996341705322</t>
   </si>
   <si>
     <t xml:space="preserve">8.89252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66008853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69757843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59260654449463</t>
+    <t xml:space="preserve">8.66008758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69757652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.84753513336182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77255725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8100471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72756862640381</t>
+    <t xml:space="preserve">8.77255630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81004619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756958007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.70507526397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79505062103271</t>
+    <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6900806427002</t>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69007968902588</t>
   </si>
   <si>
     <t xml:space="preserve">8.60010433197021</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259864807129</t>
+    <t xml:space="preserve">8.38266658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54761791229248</t>
+    <t xml:space="preserve">8.5476188659668</t>
   </si>
   <si>
     <t xml:space="preserve">8.41265678405762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28519248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268238067627</t>
+    <t xml:space="preserve">8.28519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268142700195</t>
   </si>
   <si>
     <t xml:space="preserve">8.73506641387939</t>
@@ -383,46 +383,46 @@
     <t xml:space="preserve">8.90002155303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67508411407471</t>
+    <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.51762676239014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58510875701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5101318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36017227172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31518459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766025543213</t>
+    <t xml:space="preserve">8.58510971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51012897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3601713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31518363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17272281646729</t>
+    <t xml:space="preserve">8.17272472381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.20271492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45764350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4201545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21021270751953</t>
+    <t xml:space="preserve">8.45764446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21021366119385</t>
   </si>
   <si>
     <t xml:space="preserve">8.11273956298828</t>
@@ -431,37 +431,37 @@
     <t xml:space="preserve">8.09024810791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06775283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08274745941162</t>
+    <t xml:space="preserve">8.06775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">8.12773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777843475342</t>
+    <t xml:space="preserve">8.18772125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777938842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22520923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1202392578125</t>
+    <t xml:space="preserve">8.13523387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2252082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12023735046387</t>
   </si>
   <si>
     <t xml:space="preserve">8.00777053833008</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781982421875</t>
+    <t xml:space="preserve">7.82781887054443</t>
   </si>
   <si>
     <t xml:space="preserve">7.81282424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03026485443115</t>
+    <t xml:space="preserve">8.03026294708252</t>
   </si>
   <si>
     <t xml:space="preserve">7.95528411865234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03776073455811</t>
+    <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522598266602</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">7.93279075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88780307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778728485107</t>
+    <t xml:space="preserve">7.88780498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778633117676</t>
   </si>
   <si>
     <t xml:space="preserve">7.87280750274658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91029644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033782958984</t>
+    <t xml:space="preserve">7.91029739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09667873382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967908859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390157699585</t>
+    <t xml:space="preserve">8.09667778015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956992149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
   </si>
   <si>
     <t xml:space="preserve">7.86534547805786</t>
@@ -539,70 +539,70 @@
     <t xml:space="preserve">8.21234512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82678985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112298965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55690050125122</t>
+    <t xml:space="preserve">7.82678890228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112203598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690097808838</t>
   </si>
   <si>
     <t xml:space="preserve">7.51063299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47978830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32556629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
+    <t xml:space="preserve">7.6185884475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47978782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41809892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725423812866</t>
   </si>
   <si>
     <t xml:space="preserve">7.21760988235474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303365707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387643814087</t>
+    <t xml:space="preserve">7.03254413604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387786865234</t>
   </si>
   <si>
     <t xml:space="preserve">7.12507629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27929830551147</t>
+    <t xml:space="preserve">7.27929925918579</t>
   </si>
   <si>
     <t xml:space="preserve">7.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20218944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14050006866455</t>
+    <t xml:space="preserve">7.20218896865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965585708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14050054550171</t>
   </si>
   <si>
     <t xml:space="preserve">7.07881116867065</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">7.00169944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205413818359</t>
+    <t xml:space="preserve">6.90916538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.92458820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952150344849</t>
+    <t xml:space="preserve">6.72409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">6.86289882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01712226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001054763794</t>
+    <t xml:space="preserve">7.01712131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7857871055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94000911712646</t>
   </si>
   <si>
     <t xml:space="preserve">6.9554328918457</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">6.70867681503296</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6315655708313</t>
+    <t xml:space="preserve">6.63156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">6.47734260559082</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">6.46192073822021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53903102874756</t>
+    <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
     <t xml:space="preserve">6.61614322662354</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">6.52361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19974279403687</t>
+    <t xml:space="preserve">6.19974231719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.23058748245239</t>
@@ -692,61 +692,61 @@
     <t xml:space="preserve">6.26143169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27685403823853</t>
+    <t xml:space="preserve">6.27685356140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29227590560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565370559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55445432662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663179397583</t>
+    <t xml:space="preserve">6.29227542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5544548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.89374303817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036619186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16889810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09178686141968</t>
+    <t xml:space="preserve">6.6469874382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7703652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16889762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09178638458252</t>
   </si>
   <si>
     <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99925327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24600887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66241025924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396528244019</t>
+    <t xml:space="preserve">5.99925374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.246009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66240978240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276494979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396480560303</t>
   </si>
   <si>
     <t xml:space="preserve">6.44649791717529</t>
@@ -761,61 +761,61 @@
     <t xml:space="preserve">6.75494337081909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87832117080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676519393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314245223999</t>
+    <t xml:space="preserve">6.87832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085475921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338739395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20115089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.07313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64106178283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00912094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113809585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88109970092773</t>
+    <t xml:space="preserve">6.64106225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00912046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110065460205</t>
   </si>
   <si>
     <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78508329391479</t>
+    <t xml:space="preserve">6.78508377075195</t>
   </si>
   <si>
     <t xml:space="preserve">6.75307893753052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73707675933838</t>
+    <t xml:space="preserve">6.73707723617554</t>
   </si>
   <si>
     <t xml:space="preserve">6.72107410430908</t>
@@ -833,37 +833,37 @@
     <t xml:space="preserve">6.76908254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81709003448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56104898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65706396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59305334091187</t>
+    <t xml:space="preserve">6.80108785629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710187911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81708908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56104850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65706348419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
     <t xml:space="preserve">6.62505865097046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57705163955688</t>
+    <t xml:space="preserve">6.57705211639404</t>
   </si>
   <si>
     <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51304149627686</t>
+    <t xml:space="preserve">6.43302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
     <t xml:space="preserve">6.44903087615967</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701276779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22499513626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08097171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04896688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697437286377</t>
+    <t xml:space="preserve">6.33701324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22499561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08097219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04896640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496953964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697484970093</t>
   </si>
   <si>
     <t xml:space="preserve">6.1609845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0009593963623</t>
+    <t xml:space="preserve">6.00095891952515</t>
   </si>
   <si>
     <t xml:space="preserve">5.95295190811157</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">6.0169620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96895456314087</t>
+    <t xml:space="preserve">5.96895360946655</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094707489014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76092052459717</t>
+    <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
     <t xml:space="preserve">5.74491786956787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.680908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71291255950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82493114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494394302368</t>
+    <t xml:space="preserve">5.68090772628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71291303634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494346618652</t>
   </si>
   <si>
     <t xml:space="preserve">5.87293863296509</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">5.98495674133301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11297702789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24099731445312</t>
+    <t xml:space="preserve">6.11297655105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24099779129028</t>
   </si>
   <si>
     <t xml:space="preserve">6.32101058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27300262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20899295806885</t>
+    <t xml:space="preserve">6.27300310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38502073287964</t>
+    <t xml:space="preserve">6.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14498233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25700092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500793457031</t>
+    <t xml:space="preserve">6.1449818611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500841140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694877624512</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">5.63290023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5528883934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39286184310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50488042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36085653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081909179688</t>
+    <t xml:space="preserve">5.55288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39286136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487947463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3608570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081861495972</t>
   </si>
   <si>
     <t xml:space="preserve">4.73675727844238</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">4.6727466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871091842651</t>
+    <t xml:space="preserve">4.44871139526367</t>
   </si>
   <si>
     <t xml:space="preserve">4.24067783355713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92062616348267</t>
+    <t xml:space="preserve">3.92062664031982</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868579864502</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16066455841064</t>
+    <t xml:space="preserve">4.16066551208496</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065223693848</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72075462341309</t>
+    <t xml:space="preserve">4.72075510025024</t>
   </si>
   <si>
     <t xml:space="preserve">4.92878770828247</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52088260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32885217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3128490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18482828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880002975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882610321045</t>
+    <t xml:space="preserve">5.52088308334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40886449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32885122299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31284952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18482875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880098342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882658004761</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23283576965332</t>
+    <t xml:space="preserve">5.23283624649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287464141846</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">5.58489322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42486763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56888961791992</t>
+    <t xml:space="preserve">5.42486715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889009475708</t>
   </si>
   <si>
     <t xml:space="preserve">5.34485387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44086980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685918807983</t>
+    <t xml:space="preserve">5.44086933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685966491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.26484155654907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45687294006348</t>
+    <t xml:space="preserve">5.24883890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45687246322632</t>
   </si>
   <si>
     <t xml:space="preserve">5.53688478469849</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">5.29684638977051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683406829834</t>
+    <t xml:space="preserve">5.2168345451355</t>
   </si>
   <si>
     <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900527954102</t>
+    <t xml:space="preserve">6.28900575637817</t>
   </si>
   <si>
     <t xml:space="preserve">6.4970383644104</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306709289551</t>
+    <t xml:space="preserve">6.67306661605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.91310501098633</t>
@@ -1160,67 +1160,67 @@
     <t xml:space="preserve">7.26516151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121488571167</t>
+    <t xml:space="preserve">7.28116369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121536254883</t>
   </si>
   <si>
     <t xml:space="preserve">7.52120161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53720474243164</t>
+    <t xml:space="preserve">7.5372052192688</t>
   </si>
   <si>
     <t xml:space="preserve">7.47319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44118928909302</t>
+    <t xml:space="preserve">7.44118881225586</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40918397903442</t>
+    <t xml:space="preserve">7.40918493270874</t>
   </si>
   <si>
     <t xml:space="preserve">7.39318132400513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3131685256958</t>
+    <t xml:space="preserve">7.23315668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316900253296</t>
   </si>
   <si>
     <t xml:space="preserve">7.42518663406372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716634750366</t>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716682434082</t>
   </si>
   <si>
     <t xml:space="preserve">7.74523782730103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84125232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526294708252</t>
+    <t xml:space="preserve">7.84125328063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82524967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526390075684</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">7.92126560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726968765259</t>
+    <t xml:space="preserve">7.93726778030396</t>
   </si>
   <si>
     <t xml:space="preserve">8.0012788772583</t>
@@ -1241,37 +1241,37 @@
     <t xml:space="preserve">7.8732590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95327138900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44134998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139263153076</t>
+    <t xml:space="preserve">7.95327043533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28132438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44134902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139358520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8414134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0414457321167</t>
+    <t xml:space="preserve">8.84141445159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04144668579102</t>
   </si>
   <si>
     <t xml:space="preserve">8.9614315032959</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48151588439941</t>
+    <t xml:space="preserve">9.4815149307251</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155284881592</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">10.0816106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1216173171997</t>
+    <t xml:space="preserve">10.121618270874</t>
   </si>
   <si>
     <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3216485977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217130661011</t>
+    <t xml:space="preserve">10.3216505050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217140197754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3218097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2017908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0417652130127</t>
+    <t xml:space="preserve">11.201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217775344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.041766166687</t>
   </si>
   <si>
     <t xml:space="preserve">10.9617519378662</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8417329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.881739616394</t>
+    <t xml:space="preserve">10.8417339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8817386627197</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818353652954</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">11.0817708969116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7617197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216817855835</t>
+    <t xml:space="preserve">10.7617206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017566680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216827392578</t>
   </si>
   <si>
     <t xml:space="preserve">10.6016941070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818040847778</t>
+    <t xml:space="preserve">11.2818031311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.6965761184692</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7011213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4937353134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0374879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.161919593811</t>
+    <t xml:space="preserve">10.7011222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4937362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0374870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1619186401367</t>
   </si>
   <si>
     <t xml:space="preserve">10.0789632797241</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">9.95453262329102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4107828140259</t>
+    <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
+    <t xml:space="preserve">10.9914636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.742600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.825553894043</t>
   </si>
   <si>
     <t xml:space="preserve">10.5766906738281</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">10.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6181688308716</t>
+    <t xml:space="preserve">10.6181678771973</t>
   </si>
   <si>
     <t xml:space="preserve">10.3693046569824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2863502502441</t>
+    <t xml:space="preserve">10.2863492965698</t>
   </si>
   <si>
     <t xml:space="preserve">10.244873046875</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">9.87157726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522581100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9499855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840766906738</t>
+    <t xml:space="preserve">10.4522590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9499864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840776443481</t>
   </si>
   <si>
     <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5352144241333</t>
+    <t xml:space="preserve">10.9085092544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.6596450805664</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">11.032940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.323281288147</t>
+    <t xml:space="preserve">11.3232803344727</t>
   </si>
   <si>
     <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2403259277344</t>
+    <t xml:space="preserve">11.2403268814087</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5306673049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.5306663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
@@ -1481,52 +1481,52 @@
     <t xml:space="preserve">12.3187341690063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5261201858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8164596557617</t>
+    <t xml:space="preserve">12.5261211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5675983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.816460609436</t>
   </si>
   <si>
     <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5630521774292</t>
+    <t xml:space="preserve">13.5630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">13.8119134902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6460056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3141870498657</t>
+    <t xml:space="preserve">13.6460065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3141860961914</t>
   </si>
   <si>
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0192985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312326431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8994150161743</t>
+    <t xml:space="preserve">14.0193004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.189754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8994140625</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">11.4062347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8210067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988487243652</t>
+    <t xml:space="preserve">11.8210077285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988496780396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">9.78862380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
+    <t xml:space="preserve">9.66419219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714660644531</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624849319458</t>
@@ -1571,28 +1571,28 @@
     <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4808931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0661220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177133560181</t>
+    <t xml:space="preserve">11.4808950424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.066123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177143096924</t>
   </si>
   <si>
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343044281006</t>
+    <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6347579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679410934448</t>
+    <t xml:space="preserve">10.6347589492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
     <t xml:space="preserve">10.8504400253296</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">10.9168043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8006687164307</t>
+    <t xml:space="preserve">10.8006677627563</t>
   </si>
   <si>
     <t xml:space="preserve">10.9002132415771</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">10.8172588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7674856185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8338499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849857330322</t>
+    <t xml:space="preserve">10.767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8338508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
@@ -1631,34 +1631,34 @@
     <t xml:space="preserve">11.331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2279100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866170883179</t>
+    <t xml:space="preserve">11.2279090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866161346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2454929351807</t>
+    <t xml:space="preserve">12.2454919815063</t>
   </si>
   <si>
     <t xml:space="preserve">12.2109975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2282457351685</t>
+    <t xml:space="preserve">12.2282466888428</t>
   </si>
   <si>
     <t xml:space="preserve">12.1592569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4179630279541</t>
+    <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.1937503814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.021279335022</t>
+    <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5038642883301</t>
+    <t xml:space="preserve">11.5038652420044</t>
   </si>
   <si>
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106618881226</t>
+    <t xml:space="preserve">11.2106628417969</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
@@ -1682,31 +1682,31 @@
     <t xml:space="preserve">10.7794828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6932468414307</t>
+    <t xml:space="preserve">10.6932458877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6242580413818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0036954879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1589202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625722885132</t>
+    <t xml:space="preserve">11.0036964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1589193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
     <t xml:space="preserve">11.831561088562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3831329345703</t>
+    <t xml:space="preserve">11.3831338882446</t>
   </si>
   <si>
     <t xml:space="preserve">11.9522895812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7280778884888</t>
+    <t xml:space="preserve">11.7280769348145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5728530883789</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">11.7453231811523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6935834884644</t>
+    <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2627391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9867849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1765041351318</t>
+    <t xml:space="preserve">11.8660545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2627401351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9867839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1765031814575</t>
   </si>
   <si>
     <t xml:space="preserve">12.3144798278809</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">11.9695386886597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">11.9350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970657348633</t>
+    <t xml:space="preserve">11.7970666885376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073474884033</t>
+    <t xml:space="preserve">11.607346534729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5556049346924</t>
@@ -1784,31 +1784,31 @@
     <t xml:space="preserve">11.5900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6418409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4348745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209426879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1244249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1416730880737</t>
+    <t xml:space="preserve">11.6418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.020941734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.141674041748</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8829660415649</t>
+    <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
     <t xml:space="preserve">10.641505241394</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207748413086</t>
+    <t xml:space="preserve">10.5207738876343</t>
   </si>
   <si>
     <t xml:space="preserve">10.3483037948608</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193078994751</t>
+    <t xml:space="preserve">10.1930780410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312253952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383577346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245937347412</t>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245927810669</t>
   </si>
   <si>
     <t xml:space="preserve">11.4176273345947</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">12.3662233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4524583816528</t>
+    <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869518280029</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5214471817017</t>
+    <t xml:space="preserve">12.521448135376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386934280396</t>
@@ -1892,67 +1892,67 @@
     <t xml:space="preserve">12.2799854278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4352111816406</t>
+    <t xml:space="preserve">12.4352121353149</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108306884766</t>
+    <t xml:space="preserve">11.7108297348022</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2624034881592</t>
+    <t xml:space="preserve">11.4521217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2624044418335</t>
   </si>
   <si>
     <t xml:space="preserve">11.2796497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9519548416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0899324417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554361343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967290878296</t>
+    <t xml:space="preserve">11.3141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9519538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0899314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967309951782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347076416016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8657178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5725173950195</t>
+    <t xml:space="preserve">10.8657188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
     <t xml:space="preserve">10.6070108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4517869949341</t>
+    <t xml:space="preserve">10.4345388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4517850875854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4690341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5380210876465</t>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">10.2590627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3850507736206</t>
+    <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
     <t xml:space="preserve">10.4930419921875</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0430822372437</t>
+    <t xml:space="preserve">10.043083190918</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89909553527832</t>
+    <t xml:space="preserve">9.93509197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
     <t xml:space="preserve">9.95309066772461</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790796279907</t>
+    <t xml:space="preserve">10.0790786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910396575928</t>
+    <t xml:space="preserve">10.1510715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210481643677</t>
+    <t xml:space="preserve">10.4210472106934</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3130578994751</t>
+    <t xml:space="preserve">10.4030504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3130588531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950592041016</t>
@@ -2051,19 +2051,19 @@
     <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">9.79110622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111465454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41314029693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17916107177734</t>
+    <t xml:space="preserve">9.41313934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17916202545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">9.53912830352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37714290618896</t>
+    <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.35914516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32314872741699</t>
+    <t xml:space="preserve">9.32314777374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.25115489959717</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318992614746</t>
+    <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97218132019043</t>
+    <t xml:space="preserve">8.97218036651611</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2120,37 +2120,37 @@
     <t xml:space="preserve">8.47722625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62121295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63021183013916</t>
+    <t xml:space="preserve">8.62121200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63921165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63021087646484</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60321521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123634338379</t>
+    <t xml:space="preserve">8.60321426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.20725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90127754211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0992603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04526424407959</t>
+    <t xml:space="preserve">7.90127801895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09925937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
     <t xml:space="preserve">8.05426406860352</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91027736663818</t>
+    <t xml:space="preserve">7.96427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
     <t xml:space="preserve">7.81128692626953</t>
@@ -2171,31 +2171,31 @@
     <t xml:space="preserve">7.89227962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97327184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428840637207</t>
+    <t xml:space="preserve">7.97327089309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927576065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
     <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64930200576782</t>
+    <t xml:space="preserve">7.64930152893066</t>
   </si>
   <si>
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533121109009</t>
+    <t xml:space="preserve">7.63130235671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32533073425293</t>
   </si>
   <si>
     <t xml:space="preserve">7.19934272766113</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">6.69538831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74038362503052</t>
+    <t xml:space="preserve">6.74038410186768</t>
   </si>
   <si>
     <t xml:space="preserve">6.77638101577759</t>
@@ -2228,37 +2228,37 @@
     <t xml:space="preserve">6.95636463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19034290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16334533691406</t>
+    <t xml:space="preserve">7.19034242630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
     <t xml:space="preserve">7.10935068130493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25333786010742</t>
+    <t xml:space="preserve">7.25333738327026</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4243221282959</t>
+    <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
     <t xml:space="preserve">7.5143141746521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49631547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733203887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46931791305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28933477401733</t>
+    <t xml:space="preserve">7.49631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733251571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46931838989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28933429718018</t>
   </si>
   <si>
     <t xml:space="preserve">7.28033494949341</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0553560256958</t>
+    <t xml:space="preserve">7.05535554885864</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">7.68529796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99126958847046</t>
+    <t xml:space="preserve">7.99127006530762</t>
   </si>
   <si>
     <t xml:space="preserve">7.92827606201172</t>
@@ -2300,19 +2300,19 @@
     <t xml:space="preserve">8.27024364471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37823486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821895599365</t>
+    <t xml:space="preserve">8.37823581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821800231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.75619888305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66620922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74720096588135</t>
+    <t xml:space="preserve">8.66620826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74720191955566</t>
   </si>
   <si>
     <t xml:space="preserve">8.56721782684326</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923599243164</t>
+    <t xml:space="preserve">8.36923503875732</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">8.19825077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06326293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11725997924805</t>
+    <t xml:space="preserve">8.06326389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11725902557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922756195068</t>
+    <t xml:space="preserve">8.45922660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9789972305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8350114822388</t>
+    <t xml:space="preserve">10.9789962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8350105285645</t>
   </si>
   <si>
     <t xml:space="preserve">10.6370277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9070043563843</t>
+    <t xml:space="preserve">10.90700340271</t>
   </si>
   <si>
     <t xml:space="preserve">10.6010313034058</t>
@@ -2387,16 +2387,16 @@
     <t xml:space="preserve">10.7990131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730251312256</t>
+    <t xml:space="preserve">10.6730241775513</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489728927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1229829788208</t>
+    <t xml:space="preserve">11.2489719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1229839324951</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749618530273</t>
+    <t xml:space="preserve">11.374960899353</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
@@ -2435,102 +2435,105 @@
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
+    <t xml:space="preserve">11.9689073562622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709245681763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349290847778</t>
+    <t xml:space="preserve">11.8249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349281311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529268264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429174423218</t>
+    <t xml:space="preserve">11.7529277801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806921005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6198072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5262498855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.320424079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.488826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5075387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3391351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3578481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4326934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4514045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4701156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.208155632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.601095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8256330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8443450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0314588546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9940366744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7133655548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7507877349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6572303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
     <t xml:space="preserve">11.8069219589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6198072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5262498855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.320424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.488826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5075387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3391351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3578481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4326934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4514045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4701156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.208155632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8256330490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0314588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9940366744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7133655548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7507877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6572303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.4139804840088</t>
   </si>
   <si>
@@ -3108,6 +3111,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -59884,7 +59890,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59936,7 +59942,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60040,7 +60046,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60066,7 +60072,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60092,7 +60098,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60118,7 +60124,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60170,7 +60176,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60274,7 +60280,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60300,7 +60306,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60326,7 +60332,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60352,7 +60358,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60456,7 +60462,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60482,7 +60488,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60508,7 +60514,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60534,7 +60540,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60560,7 +60566,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60664,7 +60670,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60794,7 +60800,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60820,7 +60826,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60846,7 +60852,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60898,7 +60904,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60924,7 +60930,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60976,7 +60982,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61002,7 +61008,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61028,7 +61034,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61054,7 +61060,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61106,7 +61112,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61158,7 +61164,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61184,7 +61190,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61236,7 +61242,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61262,7 +61268,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61288,7 +61294,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61340,7 +61346,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61366,7 +61372,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61418,7 +61424,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61574,7 +61580,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61678,7 +61684,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61704,7 +61710,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61860,7 +61866,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61886,7 +61892,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61912,7 +61918,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61938,7 +61944,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61964,7 +61970,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61990,7 +61996,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62016,7 +62022,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62042,7 +62048,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62068,7 +62074,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62094,7 +62100,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62120,7 +62126,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62146,7 +62152,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62172,7 +62178,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62198,7 +62204,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62224,7 +62230,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62250,7 +62256,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62276,7 +62282,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62302,7 +62308,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62328,7 +62334,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62354,7 +62360,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62380,7 +62386,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62406,7 +62412,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62432,7 +62438,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62458,7 +62464,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62484,7 +62490,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62510,7 +62516,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62536,7 +62542,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62562,7 +62568,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62588,7 +62594,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62614,7 +62620,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62640,7 +62646,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62666,7 +62672,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62692,7 +62698,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62718,7 +62724,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62744,7 +62750,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62770,7 +62776,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62796,7 +62802,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62822,7 +62828,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62848,7 +62854,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62874,7 +62880,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62900,7 +62906,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62926,7 +62932,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62952,7 +62958,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62978,7 +62984,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63004,7 +63010,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63030,7 +63036,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63056,7 +63062,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63082,7 +63088,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63108,7 +63114,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63134,7 +63140,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63160,7 +63166,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63186,7 +63192,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63212,7 +63218,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63238,7 +63244,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63264,7 +63270,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63290,7 +63296,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63316,7 +63322,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63342,7 +63348,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63368,7 +63374,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63394,7 +63400,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63420,7 +63426,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63446,7 +63452,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63472,7 +63478,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63498,7 +63504,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63524,7 +63530,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63550,7 +63556,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63576,7 +63582,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63602,7 +63608,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63628,7 +63634,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63654,7 +63660,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63680,7 +63686,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63706,7 +63712,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63732,7 +63738,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63758,7 +63764,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63784,7 +63790,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63810,7 +63816,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63836,7 +63842,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63862,7 +63868,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63888,7 +63894,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63914,7 +63920,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63940,7 +63946,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63966,7 +63972,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63992,7 +63998,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64018,7 +64024,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64044,7 +64050,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64070,7 +64076,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64096,7 +64102,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64122,7 +64128,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64148,7 +64154,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64174,7 +64180,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64200,7 +64206,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64226,7 +64232,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64252,7 +64258,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64278,7 +64284,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64304,7 +64310,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64330,7 +64336,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64356,7 +64362,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64382,7 +64388,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64408,7 +64414,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64434,7 +64440,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64460,7 +64466,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64486,7 +64492,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64512,7 +64518,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64538,7 +64544,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64564,7 +64570,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64590,7 +64596,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64616,7 +64622,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64642,7 +64648,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64668,7 +64674,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64694,7 +64700,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64720,7 +64726,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64746,7 +64752,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64772,7 +64778,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64798,7 +64804,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64824,7 +64830,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64850,7 +64856,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64876,7 +64882,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64902,7 +64908,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64928,7 +64934,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64954,7 +64960,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64980,7 +64986,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65006,7 +65012,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65032,7 +65038,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65058,7 +65064,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65084,7 +65090,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65110,7 +65116,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65136,7 +65142,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65162,7 +65168,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65188,7 +65194,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65214,7 +65220,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65240,7 +65246,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65266,7 +65272,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65292,7 +65298,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65318,7 +65324,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65344,7 +65350,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65370,7 +65376,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65396,7 +65402,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65422,7 +65428,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65448,7 +65454,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65474,7 +65480,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65500,7 +65506,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65526,7 +65532,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65552,7 +65558,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65578,7 +65584,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65604,7 +65610,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65630,7 +65636,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65656,7 +65662,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65682,7 +65688,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65708,7 +65714,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65734,7 +65740,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65760,7 +65766,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65786,7 +65792,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65812,7 +65818,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65838,7 +65844,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65864,7 +65870,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65890,7 +65896,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65916,7 +65922,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65942,7 +65948,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65968,7 +65974,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65994,7 +66000,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66020,7 +66026,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66046,7 +66052,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66072,7 +66078,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66098,7 +66104,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66124,7 +66130,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66150,7 +66156,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66176,7 +66182,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66202,7 +66208,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66228,7 +66234,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66254,7 +66260,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66280,7 +66286,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66306,7 +66312,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66332,7 +66338,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66358,7 +66364,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66384,7 +66390,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66410,7 +66416,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66436,7 +66442,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66462,7 +66468,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66488,7 +66494,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66514,7 +66520,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66540,7 +66546,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66566,7 +66572,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66592,7 +66598,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66618,7 +66624,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66644,7 +66650,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66670,7 +66676,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66696,7 +66702,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66722,7 +66728,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66748,7 +66754,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66774,7 +66780,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66800,7 +66806,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66826,7 +66832,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66852,7 +66858,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66878,7 +66884,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66904,7 +66910,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66930,7 +66936,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66956,7 +66962,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66982,7 +66988,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67008,7 +67014,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67034,7 +67040,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67060,7 +67066,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67086,7 +67092,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67112,7 +67118,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67138,7 +67144,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67164,7 +67170,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67190,7 +67196,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67216,7 +67222,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67242,7 +67248,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67268,7 +67274,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67294,7 +67300,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67320,7 +67326,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67346,7 +67352,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67372,7 +67378,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67398,7 +67404,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67424,7 +67430,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67450,7 +67456,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67476,7 +67482,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67502,7 +67508,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67528,7 +67534,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67554,7 +67560,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67580,7 +67586,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67606,7 +67612,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67632,7 +67638,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67658,7 +67664,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67684,7 +67690,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67710,7 +67716,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67736,7 +67742,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67762,7 +67768,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67788,7 +67794,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67814,7 +67820,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67840,7 +67846,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67866,7 +67872,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67892,7 +67898,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67918,7 +67924,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67944,7 +67950,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67970,7 +67976,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67996,7 +68002,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68022,7 +68028,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68048,7 +68054,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68074,7 +68080,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68100,7 +68106,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68108,7 +68114,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493518519</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>55856</v>
@@ -68126,9 +68132,35 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493171296</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>58594</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>17.8799991607666</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>17.5599994659424</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>17.7800006866455</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>17.8400001525879</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,124 +38,124 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217420578003</t>
+    <t xml:space="preserve">7.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0728006362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634214401245</t>
+    <t xml:space="preserve">7.16394472122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9670729637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634309768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.00717687606812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96342754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2514443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696466445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446285247803</t>
+    <t xml:space="preserve">6.96342706680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446332931519</t>
   </si>
   <si>
     <t xml:space="preserve">7.29154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32800483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863126754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362955093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4373779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790140151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425598144531</t>
+    <t xml:space="preserve">7.32800579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863174438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821170806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362764358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425550460815</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029348373413</t>
+    <t xml:space="preserve">7.51029443740845</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154195785522</t>
+    <t xml:space="preserve">7.64154148101807</t>
   </si>
   <si>
     <t xml:space="preserve">7.48841953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48112821578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61966514587402</t>
+    <t xml:space="preserve">7.48112773895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30613040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6196665763855</t>
   </si>
   <si>
     <t xml:space="preserve">7.54675149917603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53216886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34988021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29884004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873565673828</t>
+    <t xml:space="preserve">7.5321683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25508975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34987926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29883909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873517990112</t>
   </si>
   <si>
     <t xml:space="preserve">7.24779748916626</t>
@@ -164,64 +164,64 @@
     <t xml:space="preserve">7.21498727798462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24050712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769453048706</t>
+    <t xml:space="preserve">7.24050617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769500732422</t>
   </si>
   <si>
     <t xml:space="preserve">6.99988460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02175951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623918533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9780101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
+    <t xml:space="preserve">7.02176094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633680343628</t>
   </si>
   <si>
     <t xml:space="preserve">7.50300168991089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56133413314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320903778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778680801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528499603271</t>
+    <t xml:space="preserve">7.56133365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528594970703</t>
   </si>
   <si>
     <t xml:space="preserve">8.12278366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98424291610718</t>
+    <t xml:space="preserve">7.98424482345581</t>
   </si>
   <si>
     <t xml:space="preserve">8.14273262023926</t>
@@ -236,31 +236,31 @@
     <t xml:space="preserve">8.09774494171143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07525157928467</t>
+    <t xml:space="preserve">8.07525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">7.88030576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79782915115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787843704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535852432251</t>
+    <t xml:space="preserve">7.79782867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
   </si>
   <si>
     <t xml:space="preserve">7.6478705406189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527574539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8953013420105</t>
+    <t xml:space="preserve">7.85781145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.985276222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530038833618</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276515960693</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">8.06025505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68258094787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47264099121094</t>
+    <t xml:space="preserve">8.68258190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47264003753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.84003829956055</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">9.4398717880249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25992107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240558624268</t>
+    <t xml:space="preserve">9.25992202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
     <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13245677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.982497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251682281494</t>
+    <t xml:space="preserve">9.13245582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251491546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.99749374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008853912354</t>
+    <t xml:space="preserve">9.10996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008758544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.69757747650146</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">8.77255630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004619598389</t>
+    <t xml:space="preserve">8.81004524230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.81754493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72756862640381</t>
+    <t xml:space="preserve">8.72757053375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.70507621765137</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64509296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007083892822</t>
+    <t xml:space="preserve">8.64509201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007274627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.69007968902588</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3676700592041</t>
+    <t xml:space="preserve">8.36766815185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266563415527</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">8.62259769439697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54761695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265678405762</t>
+    <t xml:space="preserve">8.61509990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5476188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265773773193</t>
   </si>
   <si>
     <t xml:space="preserve">8.28519248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87002944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002059936523</t>
+    <t xml:space="preserve">8.32268333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87002849578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002155303955</t>
   </si>
   <si>
     <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51762771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510780334473</t>
+    <t xml:space="preserve">8.51762676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510971069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.51012992858887</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3601713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31518459320068</t>
+    <t xml:space="preserve">8.36017036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.315185546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.39766120910645</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17272186279297</t>
+    <t xml:space="preserve">8.1727237701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.20271492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45764446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42015552520752</t>
+    <t xml:space="preserve">8.45764541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021270751953</t>
@@ -431,34 +431,34 @@
     <t xml:space="preserve">8.09024620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06775379180908</t>
+    <t xml:space="preserve">8.06775283813477</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
+    <t xml:space="preserve">8.12773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777938842773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523292541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22520923614502</t>
+    <t xml:space="preserve">8.01526832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2252082824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.1202392578125</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">7.76783561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282377243042</t>
+    <t xml:space="preserve">7.82781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282424926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026294708252</t>
@@ -482,70 +482,70 @@
     <t xml:space="preserve">7.95528411865234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03776168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780307769775</t>
+    <t xml:space="preserve">8.03776073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93278980255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780355453491</t>
   </si>
   <si>
     <t xml:space="preserve">7.92529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8728084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029739379883</t>
+    <t xml:space="preserve">7.94778633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029691696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.76033878326416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83531856536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69569969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7496771812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101186752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90389966964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86534547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21234512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485548019409</t>
+    <t xml:space="preserve">7.83531808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09667873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69569873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8653450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2123441696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678937911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485500335693</t>
   </si>
   <si>
     <t xml:space="preserve">7.55690050125122</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">7.51063299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6185884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147672653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47978830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32556676864624</t>
+    <t xml:space="preserve">7.61858797073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5414776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47978734970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556581497192</t>
   </si>
   <si>
     <t xml:space="preserve">7.41809940338135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38725471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761083602905</t>
+    <t xml:space="preserve">7.38725662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761035919189</t>
   </si>
   <si>
     <t xml:space="preserve">7.03254365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23303318023682</t>
+    <t xml:space="preserve">7.23303270339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.24845552444458</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">7.26387691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12507772445679</t>
+    <t xml:space="preserve">7.12507677078247</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929830551147</t>
@@ -596,61 +596,61 @@
     <t xml:space="preserve">7.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20218896865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965490341187</t>
+    <t xml:space="preserve">7.20218849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965585708618</t>
   </si>
   <si>
     <t xml:space="preserve">7.14049959182739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07881116867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2947211265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014394760132</t>
+    <t xml:space="preserve">7.0788106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472255706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.0942325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00169897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205509185791</t>
+    <t xml:space="preserve">7.00169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9091649055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205461502075</t>
   </si>
   <si>
     <t xml:space="preserve">6.92458772659302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952102661133</t>
+    <t xml:space="preserve">6.72409868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952150344849</t>
   </si>
   <si>
     <t xml:space="preserve">6.86289882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0171217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95543193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98627710342407</t>
+    <t xml:space="preserve">7.01712131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543384552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98627662658691</t>
   </si>
   <si>
     <t xml:space="preserve">6.67783212661743</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">6.46192121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53903102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614274978638</t>
+    <t xml:space="preserve">6.53903198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614322662354</t>
   </si>
   <si>
     <t xml:space="preserve">6.52360963821411</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">6.32312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.400230884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26143169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27685356140137</t>
+    <t xml:space="preserve">6.40023136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2614312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.56987714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29227542877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565418243408</t>
+    <t xml:space="preserve">6.29227590560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565370559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.5544548034668</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">6.81663274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374303817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036571502686</t>
+    <t xml:space="preserve">6.89374351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6469874382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7703652381897</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107604980469</t>
@@ -725,31 +725,31 @@
     <t xml:space="preserve">6.10720920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16889762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09178638458252</t>
+    <t xml:space="preserve">6.16889810562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09178686141968</t>
   </si>
   <si>
     <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99925374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.246009349823</t>
+    <t xml:space="preserve">5.99925327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24600982666016</t>
   </si>
   <si>
     <t xml:space="preserve">6.66241025924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649744033813</t>
+    <t xml:space="preserve">6.49276542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649791717529</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516513824463</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">6.36938762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
+    <t xml:space="preserve">6.75494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085523605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592193603516</t>
   </si>
   <si>
     <t xml:space="preserve">7.18676614761353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338834762573</t>
+    <t xml:space="preserve">7.06338739395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.2011513710022</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">7.00912046432495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913373947144</t>
+    <t xml:space="preserve">7.08913278579712</t>
   </si>
   <si>
     <t xml:space="preserve">7.12113809585571</t>
@@ -806,37 +806,37 @@
     <t xml:space="preserve">6.88110017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8650975227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75307941436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73707723617554</t>
+    <t xml:space="preserve">6.86509799957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48103618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504680633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76908254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710283279419</t>
+    <t xml:space="preserve">6.4810357093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76908206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108785629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710235595703</t>
   </si>
   <si>
     <t xml:space="preserve">6.81709003448486</t>
@@ -845,31 +845,31 @@
     <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59305334091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705163955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51304197311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702651977539</t>
+    <t xml:space="preserve">6.65706348419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59305381774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51304149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702604293823</t>
   </si>
   <si>
     <t xml:space="preserve">6.40102291107178</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">6.33701324462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22499513626099</t>
+    <t xml:space="preserve">6.22499465942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097219467163</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">6.06496953964233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09697484970093</t>
+    <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.16098499298096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00095987319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95295190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01696157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92094707489014</t>
+    <t xml:space="preserve">6.0009593963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95295143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01696252822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895360946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.76092147827148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74491834640503</t>
+    <t xml:space="preserve">5.74491786956787</t>
   </si>
   <si>
     <t xml:space="preserve">5.680908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71291351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82493114471436</t>
+    <t xml:space="preserve">5.71291303634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493162155151</t>
   </si>
   <si>
     <t xml:space="preserve">5.90494441986084</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">5.87293863296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79292583465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98495721817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11297702789307</t>
+    <t xml:space="preserve">5.7929253578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98495626449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11297750473022</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101058959961</t>
+    <t xml:space="preserve">6.32101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">6.27300310134888</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17698764801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38502073287964</t>
+    <t xml:space="preserve">6.1769871711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498233795166</t>
+    <t xml:space="preserve">6.12897872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14498138427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">5.93694925308228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03296422958374</t>
+    <t xml:space="preserve">6.0329647064209</t>
   </si>
   <si>
     <t xml:space="preserve">5.61689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48887825012207</t>
+    <t xml:space="preserve">5.48887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">5.55288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50487995147705</t>
+    <t xml:space="preserve">5.39286184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50488042831421</t>
   </si>
   <si>
     <t xml:space="preserve">5.60089540481567</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67274713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24067783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9206268787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2886848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04864645004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1606650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40070390701294</t>
+    <t xml:space="preserve">4.67274761199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24067831039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062711715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28868532180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04864692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16066551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08065271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40070295333862</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075414657593</t>
@@ -1046,31 +1046,31 @@
     <t xml:space="preserve">5.13682126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52088308334351</t>
+    <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32885217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3128490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1848292350769</t>
+    <t xml:space="preserve">5.3288516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31284952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18482828140259</t>
   </si>
   <si>
     <t xml:space="preserve">5.00880098342896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28084373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05680847167969</t>
+    <t xml:space="preserve">5.16882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28084421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05680894851685</t>
   </si>
   <si>
     <t xml:space="preserve">5.23283624649048</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891569137573</t>
+    <t xml:space="preserve">5.72891521453857</t>
   </si>
   <si>
     <t xml:space="preserve">5.88894128799438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84093427658081</t>
+    <t xml:space="preserve">5.84093379974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69691038131714</t>
+    <t xml:space="preserve">5.77692317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69690990447998</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693693161011</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">5.56889057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34485483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44087028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685966491699</t>
+    <t xml:space="preserve">5.34485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44086933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685918807983</t>
   </si>
   <si>
     <t xml:space="preserve">5.26484155654907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883937835693</t>
+    <t xml:space="preserve">5.24883890151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
@@ -1130,118 +1130,118 @@
     <t xml:space="preserve">5.53688478469849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29684686660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21683359146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35301637649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28900527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49703884124756</t>
+    <t xml:space="preserve">5.29684638977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3530158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28900575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49703788757324</t>
   </si>
   <si>
     <t xml:space="preserve">6.7050724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915933609009</t>
+    <t xml:space="preserve">6.67306613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915838241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.26516103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121488571167</t>
+    <t xml:space="preserve">7.28116369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121393203735</t>
   </si>
   <si>
     <t xml:space="preserve">7.5212025642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53720474243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319555282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118928909302</t>
+    <t xml:space="preserve">7.5372052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319459915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118976593018</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40918445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315668106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
+    <t xml:space="preserve">7.40918350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3131685256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.42518711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125375747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526342391968</t>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04128456115723</t>
+    <t xml:space="preserve">8.04128646850586</t>
   </si>
   <si>
     <t xml:space="preserve">7.92126607894897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0012788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8732590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327043533325</t>
+    <t xml:space="preserve">7.93726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00127983093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325763702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327138900757</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
@@ -1250,46 +1250,46 @@
     <t xml:space="preserve">7.96927404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28132343292236</t>
+    <t xml:space="preserve">8.28132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44134902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139263153076</t>
+    <t xml:space="preserve">8.44134998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139358520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8414134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9614315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48151683807373</t>
+    <t xml:space="preserve">8.84141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96143245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84157276153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1616249084473</t>
+    <t xml:space="preserve">9.84157371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1616239547729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816116333008</t>
@@ -1316,127 +1316,127 @@
     <t xml:space="preserve">11.1217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.041766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9617528915405</t>
+    <t xml:space="preserve">11.0417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9617509841919</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8417339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8817405700684</t>
+    <t xml:space="preserve">10.8417320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8817386627197</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817728042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7617197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216808319092</t>
+    <t xml:space="preserve">11.2417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7617206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
     <t xml:space="preserve">10.60169506073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818050384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6965761184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7011213302612</t>
+    <t xml:space="preserve">11.2818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6965751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7011222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1619176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789632797241</t>
+    <t xml:space="preserve">10.0374879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204414367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1619186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.99600982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91305541992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9545316696167</t>
+    <t xml:space="preserve">9.91305637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95453262329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7425985336304</t>
+    <t xml:space="preserve">10.3278284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7425994873047</t>
   </si>
   <si>
     <t xml:space="preserve">10.825553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5766897201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8670320510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181669235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863492965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033958435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87157917022705</t>
+    <t xml:space="preserve">10.5766906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693056106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2448740005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033967971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522590637207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9499845504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115894317627</t>
+    <t xml:space="preserve">10.9499855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840757369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1158952713013</t>
   </si>
   <si>
     <t xml:space="preserve">10.9085083007812</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">10.6596460342407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
+    <t xml:space="preserve">11.032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232793807983</t>
   </si>
   <si>
     <t xml:space="preserve">11.4891901016235</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">12.3602104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3187351226807</t>
+    <t xml:space="preserve">12.6505517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3187341690063</t>
   </si>
   <si>
     <t xml:space="preserve">12.5261201858521</t>
@@ -1493,31 +1493,31 @@
     <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5630502700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215721130371</t>
+    <t xml:space="preserve">13.5630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215730667114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3556652069092</t>
+    <t xml:space="preserve">13.3556642532349</t>
   </si>
   <si>
     <t xml:space="preserve">14.0193004608154</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
+    <t xml:space="preserve">13.894868850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874837875366</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3647575378418</t>
+    <t xml:space="preserve">12.4846429824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0283937454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3647565841675</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062347412109</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">11.8210077285767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4477119445801</t>
+    <t xml:space="preserve">11.1988487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
     <t xml:space="preserve">11.7380523681641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74714660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6136207580566</t>
+    <t xml:space="preserve">9.78862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6641902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.747145652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">11.0661220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9665756225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.734302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.651349067688</t>
+    <t xml:space="preserve">10.7177133560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9665765762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7343044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679391860962</t>
+    <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
     <t xml:space="preserve">10.8504400253296</t>
@@ -1601,34 +1601,34 @@
     <t xml:space="preserve">10.9168043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8006687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002132415771</t>
+    <t xml:space="preserve">10.8006677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002141952515</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7674865722656</t>
+    <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849866867065</t>
+    <t xml:space="preserve">10.8338489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.331392288208</t>
+    <t xml:space="preserve">11.4693689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313913345337</t>
   </si>
   <si>
     <t xml:space="preserve">11.2279100418091</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">12.2454929351807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2109975814819</t>
+    <t xml:space="preserve">12.2109966278076</t>
   </si>
   <si>
     <t xml:space="preserve">12.2282457351685</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">12.1592569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4179630279541</t>
+    <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.1937503814697</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0730209350586</t>
+    <t xml:space="preserve">12.0730199813843</t>
   </si>
   <si>
     <t xml:space="preserve">11.2106618881226</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">11.1589202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625722885132</t>
+    <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
     <t xml:space="preserve">11.831561088562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9522895812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7280778884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5728530883789</t>
+    <t xml:space="preserve">11.3831338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9522905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7280769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
     <t xml:space="preserve">11.7453231811523</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2627391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9867849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177961349487</t>
+    <t xml:space="preserve">11.8660545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2627401351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9867839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3144798278809</t>
+    <t xml:space="preserve">12.3144807815552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3317279815674</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350423812866</t>
+    <t xml:space="preserve">11.9695377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">12.107515335083</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970657348633</t>
+    <t xml:space="preserve">11.7970666885376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.245156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3658866882324</t>
+    <t xml:space="preserve">11.607346534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2451572418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3658876419067</t>
   </si>
   <si>
     <t xml:space="preserve">11.521110534668</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">11.6418409347534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
+    <t xml:space="preserve">11.4348754882812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0381908416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1071796417236</t>
+    <t xml:space="preserve">11.1071786880493</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209426879883</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193078994751</t>
+    <t xml:space="preserve">10.1930780410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312253952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383577346802</t>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
@@ -1862,28 +1862,28 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524583816528</t>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869518280029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.573187828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6421766281128</t>
+    <t xml:space="preserve">12.5731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6421775817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5214471817017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386934280396</t>
+    <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521226882935</t>
+    <t xml:space="preserve">11.4521217346191</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">11.3141450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9519548416138</t>
+    <t xml:space="preserve">10.9519538879395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0899324417114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554361343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967290878296</t>
+    <t xml:space="preserve">11.0554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347076416016</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5725173950195</t>
+    <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
     <t xml:space="preserve">10.6070108413696</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">10.4517869949341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380210876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4000453948975</t>
+    <t xml:space="preserve">10.469033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4000444412231</t>
   </si>
   <si>
     <t xml:space="preserve">10.277060508728</t>
@@ -16759,7 +16759,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16785,7 +16785,7 @@
         <v>10.5</v>
       </c>
       <c r="G513" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16811,7 +16811,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G514" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16837,7 +16837,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16863,7 +16863,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G516" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16915,7 +16915,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17071,7 +17071,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17097,7 +17097,7 @@
         <v>10.5</v>
       </c>
       <c r="G525" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17123,7 +17123,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G526" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17721,7 +17721,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G549" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17851,7 +17851,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G554" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17877,7 +17877,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17955,7 +17955,7 @@
         <v>10.5</v>
       </c>
       <c r="G558" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17981,7 +17981,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18033,7 +18033,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18059,7 +18059,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G562" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18085,7 +18085,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G563" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18111,7 +18111,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18163,7 +18163,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G566" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18215,7 +18215,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18345,7 +18345,7 @@
         <v>10.5</v>
       </c>
       <c r="G573" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18397,7 +18397,7 @@
         <v>10.5</v>
       </c>
       <c r="G575" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18423,7 +18423,7 @@
         <v>10.5</v>
       </c>
       <c r="G576" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18449,7 +18449,7 @@
         <v>10.5</v>
       </c>
       <c r="G577" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18995,7 +18995,7 @@
         <v>10.5</v>
       </c>
       <c r="G598" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19021,7 +19021,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19047,7 +19047,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G600" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19073,7 +19073,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19099,7 +19099,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G602" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19125,7 +19125,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19151,7 +19151,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19177,7 +19177,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19203,7 +19203,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G606" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19229,7 +19229,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G607" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19255,7 +19255,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19281,7 +19281,7 @@
         <v>10.5</v>
       </c>
       <c r="G609" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19307,7 +19307,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19333,7 +19333,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G611" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19385,7 +19385,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19411,7 +19411,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19489,7 +19489,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19515,7 +19515,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19697,7 +19697,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19723,7 +19723,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19749,7 +19749,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G627" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19775,7 +19775,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19801,7 +19801,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20087,7 +20087,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G640" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20165,7 +20165,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -68247,7 +68247,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493055556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>29130</v>
@@ -68268,6 +68268,32 @@
         <v>1011</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493171296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>41806</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>17.3999996185303</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>17.6399993896484</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,226 +38,226 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217515945435</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10925817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061494827271</t>
+    <t xml:space="preserve">7.16394519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0728006362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925912857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061542510986</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051246643066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14207172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9670729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634309768677</t>
+    <t xml:space="preserve">7.14207029342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634357452393</t>
   </si>
   <si>
     <t xml:space="preserve">7.00717687606812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96342706680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696323394775</t>
+    <t xml:space="preserve">6.96342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
   </si>
   <si>
     <t xml:space="preserve">7.36446332931519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29154682159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863174438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821170806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362764358521</t>
+    <t xml:space="preserve">7.2915472984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2623815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821218490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362955093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.43737840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28790092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029443740845</t>
+    <t xml:space="preserve">7.28790187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008756637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029348373413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154148101807</t>
+    <t xml:space="preserve">7.64154052734375</t>
   </si>
   <si>
     <t xml:space="preserve">7.48841953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6196665763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675149917603</t>
+    <t xml:space="preserve">7.48112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30613088607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675197601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.5321683883667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34987926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29883909225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873517990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24779748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050617218018</t>
+    <t xml:space="preserve">7.25508832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34988021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29883861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050760269165</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99988460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02176094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383737564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300168991089</t>
+    <t xml:space="preserve">6.99988603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9780101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633871078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.56133365631104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5832085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770355224609</t>
+    <t xml:space="preserve">7.58320903778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445798873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72903966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487316131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778490066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770450592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09774494171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525062561035</t>
+    <t xml:space="preserve">8.09774589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
     <t xml:space="preserve">7.88030576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79782867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6478705406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.985276222229</t>
+    <t xml:space="preserve">7.79782819747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98527574539185</t>
   </si>
   <si>
     <t xml:space="preserve">7.89530038833618</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">8.02276515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06025505065918</t>
+    <t xml:space="preserve">8.06025409698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47264003753662</t>
+    <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.84003829956055</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">9.4398717880249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25992202758789</t>
+    <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31990432739258</t>
+    <t xml:space="preserve">9.31990528106689</t>
   </si>
   <si>
     <t xml:space="preserve">9.13245582580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98249816894531</t>
+    <t xml:space="preserve">8.982497215271</t>
   </si>
   <si>
     <t xml:space="preserve">8.92251491546631</t>
@@ -302,79 +302,79 @@
     <t xml:space="preserve">8.99749374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008758544922</t>
+    <t xml:space="preserve">9.10996246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008853912354</t>
   </si>
   <si>
     <t xml:space="preserve">8.69757747650146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753608703613</t>
+    <t xml:space="preserve">8.59260654449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753513336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507621765137</t>
+    <t xml:space="preserve">8.8100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507526397705</t>
   </si>
   <si>
     <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64509201049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007274627686</t>
+    <t xml:space="preserve">8.64509296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007083892822</t>
   </si>
   <si>
     <t xml:space="preserve">8.69007968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36766815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259769439697</t>
+    <t xml:space="preserve">8.60010623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36766910552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259864807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5476188659668</t>
+    <t xml:space="preserve">8.54761791229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.41265773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28519248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506546020508</t>
+    <t xml:space="preserve">8.28519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506736755371</t>
   </si>
   <si>
     <t xml:space="preserve">8.87002849578857</t>
@@ -386,43 +386,43 @@
     <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51762676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51012992858887</t>
+    <t xml:space="preserve">8.51762771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510780334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51013088226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36017036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.315185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766120910645</t>
+    <t xml:space="preserve">8.3601713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31518459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766216278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1727237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20271492004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4201545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21021270751953</t>
+    <t xml:space="preserve">8.17272281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20271587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21021366119385</t>
   </si>
   <si>
     <t xml:space="preserve">8.1127405166626</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277353286743</t>
+    <t xml:space="preserve">8.12773513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277400970459</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777938842773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01526832580566</t>
+    <t xml:space="preserve">8.01526641845703</t>
   </si>
   <si>
     <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24020576477051</t>
+    <t xml:space="preserve">8.24020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.2252082824707</t>
@@ -464,49 +464,49 @@
     <t xml:space="preserve">8.1202392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00777053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76783561706543</t>
+    <t xml:space="preserve">8.00777149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76783514022827</t>
   </si>
   <si>
     <t xml:space="preserve">7.82781982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81282424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
+    <t xml:space="preserve">7.81282329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.03776073455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93278980255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033878326416</t>
+    <t xml:space="preserve">8.16522598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93279123306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9477858543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033926010132</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531808853149</t>
@@ -515,130 +515,130 @@
     <t xml:space="preserve">8.09667873382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78823471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69569873809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2123441696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678937911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112251281738</t>
+    <t xml:space="preserve">7.7882342338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69570016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7496771812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101186752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112203598022</t>
   </si>
   <si>
     <t xml:space="preserve">7.66485500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55690050125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858797073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5414776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47978734970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32556581497192</t>
+    <t xml:space="preserve">7.55689907073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4797887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556629180908</t>
   </si>
   <si>
     <t xml:space="preserve">7.41809940338135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38725662231445</t>
+    <t xml:space="preserve">7.38725519180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.21761035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03254365921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303270339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845552444458</t>
+    <t xml:space="preserve">7.03254413604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845504760742</t>
   </si>
   <si>
     <t xml:space="preserve">7.26387691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17134428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218849182129</t>
+    <t xml:space="preserve">7.12507724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929878234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17134380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218896865845</t>
   </si>
   <si>
     <t xml:space="preserve">7.10965585708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14049959182739</t>
+    <t xml:space="preserve">7.14049911499023</t>
   </si>
   <si>
     <t xml:space="preserve">7.0788106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29472255706787</t>
+    <t xml:space="preserve">7.29472208023071</t>
   </si>
   <si>
     <t xml:space="preserve">7.31014442443848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9091649055481</t>
+    <t xml:space="preserve">7.09423208236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916585922241</t>
   </si>
   <si>
     <t xml:space="preserve">6.83205461502075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92458772659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952150344849</t>
+    <t xml:space="preserve">6.92458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">6.86289882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01712131500244</t>
+    <t xml:space="preserve">7.0171217918396</t>
   </si>
   <si>
     <t xml:space="preserve">6.78578805923462</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">6.94001007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95543384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98627662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67783212661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7086763381958</t>
+    <t xml:space="preserve">6.95543241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98627758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67783117294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70867681503296</t>
   </si>
   <si>
     <t xml:space="preserve">6.63156509399414</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">6.46192121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53903198242188</t>
+    <t xml:space="preserve">6.53903102874756</t>
   </si>
   <si>
     <t xml:space="preserve">6.61614322662354</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">6.19974231719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23058700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32312059402466</t>
+    <t xml:space="preserve">6.23058748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3231201171875</t>
   </si>
   <si>
     <t xml:space="preserve">6.40023136138916</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">6.2614312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27685403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56987714767456</t>
+    <t xml:space="preserve">6.27685356140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565370559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5544548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663274765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89374351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6469874382019</t>
+    <t xml:space="preserve">6.41565418243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445432662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89374303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698839187622</t>
   </si>
   <si>
     <t xml:space="preserve">6.7703652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43107604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720920562744</t>
+    <t xml:space="preserve">6.43107557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1072096824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889810562134</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24600982666016</t>
+    <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
     <t xml:space="preserve">6.66241025924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21516513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36938762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832117080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085523605347</t>
+    <t xml:space="preserve">6.49276494979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21516561508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36938714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494337081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085475921631</t>
   </si>
   <si>
     <t xml:space="preserve">7.04796600341797</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">7.18676614761353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2011513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314340591431</t>
+    <t xml:space="preserve">7.06338882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20115089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.07313108444214</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">7.00912046432495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913278579712</t>
+    <t xml:space="preserve">7.08913373947144</t>
   </si>
   <si>
     <t xml:space="preserve">7.12113809585571</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">6.88110017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86509799957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73707628250122</t>
+    <t xml:space="preserve">6.8650975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75307941436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
     <t xml:space="preserve">6.72107410430908</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">6.4810357093811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54504632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905694961548</t>
+    <t xml:space="preserve">6.54504680633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905647277832</t>
   </si>
   <si>
     <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710235595703</t>
+    <t xml:space="preserve">6.80108737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710283279419</t>
   </si>
   <si>
     <t xml:space="preserve">6.81709003448486</t>
@@ -845,73 +845,73 @@
     <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706348419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59305381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302822113037</t>
+    <t xml:space="preserve">6.65706396102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59305334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302869796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.51304149627686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903182983398</t>
+    <t xml:space="preserve">6.44903087615967</t>
   </si>
   <si>
     <t xml:space="preserve">6.41702604293823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40102291107178</t>
+    <t xml:space="preserve">6.40102338790894</t>
   </si>
   <si>
     <t xml:space="preserve">6.33701324462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22499465942383</t>
+    <t xml:space="preserve">6.2249960899353</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04896688461304</t>
+    <t xml:space="preserve">6.0489673614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496953964233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09697437286377</t>
+    <t xml:space="preserve">6.09697484970093</t>
   </si>
   <si>
     <t xml:space="preserve">6.16098499298096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0009593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95295143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01696252822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895360946655</t>
+    <t xml:space="preserve">6.00095987319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95295190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76092147827148</t>
+    <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
     <t xml:space="preserve">5.74491786956787</t>
@@ -923,55 +923,55 @@
     <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82493162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7929253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98495626449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11297750473022</t>
+    <t xml:space="preserve">5.82493114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494394302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293910980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79292583465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98495674133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101011276245</t>
+    <t xml:space="preserve">6.32101058959961</t>
   </si>
   <si>
     <t xml:space="preserve">6.27300310134888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20899248123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1769871711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38502025604248</t>
+    <t xml:space="preserve">6.20899295806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17698764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498138427734</t>
+    <t xml:space="preserve">6.12897968292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14498233795166</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30500793457031</t>
+    <t xml:space="preserve">6.30500841140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">5.61689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48887729644775</t>
+    <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39286184310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50488042831421</t>
+    <t xml:space="preserve">5.55288743972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487995147705</t>
   </si>
   <si>
     <t xml:space="preserve">5.60089540481567</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67274761199951</t>
+    <t xml:space="preserve">4.6727466583252</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871091842651</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">4.24067831039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92062711715698</t>
+    <t xml:space="preserve">3.9206268787384</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868532180786</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16066551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08065271377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40070295333862</t>
+    <t xml:space="preserve">4.1606650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08065223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40070390701294</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075414657593</t>
@@ -1046,157 +1046,157 @@
     <t xml:space="preserve">5.13682126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52088260650635</t>
+    <t xml:space="preserve">5.52088308334351</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.32885217666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.31284952163696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482828140259</t>
+    <t xml:space="preserve">5.18482875823975</t>
   </si>
   <si>
     <t xml:space="preserve">5.00880098342896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16882610321045</t>
+    <t xml:space="preserve">5.16882658004761</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680894851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283624649048</t>
+    <t xml:space="preserve">5.05680847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283672332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891521453857</t>
+    <t xml:space="preserve">5.72891569137573</t>
   </si>
   <si>
     <t xml:space="preserve">5.88894128799438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84093379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64890289306641</t>
+    <t xml:space="preserve">5.84093427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64890336990356</t>
   </si>
   <si>
     <t xml:space="preserve">5.77692317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69690990447998</t>
+    <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486715316772</t>
+    <t xml:space="preserve">5.58489227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486763000488</t>
   </si>
   <si>
     <t xml:space="preserve">5.56889057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34485387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44086933135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685918807983</t>
+    <t xml:space="preserve">5.34485483169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44087028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685966491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.26484155654907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883890151978</t>
+    <t xml:space="preserve">5.24883937835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53688478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29684638977051</t>
+    <t xml:space="preserve">5.53688430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29684734344482</t>
   </si>
   <si>
     <t xml:space="preserve">5.21683406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3530158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49703788757324</t>
+    <t xml:space="preserve">6.35301637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4970383644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.7050724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915838241577</t>
+    <t xml:space="preserve">6.67306661605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915981292725</t>
   </si>
   <si>
     <t xml:space="preserve">7.26516103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28116369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121393203735</t>
+    <t xml:space="preserve">7.28116464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521127700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.5212025642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5372052192688</t>
+    <t xml:space="preserve">7.53720426559448</t>
   </si>
   <si>
     <t xml:space="preserve">7.47319459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44118976593018</t>
+    <t xml:space="preserve">7.44118928909302</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40918350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3131685256958</t>
+    <t xml:space="preserve">7.40918445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316947937012</t>
   </si>
   <si>
     <t xml:space="preserve">7.42518711090088</t>
@@ -1205,43 +1205,43 @@
     <t xml:space="preserve">7.50519990921021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36117601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716730117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08129215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04128646850586</t>
+    <t xml:space="preserve">7.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526342391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08129119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04128456115723</t>
   </si>
   <si>
     <t xml:space="preserve">7.92126607894897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726968765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87325763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327138900757</t>
+    <t xml:space="preserve">7.93726873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00127792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8732590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327043533325</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">7.96927404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44134998321533</t>
+    <t xml:space="preserve">8.28132343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.72139358520508</t>
@@ -1265,88 +1265,88 @@
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0414457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152252197266</t>
+    <t xml:space="preserve">8.8414134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04144477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9614315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.48151588439941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72155380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84157371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1616239547729</t>
+    <t xml:space="preserve">9.72155475616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84157276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1616249084473</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.121618270874</t>
+    <t xml:space="preserve">10.1216173171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.2816438674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3216495513916</t>
+    <t xml:space="preserve">10.3216505050659</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217140197754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218088150024</t>
+    <t xml:space="preserve">11.3218107223511</t>
   </si>
   <si>
     <t xml:space="preserve">11.2017908096313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1217775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0417652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9617509841919</t>
+    <t xml:space="preserve">11.1217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.041766166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8417320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8817386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818353652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2417964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817718505859</t>
+    <t xml:space="preserve">10.8417329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818363189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2417974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817728042603</t>
   </si>
   <si>
     <t xml:space="preserve">10.7617206573486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0017585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216817855835</t>
+    <t xml:space="preserve">11.0017576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216808319092</t>
   </si>
   <si>
     <t xml:space="preserve">10.60169506073</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">11.6965751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1573724746704</t>
+    <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.7011222839355</t>
@@ -1367,31 +1367,31 @@
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1619186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99600982666016</t>
+    <t xml:space="preserve">10.0374870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1619176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95453262329102</t>
+    <t xml:space="preserve">9.9545316696167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278284072876</t>
+    <t xml:space="preserve">10.3278274536133</t>
   </si>
   <si>
     <t xml:space="preserve">10.9914636611938</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">10.6181678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3693056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033967971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87157821655273</t>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033958435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87157917022705</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522590637207</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">10.7840757369995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1158952713013</t>
+    <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">10.9085083007812</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">10.6596460342407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.032940864563</t>
+    <t xml:space="preserve">11.0329399108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.3232793807983</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">13.5630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8119144439697</t>
+    <t xml:space="preserve">13.8119125366211</t>
   </si>
   <si>
     <t xml:space="preserve">13.6460065841675</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">13.3556642532349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0193004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6874837875366</t>
+    <t xml:space="preserve">14.0192995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874828338623</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">11.4062347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8210077285767</t>
+    <t xml:space="preserve">11.8210067749023</t>
   </si>
   <si>
     <t xml:space="preserve">11.1988487243652</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">11.7380523681641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78862285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6641902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624849319458</t>
+    <t xml:space="preserve">9.78862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624839782715</t>
   </si>
   <si>
     <t xml:space="preserve">11.613621711731</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6513500213623</t>
+    <t xml:space="preserve">10.7343034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651349067688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504400253296</t>
+    <t xml:space="preserve">10.6679391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504390716553</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168043136597</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">10.9002141952515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8172588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7674856185913</t>
+    <t xml:space="preserve">10.8172578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.767484664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997587203979</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">10.8338489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5849876403809</t>
+    <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
@@ -68273,7 +68273,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493171296</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>41806</v>
@@ -68294,6 +68294,32 @@
         <v>1015</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6493518519</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>113889</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>17.5599994659424</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>17.1399993896484</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>17.2800006866455</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217325210571</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394567489624</t>
+    <t xml:space="preserve">7.16394472122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07280111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10925769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634309768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
+    <t xml:space="preserve">7.07279968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14206981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0071759223938</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342706680298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2769627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2623815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.393630027771</t>
+    <t xml:space="preserve">7.25144386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821075439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362859725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.4373779296875</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">7.28790187835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28425693511963</t>
+    <t xml:space="preserve">7.28425645828247</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008613586426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154195785522</t>
+    <t xml:space="preserve">7.51029491424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154100418091</t>
   </si>
   <si>
     <t xml:space="preserve">7.4884204864502</t>
@@ -137,169 +137,169 @@
     <t xml:space="preserve">7.6196665763855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54675102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216791152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
+    <t xml:space="preserve">7.5467529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529615402222</t>
   </si>
   <si>
     <t xml:space="preserve">7.3498797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29883861541748</t>
+    <t xml:space="preserve">7.29883909225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.25873470306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24779653549194</t>
+    <t xml:space="preserve">7.24779748916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.21498680114746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24050712585449</t>
+    <t xml:space="preserve">7.24050760269165</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99988555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02176141738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99624061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300216674805</t>
+    <t xml:space="preserve">6.99988508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0217604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97800970077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3863377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300168991089</t>
   </si>
   <si>
     <t xml:space="preserve">7.56133508682251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58320903778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778490066528</t>
+    <t xml:space="preserve">7.58320951461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72903966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487173080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778537750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.03528499603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12278270721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273166656494</t>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273262023926</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770355224609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1802225112915</t>
+    <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
     <t xml:space="preserve">8.09774494171143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07525157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88030481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787939071655</t>
+    <t xml:space="preserve">8.07525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88030529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787700653076</t>
   </si>
   <si>
     <t xml:space="preserve">7.68535995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64787006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527479171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89530038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06025409698486</t>
+    <t xml:space="preserve">7.64786958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.985276222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06025505065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84003925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992107391357</t>
+    <t xml:space="preserve">8.47264194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4398717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992202758789</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31990337371826</t>
+    <t xml:space="preserve">9.31990623474121</t>
   </si>
   <si>
     <t xml:space="preserve">9.1324577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98249816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9974946975708</t>
+    <t xml:space="preserve">8.98249912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99749565124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996246337891</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">8.69757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59260654449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753513336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255725860596</t>
+    <t xml:space="preserve">8.59260749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255630493164</t>
   </si>
   <si>
     <t xml:space="preserve">8.8100471496582</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">8.72756958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507526397705</t>
+    <t xml:space="preserve">8.70507621765137</t>
   </si>
   <si>
     <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64509296417236</t>
+    <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72007179260254</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36767101287842</t>
+    <t xml:space="preserve">8.36766910552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266468048096</t>
@@ -359,67 +359,67 @@
     <t xml:space="preserve">8.62259769439697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6151008605957</t>
+    <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
     <t xml:space="preserve">8.54761981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41265773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268238067627</t>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268333435059</t>
   </si>
   <si>
     <t xml:space="preserve">8.73506641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87003040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002155303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67508316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51762676239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510875701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51013088226318</t>
+    <t xml:space="preserve">8.87002944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67508411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51762771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51012992858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36017227172852</t>
+    <t xml:space="preserve">8.3601713180542</t>
   </si>
   <si>
     <t xml:space="preserve">8.31518459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39766120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30018901824951</t>
+    <t xml:space="preserve">8.39766025543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30018711090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.17272281646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42015552520752</t>
+    <t xml:space="preserve">8.20271492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021366119385</t>
@@ -428,37 +428,37 @@
     <t xml:space="preserve">8.11273956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09024620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08274936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9777774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526641845703</t>
+    <t xml:space="preserve">8.09024715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08274745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277305603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
     <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2252082824707</t>
+    <t xml:space="preserve">8.24020481109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22521018981934</t>
   </si>
   <si>
     <t xml:space="preserve">8.12023830413818</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">8.00777053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82782030105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279027938843</t>
+    <t xml:space="preserve">7.76783561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82781887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528316497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93279075622559</t>
   </si>
   <si>
     <t xml:space="preserve">7.88780403137207</t>
@@ -497,58 +497,58 @@
     <t xml:space="preserve">7.92529201507568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9477858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.760338306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09667778015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69569873809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2123441696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112298965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485357284546</t>
+    <t xml:space="preserve">7.94778633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8728084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69570016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678890228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112203598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">7.55690002441406</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">7.51063299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5414776802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4797887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3255672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
+    <t xml:space="preserve">7.61858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47978734970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41810035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725614547729</t>
   </si>
   <si>
     <t xml:space="preserve">7.21761035919189</t>
@@ -581,73 +581,73 @@
     <t xml:space="preserve">7.03254365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23303270339966</t>
+    <t xml:space="preserve">7.23303413391113</t>
   </si>
   <si>
     <t xml:space="preserve">7.24845457077026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2638783454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929925918579</t>
+    <t xml:space="preserve">7.26387739181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507629394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929830551147</t>
   </si>
   <si>
     <t xml:space="preserve">7.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20218896865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14049959182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07881116867065</t>
+    <t xml:space="preserve">7.20218849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14049911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0788106918335</t>
   </si>
   <si>
     <t xml:space="preserve">7.29472208023071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31014347076416</t>
+    <t xml:space="preserve">7.31014394760132</t>
   </si>
   <si>
     <t xml:space="preserve">7.09423208236694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00169944763184</t>
+    <t xml:space="preserve">7.00169992446899</t>
   </si>
   <si>
     <t xml:space="preserve">6.90916538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83205461502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458772659302</t>
+    <t xml:space="preserve">6.83205413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458724975586</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73952150344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86289930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712274551392</t>
+    <t xml:space="preserve">6.73952054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86289834976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712131500244</t>
   </si>
   <si>
     <t xml:space="preserve">6.78578758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94000959396362</t>
+    <t xml:space="preserve">6.94001054763794</t>
   </si>
   <si>
     <t xml:space="preserve">6.9554328918457</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">6.98627710342407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70867586135864</t>
+    <t xml:space="preserve">6.67783308029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7086763381958</t>
   </si>
   <si>
     <t xml:space="preserve">6.6315655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47734260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52361011505127</t>
+    <t xml:space="preserve">6.47734308242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52360963821411</t>
   </si>
   <si>
     <t xml:space="preserve">6.19974231719971</t>
@@ -689,43 +689,43 @@
     <t xml:space="preserve">6.32312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40023183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26143169403076</t>
+    <t xml:space="preserve">6.40023231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26143074035645</t>
   </si>
   <si>
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5698766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29227590560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565275192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5544548034668</t>
+    <t xml:space="preserve">6.56987619400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29227542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565370559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374256134033</t>
+    <t xml:space="preserve">6.89374351501465</t>
   </si>
   <si>
     <t xml:space="preserve">6.6469874382019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77036571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720872879028</t>
+    <t xml:space="preserve">6.77036476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1072096824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889810562134</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">6.30769824981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99925327301025</t>
+    <t xml:space="preserve">5.99925374984741</t>
   </si>
   <si>
     <t xml:space="preserve">6.246009349823</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">6.66240978240967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396480560303</t>
+    <t xml:space="preserve">6.49276494979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
   </si>
   <si>
     <t xml:space="preserve">6.44649791717529</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">6.21516466140747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
+    <t xml:space="preserve">6.36938714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676519393921</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338787078857</t>
@@ -785,34 +785,34 @@
     <t xml:space="preserve">7.2011513710022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313108444214</t>
+    <t xml:space="preserve">7.15314340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00912046432495</t>
+    <t xml:space="preserve">7.00912094116211</t>
   </si>
   <si>
     <t xml:space="preserve">7.08913278579712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12113809585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83309173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110017776489</t>
+    <t xml:space="preserve">7.12113761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.833092212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88109970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78508424758911</t>
+    <t xml:space="preserve">6.78508377075195</t>
   </si>
   <si>
     <t xml:space="preserve">6.75307893753052</t>
@@ -824,52 +824,52 @@
     <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48103618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905647277832</t>
+    <t xml:space="preserve">6.4810357093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905599594116</t>
   </si>
   <si>
     <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81709003448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56104850769043</t>
+    <t xml:space="preserve">6.80108737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710283279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81708955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
     <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59305381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505865097046</t>
+    <t xml:space="preserve">6.59305429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505912780762</t>
   </si>
   <si>
     <t xml:space="preserve">6.57705116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52904415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51304149627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903135299683</t>
+    <t xml:space="preserve">6.52904367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5130410194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903087615967</t>
   </si>
   <si>
     <t xml:space="preserve">6.41702604293823</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">6.40102338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22499513626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08097219467163</t>
+    <t xml:space="preserve">6.33701372146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22499561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08097124099731</t>
   </si>
   <si>
     <t xml:space="preserve">6.04896640777588</t>
@@ -905,49 +905,49 @@
     <t xml:space="preserve">5.95295143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895408630371</t>
+    <t xml:space="preserve">6.01696157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895456314087</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76092052459717</t>
+    <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
     <t xml:space="preserve">5.74491834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.680908203125</t>
+    <t xml:space="preserve">5.68090772628784</t>
   </si>
   <si>
     <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82493114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494394302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7929253578186</t>
+    <t xml:space="preserve">5.82493162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8729395866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79292583465576</t>
   </si>
   <si>
     <t xml:space="preserve">5.98495674133301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11297702789307</t>
+    <t xml:space="preserve">6.11297655105591</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101011276245</t>
+    <t xml:space="preserve">6.32101058959961</t>
   </si>
   <si>
     <t xml:space="preserve">6.27300310134888</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17698764801025</t>
+    <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
     <t xml:space="preserve">6.38502025604248</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">6.12897920608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1449818611145</t>
+    <t xml:space="preserve">6.14498138427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30500793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93694925308228</t>
+    <t xml:space="preserve">6.30500841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93694972991943</t>
   </si>
   <si>
     <t xml:space="preserve">6.03296422958374</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">5.61689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48887777328491</t>
+    <t xml:space="preserve">5.48887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
@@ -995,40 +995,40 @@
     <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50487995147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089492797852</t>
+    <t xml:space="preserve">5.39286184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50488042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089540481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.36085653305054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12081861495972</t>
+    <t xml:space="preserve">5.12081813812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67274761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24067831039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062664031982</t>
+    <t xml:space="preserve">4.67274713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24067783355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062711715698</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864740371704</t>
+    <t xml:space="preserve">4.0486478805542</t>
   </si>
   <si>
     <t xml:space="preserve">4.1606650352478</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">4.08065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40070295333862</t>
+    <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075462341309</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.40886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32885122299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880098342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882610321045</t>
+    <t xml:space="preserve">5.18482875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0088005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882658004761</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680799484253</t>
+    <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.23283624649048</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">5.72891521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88894081115723</t>
+    <t xml:space="preserve">5.88894128799438</t>
   </si>
   <si>
     <t xml:space="preserve">5.84093379974365</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85693597793579</t>
+    <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
     <t xml:space="preserve">5.58489274978638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42486667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56888961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34485387802124</t>
+    <t xml:space="preserve">5.42486715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3448543548584</t>
   </si>
   <si>
     <t xml:space="preserve">5.44086980819702</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">5.26484107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45687294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29684686660767</t>
+    <t xml:space="preserve">5.24883937835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45687246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29684638977051</t>
   </si>
   <si>
     <t xml:space="preserve">5.21683406829834</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900527954102</t>
+    <t xml:space="preserve">6.28900575637817</t>
   </si>
   <si>
     <t xml:space="preserve">6.4970383644104</t>
@@ -1154,37 +1154,37 @@
     <t xml:space="preserve">6.67306661605835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91310548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922332763672</t>
+    <t xml:space="preserve">6.91310501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516199111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922285079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60121583938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5212025642395</t>
+    <t xml:space="preserve">7.60121536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52120161056519</t>
   </si>
   <si>
     <t xml:space="preserve">7.53720474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47319459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118928909302</t>
+    <t xml:space="preserve">7.47319507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118976593018</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719146728516</t>
@@ -1196,61 +1196,61 @@
     <t xml:space="preserve">7.39318180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519990921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716634750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125328063965</t>
+    <t xml:space="preserve">7.23315715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3131685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50520038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">7.82524967193604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90526342391968</t>
+    <t xml:space="preserve">7.90526390075684</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04128646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126607894897</t>
+    <t xml:space="preserve">8.04128551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126560211182</t>
   </si>
   <si>
     <t xml:space="preserve">7.93726873397827</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00127983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87325859069824</t>
+    <t xml:space="preserve">8.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325811386108</t>
   </si>
   <si>
     <t xml:space="preserve">7.95327043533325</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927309036255</t>
+    <t xml:space="preserve">8.12129688262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927452087402</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132438659668</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72139453887939</t>
+    <t xml:space="preserve">8.72139358520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143909454346</t>
@@ -1280,40 +1280,40 @@
     <t xml:space="preserve">8.96143245697021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52152252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48151683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72155284881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84157180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1616230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0816125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.121618270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.281641960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216485977173</t>
+    <t xml:space="preserve">9.52152156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72155380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84157466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1616239547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0816116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1216173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2816429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216495513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.201789855957</t>
+    <t xml:space="preserve">11.3218097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2017908096313</t>
   </si>
   <si>
     <t xml:space="preserve">11.1217775344849</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7617197036743</t>
+    <t xml:space="preserve">11.2417974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817708969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7617206573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.0017585754395</t>
@@ -1352,117 +1352,117 @@
     <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6016941070557</t>
+    <t xml:space="preserve">10.60169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818040847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6965761184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7011222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4937362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0374879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204414367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1619186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99601078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95453262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4107818603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3278274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2448740005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033967971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87157726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9499864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.115894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5352125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6596450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6965751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7011213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4937362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0374870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1619176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789632797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99600887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95453262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4107818603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.327826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7425985336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8670310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033948898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.452260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9499855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840776443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5352125167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6596441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4891901016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818040847778</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.2403259277344</t>
   </si>
   <si>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261201858521</t>
+    <t xml:space="preserve">12.3187351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261211395264</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">12.816460609436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2727108001709</t>
+    <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
     <t xml:space="preserve">13.5630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8119125366211</t>
+    <t xml:space="preserve">13.8119134902954</t>
   </si>
   <si>
     <t xml:space="preserve">13.6460065841675</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">13.5215730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.31418800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3556642532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0192995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8948678970337</t>
+    <t xml:space="preserve">13.3141870498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3556652069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0193004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.894868850708</t>
   </si>
   <si>
     <t xml:space="preserve">13.687481880188</t>
@@ -1532,40 +1532,40 @@
     <t xml:space="preserve">13.1897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8994159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6090745925903</t>
+    <t xml:space="preserve">12.8994150161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.609073638916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846429824829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3647575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062347412109</t>
+    <t xml:space="preserve">12.0283937454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3647565841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062356948853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8210077285767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988487243652</t>
+    <t xml:space="preserve">11.1988496780396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380514144897</t>
+    <t xml:space="preserve">11.7380523681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.78862380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66419124603271</t>
+    <t xml:space="preserve">9.6641902923584</t>
   </si>
   <si>
     <t xml:space="preserve">9.74714660644531</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6136207580566</t>
+    <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0661211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9665765762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.734302520752</t>
+    <t xml:space="preserve">11.0661220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9665775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7343044281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6513500213623</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504400253296</t>
+    <t xml:space="preserve">10.6679401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168033599854</t>
@@ -1616,19 +1616,19 @@
     <t xml:space="preserve">10.8172588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7674865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997577667236</t>
+    <t xml:space="preserve">10.767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997587203979</t>
   </si>
   <si>
     <t xml:space="preserve">10.8338499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5849857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4003810882568</t>
+    <t xml:space="preserve">10.5849866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4003820419312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4693698883057</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">11.2279100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4866170883179</t>
+    <t xml:space="preserve">11.4866161346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">12.2454919815063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2109975814819</t>
+    <t xml:space="preserve">12.2109966278076</t>
   </si>
   <si>
     <t xml:space="preserve">12.2282457351685</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">12.1937503814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0212783813477</t>
+    <t xml:space="preserve">12.021279335022</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0730199813843</t>
+    <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
     <t xml:space="preserve">11.2106618881226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5035276412964</t>
+    <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
     <t xml:space="preserve">10.7794828414917</t>
@@ -1700,31 +1700,31 @@
     <t xml:space="preserve">11.1589202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7625713348389</t>
+    <t xml:space="preserve">11.7625722885132</t>
   </si>
   <si>
     <t xml:space="preserve">11.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9522905349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7280778884888</t>
+    <t xml:space="preserve">11.3831338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9522895812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7280769348145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453231811523</t>
+    <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
     <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6763362884521</t>
+    <t xml:space="preserve">11.6763343811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.8660554885864</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">12.2627401351929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9867849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177951812744</t>
+    <t xml:space="preserve">11.9867839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177961349487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3144807815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3317279815674</t>
+    <t xml:space="preserve">12.3144798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3317289352417</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">11.9695377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">11.9350433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970666885376</t>
+    <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2451553344727</t>
+    <t xml:space="preserve">11.6073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.245156288147</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381908416748</t>
+    <t xml:space="preserve">11.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381898880005</t>
   </si>
   <si>
     <t xml:space="preserve">11.1071786880493</t>
@@ -1805,28 +1805,28 @@
     <t xml:space="preserve">11.0209426879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1244249343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1416730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9692010879517</t>
+    <t xml:space="preserve">11.1244258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.141674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.969202041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.641505241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1758308410645</t>
+    <t xml:space="preserve">10.6415061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5207748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3483018875122</t>
+    <t xml:space="preserve">10.3483037948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">10.1930780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4862794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.831223487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383586883545</t>
+    <t xml:space="preserve">10.4862804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383596420288</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.417628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8143129348755</t>
+    <t xml:space="preserve">11.4176273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8143119812012</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557727813721</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524583816528</t>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869527816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5731887817383</t>
+    <t xml:space="preserve">12.573187828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6421766281128</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5041990280151</t>
+    <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
     <t xml:space="preserve">12.2799863815308</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">11.7108297348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2968969345093</t>
+    <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521217346191</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9519538879395</t>
+    <t xml:space="preserve">11.3141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9519529342651</t>
   </si>
   <si>
     <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967290878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347066879272</t>
+    <t xml:space="preserve">11.0554361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347076416016</t>
   </si>
   <si>
     <t xml:space="preserve">10.8657188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7622346878052</t>
+    <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6070098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345388412476</t>
+    <t xml:space="preserve">10.6070117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">10.4517860412598</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">10.469033241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5380220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4000453948975</t>
+    <t xml:space="preserve">10.5380229949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4000444412231</t>
   </si>
   <si>
     <t xml:space="preserve">10.2770614624023</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.043083190918</t>
+    <t xml:space="preserve">10.0430822372437</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1991,22 +1991,22 @@
     <t xml:space="preserve">10.1690721511841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1150760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93509197235107</t>
+    <t xml:space="preserve">10.1150751113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93509292602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.187068939209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97108840942383</t>
+    <t xml:space="preserve">9.97108936309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95309162139893</t>
+    <t xml:space="preserve">9.95309066772461</t>
   </si>
   <si>
     <t xml:space="preserve">10.0250844955444</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790796279907</t>
+    <t xml:space="preserve">10.0790786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">10.421049118042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5290384292603</t>
+    <t xml:space="preserve">10.5290374755859</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950601577759</t>
+    <t xml:space="preserve">10.3130588531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950592041016</t>
   </si>
   <si>
     <t xml:space="preserve">10.3670530319214</t>
@@ -2060,19 +2060,19 @@
     <t xml:space="preserve">9.79110527038574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">9.70111274719238</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41313934326172</t>
+    <t xml:space="preserve">9.41314029693604</t>
   </si>
   <si>
     <t xml:space="preserve">9.17916107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19715976715088</t>
+    <t xml:space="preserve">9.1971607208252</t>
   </si>
   <si>
     <t xml:space="preserve">9.28715038299561</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85519027709961</t>
+    <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.97218132019043</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">8.4772253036499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62121200561523</t>
+    <t xml:space="preserve">8.62121295928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.63921070098877</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">8.63021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72920227050781</t>
+    <t xml:space="preserve">8.7292013168335</t>
   </si>
   <si>
     <t xml:space="preserve">8.60321426391602</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">8.40523242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35123729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20724964141846</t>
+    <t xml:space="preserve">8.35123634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20725059509277</t>
   </si>
   <si>
     <t xml:space="preserve">7.9012770652771</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81128644943237</t>
+    <t xml:space="preserve">7.81128740310669</t>
   </si>
   <si>
     <t xml:space="preserve">7.89227914810181</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">7.97327136993408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83828353881836</t>
+    <t xml:space="preserve">7.83828449249268</t>
   </si>
   <si>
     <t xml:space="preserve">7.91927671432495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78428888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79328775405884</t>
+    <t xml:space="preserve">7.78428792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79328870773315</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">7.19934225082397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1813440322876</t>
+    <t xml:space="preserve">7.18134355545044</t>
   </si>
   <si>
     <t xml:space="preserve">7.01035976409912</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">6.76738166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65039253234863</t>
+    <t xml:space="preserve">6.65039205551147</t>
   </si>
   <si>
     <t xml:space="preserve">6.69538831710815</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51431369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631452560425</t>
+    <t xml:space="preserve">7.5143141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631500244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.30733203887939</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">7.28033542633057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0283579826355</t>
+    <t xml:space="preserve">7.02835750579834</t>
   </si>
   <si>
     <t xml:space="preserve">7.15434646606445</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136041641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05535554885864</t>
+    <t xml:space="preserve">7.00136089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0553560256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024459838867</t>
+    <t xml:space="preserve">8.27024364471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.37823486328125</t>
@@ -2312,25 +2312,25 @@
     <t xml:space="preserve">8.55821895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75619983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66620826721191</t>
+    <t xml:space="preserve">8.75619888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66620922088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56721878051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61221313476562</t>
+    <t xml:space="preserve">8.56721782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61221218109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923503875732</t>
+    <t xml:space="preserve">8.36923599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.11725902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.414231300354</t>
+    <t xml:space="preserve">8.41423225402832</t>
   </si>
   <si>
     <t xml:space="preserve">8.54921913146973</t>
@@ -2372,28 +2372,28 @@
     <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8350105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6370286941528</t>
+    <t xml:space="preserve">10.8350114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.90700340271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6010313034058</t>
+    <t xml:space="preserve">10.6010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550264358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7990131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6730241775513</t>
+    <t xml:space="preserve">10.6550273895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7990140914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6730251312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">11.1589803695679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4829511642456</t>
+    <t xml:space="preserve">11.4829521179199</t>
   </si>
   <si>
     <t xml:space="preserve">11.4649524688721</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3389654159546</t>
+    <t xml:space="preserve">11.3389644622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5009498596191</t>
+    <t xml:space="preserve">11.5009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709255218506</t>
+    <t xml:space="preserve">11.9689073562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709245681763</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249197006226</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">11.8429174423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8069219589233</t>
+    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6198072433472</t>
@@ -2537,9 +2537,6 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.806921005249</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
@@ -3129,6 +3126,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.3600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -59905,7 +59905,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>841</v>
+        <v>816</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59957,7 +59957,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60061,7 +60061,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60087,7 +60087,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60113,7 +60113,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60139,7 +60139,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60191,7 +60191,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60295,7 +60295,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60321,7 +60321,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60347,7 +60347,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60373,7 +60373,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60477,7 +60477,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60503,7 +60503,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60529,7 +60529,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60555,7 +60555,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60581,7 +60581,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60685,7 +60685,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60815,7 +60815,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60841,7 +60841,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60867,7 +60867,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60919,7 +60919,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60945,7 +60945,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60997,7 +60997,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61023,7 +61023,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61049,7 +61049,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61075,7 +61075,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61127,7 +61127,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61179,7 +61179,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61205,7 +61205,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61257,7 +61257,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61283,7 +61283,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>841</v>
+        <v>816</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61309,7 +61309,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61361,7 +61361,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61387,7 +61387,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61439,7 +61439,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61595,7 +61595,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61699,7 +61699,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61725,7 +61725,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61881,7 +61881,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61907,7 +61907,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61933,7 +61933,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61959,7 +61959,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61985,7 +61985,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62011,7 +62011,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62037,7 +62037,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62063,7 +62063,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62089,7 +62089,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62115,7 +62115,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62141,7 +62141,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62167,7 +62167,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62193,7 +62193,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62219,7 +62219,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62245,7 +62245,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62271,7 +62271,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62297,7 +62297,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62323,7 +62323,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62349,7 +62349,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62375,7 +62375,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62401,7 +62401,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62427,7 +62427,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62453,7 +62453,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62479,7 +62479,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62505,7 +62505,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62531,7 +62531,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62557,7 +62557,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62583,7 +62583,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62609,7 +62609,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62635,7 +62635,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62661,7 +62661,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62687,7 +62687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62713,7 +62713,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62739,7 +62739,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62765,7 +62765,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62791,7 +62791,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62817,7 +62817,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62843,7 +62843,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62869,7 +62869,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62895,7 +62895,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62921,7 +62921,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62947,7 +62947,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62973,7 +62973,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62999,7 +62999,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63025,7 +63025,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63051,7 +63051,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63077,7 +63077,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63103,7 +63103,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63129,7 +63129,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63155,7 +63155,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63181,7 +63181,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63207,7 +63207,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63233,7 +63233,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63259,7 +63259,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63285,7 +63285,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63311,7 +63311,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63337,7 +63337,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63363,7 +63363,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63389,7 +63389,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63415,7 +63415,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63441,7 +63441,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63467,7 +63467,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63493,7 +63493,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63519,7 +63519,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63545,7 +63545,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63571,7 +63571,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63597,7 +63597,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63623,7 +63623,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63649,7 +63649,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63675,7 +63675,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63701,7 +63701,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63727,7 +63727,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63753,7 +63753,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63779,7 +63779,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63805,7 +63805,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63831,7 +63831,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63857,7 +63857,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63883,7 +63883,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63909,7 +63909,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63935,7 +63935,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63961,7 +63961,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63987,7 +63987,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64013,7 +64013,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64039,7 +64039,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64065,7 +64065,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64091,7 +64091,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64117,7 +64117,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64143,7 +64143,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64169,7 +64169,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64195,7 +64195,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64221,7 +64221,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64247,7 +64247,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64273,7 +64273,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64299,7 +64299,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64325,7 +64325,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64351,7 +64351,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64377,7 +64377,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64403,7 +64403,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64429,7 +64429,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64455,7 +64455,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64481,7 +64481,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64507,7 +64507,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64533,7 +64533,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64559,7 +64559,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64585,7 +64585,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64611,7 +64611,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64637,7 +64637,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64663,7 +64663,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64689,7 +64689,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64715,7 +64715,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64741,7 +64741,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64767,7 +64767,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64793,7 +64793,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64819,7 +64819,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64845,7 +64845,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64871,7 +64871,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64897,7 +64897,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64923,7 +64923,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64949,7 +64949,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64975,7 +64975,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65001,7 +65001,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65027,7 +65027,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65053,7 +65053,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65079,7 +65079,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65105,7 +65105,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65131,7 +65131,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65157,7 +65157,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65183,7 +65183,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65209,7 +65209,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65235,7 +65235,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65261,7 +65261,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65287,7 +65287,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65313,7 +65313,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65339,7 +65339,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65365,7 +65365,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65391,7 +65391,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65417,7 +65417,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65443,7 +65443,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65469,7 +65469,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65495,7 +65495,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65521,7 +65521,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65547,7 +65547,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65573,7 +65573,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65599,7 +65599,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65625,7 +65625,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65651,7 +65651,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65677,7 +65677,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65703,7 +65703,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65729,7 +65729,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65755,7 +65755,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65781,7 +65781,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65807,7 +65807,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65833,7 +65833,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65859,7 +65859,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65885,7 +65885,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65911,7 +65911,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65937,7 +65937,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65963,7 +65963,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65989,7 +65989,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66015,7 +66015,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66041,7 +66041,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66067,7 +66067,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66093,7 +66093,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66119,7 +66119,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66145,7 +66145,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66171,7 +66171,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66197,7 +66197,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66223,7 +66223,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66249,7 +66249,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66275,7 +66275,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66301,7 +66301,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66327,7 +66327,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66353,7 +66353,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66379,7 +66379,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66405,7 +66405,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66431,7 +66431,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66457,7 +66457,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66483,7 +66483,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66509,7 +66509,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66535,7 +66535,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66561,7 +66561,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66587,7 +66587,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66613,7 +66613,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66639,7 +66639,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66665,7 +66665,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66691,7 +66691,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66717,7 +66717,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66743,7 +66743,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66769,7 +66769,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66795,7 +66795,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66821,7 +66821,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66847,7 +66847,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66873,7 +66873,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66899,7 +66899,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66925,7 +66925,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66951,7 +66951,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66977,7 +66977,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67003,7 +67003,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67029,7 +67029,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67055,7 +67055,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67081,7 +67081,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67107,7 +67107,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67133,7 +67133,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67159,7 +67159,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67185,7 +67185,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67211,7 +67211,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67237,7 +67237,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67263,7 +67263,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67289,7 +67289,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67315,7 +67315,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67341,7 +67341,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67367,7 +67367,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67393,7 +67393,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67419,7 +67419,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67445,7 +67445,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67471,7 +67471,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67497,7 +67497,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67523,7 +67523,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67549,7 +67549,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67575,7 +67575,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67601,7 +67601,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67627,7 +67627,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67653,7 +67653,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67679,7 +67679,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67705,7 +67705,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67731,7 +67731,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67757,7 +67757,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67783,7 +67783,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67809,7 +67809,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67835,7 +67835,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67861,7 +67861,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67887,7 +67887,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67913,7 +67913,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67939,7 +67939,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67965,7 +67965,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67991,7 +67991,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68043,7 +68043,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68095,7 +68095,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68121,7 +68121,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68147,7 +68147,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68173,7 +68173,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2489" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68199,7 +68199,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2490" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68225,7 +68225,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2491" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68251,7 +68251,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2492" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68277,7 +68277,7 @@
         <v>17.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68303,7 +68303,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2494" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68329,7 +68329,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2495" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68355,7 +68355,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2496" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68363,13 +68363,13 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493171296</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>82018</v>
       </c>
       <c r="C2497" t="n">
-        <v>17.3199996948242</v>
+        <v>17.3600006103516</v>
       </c>
       <c r="D2497" t="n">
         <v>17.0200004577637</v>
@@ -68381,9 +68381,35 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2497" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6913888889</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>42103</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>17.1200008392334</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="G2498" t="s">
         <v>1038</v>
       </c>
-      <c r="H2497" t="s">
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="1040">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217325210571</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10925817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051294326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
+    <t xml:space="preserve">7.16394424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07280206680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1092586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061590194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634214401245</t>
   </si>
   <si>
     <t xml:space="preserve">7.00717687606812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96342658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800436019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821218490601</t>
+    <t xml:space="preserve">6.96342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154682159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800626754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821266174316</t>
   </si>
   <si>
     <t xml:space="preserve">7.39362955093384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43737840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790140151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.284255027771</t>
+    <t xml:space="preserve">7.4373779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029443740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112726211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613136291504</t>
+    <t xml:space="preserve">7.51029348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341733932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30613040924072</t>
   </si>
   <si>
     <t xml:space="preserve">7.6196665763855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5467529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5321683883667</t>
+    <t xml:space="preserve">7.54675102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216791152954</t>
   </si>
   <si>
     <t xml:space="preserve">7.25508975982666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33529758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34988021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29883861541748</t>
+    <t xml:space="preserve">7.33529663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34987926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2988395690918</t>
   </si>
   <si>
     <t xml:space="preserve">7.25873470306396</t>
@@ -161,76 +161,76 @@
     <t xml:space="preserve">7.2477970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2149863243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
+    <t xml:space="preserve">7.21498584747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050617218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99988555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217604637146</t>
+    <t xml:space="preserve">6.99988508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175998687744</t>
   </si>
   <si>
     <t xml:space="preserve">6.99624013900757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97801113128662</t>
+    <t xml:space="preserve">6.9780101776123</t>
   </si>
   <si>
     <t xml:space="preserve">7.52487659454346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47383594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300168991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58321046829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445798873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904014587402</t>
+    <t xml:space="preserve">7.47383546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320951461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904109954834</t>
   </si>
   <si>
     <t xml:space="preserve">7.8748722076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278461456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273166656494</t>
+    <t xml:space="preserve">7.94778537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424386978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273357391357</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1802225112915</t>
+    <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
     <t xml:space="preserve">8.09774494171143</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787986755371</t>
+    <t xml:space="preserve">7.88030576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787939071655</t>
   </si>
   <si>
     <t xml:space="preserve">7.68535900115967</t>
@@ -254,52 +254,52 @@
     <t xml:space="preserve">7.64786958694458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781192779541</t>
+    <t xml:space="preserve">7.85781049728394</t>
   </si>
   <si>
     <t xml:space="preserve">7.98527526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89530181884766</t>
+    <t xml:space="preserve">7.89530038833618</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06025505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258285522461</t>
+    <t xml:space="preserve">8.0602560043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003734588623</t>
+    <t xml:space="preserve">8.84003829956055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43987083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25992107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990528106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13245677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98249816894531</t>
+    <t xml:space="preserve">9.25992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.982497215271</t>
   </si>
   <si>
     <t xml:space="preserve">8.92251491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9974946975708</t>
+    <t xml:space="preserve">8.99749279022217</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996246337891</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">8.89252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6600866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69757747650146</t>
+    <t xml:space="preserve">8.66008758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69757843017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.59260749816895</t>
@@ -320,70 +320,70 @@
     <t xml:space="preserve">8.84753608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77255821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754398345947</t>
+    <t xml:space="preserve">8.77255725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81004524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754493713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.72756958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507526397705</t>
+    <t xml:space="preserve">8.70507431030273</t>
   </si>
   <si>
     <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64509105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6900806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3676700592041</t>
+    <t xml:space="preserve">8.64509201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36766910552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61510181427002</t>
+    <t xml:space="preserve">8.62259864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
     <t xml:space="preserve">8.5476188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41265678405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268238067627</t>
+    <t xml:space="preserve">8.41265773773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268333435059</t>
   </si>
   <si>
     <t xml:space="preserve">8.73506641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87002944946289</t>
+    <t xml:space="preserve">8.87002849578857</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002155303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67508411407471</t>
+    <t xml:space="preserve">8.67508506774902</t>
   </si>
   <si>
     <t xml:space="preserve">8.51762676239014</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">8.58510971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012897491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3601713180542</t>
+    <t xml:space="preserve">8.51012992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515995025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36017036437988</t>
   </si>
   <si>
     <t xml:space="preserve">8.315185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39766216278076</t>
+    <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.30018901824951</t>
@@ -413,46 +413,46 @@
     <t xml:space="preserve">8.1727237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764446258545</t>
+    <t xml:space="preserve">8.20271396636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764541625977</t>
   </si>
   <si>
     <t xml:space="preserve">8.42015552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21021461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11273956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09024620056152</t>
+    <t xml:space="preserve">8.21021366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11274147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09024524688721</t>
   </si>
   <si>
     <t xml:space="preserve">8.06775283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08274936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777795791626</t>
+    <t xml:space="preserve">8.08274841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777843475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523578643799</t>
+    <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.24020576477051</t>
@@ -470,40 +470,43 @@
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82782030105591</t>
+    <t xml:space="preserve">7.82781887054443</t>
   </si>
   <si>
     <t xml:space="preserve">7.81282424926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776073455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93278932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529153823853</t>
+    <t xml:space="preserve">8.03026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93279075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780546188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778728485107</t>
   </si>
   <si>
     <t xml:space="preserve">7.87280702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91029834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76034069061279</t>
+    <t xml:space="preserve">7.91029691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531808853149</t>
@@ -512,121 +515,118 @@
     <t xml:space="preserve">8.09667873382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7882342338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90389966964722</t>
+    <t xml:space="preserve">7.78823375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69569969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390110015869</t>
   </si>
   <si>
     <t xml:space="preserve">7.86534404754639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21234512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678890228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7111234664917</t>
+    <t xml:space="preserve">8.2123441696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678937911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112251281738</t>
   </si>
   <si>
     <t xml:space="preserve">7.66485500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55690002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858892440796</t>
+    <t xml:space="preserve">7.5568995475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
   </si>
   <si>
     <t xml:space="preserve">7.5414776802063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47978782653809</t>
+    <t xml:space="preserve">7.4797887802124</t>
   </si>
   <si>
     <t xml:space="preserve">7.32556676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41810035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21760988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254413604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303270339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
+    <t xml:space="preserve">7.41809988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761035919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387739181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507629394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1713433265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218753814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965490341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14049959182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0788106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472208023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014394760132</t>
+    <t xml:space="preserve">7.17134475708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14050006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881021499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.09423303604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00169992446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458820343018</t>
+    <t xml:space="preserve">7.00169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458772659302</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409915924072</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95543384552002</t>
+    <t xml:space="preserve">6.86289882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0171217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94000959396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543336868286</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627758026123</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">6.6315655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47734212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614322662354</t>
+    <t xml:space="preserve">6.47734308242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614274978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.52361011505127</t>
@@ -680,40 +680,40 @@
     <t xml:space="preserve">6.19974231719971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23058652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3231201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40023136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2614312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27685356140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56987619400024</t>
+    <t xml:space="preserve">6.23058700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32312107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40023183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26143169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27685403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227638244629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565370559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55445432662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663274765015</t>
+    <t xml:space="preserve">6.41565322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.89374256134033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64698791503906</t>
+    <t xml:space="preserve">6.6469874382019</t>
   </si>
   <si>
     <t xml:space="preserve">6.7703652381897</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">6.43107652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16889762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09178638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30769824981689</t>
+    <t xml:space="preserve">6.10720920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16889810562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09178686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24600982666016</t>
+    <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
     <t xml:space="preserve">6.66240978240967</t>
@@ -749,61 +749,61 @@
     <t xml:space="preserve">6.35396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44649791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21516466140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36938762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796743392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676519393921</t>
+    <t xml:space="preserve">6.44649744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21516513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36938714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676614761353</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338787078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20115184783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314245223999</t>
+    <t xml:space="preserve">7.20114994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.07313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64106130599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00912141799927</t>
+    <t xml:space="preserve">6.64106178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00912094116211</t>
   </si>
   <si>
     <t xml:space="preserve">7.08913230895996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12113761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83309173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110017776489</t>
+    <t xml:space="preserve">7.12113857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.833092212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110065460205</t>
   </si>
   <si>
     <t xml:space="preserve">6.8650975227356</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72107362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48103666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504632949829</t>
+    <t xml:space="preserve">6.72107458114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4810357093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504680633545</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905694961548</t>
@@ -833,49 +833,49 @@
     <t xml:space="preserve">6.76908254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81708955764771</t>
+    <t xml:space="preserve">6.80108642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81709003448486</t>
   </si>
   <si>
     <t xml:space="preserve">6.56104850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706396102905</t>
+    <t xml:space="preserve">6.65706348419189</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705163955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904415130615</t>
+    <t xml:space="preserve">6.62505865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
     <t xml:space="preserve">6.43302822113037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5130410194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702651977539</t>
+    <t xml:space="preserve">6.51304149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702604293823</t>
   </si>
   <si>
     <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701276779175</t>
+    <t xml:space="preserve">6.33701372146606</t>
   </si>
   <si>
     <t xml:space="preserve">6.22499513626099</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">6.08097219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04896688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496953964233</t>
+    <t xml:space="preserve">6.04896640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">6.09697437286377</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">5.95295143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895360946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92094612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76092052459717</t>
+    <t xml:space="preserve">6.01696157455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92094659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
     <t xml:space="preserve">5.74491834640503</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">5.82493162155151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90494394302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79292583465576</t>
+    <t xml:space="preserve">5.90494441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7929253578186</t>
   </si>
   <si>
     <t xml:space="preserve">5.98495674133301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11297750473022</t>
+    <t xml:space="preserve">6.11297655105591</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099779129028</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">6.27300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20899295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1769871711731</t>
+    <t xml:space="preserve">6.20899248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17698764801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.38502073287964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19298934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12897968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498138427734</t>
+    <t xml:space="preserve">6.19298982620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12897920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1449818611145</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
@@ -986,37 +986,37 @@
     <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63290071487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55288743972778</t>
+    <t xml:space="preserve">5.63289976119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50487947463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089492797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36085653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081861495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73675680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6727466583252</t>
+    <t xml:space="preserve">5.50488042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089540481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36085605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73675775527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67274713516235</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24067783355713</t>
+    <t xml:space="preserve">4.24067831039429</t>
   </si>
   <si>
     <t xml:space="preserve">3.92062664031982</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">4.04864740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16066551208496</t>
+    <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40070390701294</t>
+    <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075462341309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92878818511963</t>
+    <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
     <t xml:space="preserve">5.13682126998901</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.40886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32885217666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1848292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880002975464</t>
+    <t xml:space="preserve">5.18482875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882658004761</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23283624649048</t>
+    <t xml:space="preserve">5.23283672332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093427658081</t>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
@@ -1094,58 +1094,58 @@
     <t xml:space="preserve">5.77692270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69691133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85693645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486715316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56889009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34485483169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44087028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24883937835693</t>
+    <t xml:space="preserve">5.69691038131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85693693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58489322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44086980819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24883842468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53688526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29684734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21683359146118</t>
+    <t xml:space="preserve">5.53688478469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29684638977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683406829834</t>
   </si>
   <si>
     <t xml:space="preserve">6.3530158996582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900527954102</t>
+    <t xml:space="preserve">6.28900575637817</t>
   </si>
   <si>
     <t xml:space="preserve">6.4970383644104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70507192611694</t>
+    <t xml:space="preserve">6.7050724029541</t>
   </si>
   <si>
     <t xml:space="preserve">6.67306709289551</t>
@@ -1154,61 +1154,61 @@
     <t xml:space="preserve">6.91310501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24915933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516199111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116464614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922285079956</t>
+    <t xml:space="preserve">7.24915885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922380447388</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60121536254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52120208740234</t>
+    <t xml:space="preserve">7.60121583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52120113372803</t>
   </si>
   <si>
     <t xml:space="preserve">7.5372052192688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47319364547729</t>
+    <t xml:space="preserve">7.47319459915161</t>
   </si>
   <si>
     <t xml:space="preserve">7.44118881225586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.457190990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40918445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31317043304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716682434082</t>
+    <t xml:space="preserve">7.45719146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40918493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50520038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716634750366</t>
   </si>
   <si>
     <t xml:space="preserve">7.74523782730103</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">7.84125328063965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08129215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04128551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126655578613</t>
+    <t xml:space="preserve">7.82525157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526437759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08129119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126607894897</t>
   </si>
   <si>
     <t xml:space="preserve">7.93726873397827</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">8.00127983093262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87325763702393</t>
+    <t xml:space="preserve">7.87325859069824</t>
   </si>
   <si>
     <t xml:space="preserve">7.95327043533325</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927356719971</t>
+    <t xml:space="preserve">8.12129878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927404403687</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132438659668</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">8.40134334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44134998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139453887939</t>
+    <t xml:space="preserve">8.44134902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139358520508</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143909454346</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">8.84141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12145900726318</t>
+    <t xml:space="preserve">9.12145709991455</t>
   </si>
   <si>
     <t xml:space="preserve">9.0414457321167</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">8.9614315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52152061462402</t>
+    <t xml:space="preserve">9.52152252197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.48151588439941</t>
@@ -1286,40 +1286,40 @@
     <t xml:space="preserve">9.72155380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84157371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1616249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0816125869751</t>
+    <t xml:space="preserve">9.84157276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1616239547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0816106796265</t>
   </si>
   <si>
     <t xml:space="preserve">10.121618270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2816438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3218107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.201789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217775344849</t>
+    <t xml:space="preserve">10.281641960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216485977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217121124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3218097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2017908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217784881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617519378662</t>
+    <t xml:space="preserve">10.9617509841919</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617832183838</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">10.8417339324951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8817405700684</t>
+    <t xml:space="preserve">10.881739616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417984008789</t>
+    <t xml:space="preserve">11.2417964935303</t>
   </si>
   <si>
     <t xml:space="preserve">11.0817708969116</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">11.0017585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5216827392578</t>
+    <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
     <t xml:space="preserve">10.6016941070557</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1204423904419</t>
+    <t xml:space="preserve">10.1204404830933</t>
   </si>
   <si>
     <t xml:space="preserve">10.1619186401367</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600887298584</t>
+    <t xml:space="preserve">9.99600982666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305541992188</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.327826499939</t>
+    <t xml:space="preserve">10.3278284072876</t>
   </si>
   <si>
     <t xml:space="preserve">10.9914627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7425994873047</t>
+    <t xml:space="preserve">10.742600440979</t>
   </si>
   <si>
     <t xml:space="preserve">10.8255548477173</t>
@@ -1409,25 +1409,25 @@
     <t xml:space="preserve">10.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
+    <t xml:space="preserve">10.6181688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
     <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87157726287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.452260017395</t>
+    <t xml:space="preserve">9.87157821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522581100464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
@@ -1439,34 +1439,34 @@
     <t xml:space="preserve">11.1158933639526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085092544556</t>
+    <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0329399108887</t>
+    <t xml:space="preserve">10.6596441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.032940864563</t>
   </si>
   <si>
     <t xml:space="preserve">11.323281288147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4891901016235</t>
+    <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
     <t xml:space="preserve">11.2403268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5721435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.530665397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.5721426010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5306673049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261201858521</t>
+    <t xml:space="preserve">12.318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261211395264</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5630521774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460065841675</t>
+    <t xml:space="preserve">13.5630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460056304932</t>
   </si>
   <si>
     <t xml:space="preserve">13.5215730667114</t>
@@ -1508,22 +1508,22 @@
     <t xml:space="preserve">13.3141860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3556642532349</t>
+    <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
     <t xml:space="preserve">14.0192985534668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
+    <t xml:space="preserve">13.894868850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874809265137</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1897554397583</t>
+    <t xml:space="preserve">13.189754486084</t>
   </si>
   <si>
     <t xml:space="preserve">12.8994150161743</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647584915161</t>
+    <t xml:space="preserve">11.3647565841675</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062347412109</t>
@@ -1553,34 +1553,34 @@
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380523681641</t>
+    <t xml:space="preserve">11.7380533218384</t>
   </si>
   <si>
     <t xml:space="preserve">9.78862380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6641902923584</t>
+    <t xml:space="preserve">9.66419219970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.747145652771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8624839782715</t>
+    <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
     <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4808950424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.066123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9665765762329</t>
+    <t xml:space="preserve">11.4808940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0661211013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9665775299072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7343034744263</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">10.6347589492798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679410934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168033599854</t>
+    <t xml:space="preserve">10.6679401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168043136597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8006687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9002122879028</t>
+    <t xml:space="preserve">10.9002132415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172588348389</t>
@@ -1613,28 +1613,28 @@
     <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997577667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8338489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4003810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4693689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3313913345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866161346436</t>
+    <t xml:space="preserve">10.9997587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8338499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849866867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4003820419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.331392288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866170883179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.193751335144</t>
+    <t xml:space="preserve">12.1937503814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1420087814331</t>
+    <t xml:space="preserve">12.1420078277588</t>
   </si>
   <si>
     <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5038642883301</t>
+    <t xml:space="preserve">11.5038633346558</t>
   </si>
   <si>
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106609344482</t>
+    <t xml:space="preserve">11.2106618881226</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">10.7794828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6242580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0036954879761</t>
+    <t xml:space="preserve">10.6932458877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6242570877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.1589193344116</t>
@@ -1697,49 +1697,49 @@
     <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8315601348877</t>
+    <t xml:space="preserve">11.831561088562</t>
   </si>
   <si>
     <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9522905349731</t>
+    <t xml:space="preserve">11.9522895812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5728521347046</t>
+    <t xml:space="preserve">11.5728530883789</t>
   </si>
   <si>
     <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.69358253479</t>
+    <t xml:space="preserve">11.6935834884644</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2627401351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9867839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1765041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3144807815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3317279815674</t>
+    <t xml:space="preserve">11.8660554885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2627391815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9867849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177961349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1765031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3144798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3317289352417</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6590881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607346534729</t>
+    <t xml:space="preserve">11.6590890884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073474884033</t>
   </si>
   <si>
     <t xml:space="preserve">11.5556039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3486385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2451553344727</t>
+    <t xml:space="preserve">11.3486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.245156288147</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
@@ -1787,28 +1787,28 @@
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381898880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.020941734314</t>
+    <t xml:space="preserve">11.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1071796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209426879883</t>
   </si>
   <si>
     <t xml:space="preserve">11.1244249343872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1416730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9692010879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8829641342163</t>
+    <t xml:space="preserve">11.141674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415061950684</t>
@@ -1817,73 +1817,73 @@
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3483028411865</t>
+    <t xml:space="preserve">10.5207738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3483037948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172925949097</t>
+    <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.831223487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383577346802</t>
+    <t xml:space="preserve">10.1930780410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.417628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8143129348755</t>
+    <t xml:space="preserve">11.4176273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8143119812012</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.469705581665</t>
+    <t xml:space="preserve">12.4697065353394</t>
   </si>
   <si>
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007177352905</t>
+    <t xml:space="preserve">12.4007167816162</t>
   </si>
   <si>
     <t xml:space="preserve">12.3662233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4524583816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869527816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5731887817383</t>
+    <t xml:space="preserve">12.4524574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.573187828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521448135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386943817139</t>
+    <t xml:space="preserve">12.5214471817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386934280396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108297348022</t>
+    <t xml:space="preserve">11.7108287811279</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141450881958</t>
+    <t xml:space="preserve">11.3141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">11.0554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7967290878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657188415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622356414795</t>
+    <t xml:space="preserve">10.7967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657178878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622346878052</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">10.4517860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.469033241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380229949951</t>
+    <t xml:space="preserve">10.4690341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380220413208</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2770614624023</t>
+    <t xml:space="preserve">10.277060508728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4930410385132</t>
+    <t xml:space="preserve">10.4930419921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">9.93509197235107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
+    <t xml:space="preserve">10.1870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250844955444</t>
+    <t xml:space="preserve">9.95309066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790796279907</t>
+    <t xml:space="preserve">10.0790786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510725021362</t>
+    <t xml:space="preserve">10.1510715484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.421049118042</t>
+    <t xml:space="preserve">10.4210472106934</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950601577759</t>
+    <t xml:space="preserve">10.3130588531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950592041016</t>
   </si>
   <si>
     <t xml:space="preserve">10.3670530319214</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">9.79110622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111465454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17916107177734</t>
+    <t xml:space="preserve">9.17916202545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48513412475586</t>
+    <t xml:space="preserve">9.28715133666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85519027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97218132019043</t>
+    <t xml:space="preserve">8.85519123077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97218036651611</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4772253036499</t>
+    <t xml:space="preserve">8.47722625732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.62121200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63021183013916</t>
+    <t xml:space="preserve">8.63921165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63021087646484</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9012770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0992603302002</t>
+    <t xml:space="preserve">8.20725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90127801895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09925937652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.04526519775391</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427249908447</t>
+    <t xml:space="preserve">7.96427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81128644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227914810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927671432495</t>
+    <t xml:space="preserve">7.81128692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327089309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927576065063</t>
   </si>
   <si>
     <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79328775405884</t>
+    <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">7.63130235671997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32533121109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19934225082397</t>
+    <t xml:space="preserve">7.32533073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19934272766113</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">6.95636463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19034290313721</t>
+    <t xml:space="preserve">7.19034242630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.16334581375122</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">7.10935068130493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25333786010742</t>
+    <t xml:space="preserve">7.25333738327026</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
@@ -2246,34 +2246,34 @@
     <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51431369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733203887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46931791305542</t>
+    <t xml:space="preserve">7.5143141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733251571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46931838989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.28933429718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28033542633057</t>
+    <t xml:space="preserve">7.28033494949341</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434646606445</t>
+    <t xml:space="preserve">7.15434598922729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136041641235</t>
+    <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.05535554885864</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">7.99127006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92827653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9462742805481</t>
+    <t xml:space="preserve">7.92827606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627380371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37823486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75619983673096</t>
+    <t xml:space="preserve">8.27024364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37823581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75619888305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74720096588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56721878051758</t>
+    <t xml:space="preserve">8.74720191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56721782684326</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19824981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326293945312</t>
+    <t xml:space="preserve">8.19825077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326389312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.11725902557373</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170127868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9789972305298</t>
+    <t xml:space="preserve">10.8170118331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9789962768555</t>
   </si>
   <si>
     <t xml:space="preserve">10.8350105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6370286941528</t>
+    <t xml:space="preserve">10.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.90700340271</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550264358521</t>
+    <t xml:space="preserve">10.6550273895264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489728927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1229829788208</t>
+    <t xml:space="preserve">11.2489719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1229839324951</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">11.4649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669706344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3389654159546</t>
+    <t xml:space="preserve">11.2669715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3389644622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749618530273</t>
+    <t xml:space="preserve">11.374960899353</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5009498596191</t>
+    <t xml:space="preserve">11.5009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249197006226</t>
+    <t xml:space="preserve">11.9689073562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709245681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249206542969</t>
   </si>
   <si>
     <t xml:space="preserve">11.7349281311035</t>
@@ -2450,91 +2450,91 @@
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529268264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429174423218</t>
+    <t xml:space="preserve">11.7529277801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806921005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6198072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5262498855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.320424079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.488826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5075387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3391351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3578481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4326934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4514045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4701156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.208155632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.601095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8256330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8443450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0314588546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9940366744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7133655548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7507877349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6572303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
     <t xml:space="preserve">11.8069219589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6198072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5262498855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.320424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.488826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5075387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3391351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3578472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4326934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4514036178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4701156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2081546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8256330490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8443441390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0314588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9940357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7507877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6572303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.806921005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4139814376831</t>
+    <t xml:space="preserve">11.4139804840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823841094971</t>
+    <t xml:space="preserve">11.5823850631714</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624383926392</t>
+    <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.919189453125</t>
+    <t xml:space="preserve">11.9191904067993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5449619293213</t>
+    <t xml:space="preserve">11.544960975647</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.058464050293</t>
+    <t xml:space="preserve">11.0584630966187</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771751403809</t>
+    <t xml:space="preserve">11.0771760940552</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842355728149</t>
+    <t xml:space="preserve">10.6842346191406</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222755432129</t>
+    <t xml:space="preserve">10.4784088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222745895386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287181854248</t>
+    <t xml:space="preserve">10.3287172317505</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977376937866</t>
+    <t xml:space="preserve">10.1977367401123</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3129,6 +3129,9 @@
   </si>
   <si>
     <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9799995422363</t>
   </si>
 </sst>
 </file>
@@ -16771,7 +16774,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16797,7 +16800,7 @@
         <v>10.5</v>
       </c>
       <c r="G513" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16823,7 +16826,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G514" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16849,7 +16852,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16875,7 +16878,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G516" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16927,7 +16930,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17083,7 +17086,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17109,7 +17112,7 @@
         <v>10.5</v>
       </c>
       <c r="G525" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17135,7 +17138,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G526" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17733,7 +17736,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G549" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17863,7 +17866,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G554" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17889,7 +17892,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17967,7 +17970,7 @@
         <v>10.5</v>
       </c>
       <c r="G558" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17993,7 +17996,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18045,7 +18048,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18071,7 +18074,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G562" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18097,7 +18100,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G563" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18123,7 +18126,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18175,7 +18178,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G566" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18227,7 +18230,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18357,7 +18360,7 @@
         <v>10.5</v>
       </c>
       <c r="G573" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18409,7 +18412,7 @@
         <v>10.5</v>
       </c>
       <c r="G575" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18435,7 +18438,7 @@
         <v>10.5</v>
       </c>
       <c r="G576" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18461,7 +18464,7 @@
         <v>10.5</v>
       </c>
       <c r="G577" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19007,7 +19010,7 @@
         <v>10.5</v>
       </c>
       <c r="G598" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19033,7 +19036,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19059,7 +19062,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G600" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19085,7 +19088,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19111,7 +19114,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G602" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19137,7 +19140,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19163,7 +19166,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19189,7 +19192,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19215,7 +19218,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G606" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19241,7 +19244,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G607" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19267,7 +19270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19293,7 +19296,7 @@
         <v>10.5</v>
       </c>
       <c r="G609" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19319,7 +19322,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19345,7 +19348,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G611" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19397,7 +19400,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19423,7 +19426,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19501,7 +19504,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19527,7 +19530,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19709,7 +19712,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19735,7 +19738,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19761,7 +19764,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G627" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19787,7 +19790,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19813,7 +19816,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20099,7 +20102,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G640" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20177,7 +20180,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -68493,7 +68496,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6912268518</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>57204</v>
@@ -68514,6 +68517,32 @@
         <v>1038</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6909953704</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>45497</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>17.1800003051758</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>16.8799991607666</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>16.9799995422363</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="1041">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217325210571</t>
+    <t xml:space="preserve">7.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280206680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
+    <t xml:space="preserve">7.16394472122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07279968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925912857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.93061590194702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89051151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207124710083</t>
+    <t xml:space="preserve">6.89051198959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207172393799</t>
   </si>
   <si>
     <t xml:space="preserve">6.96707344055176</t>
@@ -71,139 +71,139 @@
     <t xml:space="preserve">7.03634214401245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00717687606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154682159424</t>
+    <t xml:space="preserve">7.00717639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154777526855</t>
   </si>
   <si>
     <t xml:space="preserve">7.32800626754761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21863269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362955093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4373779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425455093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341733932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112869262695</t>
+    <t xml:space="preserve">7.21863222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2623815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821218490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737745285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154195785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48842000961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112630844116</t>
   </si>
   <si>
     <t xml:space="preserve">7.30613040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6196665763855</t>
+    <t xml:space="preserve">7.61966705322266</t>
   </si>
   <si>
     <t xml:space="preserve">7.54675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53216791152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34987926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2988395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2477970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498584747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769500732422</t>
+    <t xml:space="preserve">7.53216981887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25508880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3498797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29884004592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769548416138</t>
   </si>
   <si>
     <t xml:space="preserve">6.99988508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02175998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99624013900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9780101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633680343628</t>
+    <t xml:space="preserve">7.0217604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623918533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487802505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633728027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.50300216674805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56133365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445751190186</t>
+    <t xml:space="preserve">7.56133413314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320903778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
   </si>
   <si>
     <t xml:space="preserve">7.72904109954834</t>
@@ -215,61 +215,61 @@
     <t xml:space="preserve">7.94778537750244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03528499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424386978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273357391357</t>
+    <t xml:space="preserve">8.0352840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273262023926</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18022155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774494171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88030576705933</t>
+    <t xml:space="preserve">8.18022060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88030385971069</t>
   </si>
   <si>
     <t xml:space="preserve">7.79782867431641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61787939071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64786958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781049728394</t>
+    <t xml:space="preserve">7.61787796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781145095825</t>
   </si>
   <si>
     <t xml:space="preserve">7.98527526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89530038833618</t>
+    <t xml:space="preserve">7.89530229568481</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0602560043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258190155029</t>
+    <t xml:space="preserve">8.06025409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258285522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">8.84003829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43987083435059</t>
+    <t xml:space="preserve">9.43986988067627</t>
   </si>
   <si>
     <t xml:space="preserve">9.25992012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240558624268</t>
+    <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
     <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13245582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.982497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99749279022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10996246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252281188965</t>
+    <t xml:space="preserve">9.1324577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99749374389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252376556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.66008758544922</t>
@@ -314,40 +314,40 @@
     <t xml:space="preserve">8.69757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753608703613</t>
+    <t xml:space="preserve">8.59260845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753513336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72756958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7950496673584</t>
+    <t xml:space="preserve">8.81004619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507621765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79505062103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010433197021</t>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
     <t xml:space="preserve">8.36766910552979</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">8.38266563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61509990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5476188659668</t>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6151008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54761791229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.41265773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28519344329834</t>
+    <t xml:space="preserve">8.28519248962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.32268333435059</t>
@@ -377,100 +377,100 @@
     <t xml:space="preserve">8.73506641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87002849578857</t>
+    <t xml:space="preserve">8.87002944946289</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002155303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67508506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51762676239014</t>
+    <t xml:space="preserve">8.67508316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51762580871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.58510971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515995025635</t>
+    <t xml:space="preserve">8.51012897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.36017036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.315185546875</t>
+    <t xml:space="preserve">8.31518459320068</t>
   </si>
   <si>
     <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30018901824951</t>
+    <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271396636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42015552520752</t>
+    <t xml:space="preserve">8.20271492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015361785889</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11274147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09024524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775283813477</t>
+    <t xml:space="preserve">8.1127405166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09024620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775379180908</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777843475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22520923614502</t>
+    <t xml:space="preserve">8.12773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277448654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020481109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22521018981934</t>
   </si>
   <si>
     <t xml:space="preserve">8.12023830413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00776958465576</t>
+    <t xml:space="preserve">8.00777149200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781887054443</t>
+    <t xml:space="preserve">7.82781982421875</t>
   </si>
   <si>
     <t xml:space="preserve">7.81282424926758</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">8.03026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529296875</t>
+    <t xml:space="preserve">7.95528316497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93278980255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529201507568</t>
   </si>
   <si>
     <t xml:space="preserve">7.94778728485107</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">7.87280702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91029691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531808853149</t>
+    <t xml:space="preserve">7.91029739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.760338306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531761169434</t>
   </si>
   <si>
     <t xml:space="preserve">8.09667873382568</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">7.78823375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69569969177246</t>
+    <t xml:space="preserve">7.69569873809814</t>
   </si>
   <si>
     <t xml:space="preserve">7.74967861175537</t>
@@ -527,40 +527,40 @@
     <t xml:space="preserve">8.01956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98101043701172</t>
+    <t xml:space="preserve">7.98101139068604</t>
   </si>
   <si>
     <t xml:space="preserve">7.90390110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86534404754639</t>
+    <t xml:space="preserve">7.8653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">8.2123441696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82678937911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5568995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858940124512</t>
+    <t xml:space="preserve">7.82678842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112203598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485452651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858892440796</t>
   </si>
   <si>
     <t xml:space="preserve">7.5414776802063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4797887802124</t>
+    <t xml:space="preserve">7.47978782653809</t>
   </si>
   <si>
     <t xml:space="preserve">7.32556676864624</t>
@@ -569,64 +569,64 @@
     <t xml:space="preserve">7.41809988021851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38725471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761035919189</t>
+    <t xml:space="preserve">7.38725614547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761083602905</t>
   </si>
   <si>
     <t xml:space="preserve">7.03254318237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23303318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845409393311</t>
+    <t xml:space="preserve">7.23303270339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845457077026</t>
   </si>
   <si>
     <t xml:space="preserve">7.26387739181519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12507629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929925918579</t>
+    <t xml:space="preserve">7.12507724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929830551147</t>
   </si>
   <si>
     <t xml:space="preserve">7.17134475708008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20218849182129</t>
+    <t xml:space="preserve">7.20218896865845</t>
   </si>
   <si>
     <t xml:space="preserve">7.10965538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14050006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07881021499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014442443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169849395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916633605957</t>
+    <t xml:space="preserve">7.14049959182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472208023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916585922241</t>
   </si>
   <si>
     <t xml:space="preserve">6.83205413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92458772659302</t>
+    <t xml:space="preserve">6.92458820343018</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409915924072</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289882659912</t>
+    <t xml:space="preserve">6.86289930343628</t>
   </si>
   <si>
     <t xml:space="preserve">7.0171217918396</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">6.94000959396362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95543336868286</t>
+    <t xml:space="preserve">6.9554328918457</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627758026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783164978027</t>
+    <t xml:space="preserve">6.67783260345459</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086763381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6315655708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47734308242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192121505737</t>
+    <t xml:space="preserve">6.63156509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192073822021</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903102874756</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">6.23058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32312107086182</t>
+    <t xml:space="preserve">6.3231201171875</t>
   </si>
   <si>
     <t xml:space="preserve">6.40023183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26143169403076</t>
+    <t xml:space="preserve">6.2614312171936</t>
   </si>
   <si>
     <t xml:space="preserve">6.27685403823853</t>
@@ -698,109 +698,109 @@
     <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29227638244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55445384979248</t>
+    <t xml:space="preserve">6.29227590560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5544548034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374256134033</t>
+    <t xml:space="preserve">6.89374351501465</t>
   </si>
   <si>
     <t xml:space="preserve">6.6469874382019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7703652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720920562744</t>
+    <t xml:space="preserve">6.77036571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720872879028</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889810562134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09178686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30769872665405</t>
+    <t xml:space="preserve">6.09178638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30769824981689</t>
   </si>
   <si>
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.246009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66240978240967</t>
+    <t xml:space="preserve">6.24600982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66241025924683</t>
   </si>
   <si>
     <t xml:space="preserve">6.49276494979858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35396480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649744033813</t>
+    <t xml:space="preserve">6.35396528244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649791717529</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494480133057</t>
+    <t xml:space="preserve">6.36938762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">6.87832117080688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97085571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592288970947</t>
+    <t xml:space="preserve">6.97085428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796648025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.155921459198</t>
   </si>
   <si>
     <t xml:space="preserve">7.18676614761353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338787078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20114994049072</t>
+    <t xml:space="preserve">7.06338691711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2011513710022</t>
   </si>
   <si>
     <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07313108444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64106178283691</t>
+    <t xml:space="preserve">7.07313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
+    <t xml:space="preserve">7.08913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113809585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309173583984</t>
   </si>
   <si>
     <t xml:space="preserve">6.88110065460205</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78508424758911</t>
+    <t xml:space="preserve">6.78508472442627</t>
   </si>
   <si>
     <t xml:space="preserve">6.75307893753052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73707675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72107458114624</t>
+    <t xml:space="preserve">6.73707628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72107362747192</t>
   </si>
   <si>
     <t xml:space="preserve">6.4810357093811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54504680633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905694961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76908254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108642578125</t>
+    <t xml:space="preserve">6.54504585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76908206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
     <t xml:space="preserve">6.89710235595703</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">6.56104850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706348419189</t>
+    <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505865097046</t>
+    <t xml:space="preserve">6.62505912780762</t>
   </si>
   <si>
     <t xml:space="preserve">6.57705116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52904367446899</t>
+    <t xml:space="preserve">6.52904415130615</t>
   </si>
   <si>
     <t xml:space="preserve">6.43302822113037</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">6.51304149627686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903135299683</t>
+    <t xml:space="preserve">6.44903087615967</t>
   </si>
   <si>
     <t xml:space="preserve">6.41702604293823</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701372146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22499513626099</t>
+    <t xml:space="preserve">6.33701324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22499465942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097219467163</t>
@@ -887,49 +887,49 @@
     <t xml:space="preserve">6.04896640777588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1609845161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0009593963623</t>
+    <t xml:space="preserve">6.06496953964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16098499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00095987319946</t>
   </si>
   <si>
     <t xml:space="preserve">5.95295143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01696157455444</t>
+    <t xml:space="preserve">6.0169620513916</t>
   </si>
   <si>
     <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92094659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76092100143433</t>
+    <t xml:space="preserve">5.92094612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76092052459717</t>
   </si>
   <si>
     <t xml:space="preserve">5.74491834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68090772628784</t>
+    <t xml:space="preserve">5.680908203125</t>
   </si>
   <si>
     <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82493162155151</t>
+    <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
     <t xml:space="preserve">5.90494441986084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87293863296509</t>
+    <t xml:space="preserve">5.87293910980225</t>
   </si>
   <si>
     <t xml:space="preserve">5.7929253578186</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">5.98495674133301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11297655105591</t>
+    <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099779129028</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17698764801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38502073287964</t>
+    <t xml:space="preserve">6.1769871711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38501977920532</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897920608521</t>
+    <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
     <t xml:space="preserve">6.1449818611145</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">5.93694925308228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03296422958374</t>
+    <t xml:space="preserve">6.0329647064209</t>
   </si>
   <si>
     <t xml:space="preserve">5.61689758300781</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63289976119995</t>
+    <t xml:space="preserve">5.63290023803711</t>
   </si>
   <si>
     <t xml:space="preserve">5.55288791656494</t>
@@ -995,37 +995,37 @@
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50488042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36085605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73675775527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67274713516235</t>
+    <t xml:space="preserve">5.50487995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36085653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081861495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73675680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67274761199951</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24067831039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062664031982</t>
+    <t xml:space="preserve">4.24067783355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062616348267</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868532180786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864740371704</t>
+    <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
     <t xml:space="preserve">4.1606650352478</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">4.08065176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40070343017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72075462341309</t>
+    <t xml:space="preserve">4.40070295333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72075414657593</t>
   </si>
   <si>
     <t xml:space="preserve">4.92878770828247</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32885217666626</t>
+    <t xml:space="preserve">5.40886449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3288516998291</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16882658004761</t>
+    <t xml:space="preserve">5.16882610321045</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283672332764</t>
+    <t xml:space="preserve">5.05680799484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283624649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287511825562</t>
@@ -1085,31 +1085,31 @@
     <t xml:space="preserve">5.88894128799438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84093379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64890289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77692270278931</t>
+    <t xml:space="preserve">5.84093427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64890336990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77692317962646</t>
   </si>
   <si>
     <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85693693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58489322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34485387802124</t>
+    <t xml:space="preserve">5.85693645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58489274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56888961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3448543548584</t>
   </si>
   <si>
     <t xml:space="preserve">5.44086980819702</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">5.37685966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26484155654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24883842468262</t>
+    <t xml:space="preserve">5.26484107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24883890151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">5.53688478469849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29684638977051</t>
+    <t xml:space="preserve">5.29684686660767</t>
   </si>
   <si>
     <t xml:space="preserve">5.21683406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3530158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28900575637817</t>
+    <t xml:space="preserve">6.35301542282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28900527954102</t>
   </si>
   <si>
     <t xml:space="preserve">6.4970383644104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7050724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67306709289551</t>
+    <t xml:space="preserve">6.70507192611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67306661605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.91310501098633</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">7.26516103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28116369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922380447388</t>
+    <t xml:space="preserve">7.28116416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922332763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
@@ -1172,16 +1172,16 @@
     <t xml:space="preserve">7.60121583938599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52120113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5372052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118881225586</t>
+    <t xml:space="preserve">7.5212025642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53720474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319555282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118928909302</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719146728516</t>
@@ -1193,34 +1193,34 @@
     <t xml:space="preserve">7.39318180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315668106079</t>
+    <t xml:space="preserve">7.23315620422363</t>
   </si>
   <si>
     <t xml:space="preserve">7.31316947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50520038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716634750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526437759399</t>
+    <t xml:space="preserve">7.42518758773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82524967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526342391968</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129119873047</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">7.93726873397827</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00127983093262</t>
+    <t xml:space="preserve">8.0012788772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.87325859069824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95327043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927404403687</t>
+    <t xml:space="preserve">7.95326948165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129783630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927309036255</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132438659668</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72139358520508</t>
+    <t xml:space="preserve">8.72139453887939</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141254425049</t>
+    <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
     <t xml:space="preserve">9.12145709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0414457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9614315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152252197266</t>
+    <t xml:space="preserve">9.04144668579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96143245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.48151588439941</t>
@@ -1289,37 +1289,37 @@
     <t xml:space="preserve">9.84157276153564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1616239547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0816106796265</t>
+    <t xml:space="preserve">10.1616230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0816125869751</t>
   </si>
   <si>
     <t xml:space="preserve">10.121618270874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.281641960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216485977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217121124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3218097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2017908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217784881592</t>
+    <t xml:space="preserve">10.2816429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3218088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217775344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617509841919</t>
+    <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617832183838</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">10.881739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4818344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2417964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817708969116</t>
+    <t xml:space="preserve">11.4818353652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2417974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817718505859</t>
   </si>
   <si>
     <t xml:space="preserve">10.7617197036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0017585754395</t>
+    <t xml:space="preserve">11.0017595291138</t>
   </si>
   <si>
     <t xml:space="preserve">10.5216817855835</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7011213302612</t>
+    <t xml:space="preserve">10.7011222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204404830933</t>
+    <t xml:space="preserve">10.0374879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204423904419</t>
   </si>
   <si>
     <t xml:space="preserve">10.1619186401367</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600982666016</t>
+    <t xml:space="preserve">9.99600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305541992188</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278284072876</t>
+    <t xml:space="preserve">10.327826499939</t>
   </si>
   <si>
     <t xml:space="preserve">10.9914627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.742600440979</t>
+    <t xml:space="preserve">10.7425994873047</t>
   </si>
   <si>
     <t xml:space="preserve">10.8255548477173</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">10.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863492965698</t>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693056106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863502502441</t>
   </si>
   <si>
     <t xml:space="preserve">10.244873046875</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522581100464</t>
+    <t xml:space="preserve">9.87157726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.452260017395</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
@@ -1436,40 +1436,40 @@
     <t xml:space="preserve">10.7840766906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1158933639526</t>
+    <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6596441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.032940864563</t>
+    <t xml:space="preserve">10.5352125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6596450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0329399108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.323281288147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4891891479492</t>
+    <t xml:space="preserve">11.4891901016235</t>
   </si>
   <si>
     <t xml:space="preserve">11.2403268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5721426010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5306673049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7795295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772569656372</t>
+    <t xml:space="preserve">11.5721435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5306663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7795305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772560119629</t>
   </si>
   <si>
     <t xml:space="preserve">12.3602113723755</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.318733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261211395264</t>
+    <t xml:space="preserve">12.3187341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261201858521</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1496,91 +1496,91 @@
     <t xml:space="preserve">13.5630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8119144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460056304932</t>
+    <t xml:space="preserve">13.8119134902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460065841675</t>
   </si>
   <si>
     <t xml:space="preserve">13.5215730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3141860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3556652069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0192985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6874809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312326431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.189754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8994150161743</t>
+    <t xml:space="preserve">13.3141870498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3556642532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0192995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.687481880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312335968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8994159698486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846420288086</t>
+    <t xml:space="preserve">12.4846429824829</t>
   </si>
   <si>
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647565841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062347412109</t>
+    <t xml:space="preserve">11.3647575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062356948853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8210067749023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988496780396</t>
+    <t xml:space="preserve">11.1988487243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
+    <t xml:space="preserve">11.7380523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6641902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714660644531</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.613621711731</t>
+    <t xml:space="preserve">11.6136207580566</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0661211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9665775299072</t>
+    <t xml:space="preserve">11.0661220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177133560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
     <t xml:space="preserve">10.7343034744263</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8504409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8006687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002132415771</t>
+    <t xml:space="preserve">10.8504400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8006677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002122879028</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172588348389</t>
@@ -1613,28 +1613,28 @@
     <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8338499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4003820419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866170883179</t>
+    <t xml:space="preserve">10.9997577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8338489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313913345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866161346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1937503814697</t>
+    <t xml:space="preserve">12.193751335144</t>
   </si>
   <si>
     <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1420078277588</t>
+    <t xml:space="preserve">12.1420087814331</t>
   </si>
   <si>
     <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5038633346558</t>
+    <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106618881226</t>
+    <t xml:space="preserve">11.2106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">10.7794828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6932458877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6242570877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0036964416504</t>
+    <t xml:space="preserve">10.6932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6242580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0036954879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.1589193344116</t>
@@ -1697,49 +1697,49 @@
     <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.831561088562</t>
+    <t xml:space="preserve">11.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9522895812988</t>
+    <t xml:space="preserve">11.9522905349731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5728530883789</t>
+    <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
     <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6935834884644</t>
+    <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2627391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9867849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1765031814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3144798278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3317289352417</t>
+    <t xml:space="preserve">11.8660545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2627401351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9867839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1765041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3144807815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3317279815674</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6590890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6073474884033</t>
+    <t xml:space="preserve">11.6590881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.607346534729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5556039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.245156288147</t>
+    <t xml:space="preserve">11.3486385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2451553344727</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
@@ -1787,28 +1787,28 @@
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209426879883</t>
+    <t xml:space="preserve">11.4348745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.020941734314</t>
   </si>
   <si>
     <t xml:space="preserve">11.1244249343872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.141674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.969202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8829650878906</t>
+    <t xml:space="preserve">11.1416730880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9692010879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8829641342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415061950684</t>
@@ -1817,73 +1817,73 @@
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3483037948608</t>
+    <t xml:space="preserve">10.5207748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172916412354</t>
+    <t xml:space="preserve">10.4172925949097</t>
   </si>
   <si>
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1930780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383586883545</t>
+    <t xml:space="preserve">10.193078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.831223487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383577346802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4176273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8143119812012</t>
+    <t xml:space="preserve">11.417628288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8143129348755</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4697065353394</t>
+    <t xml:space="preserve">12.469705581665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
+    <t xml:space="preserve">12.4007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">12.3662233352661</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4524574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.573187828064</t>
+    <t xml:space="preserve">12.4524583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869527816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5731887817383</t>
   </si>
   <si>
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5214471817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386934280396</t>
+    <t xml:space="preserve">12.521448135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108287811279</t>
+    <t xml:space="preserve">11.7108297348022</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141441345215</t>
+    <t xml:space="preserve">11.3141450881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">11.0554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7967300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622346878052</t>
+    <t xml:space="preserve">10.7967290878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">10.4517860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380220413208</t>
+    <t xml:space="preserve">10.469033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277060508728</t>
+    <t xml:space="preserve">10.2770614624023</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4930419921875</t>
+    <t xml:space="preserve">10.4930410385132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">9.93509197235107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108936309814</t>
+    <t xml:space="preserve">10.187068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108840942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95309066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250835418701</t>
+    <t xml:space="preserve">9.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250844955444</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790786743164</t>
+    <t xml:space="preserve">10.0790796279907</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510715484619</t>
+    <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
     <t xml:space="preserve">9.80910301208496</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210472106934</t>
+    <t xml:space="preserve">10.421049118042</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950592041016</t>
+    <t xml:space="preserve">10.3130578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950601577759</t>
   </si>
   <si>
     <t xml:space="preserve">10.3670530319214</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70111465454102</t>
+    <t xml:space="preserve">9.79110527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7011137008667</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17916202545166</t>
+    <t xml:space="preserve">9.17916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715133666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48513317108154</t>
+    <t xml:space="preserve">9.28715038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48513412475586</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85519123077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97218036651611</t>
+    <t xml:space="preserve">8.85519027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97218132019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47722625732422</t>
+    <t xml:space="preserve">8.4772253036499</t>
   </si>
   <si>
     <t xml:space="preserve">8.62121200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63921165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63021087646484</t>
+    <t xml:space="preserve">8.63921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63021183013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20725059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90127801895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09925937652588</t>
+    <t xml:space="preserve">8.20724964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9012770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.04526519775391</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427297592163</t>
+    <t xml:space="preserve">7.96427249908447</t>
   </si>
   <si>
     <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81128692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327089309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828401565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927576065063</t>
+    <t xml:space="preserve">7.81128644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227914810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927671432495</t>
   </si>
   <si>
     <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.793288230896</t>
+    <t xml:space="preserve">7.79328775405884</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">7.63130235671997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32533073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19934272766113</t>
+    <t xml:space="preserve">7.32533121109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19934225082397</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">6.95636463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19034242630005</t>
+    <t xml:space="preserve">7.19034290313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.16334581375122</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">7.10935068130493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25333738327026</t>
+    <t xml:space="preserve">7.25333786010742</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
@@ -2246,34 +2246,34 @@
     <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5143141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46931838989258</t>
+    <t xml:space="preserve">7.51431369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.28933429718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28033494949341</t>
+    <t xml:space="preserve">7.28033542633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434598922729</t>
+    <t xml:space="preserve">7.15434646606445</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136089324951</t>
+    <t xml:space="preserve">7.00136041641235</t>
   </si>
   <si>
     <t xml:space="preserve">7.05535554885864</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">7.99127006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92827606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627380371094</t>
+    <t xml:space="preserve">7.92827653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9462742805481</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37823581695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75619888305664</t>
+    <t xml:space="preserve">8.27024459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37823486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75619983673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74720191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56721782684326</t>
+    <t xml:space="preserve">8.74720096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56721878051758</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19825077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326389312744</t>
+    <t xml:space="preserve">8.19824981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.11725902557373</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170118331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9789962768555</t>
+    <t xml:space="preserve">10.8170127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
     <t xml:space="preserve">10.8350105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6370277404785</t>
+    <t xml:space="preserve">10.6370286941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.90700340271</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550273895264</t>
+    <t xml:space="preserve">10.6550264358521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1229839324951</t>
+    <t xml:space="preserve">11.2489728927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1229829788208</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">11.4649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669715881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3389644622803</t>
+    <t xml:space="preserve">11.2669706344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3389654159546</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374960899353</t>
+    <t xml:space="preserve">11.3749618530273</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5009489059448</t>
+    <t xml:space="preserve">11.5009498596191</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689073562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709245681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249206542969</t>
+    <t xml:space="preserve">11.9689064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709255218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249197006226</t>
   </si>
   <si>
     <t xml:space="preserve">11.7349281311035</t>
@@ -2450,91 +2450,91 @@
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529277801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429183959961</t>
+    <t xml:space="preserve">11.7529268264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429174423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8069219589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6198072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5262498855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.320424079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.488826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5075387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3391351699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3578472137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4326934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4514036178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4701156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2081546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.601095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8256330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8443441390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0314588546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9940357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7133646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7507877349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6572303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
     <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6198072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5262498855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.320424079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.488826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5075387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3391351699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3578481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4326934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4514045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4701156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.208155632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.601095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8256330490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0314588546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9940366744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7133655548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7507877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6572303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4139804840088</t>
+    <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823850631714</t>
+    <t xml:space="preserve">11.5823841094971</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624393463135</t>
+    <t xml:space="preserve">12.1624383926392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191904067993</t>
+    <t xml:space="preserve">11.919189453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.544960975647</t>
+    <t xml:space="preserve">11.5449619293213</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0584630966187</t>
+    <t xml:space="preserve">11.058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771760940552</t>
+    <t xml:space="preserve">11.0771751403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842346191406</t>
+    <t xml:space="preserve">10.6842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222745895386</t>
+    <t xml:space="preserve">10.4784097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222755432129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287172317505</t>
+    <t xml:space="preserve">10.3287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977367401123</t>
+    <t xml:space="preserve">10.1977376937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3132,6 +3132,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.9799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -68522,7 +68525,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6909953704</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>45497</v>
@@ -68543,6 +68546,32 @@
         <v>1039</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912847222</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>65506</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>17.0400009155273</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>16.6399993896484</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217420578003</t>
+    <t xml:space="preserve">7.18217515945435</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280111312866</t>
+    <t xml:space="preserve">7.16394472122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0728006362915</t>
   </si>
   <si>
     <t xml:space="preserve">7.1092586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93061590194702</t>
+    <t xml:space="preserve">6.93061637878418</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051198959351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14206981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9670729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634309768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717639923096</t>
+    <t xml:space="preserve">7.14207029342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717687606812</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821170806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362859725952</t>
+    <t xml:space="preserve">7.25144386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2769627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863174438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362907409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.4373779296875</t>
@@ -110,121 +110,121 @@
     <t xml:space="preserve">7.28790092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28425550460815</t>
+    <t xml:space="preserve">7.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008756637573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029491424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341590881348</t>
+    <t xml:space="preserve">7.51029396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341543197632</t>
   </si>
   <si>
     <t xml:space="preserve">7.64154100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48841953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112821578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61966753005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216791152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34987926483154</t>
+    <t xml:space="preserve">7.48842000961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30612993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34988117218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.29883861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25873613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24779748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498537063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988508224487</t>
+    <t xml:space="preserve">7.25873565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779844284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050569534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988555908203</t>
   </si>
   <si>
     <t xml:space="preserve">7.0217604637146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99623870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633680343628</t>
+    <t xml:space="preserve">6.99623966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633728027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.50300168991089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56133317947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832085609436</t>
+    <t xml:space="preserve">7.56133365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320999145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.7144570350647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7290415763855</t>
+    <t xml:space="preserve">7.72904014587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.87487173080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778537750244</t>
+    <t xml:space="preserve">7.9477858543396</t>
   </si>
   <si>
     <t xml:space="preserve">8.03528594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273166656494</t>
+    <t xml:space="preserve">8.12278461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424386978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273262023926</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770355224609</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535900115967</t>
+    <t xml:space="preserve">7.88030481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
   </si>
   <si>
     <t xml:space="preserve">7.64786958694458</t>
@@ -257,61 +257,61 @@
     <t xml:space="preserve">7.85781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.985276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89530181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0602560043335</t>
+    <t xml:space="preserve">7.98527526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530038833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06025505065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47264194488525</t>
+    <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.84003734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992202758789</t>
+    <t xml:space="preserve">9.4398717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31990623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13245677947998</t>
+    <t xml:space="preserve">9.31990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245582580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.98249816894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92251396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99749660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10996341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69757843017578</t>
+    <t xml:space="preserve">8.92251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99749374389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10996246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69757747650146</t>
   </si>
   <si>
     <t xml:space="preserve">8.59260749816895</t>
@@ -323,64 +323,64 @@
     <t xml:space="preserve">8.77255725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8100471496582</t>
+    <t xml:space="preserve">8.81004619598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.81754493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79505062103271</t>
+    <t xml:space="preserve">8.72756862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.64509105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69007968902588</t>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6900806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36766910552979</t>
+    <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61509990692139</t>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6151008605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.54761981964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41265678405762</t>
+    <t xml:space="preserve">8.41265773773193</t>
   </si>
   <si>
     <t xml:space="preserve">8.28519344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32268142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506832122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87003040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002250671387</t>
+    <t xml:space="preserve">8.32268238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87002944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90001964569092</t>
   </si>
   <si>
     <t xml:space="preserve">8.67508316040039</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">8.51762771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58510971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51013088226318</t>
+    <t xml:space="preserve">8.58510875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51012897491455</t>
   </si>
   <si>
     <t xml:space="preserve">8.40515899658203</t>
@@ -410,142 +410,142 @@
     <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1727237701416</t>
+    <t xml:space="preserve">8.17272281646729</t>
   </si>
   <si>
     <t xml:space="preserve">8.20271587371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45764350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4201545715332</t>
+    <t xml:space="preserve">8.45764541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11273956298828</t>
+    <t xml:space="preserve">8.1127405166626</t>
   </si>
   <si>
     <t xml:space="preserve">8.09024620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06775379180908</t>
+    <t xml:space="preserve">8.06775283813477</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
+    <t xml:space="preserve">8.12773513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2252082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12023735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00776958465576</t>
+    <t xml:space="preserve">8.01526832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020481109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22520923614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1202392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00776863098145</t>
   </si>
   <si>
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776073455811</t>
+    <t xml:space="preserve">7.82781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93279075622559</t>
+    <t xml:space="preserve">7.9327917098999</t>
   </si>
   <si>
     <t xml:space="preserve">7.88780307769775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778728485107</t>
+    <t xml:space="preserve">7.92529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778633117676</t>
   </si>
   <si>
     <t xml:space="preserve">7.87280750274658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91029739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531856536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09667778015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823375701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967908859253</t>
+    <t xml:space="preserve">7.91029787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.760338306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531713485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823328018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69569969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967813491821</t>
   </si>
   <si>
     <t xml:space="preserve">8.01956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98101139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390062332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86534452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21234607696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678890228271</t>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90389966964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8267879486084</t>
   </si>
   <si>
     <t xml:space="preserve">7.71112298965454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66485500335693</t>
+    <t xml:space="preserve">7.66485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">7.55690002441406</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">7.51063251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858987808228</t>
+    <t xml:space="preserve">7.61858892440796</t>
   </si>
   <si>
     <t xml:space="preserve">7.54147720336914</t>
@@ -566,82 +566,82 @@
     <t xml:space="preserve">7.32556676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41809940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254365921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303365707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
+    <t xml:space="preserve">7.41809988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21760988235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254413604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2330322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507629394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929878234863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17134428024292</t>
+    <t xml:space="preserve">7.17134380340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.20218896865845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10965538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0788106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472255706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423208236694</t>
+    <t xml:space="preserve">7.10965490341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14049959182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881021499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472208023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423303604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.00169897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90916538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205461502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409963607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86289834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578758239746</t>
+    <t xml:space="preserve">6.90916633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86289930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0171217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578805923462</t>
   </si>
   <si>
     <t xml:space="preserve">6.94000959396362</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">6.95543336868286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98627662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67783212661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7086763381958</t>
+    <t xml:space="preserve">6.98627710342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67783164978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70867538452148</t>
   </si>
   <si>
     <t xml:space="preserve">6.6315655708313</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">6.46192073822021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53903102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52361011505127</t>
+    <t xml:space="preserve">6.53903150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52360963821411</t>
   </si>
   <si>
     <t xml:space="preserve">6.19974279403687</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">6.2614312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27685451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5698766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29227590560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565322875977</t>
+    <t xml:space="preserve">6.27685403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56987714767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29227542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565370559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81663227081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89374351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6469874382019</t>
+    <t xml:space="preserve">6.81663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89374303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698791503906</t>
   </si>
   <si>
     <t xml:space="preserve">6.77036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43107652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720920562744</t>
+    <t xml:space="preserve">6.431077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720872879028</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889762878418</t>
@@ -734,82 +734,82 @@
     <t xml:space="preserve">6.30769824981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99925374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66240978240967</t>
+    <t xml:space="preserve">5.99925327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.246009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66240930557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.49276494979858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35396480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21516466140747</t>
+    <t xml:space="preserve">6.35396432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
     <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832164764404</t>
+    <t xml:space="preserve">6.75494432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832117080688</t>
   </si>
   <si>
     <t xml:space="preserve">6.97085475921631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04796695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676519393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">7.04796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
     <t xml:space="preserve">7.20115089416504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313108444214</t>
+    <t xml:space="preserve">7.15314245223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00912094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113761901855</t>
+    <t xml:space="preserve">7.00912141799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913230895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113857269287</t>
   </si>
   <si>
     <t xml:space="preserve">6.833092212677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88109970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509799957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508377075195</t>
+    <t xml:space="preserve">6.88110065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86509704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508424758911</t>
   </si>
   <si>
     <t xml:space="preserve">6.75307893753052</t>
@@ -818,61 +818,61 @@
     <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72107410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48103618621826</t>
+    <t xml:space="preserve">6.72107458114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48103666305542</t>
   </si>
   <si>
     <t xml:space="preserve">6.54504632949829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60905599594116</t>
+    <t xml:space="preserve">6.60905647277832</t>
   </si>
   <si>
     <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108785629272</t>
+    <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
     <t xml:space="preserve">6.89710283279419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81708955764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56104898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65706348419189</t>
+    <t xml:space="preserve">6.81709003448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56104850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51304149627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702604293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102386474609</t>
+    <t xml:space="preserve">6.6250581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705211639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5130410194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102338790894</t>
   </si>
   <si>
     <t xml:space="preserve">6.33701276779175</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16098499298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0009593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95295190811157</t>
+    <t xml:space="preserve">6.1609845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00095891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95295143127441</t>
   </si>
   <si>
     <t xml:space="preserve">6.01696157455444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96895456314087</t>
+    <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094659805298</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">5.74491786956787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68090772628784</t>
+    <t xml:space="preserve">5.680908203125</t>
   </si>
   <si>
     <t xml:space="preserve">5.71291303634644</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8729395866394</t>
+    <t xml:space="preserve">5.90494346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293863296509</t>
   </si>
   <si>
     <t xml:space="preserve">5.79292583465576</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19298982620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12897968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25699996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500793457031</t>
+    <t xml:space="preserve">6.38502073287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19298934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12897920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14498233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25700044631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500745773315</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">6.03296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55288743972778</t>
+    <t xml:space="preserve">5.61689805984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887729644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290071487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50487995147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089540481567</t>
+    <t xml:space="preserve">5.50488042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089492797852</t>
   </si>
   <si>
     <t xml:space="preserve">5.3608570098877</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">5.12081861495972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73675727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67274713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871187210083</t>
+    <t xml:space="preserve">4.73675775527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67274761199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.24067783355713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92062711715698</t>
+    <t xml:space="preserve">3.92062616348267</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868532180786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16066455841064</t>
+    <t xml:space="preserve">4.04864692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065223693848</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72075414657593</t>
+    <t xml:space="preserve">4.72075462341309</t>
   </si>
   <si>
     <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13682126998901</t>
+    <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.40886545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32885217666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">5.18482828140259</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880098342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882610321045</t>
+    <t xml:space="preserve">5.0088005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882562637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680847167969</t>
+    <t xml:space="preserve">5.05680799484253</t>
   </si>
   <si>
     <t xml:space="preserve">5.23283624649048</t>
@@ -1079,34 +1079,34 @@
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093379974365</t>
+    <t xml:space="preserve">5.72891569137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093427658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692270278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69690990447998</t>
+    <t xml:space="preserve">5.77692317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489227294922</t>
+    <t xml:space="preserve">5.58489274978638</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56889057159424</t>
+    <t xml:space="preserve">5.56889009475708</t>
   </si>
   <si>
     <t xml:space="preserve">5.3448543548584</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">5.44086980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37685966491699</t>
+    <t xml:space="preserve">5.37685918807983</t>
   </si>
   <si>
     <t xml:space="preserve">5.26484107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883937835693</t>
+    <t xml:space="preserve">5.24883890151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">5.53688526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29684638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21683406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35301542282104</t>
+    <t xml:space="preserve">5.29684686660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683359146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35301637649536</t>
   </si>
   <si>
     <t xml:space="preserve">6.28900575637817</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4970383644104</t>
+    <t xml:space="preserve">6.49703884124756</t>
   </si>
   <si>
     <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306661605835</t>
+    <t xml:space="preserve">6.67306709289551</t>
   </si>
   <si>
     <t xml:space="preserve">6.91310548782349</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">7.24915885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26516056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116416931152</t>
+    <t xml:space="preserve">7.26516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116464614868</t>
   </si>
   <si>
     <t xml:space="preserve">7.64922380447388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58521127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121488571167</t>
+    <t xml:space="preserve">7.58521223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121583938599</t>
   </si>
   <si>
     <t xml:space="preserve">7.52120161056519</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">7.53720474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47319412231445</t>
+    <t xml:space="preserve">7.47319555282593</t>
   </si>
   <si>
     <t xml:space="preserve">7.44118976593018</t>
@@ -1187,37 +1187,37 @@
     <t xml:space="preserve">7.45719146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40918350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3131685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117696762085</t>
+    <t xml:space="preserve">7.40918445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518758773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519895553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117649078369</t>
   </si>
   <si>
     <t xml:space="preserve">7.29716682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74523878097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525014877319</t>
+    <t xml:space="preserve">7.74523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125232696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">7.90526390075684</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.92126655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127792358398</t>
+    <t xml:space="preserve">7.93726825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00127983093262</t>
   </si>
   <si>
     <t xml:space="preserve">7.8732590675354</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">7.95327043533325</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12129688262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927452087402</t>
+    <t xml:space="preserve">8.12129783630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927309036255</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40134334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4413480758667</t>
+    <t xml:space="preserve">8.40134239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44134998321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.72139453887939</t>
@@ -1265,28 +1265,28 @@
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141445159912</t>
+    <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
     <t xml:space="preserve">9.12145805358887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04144668579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4815149307251</t>
+    <t xml:space="preserve">9.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96143245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84157371520996</t>
+    <t xml:space="preserve">9.84157180786133</t>
   </si>
   <si>
     <t xml:space="preserve">10.1616239547729</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">10.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1216173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2816438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216495513916</t>
+    <t xml:space="preserve">10.1216163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2816429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216485977173</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217140197754</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.3218097686768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2017908096313</t>
+    <t xml:space="preserve">11.201789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.1217775344849</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617832183838</t>
+    <t xml:space="preserve">11.1617841720581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8417329788208</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">10.881739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4818353652954</t>
+    <t xml:space="preserve">11.4818363189697</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417974472046</t>
@@ -1340,25 +1340,25 @@
     <t xml:space="preserve">11.0817718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7617206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6016941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6965751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1573724746704</t>
+    <t xml:space="preserve">10.7617197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6016960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818040847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6965761184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1573705673218</t>
   </si>
   <si>
     <t xml:space="preserve">10.7011222839355</t>
@@ -1367,94 +1367,94 @@
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374879837036</t>
+    <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.1204414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1619186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789632797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99601078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9545316696167</t>
+    <t xml:space="preserve">10.161919593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95453262329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.742600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766897201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8670310974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693046569824</t>
+    <t xml:space="preserve">10.327826499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8670301437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693056106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2863502502441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2448740005493</t>
+    <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
     <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87157726287842</t>
+    <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522590637207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9499864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1158952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5352125167847</t>
+    <t xml:space="preserve">10.9499855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840776443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.115894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085073471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.6596450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4891901016235</t>
+    <t xml:space="preserve">11.032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.323281288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
     <t xml:space="preserve">11.2403259277344</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">11.5721435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5306663513184</t>
+    <t xml:space="preserve">11.5306673049927</t>
   </si>
   <si>
     <t xml:space="preserve">11.7795295715332</t>
@@ -1478,31 +1478,31 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261211395264</t>
+    <t xml:space="preserve">12.3187341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261192321777</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8164596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215721130371</t>
+    <t xml:space="preserve">12.816460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2727098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460046768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215730667114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141860961914</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0193004608154</t>
+    <t xml:space="preserve">14.0192995071411</t>
   </si>
   <si>
     <t xml:space="preserve">13.894868850708</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">13.6874828338623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2312326431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.189754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8994150161743</t>
+    <t xml:space="preserve">13.2312316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8994159698486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647565841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.821008682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4477128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7380523681641</t>
+    <t xml:space="preserve">11.3647575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062356948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8210067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988496780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4477119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7380533218384</t>
   </si>
   <si>
     <t xml:space="preserve">9.78862380981445</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.613621711731</t>
+    <t xml:space="preserve">11.6136207580566</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">11.0661220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177143096924</t>
+    <t xml:space="preserve">10.7177133560181</t>
   </si>
   <si>
     <t xml:space="preserve">10.9665765762329</t>
@@ -1589,52 +1589,52 @@
     <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6347579956055</t>
+    <t xml:space="preserve">10.6347589492798</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8504409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8006687164307</t>
+    <t xml:space="preserve">10.8504400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8006677627563</t>
   </si>
   <si>
     <t xml:space="preserve">10.9002132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8172597885132</t>
+    <t xml:space="preserve">10.8172578811646</t>
   </si>
   <si>
     <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8338499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849857330322</t>
+    <t xml:space="preserve">10.9997577667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8338489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4693689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.331392288208</t>
+    <t xml:space="preserve">11.46937084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313932418823</t>
   </si>
   <si>
     <t xml:space="preserve">11.2279100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4866161346436</t>
+    <t xml:space="preserve">11.4866170883179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">12.2454919815063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2109966278076</t>
+    <t xml:space="preserve">12.2109975814819</t>
   </si>
   <si>
     <t xml:space="preserve">12.2282457351685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592559814453</t>
+    <t xml:space="preserve">12.1592569351196</t>
   </si>
   <si>
     <t xml:space="preserve">12.4179639816284</t>
@@ -1658,25 +1658,25 @@
     <t xml:space="preserve">12.1937503814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.021279335022</t>
+    <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8833017349243</t>
+    <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
     <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0730209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2106618881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035285949707</t>
+    <t xml:space="preserve">12.0730199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2106628417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035276412964</t>
   </si>
   <si>
     <t xml:space="preserve">10.7794828414917</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">10.6242570877075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0036954879761</t>
+    <t xml:space="preserve">11.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.1589202880859</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3831338882446</t>
+    <t xml:space="preserve">11.831561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
     <t xml:space="preserve">11.9522905349731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7280769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5728521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7453241348267</t>
+    <t xml:space="preserve">11.7280778884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5728530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7453231811523</t>
   </si>
   <si>
     <t xml:space="preserve">11.69358253479</t>
@@ -1721,43 +1721,43 @@
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660545349121</t>
+    <t xml:space="preserve">11.8660554885864</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627401351929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9867839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1765041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3144807815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3317289352417</t>
+    <t xml:space="preserve">11.9867849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1765031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3144798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3317279815674</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075143814087</t>
+    <t xml:space="preserve">11.9695386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350423812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107515335083</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970657348633</t>
+    <t xml:space="preserve">11.7970666885376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">11.6073474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2451572418213</t>
+    <t xml:space="preserve">11.5556039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.245156288147</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">11.521110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5901002883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6418409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381898880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.107177734375</t>
+    <t xml:space="preserve">11.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4348745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1071796417236</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209426879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.141674041748</t>
+    <t xml:space="preserve">11.1244249343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3655500411987</t>
+    <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">10.1930780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4862804412842</t>
+    <t xml:space="preserve">10.4862794876099</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5383596420288</t>
+    <t xml:space="preserve">11.5383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">12.0557727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.469705581665</t>
+    <t xml:space="preserve">12.4697065353394</t>
   </si>
   <si>
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007177352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662223815918</t>
+    <t xml:space="preserve">12.4007167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662233352661</t>
   </si>
   <si>
     <t xml:space="preserve">12.4524574279785</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">12.573187828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6421775817871</t>
+    <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5214471817017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386943817139</t>
+    <t xml:space="preserve">12.5386934280396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">12.2799863815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4352111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7798185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7108306884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2968978881836</t>
+    <t xml:space="preserve">12.4352121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7798175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2968969345093</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521217346191</t>
@@ -1910,22 +1910,22 @@
     <t xml:space="preserve">11.2624034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2796506881714</t>
+    <t xml:space="preserve">11.2796497344971</t>
   </si>
   <si>
     <t xml:space="preserve">11.3141450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9519529342651</t>
+    <t xml:space="preserve">10.9519538879395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554361343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967300415039</t>
+    <t xml:space="preserve">11.0554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967290878296</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347076416016</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">10.8657188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7622356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5725164413452</t>
+    <t xml:space="preserve">10.7622346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5725173950195</t>
   </si>
   <si>
     <t xml:space="preserve">10.6070108413696</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4517869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.469033241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380229949951</t>
+    <t xml:space="preserve">10.4517860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4690341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380220413208</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277060508728</t>
+    <t xml:space="preserve">10.2770614624023</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3850507736206</t>
+    <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
     <t xml:space="preserve">10.4930419921875</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0430822372437</t>
+    <t xml:space="preserve">10.043083190918</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">9.93509292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89909553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95309066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250835418701</t>
+    <t xml:space="preserve">10.1870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89909648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250844955444</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
@@ -2036,31 +2036,31 @@
     <t xml:space="preserve">10.5290384292603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030494689941</t>
+    <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.3130578994751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3670530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84510040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">10.2950601577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3670539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79110622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111465454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41314029693604</t>
+    <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
     <t xml:space="preserve">9.17916107177734</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715133666992</t>
+    <t xml:space="preserve">9.28715038299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.48513317108154</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">9.53912830352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37714290618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35914516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32314872741699</t>
+    <t xml:space="preserve">9.37714385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35914421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32314777374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.25115489959717</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">9.01717662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08917045593262</t>
+    <t xml:space="preserve">9.0891695022583</t>
   </si>
   <si>
     <t xml:space="preserve">9.05317306518555</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318992614746</t>
+    <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.85519123077393</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47722625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62121295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63921070098877</t>
+    <t xml:space="preserve">8.4772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62121200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.63021183013916</t>
@@ -2132,37 +2132,37 @@
     <t xml:space="preserve">8.72920227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60321521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123634338379</t>
+    <t xml:space="preserve">8.60321426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.20725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90127754211426</t>
+    <t xml:space="preserve">7.90127801895142</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04526424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05426406860352</t>
+    <t xml:space="preserve">8.04526519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05426502227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91027736663818</t>
+    <t xml:space="preserve">7.96427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
     <t xml:space="preserve">7.81128692626953</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">7.97327184677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83828449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428840637207</t>
+    <t xml:space="preserve">7.83828401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
     <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64930200576782</t>
+    <t xml:space="preserve">7.64930152893066</t>
   </si>
   <si>
     <t xml:space="preserve">7.72129487991333</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">6.69538831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74038362503052</t>
+    <t xml:space="preserve">6.74038410186768</t>
   </si>
   <si>
     <t xml:space="preserve">6.77638101577759</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636463165283</t>
+    <t xml:space="preserve">6.95636415481567</t>
   </si>
   <si>
     <t xml:space="preserve">7.19034290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16334533691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10935068130493</t>
+    <t xml:space="preserve">7.16334581375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10935115814209</t>
   </si>
   <si>
     <t xml:space="preserve">7.25333786010742</t>
@@ -2243,31 +2243,31 @@
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4243221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5143141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733203887939</t>
+    <t xml:space="preserve">7.42432165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51431369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733251571655</t>
   </si>
   <si>
     <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28033494949341</t>
+    <t xml:space="preserve">7.28933429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28033542633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434598922729</t>
+    <t xml:space="preserve">7.15434646606445</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
@@ -2276,40 +2276,40 @@
     <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0553560256958</t>
+    <t xml:space="preserve">7.05535554885864</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68529796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99126958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627380371094</t>
+    <t xml:space="preserve">7.68529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99127054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627475738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37823486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75619888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66620922088623</t>
+    <t xml:space="preserve">8.27024459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37823581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821800231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75619983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">8.74720096588135</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923599243164</t>
+    <t xml:space="preserve">8.36923503875732</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">8.19825077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06326293945312</t>
+    <t xml:space="preserve">8.06326389312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.11725997924805</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8350114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6370277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9070043563843</t>
+    <t xml:space="preserve">10.8350105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6370286941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.90700340271</t>
   </si>
   <si>
     <t xml:space="preserve">10.6010313034058</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550273895264</t>
+    <t xml:space="preserve">10.6550264358521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730251312256</t>
+    <t xml:space="preserve">10.6730241775513</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489728927612</t>
+    <t xml:space="preserve">11.2489719390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.1229829788208</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">11.4829511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4649524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2669715881348</t>
+    <t xml:space="preserve">11.4649515151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
     <t xml:space="preserve">11.3389644622803</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749618530273</t>
+    <t xml:space="preserve">11.374960899353</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089391708374</t>
+    <t xml:space="preserve">11.6089382171631</t>
   </si>
   <si>
     <t xml:space="preserve">11.5009489059448</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
+    <t xml:space="preserve">11.9689073562622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709245681763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349290847778</t>
+    <t xml:space="preserve">11.8249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349271774292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">11.7529268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8069219589233</t>
+    <t xml:space="preserve">11.8429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6198072433472</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578481674194</t>
+    <t xml:space="preserve">11.3578472137451</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514045715332</t>
+    <t xml:space="preserve">11.4514036178589</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.208155632019</t>
+    <t xml:space="preserve">11.2081546783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
+    <t xml:space="preserve">11.8443441390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688810348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940366744995</t>
+    <t xml:space="preserve">11.9940357208252</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133655548096</t>
+    <t xml:space="preserve">11.7133646011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4139804840088</t>
+    <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823850631714</t>
+    <t xml:space="preserve">11.5823841094971</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624393463135</t>
+    <t xml:space="preserve">12.1624383926392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191904067993</t>
+    <t xml:space="preserve">11.919189453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.544960975647</t>
+    <t xml:space="preserve">11.5449619293213</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0584630966187</t>
+    <t xml:space="preserve">11.058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771760940552</t>
+    <t xml:space="preserve">11.0771751403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842346191406</t>
+    <t xml:space="preserve">10.6842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2612,22 +2612,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222745895386</t>
+    <t xml:space="preserve">10.4784097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222755432129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287172317505</t>
+    <t xml:space="preserve">10.3287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977367401123</t>
+    <t xml:space="preserve">10.1977376937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -68577,27 +68577,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911226852</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>78203</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>114518</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>17.0200004577637</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>126915</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>17.2600002288818</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>16.8199996948242</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>16.8600006103516</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>17.2399997711182</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1040</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6912268518</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>74839</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>17.2800006866455</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>17.3199996948242</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="1047">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217515945435</t>
+    <t xml:space="preserve">7.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394519805908</t>
+    <t xml:space="preserve">7.16394472122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0728006362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061685562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207029342651</t>
+    <t xml:space="preserve">7.07280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061590194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14206981658936</t>
   </si>
   <si>
     <t xml:space="preserve">6.96707391738892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03634309768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0071759223938</t>
+    <t xml:space="preserve">7.03634262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717639923096</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2514443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696466445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446237564087</t>
+    <t xml:space="preserve">7.25144338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446189880371</t>
   </si>
   <si>
     <t xml:space="preserve">7.2915472984314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32800483703613</t>
+    <t xml:space="preserve">7.32800436019897</t>
   </si>
   <si>
     <t xml:space="preserve">7.21863222122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821218490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4300856590271</t>
+    <t xml:space="preserve">7.2623815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821170806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362955093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737697601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790140151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425455093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008661270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.51029443740845</t>
@@ -122,49 +122,49 @@
     <t xml:space="preserve">7.66341590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841953277588</t>
+    <t xml:space="preserve">7.64154100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841905593872</t>
   </si>
   <si>
     <t xml:space="preserve">7.48112773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30613040924072</t>
+    <t xml:space="preserve">7.3061318397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.61966753005981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54675245285034</t>
+    <t xml:space="preserve">7.5467529296875</t>
   </si>
   <si>
     <t xml:space="preserve">7.53216886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34988021850586</t>
+    <t xml:space="preserve">7.25509023666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34987878799438</t>
   </si>
   <si>
     <t xml:space="preserve">7.2988395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25873517990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24779748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2149863243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050760269165</t>
+    <t xml:space="preserve">7.25873470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498584747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050664901733</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769453048706</t>
@@ -176,118 +176,118 @@
     <t xml:space="preserve">7.0217604637146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99623966217041</t>
+    <t xml:space="preserve">6.99624061584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.97801113128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52487564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
+    <t xml:space="preserve">7.5248761177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633680343628</t>
   </si>
   <si>
     <t xml:space="preserve">7.50300216674805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56133317947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320903778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904062271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528499603271</t>
+    <t xml:space="preserve">7.56133460998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72903966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528594970703</t>
   </si>
   <si>
     <t xml:space="preserve">8.12278366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98424434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770355224609</t>
+    <t xml:space="preserve">7.98424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770259857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09774494171143</t>
+    <t xml:space="preserve">8.09774589538574</t>
   </si>
   <si>
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030529022217</t>
+    <t xml:space="preserve">7.88030433654785</t>
   </si>
   <si>
     <t xml:space="preserve">7.79782772064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61787700653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6478705406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527431488037</t>
+    <t xml:space="preserve">7.61787843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64786958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.985276222229</t>
   </si>
   <si>
     <t xml:space="preserve">7.89529991149902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02276611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06025505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4726390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992202758789</t>
+    <t xml:space="preserve">8.02276420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0602560043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4398717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31990528106689</t>
+    <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">9.13245677947998</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">8.982497215271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92251491546631</t>
+    <t xml:space="preserve">8.92251396179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.99749374389648</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252281188965</t>
+    <t xml:space="preserve">8.89252185821533</t>
   </si>
   <si>
     <t xml:space="preserve">8.66008758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69757843017578</t>
+    <t xml:space="preserve">8.69757747650146</t>
   </si>
   <si>
     <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84753608703613</t>
+    <t xml:space="preserve">8.84753704071045</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004619598389</t>
+    <t xml:space="preserve">8.8100471496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.81754493713379</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">8.72756958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7950496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64509201049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69007968902588</t>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79505062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6900806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36766910552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266563415527</t>
+    <t xml:space="preserve">8.3676700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266658782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.62259864807129</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54761981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519344329834</t>
+    <t xml:space="preserve">8.5476188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519248962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.32268238067627</t>
@@ -389,22 +389,22 @@
     <t xml:space="preserve">8.51762771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58510971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51013088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515995025635</t>
+    <t xml:space="preserve">8.58510780334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51012992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.3601713180542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31518459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766025543213</t>
+    <t xml:space="preserve">8.31518363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.3001880645752</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">8.1727237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271492004395</t>
+    <t xml:space="preserve">8.20271587371826</t>
   </si>
   <si>
     <t xml:space="preserve">8.45764446258545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42015361785889</t>
+    <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021270751953</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">8.11273956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09024620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775283813477</t>
+    <t xml:space="preserve">8.09024715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775379180908</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277496337891</t>
+    <t xml:space="preserve">8.12773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277400970459</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777843475342</t>
@@ -470,145 +470,145 @@
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282424926758</t>
+    <t xml:space="preserve">7.82781887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282329559326</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026390075684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522598266602</t>
+    <t xml:space="preserve">7.95528411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03775978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522407531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.93278980255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88780212402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280750274658</t>
+    <t xml:space="preserve">7.88780307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280654907227</t>
   </si>
   <si>
     <t xml:space="preserve">7.91029644012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76033878326416</t>
+    <t xml:space="preserve">7.76033973693848</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09667873382568</t>
+    <t xml:space="preserve">8.09667778015137</t>
   </si>
   <si>
     <t xml:space="preserve">7.78823375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6956992149353</t>
+    <t xml:space="preserve">7.69570016860962</t>
   </si>
   <si>
     <t xml:space="preserve">7.74967813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101234436035</t>
+    <t xml:space="preserve">8.01956653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101329803467</t>
   </si>
   <si>
     <t xml:space="preserve">7.90390062332153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86534547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2123441696167</t>
+    <t xml:space="preserve">7.86534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234512329102</t>
   </si>
   <si>
     <t xml:space="preserve">7.82678890228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71112394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55689907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6185884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4797887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32556629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254365921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2330322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17134380340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14049911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0788106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472208023071</t>
+    <t xml:space="preserve">7.71112203598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5568995475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47978925704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3255672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41810083389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21760988235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254413604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845600128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929925918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17134428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218896865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965490341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14049959182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472255706787</t>
   </si>
   <si>
     <t xml:space="preserve">7.31014394760132</t>
@@ -623,70 +623,70 @@
     <t xml:space="preserve">6.90916585922241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83205461502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409963607788</t>
+    <t xml:space="preserve">6.83205413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458772659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409915924072</t>
   </si>
   <si>
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8628978729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0171217918396</t>
+    <t xml:space="preserve">6.86289834976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712131500244</t>
   </si>
   <si>
     <t xml:space="preserve">6.78578805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94001007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9554328918457</t>
+    <t xml:space="preserve">6.94001054763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543336868286</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627710342407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70867729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63156461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47734355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192073822021</t>
+    <t xml:space="preserve">6.67783212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7086763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63156604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192121505737</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61614370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974279403687</t>
+    <t xml:space="preserve">6.61614322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52361011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974231719971</t>
   </si>
   <si>
     <t xml:space="preserve">6.23058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32312059402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40023231506348</t>
+    <t xml:space="preserve">6.3231201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40023183822632</t>
   </si>
   <si>
     <t xml:space="preserve">6.26143074035645</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5698766708374</t>
+    <t xml:space="preserve">6.56987619400024</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227590560913</t>
@@ -704,46 +704,46 @@
     <t xml:space="preserve">6.41565322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55445432662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663274765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89374351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6469874382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720920562744</t>
+    <t xml:space="preserve">6.5544548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663227081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89374303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7703652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720872879028</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889762878418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09178638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30769824981689</t>
+    <t xml:space="preserve">6.09178733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.246009349823</t>
+    <t xml:space="preserve">6.24600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">6.66240978240967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276447296143</t>
+    <t xml:space="preserve">6.49276542663574</t>
   </si>
   <si>
     <t xml:space="preserve">6.35396480560303</t>
@@ -755,40 +755,40 @@
     <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832117080688</t>
+    <t xml:space="preserve">6.36938762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832164764404</t>
   </si>
   <si>
     <t xml:space="preserve">6.97085475921631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314340591431</t>
+    <t xml:space="preserve">7.04796695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592241287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338787078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2011513710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.07313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64106178283691</t>
+    <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912094116211</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">7.08913278579712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1211371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88109922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509799957275</t>
+    <t xml:space="preserve">7.12113761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
     <t xml:space="preserve">6.78508424758911</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">6.75307893753052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73707628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72107458114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48103618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504632949829</t>
+    <t xml:space="preserve">6.73707675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72107410430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4810357093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504585266113</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905647277832</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89710235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81709003448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56104898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65706348419189</t>
+    <t xml:space="preserve">6.89710283279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81708955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56104850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705163955688</t>
+    <t xml:space="preserve">6.62505865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705116271973</t>
   </si>
   <si>
     <t xml:space="preserve">6.52904367446899</t>
@@ -866,40 +866,40 @@
     <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702604293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102291107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33701324462891</t>
+    <t xml:space="preserve">6.44903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
     <t xml:space="preserve">6.22499513626099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08097219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04896688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06496953964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16098546981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00095891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95295143127441</t>
+    <t xml:space="preserve">6.08097171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0489673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06497001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1609845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0009593963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95295190811157</t>
   </si>
   <si>
     <t xml:space="preserve">6.0169620513916</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92094659805298</t>
+    <t xml:space="preserve">5.92094707489014</t>
   </si>
   <si>
     <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74491739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.680908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71291255950928</t>
+    <t xml:space="preserve">5.74491786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68090772628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
     <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8729395866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79292583465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98495674133301</t>
+    <t xml:space="preserve">5.90494394302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79292631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98495721817017</t>
   </si>
   <si>
     <t xml:space="preserve">6.11297702789307</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">6.24099731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101011276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27300310134888</t>
+    <t xml:space="preserve">6.32101106643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27300262451172</t>
   </si>
   <si>
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17698669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19299030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12897920608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498138427734</t>
+    <t xml:space="preserve">6.1769871711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38502073287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19298982620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12898015975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1449818611145</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700092315674</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">5.93694925308228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03296375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61689805984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887777328491</t>
+    <t xml:space="preserve">6.03296422958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61689758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">5.55288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50488042831421</t>
+    <t xml:space="preserve">5.39286184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487995147705</t>
   </si>
   <si>
     <t xml:space="preserve">5.60089540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3608570098877</t>
+    <t xml:space="preserve">5.36085605621338</t>
   </si>
   <si>
     <t xml:space="preserve">5.12081861495972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73675727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67274713516235</t>
+    <t xml:space="preserve">4.73675680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6727466583252</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871139526367</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864740371704</t>
+    <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
     <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08065271377563</t>
+    <t xml:space="preserve">4.08065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">4.40070343017578</t>
@@ -1043,34 +1043,34 @@
     <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13682126998901</t>
+    <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32885122299194</t>
+    <t xml:space="preserve">5.40886449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3288516998291</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0088005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882658004761</t>
+    <t xml:space="preserve">5.18482875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880002975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882610321045</t>
   </si>
   <si>
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680847167969</t>
+    <t xml:space="preserve">5.05680799484253</t>
   </si>
   <si>
     <t xml:space="preserve">5.23283624649048</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">5.72891569137573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88894128799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093332290649</t>
+    <t xml:space="preserve">5.88894176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093427658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85693597793579</t>
+    <t xml:space="preserve">5.85693693161011</t>
   </si>
   <si>
     <t xml:space="preserve">5.58489322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42486763000488</t>
+    <t xml:space="preserve">5.42486715316772</t>
   </si>
   <si>
     <t xml:space="preserve">5.56889009475708</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">5.34485387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44086933135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685871124268</t>
+    <t xml:space="preserve">5.44086980819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685918807983</t>
   </si>
   <si>
     <t xml:space="preserve">5.26484107971191</t>
@@ -1130,19 +1130,19 @@
     <t xml:space="preserve">5.53688526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29684638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2168345451355</t>
+    <t xml:space="preserve">5.29684686660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683359146118</t>
   </si>
   <si>
     <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49703788757324</t>
+    <t xml:space="preserve">6.28900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4970383644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.70507192611694</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">6.67306661605835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91310501098633</t>
+    <t xml:space="preserve">6.91310453414917</t>
   </si>
   <si>
     <t xml:space="preserve">7.24915885925293</t>
@@ -1163,64 +1163,64 @@
     <t xml:space="preserve">7.28116416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64922285079956</t>
+    <t xml:space="preserve">7.64922332763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60121488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52120208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5372052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.457190990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40918397903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318132400513</t>
+    <t xml:space="preserve">7.60121583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5212025642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53720474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40918493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318227767944</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315668106079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31316900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519895553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716634750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523878097534</t>
+    <t xml:space="preserve">7.31316995620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50520038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82525014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526294708252</t>
+    <t xml:space="preserve">7.82525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526390075684</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">7.92126560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726968765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8732590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327138900757</t>
+    <t xml:space="preserve">7.93726873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00127792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95326948165894</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12145805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143245697021</t>
+    <t xml:space="preserve">9.12145900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96143341064453</t>
   </si>
   <si>
     <t xml:space="preserve">9.52152156829834</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">9.72155380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84157466888428</t>
+    <t xml:space="preserve">9.84157371520996</t>
   </si>
   <si>
     <t xml:space="preserve">10.1616239547729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0816106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1216163635254</t>
+    <t xml:space="preserve">10.0816116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.121618270874</t>
   </si>
   <si>
     <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3216495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217140197754</t>
+    <t xml:space="preserve">10.3216485977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217121124268</t>
   </si>
   <si>
     <t xml:space="preserve">11.3218088150024</t>
@@ -1319,16 +1319,16 @@
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617528915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617841720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8417329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8817386627197</t>
+    <t xml:space="preserve">10.9617519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8417348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881739616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818344116211</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">11.0817708969116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7617197036743</t>
+    <t xml:space="preserve">10.7617206573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.0017585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5216817855835</t>
+    <t xml:space="preserve">10.5216827392578</t>
   </si>
   <si>
     <t xml:space="preserve">10.60169506073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818031311035</t>
+    <t xml:space="preserve">11.2818040847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.6965761184692</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">10.7011213302612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4937353134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0374879837036</t>
+    <t xml:space="preserve">10.4937362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.1204414367676</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">10.1619186401367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789632797241</t>
+    <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.99600982666016</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">9.91305541992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95453262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4107828140259</t>
+    <t xml:space="preserve">9.9545316696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278274536133</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">10.9914636611938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
+    <t xml:space="preserve">10.742600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255558013916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5766906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8670320510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181688308716</t>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
   </si>
   <si>
     <t xml:space="preserve">10.3693046569824</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">10.2448740005493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2033967971802</t>
+    <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.87157726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522581100464</t>
+    <t xml:space="preserve">10.4522590637207</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7840766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1158952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085083007812</t>
+    <t xml:space="preserve">10.7840757369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1158933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085092544556</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
@@ -1448,40 +1448,40 @@
     <t xml:space="preserve">10.6596450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
+    <t xml:space="preserve">11.0329399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.323281288147</t>
   </si>
   <si>
     <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5721445083618</t>
+    <t xml:space="preserve">11.240327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5721426010132</t>
   </si>
   <si>
     <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3602113723755</t>
+    <t xml:space="preserve">12.3602123260498</t>
   </si>
   <si>
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261201858521</t>
+    <t xml:space="preserve">12.318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261211395264</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">12.816460609436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2727098464966</t>
+    <t xml:space="preserve">13.2727108001709</t>
   </si>
   <si>
     <t xml:space="preserve">13.5630521774292</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0193004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
+    <t xml:space="preserve">14.0192985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874809265137</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
@@ -1526,28 +1526,28 @@
     <t xml:space="preserve">13.1897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8994140625</t>
+    <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846429824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0283946990967</t>
+    <t xml:space="preserve">12.4846420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3647575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8210077285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988487243652</t>
+    <t xml:space="preserve">11.4062356948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8210067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988496780396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">9.78862380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66419124603271</t>
+    <t xml:space="preserve">9.6641902923584</t>
   </si>
   <si>
     <t xml:space="preserve">9.747145652771</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343044281006</t>
+    <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6513500213623</t>
@@ -1592,46 +1592,46 @@
     <t xml:space="preserve">10.6347589492798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679410934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504400253296</t>
+    <t xml:space="preserve">10.6679401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168033599854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8006687164307</t>
+    <t xml:space="preserve">10.8006677627563</t>
   </si>
   <si>
     <t xml:space="preserve">10.9002122879028</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8172597885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7674856185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997587203979</t>
+    <t xml:space="preserve">10.8172578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997577667236</t>
   </si>
   <si>
     <t xml:space="preserve">10.8338499069214</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5849866867065</t>
+    <t xml:space="preserve">10.5849857330322</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4693698883057</t>
+    <t xml:space="preserve">11.4693689346313</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313913345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2279100418091</t>
+    <t xml:space="preserve">11.2279090881348</t>
   </si>
   <si>
     <t xml:space="preserve">11.4866161346436</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">11.9005489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2454929351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109966278076</t>
+    <t xml:space="preserve">12.2454919815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109975814819</t>
   </si>
   <si>
     <t xml:space="preserve">12.2282457351685</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">12.1592569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4179630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021279335022</t>
+    <t xml:space="preserve">12.4179639816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.193751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106618881226</t>
+    <t xml:space="preserve">11.2106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
@@ -1688,40 +1688,40 @@
     <t xml:space="preserve">10.6242580413818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0036964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1589202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7625722885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.831561088562</t>
+    <t xml:space="preserve">11.0036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1589193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7625713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9522895812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7280769348145</t>
+    <t xml:space="preserve">11.9522905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7280778884888</t>
   </si>
   <si>
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6935834884644</t>
+    <t xml:space="preserve">11.7453241348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660554885864</t>
+    <t xml:space="preserve">11.8660545349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627401351929</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177961349487</t>
+    <t xml:space="preserve">11.9177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">11.9350433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6590890884399</t>
+    <t xml:space="preserve">11.6590881347656</t>
   </si>
   <si>
     <t xml:space="preserve">11.607346534729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556058883667</t>
+    <t xml:space="preserve">11.5556039810181</t>
   </si>
   <si>
     <t xml:space="preserve">11.3486385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2451572418213</t>
+    <t xml:space="preserve">11.2451553344727</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
@@ -1781,22 +1781,22 @@
     <t xml:space="preserve">11.521110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5900983810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6418409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4348754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209426879883</t>
+    <t xml:space="preserve">11.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4348745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.020941734314</t>
   </si>
   <si>
     <t xml:space="preserve">11.1244249343872</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">10.9692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8829660415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.641505241394</t>
+    <t xml:space="preserve">10.8829641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415061950684</t>
   </si>
   <si>
     <t xml:space="preserve">10.1758317947388</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">10.5207748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3483037948608</t>
+    <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">10.4172925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3310546875</t>
+    <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
     <t xml:space="preserve">10.193078994751</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312253952026</t>
+    <t xml:space="preserve">10.831223487854</t>
   </si>
   <si>
     <t xml:space="preserve">11.5383577346802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6245946884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4176273345947</t>
+    <t xml:space="preserve">11.6245937347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.417628288269</t>
   </si>
   <si>
     <t xml:space="preserve">11.8143129348755</t>
@@ -1862,34 +1862,34 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662223815918</t>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662233352661</t>
   </si>
   <si>
     <t xml:space="preserve">12.4524583816528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869518280029</t>
+    <t xml:space="preserve">12.4869527816772</t>
   </si>
   <si>
     <t xml:space="preserve">12.5731887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6421775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5214471817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386934280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5042009353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2799854278564</t>
+    <t xml:space="preserve">12.6421766281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.521448135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386943817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5041999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2799863815308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4352111816406</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108306884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2968988418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521226882935</t>
+    <t xml:space="preserve">11.7108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2968978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521217346191</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2796497344971</t>
+    <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
     <t xml:space="preserve">11.3141450881958</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">10.9519538879395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0899324417114</t>
+    <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7967300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657178878784</t>
+    <t xml:space="preserve">10.7967290878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657188415527</t>
   </si>
   <si>
     <t xml:space="preserve">10.7622356414795</t>
@@ -1940,34 +1940,34 @@
     <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6070117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4517869949341</t>
+    <t xml:space="preserve">10.6070108413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4517860412598</t>
   </si>
   <si>
     <t xml:space="preserve">10.469033241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5380220413208</t>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277060508728</t>
+    <t xml:space="preserve">10.2770614624023</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3850507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4930419921875</t>
+    <t xml:space="preserve">10.3850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4930410385132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1976,10 +1976,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3310556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0430822372437</t>
+    <t xml:space="preserve">10.043083190918</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1991,7 +1988,7 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509292602539</t>
+    <t xml:space="preserve">9.93509197235107</t>
   </si>
   <si>
     <t xml:space="preserve">10.187068939209</t>
@@ -2000,13 +1997,13 @@
     <t xml:space="preserve">9.97108840942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89909553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95309066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250835418701</t>
+    <t xml:space="preserve">9.89909648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250844955444</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
@@ -2021,7 +2018,7 @@
     <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910396575928</t>
+    <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2033,19 +2030,19 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210481643677</t>
+    <t xml:space="preserve">10.421049118042</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030494689941</t>
+    <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.3130578994751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950592041016</t>
+    <t xml:space="preserve">10.2950601577759</t>
   </si>
   <si>
     <t xml:space="preserve">10.3670530319214</t>
@@ -2063,7 +2060,7 @@
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41314029693604</t>
+    <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
     <t xml:space="preserve">9.17916107177734</t>
@@ -2072,22 +2069,22 @@
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715133666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48513317108154</t>
+    <t xml:space="preserve">9.28715038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48513412475586</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37714290618896</t>
+    <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.35914516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32314872741699</t>
+    <t xml:space="preserve">9.32314777374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.25115489959717</t>
@@ -2105,10 +2102,10 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85519123077393</t>
+    <t xml:space="preserve">8.87318897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85519027709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.97218132019043</t>
@@ -2120,10 +2117,10 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47722625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62121295928955</t>
+    <t xml:space="preserve">8.4772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62121200561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.63921070098877</t>
@@ -2135,25 +2132,25 @@
     <t xml:space="preserve">8.72920227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60321521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20725059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90127754211426</t>
+    <t xml:space="preserve">8.60321426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20724964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9012770652771</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04526424407959</t>
+    <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
     <t xml:space="preserve">8.05426406860352</t>
@@ -2165,43 +2162,43 @@
     <t xml:space="preserve">7.96427249908447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91027736663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81128692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.793288230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64930200576782</t>
+    <t xml:space="preserve">7.91027784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81128644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227914810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79328775405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64930152893066</t>
   </si>
   <si>
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130283355713</t>
+    <t xml:space="preserve">7.63130235671997</t>
   </si>
   <si>
     <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19934272766113</t>
+    <t xml:space="preserve">7.19934225082397</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2219,7 +2216,7 @@
     <t xml:space="preserve">6.69538831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74038362503052</t>
+    <t xml:space="preserve">6.74038410186768</t>
   </si>
   <si>
     <t xml:space="preserve">6.77638101577759</t>
@@ -2234,7 +2231,7 @@
     <t xml:space="preserve">7.19034290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16334533691406</t>
+    <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
     <t xml:space="preserve">7.10935068130493</t>
@@ -2246,13 +2243,13 @@
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4243221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5143141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49631547927856</t>
+    <t xml:space="preserve">7.42432165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51431369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49631452560425</t>
   </si>
   <si>
     <t xml:space="preserve">7.30733203887939</t>
@@ -2261,25 +2258,25 @@
     <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28033494949341</t>
+    <t xml:space="preserve">7.28933429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28033542633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434598922729</t>
+    <t xml:space="preserve">7.15434646606445</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136089324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0553560256958</t>
+    <t xml:space="preserve">7.00136041641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05535554885864</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
@@ -2288,19 +2285,19 @@
     <t xml:space="preserve">7.68529796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99126958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627380371094</t>
+    <t xml:space="preserve">7.99127006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9462742805481</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024364471436</t>
+    <t xml:space="preserve">8.27024459838867</t>
   </si>
   <si>
     <t xml:space="preserve">8.37823486328125</t>
@@ -2309,16 +2306,16 @@
     <t xml:space="preserve">8.55821895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75619888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66620922088623</t>
+    <t xml:space="preserve">8.75619983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56721782684326</t>
+    <t xml:space="preserve">8.56721878051758</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2327,19 +2324,19 @@
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923599243164</t>
+    <t xml:space="preserve">8.36923503875732</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19825077056885</t>
+    <t xml:space="preserve">8.19824981689453</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11725997924805</t>
+    <t xml:space="preserve">8.11725902557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2348,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922756195068</t>
+    <t xml:space="preserve">8.45922660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2363,19 +2360,19 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170118331909</t>
+    <t xml:space="preserve">10.8170127868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8350114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6370277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9070043563843</t>
+    <t xml:space="preserve">10.8350105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6370286941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.90700340271</t>
   </si>
   <si>
     <t xml:space="preserve">10.6010313034058</t>
@@ -2384,13 +2381,13 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550273895264</t>
+    <t xml:space="preserve">10.6550264358521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730251312256</t>
+    <t xml:space="preserve">10.6730241775513</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
@@ -2414,10 +2411,10 @@
     <t xml:space="preserve">11.4649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669715881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3389644622803</t>
+    <t xml:space="preserve">11.2669706344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3389654159546</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
@@ -2432,7 +2429,7 @@
     <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5009489059448</t>
+    <t xml:space="preserve">11.5009498596191</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
@@ -2441,13 +2438,13 @@
     <t xml:space="preserve">11.9689064025879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709245681763</t>
+    <t xml:space="preserve">11.7709255218506</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249197006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349290847778</t>
+    <t xml:space="preserve">11.7349281311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
@@ -2480,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578481674194</t>
+    <t xml:space="preserve">11.3578472137451</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514045715332</t>
+    <t xml:space="preserve">11.4514036178589</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.208155632019</t>
+    <t xml:space="preserve">11.2081546783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2501,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
+    <t xml:space="preserve">11.8443441390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688810348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2513,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940366744995</t>
+    <t xml:space="preserve">11.9940357208252</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133655548096</t>
+    <t xml:space="preserve">11.7133646011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2534,7 +2531,10 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4139804840088</t>
+    <t xml:space="preserve">11.806921005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823850631714</t>
+    <t xml:space="preserve">11.5823841094971</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624393463135</t>
+    <t xml:space="preserve">12.1624383926392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191904067993</t>
+    <t xml:space="preserve">11.919189453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.544960975647</t>
+    <t xml:space="preserve">11.5449619293213</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0584630966187</t>
+    <t xml:space="preserve">11.058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771760940552</t>
+    <t xml:space="preserve">11.0771751403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842346191406</t>
+    <t xml:space="preserve">10.6842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222745895386</t>
+    <t xml:space="preserve">10.4784097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222755432129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287172317505</t>
+    <t xml:space="preserve">10.3287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977367401123</t>
+    <t xml:space="preserve">10.1977376937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3150,6 +3150,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -52386,7 +52389,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1881" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52412,7 +52415,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1882" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52438,7 +52441,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1883" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52464,7 +52467,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52516,7 +52519,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1886" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52542,7 +52545,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1887" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52568,7 +52571,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1888" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52594,7 +52597,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1889" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52620,7 +52623,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1890" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52646,7 +52649,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1891" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52672,7 +52675,7 @@
         <v>11</v>
       </c>
       <c r="G1892" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52698,7 +52701,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1893" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52724,7 +52727,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1894" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52750,7 +52753,7 @@
         <v>11</v>
       </c>
       <c r="G1895" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52776,7 +52779,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1896" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52802,7 +52805,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52828,7 +52831,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52854,7 +52857,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1899" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52880,7 +52883,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1900" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52906,7 +52909,7 @@
         <v>11</v>
       </c>
       <c r="G1901" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52932,7 +52935,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1902" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52958,7 +52961,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1903" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52984,7 +52987,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1904" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53010,7 +53013,7 @@
         <v>11.5</v>
       </c>
       <c r="G1905" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53036,7 +53039,7 @@
         <v>11.5</v>
       </c>
       <c r="G1906" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53062,7 +53065,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1907" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53114,7 +53117,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1909" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53140,7 +53143,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53166,7 +53169,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1911" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53192,7 +53195,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1912" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53218,7 +53221,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1913" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53244,7 +53247,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53270,7 +53273,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53296,7 +53299,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1916" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53348,7 +53351,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53374,7 +53377,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1919" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53400,7 +53403,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1920" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53426,7 +53429,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1921" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53452,7 +53455,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53478,7 +53481,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1923" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53504,7 +53507,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1924" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53530,7 +53533,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1925" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53556,7 +53559,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1926" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53582,7 +53585,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1927" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53608,7 +53611,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53634,7 +53637,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1929" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53660,7 +53663,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1930" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53686,7 +53689,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53712,7 +53715,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1932" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53738,7 +53741,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1933" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53764,7 +53767,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1934" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53790,7 +53793,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1935" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53816,7 +53819,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1936" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53842,7 +53845,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1937" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53868,7 +53871,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1938" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53894,7 +53897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53920,7 +53923,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1940" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53946,7 +53949,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1941" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53972,7 +53975,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1942" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53998,7 +54001,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1943" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54024,7 +54027,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54050,7 +54053,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1945" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54076,7 +54079,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1946" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54102,7 +54105,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1947" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54128,7 +54131,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1948" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54154,7 +54157,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54180,7 +54183,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1950" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54206,7 +54209,7 @@
         <v>10</v>
       </c>
       <c r="G1951" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54232,7 +54235,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1952" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54258,7 +54261,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1953" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54284,7 +54287,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1954" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54310,7 +54313,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1955" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54336,7 +54339,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1956" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54362,7 +54365,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54388,7 +54391,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54414,7 +54417,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1959" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54440,7 +54443,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1960" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54466,7 +54469,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1961" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54492,7 +54495,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1962" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54518,7 +54521,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54544,7 +54547,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1964" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54570,7 +54573,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1965" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54596,7 +54599,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1966" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54622,7 +54625,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1967" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54648,7 +54651,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54674,7 +54677,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54700,7 +54703,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54726,7 +54729,7 @@
         <v>9</v>
       </c>
       <c r="G1971" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54752,7 +54755,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1972" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54778,7 +54781,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54804,7 +54807,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1974" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54830,7 +54833,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1975" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54856,7 +54859,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54882,7 +54885,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1977" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54908,7 +54911,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1978" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54934,7 +54937,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1979" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54960,7 +54963,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54986,7 +54989,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1981" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55012,7 +55015,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1982" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55038,7 +55041,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55064,7 +55067,7 @@
         <v>8.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55090,7 +55093,7 @@
         <v>8.5</v>
       </c>
       <c r="G1985" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55116,7 +55119,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1986" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55142,7 +55145,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1987" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55168,7 +55171,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1988" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55194,7 +55197,7 @@
         <v>8</v>
       </c>
       <c r="G1989" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55220,7 +55223,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55246,7 +55249,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55272,7 +55275,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55298,7 +55301,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1993" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55324,7 +55327,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1994" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55350,7 +55353,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1995" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55376,7 +55379,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1996" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55402,7 +55405,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1997" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55428,7 +55431,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55454,7 +55457,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1999" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55480,7 +55483,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55506,7 +55509,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2001" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55532,7 +55535,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2002" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55558,7 +55561,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2003" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55584,7 +55587,7 @@
         <v>8.25</v>
       </c>
       <c r="G2004" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55610,7 +55613,7 @@
         <v>8.5</v>
       </c>
       <c r="G2005" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55636,7 +55639,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2006" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55662,7 +55665,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2007" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55688,7 +55691,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55714,7 +55717,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2009" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55740,7 +55743,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2010" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55766,7 +55769,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2011" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55792,7 +55795,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G2012" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55818,7 +55821,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2013" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55844,7 +55847,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55870,7 +55873,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2015" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55896,7 +55899,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2016" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55922,7 +55925,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2017" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55948,7 +55951,7 @@
         <v>8</v>
       </c>
       <c r="G2018" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55974,7 +55977,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2019" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56000,7 +56003,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2020" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56026,7 +56029,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2021" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56052,7 +56055,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2022" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56078,7 +56081,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2023" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56104,7 +56107,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56130,7 +56133,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2025" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56156,7 +56159,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56182,7 +56185,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56208,7 +56211,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2028" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56234,7 +56237,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2029" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56260,7 +56263,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56286,7 +56289,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2031" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56312,7 +56315,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2032" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56338,7 +56341,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2033" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56364,7 +56367,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2034" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56390,7 +56393,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2035" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56416,7 +56419,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2036" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56442,7 +56445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2037" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56468,7 +56471,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56494,7 +56497,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56520,7 +56523,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2040" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56546,7 +56549,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2041" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56572,7 +56575,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2042" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56598,7 +56601,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2043" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56624,7 +56627,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2044" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56650,7 +56653,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2045" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56676,7 +56679,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2046" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56702,7 +56705,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2047" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56728,7 +56731,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2048" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56754,7 +56757,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2049" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56780,7 +56783,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56806,7 +56809,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2051" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56832,7 +56835,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56858,7 +56861,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2053" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56884,7 +56887,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2054" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56910,7 +56913,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56936,7 +56939,7 @@
         <v>9</v>
       </c>
       <c r="G2056" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56962,7 +56965,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2057" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56988,7 +56991,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2058" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57014,7 +57017,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2059" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57040,7 +57043,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2060" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57066,7 +57069,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2061" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57092,7 +57095,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2062" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57118,7 +57121,7 @@
         <v>9.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57144,7 +57147,7 @@
         <v>9.5</v>
       </c>
       <c r="G2064" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57170,7 +57173,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2065" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57196,7 +57199,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2066" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57222,7 +57225,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2067" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57248,7 +57251,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57274,7 +57277,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2069" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57300,7 +57303,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2070" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57326,7 +57329,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2071" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57352,7 +57355,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2072" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57378,7 +57381,7 @@
         <v>11</v>
       </c>
       <c r="G2073" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57404,7 +57407,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2074" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57430,7 +57433,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2075" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57456,7 +57459,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2076" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57482,7 +57485,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2077" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57534,7 +57537,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2079" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57560,7 +57563,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2080" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57586,7 +57589,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2081" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57612,7 +57615,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2082" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57638,7 +57641,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2083" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57664,7 +57667,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57690,7 +57693,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2085" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57716,7 +57719,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57742,7 +57745,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57794,7 +57797,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2089" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57820,7 +57823,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57846,7 +57849,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2091" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57898,7 +57901,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2093" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57924,7 +57927,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57950,7 +57953,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2095" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58002,7 +58005,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2097" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58028,7 +58031,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2098" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58054,7 +58057,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2099" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58080,7 +58083,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2100" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58106,7 +58109,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2101" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58132,7 +58135,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2102" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58158,7 +58161,7 @@
         <v>12</v>
       </c>
       <c r="G2103" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58184,7 +58187,7 @@
         <v>12</v>
       </c>
       <c r="G2104" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58210,7 +58213,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2105" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58236,7 +58239,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2106" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58262,7 +58265,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2107" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58288,7 +58291,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2108" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58314,7 +58317,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2109" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58340,7 +58343,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2110" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58366,7 +58369,7 @@
         <v>12.5</v>
       </c>
       <c r="G2111" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58392,7 +58395,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2112" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58418,7 +58421,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58444,7 +58447,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58470,7 +58473,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58496,7 +58499,7 @@
         <v>12.5</v>
       </c>
       <c r="G2116" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58522,7 +58525,7 @@
         <v>12.5</v>
       </c>
       <c r="G2117" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58548,7 +58551,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2118" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58574,7 +58577,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2119" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58600,7 +58603,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2120" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58626,7 +58629,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2121" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58652,7 +58655,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58678,7 +58681,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2123" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58704,7 +58707,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2124" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58730,7 +58733,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2125" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58756,7 +58759,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2126" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58782,7 +58785,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58808,7 +58811,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G2128" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58834,7 +58837,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2129" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58860,7 +58863,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2130" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58886,7 +58889,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2131" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58912,7 +58915,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2132" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58938,7 +58941,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2133" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58964,7 +58967,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58990,7 +58993,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2135" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59016,7 +59019,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2136" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59042,7 +59045,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G2137" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59068,7 +59071,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2138" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59094,7 +59097,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2139" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59120,7 +59123,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59146,7 +59149,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2141" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59172,7 +59175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2142" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59198,7 +59201,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59224,7 +59227,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2144" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59250,7 +59253,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2145" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59276,7 +59279,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2146" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59302,7 +59305,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2147" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59328,7 +59331,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2148" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59354,7 +59357,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2149" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59380,7 +59383,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2150" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59406,7 +59409,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59432,7 +59435,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59458,7 +59461,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2153" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59484,7 +59487,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59510,7 +59513,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2155" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59536,7 +59539,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2156" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59562,7 +59565,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2157" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59588,7 +59591,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2158" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59614,7 +59617,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2159" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59640,7 +59643,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2160" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59666,7 +59669,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59692,7 +59695,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2162" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59718,7 +59721,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2163" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59744,7 +59747,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2164" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59770,7 +59773,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2165" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59796,7 +59799,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2166" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59822,7 +59825,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2167" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59848,7 +59851,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2168" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59874,7 +59877,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2169" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59900,7 +59903,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2170" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59926,7 +59929,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59952,7 +59955,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2172" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60004,7 +60007,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2174" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60030,7 +60033,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2175" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60056,7 +60059,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60186,7 +60189,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2181" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60238,7 +60241,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2183" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60264,7 +60267,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2184" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60290,7 +60293,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2185" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60420,7 +60423,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2190" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60446,7 +60449,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2191" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60472,7 +60475,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2192" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60628,7 +60631,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2198" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60654,7 +60657,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2199" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60680,7 +60683,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2200" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60732,7 +60735,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2202" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60758,7 +60761,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60784,7 +60787,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2204" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60810,7 +60813,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2205" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60914,7 +60917,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2209" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60992,7 +60995,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2212" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61122,7 +61125,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61174,7 +61177,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61252,7 +61255,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61304,7 +61307,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61356,7 +61359,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2226" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61434,7 +61437,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2229" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61486,7 +61489,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2231" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61512,7 +61515,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2232" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61538,7 +61541,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2233" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61564,7 +61567,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2234" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61590,7 +61593,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2235" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61642,7 +61645,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2237" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61668,7 +61671,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2238" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61694,7 +61697,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2239" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61772,7 +61775,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2242" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61798,7 +61801,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2243" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61824,7 +61827,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2244" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61850,7 +61853,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2245" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61876,7 +61879,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2246" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -68800,7 +68803,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911689815</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>97482</v>
@@ -68821,6 +68824,32 @@
         <v>1045</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6910648148</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>53617</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>15.1400003433228</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>14.539999961853</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="1046">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394472122192</t>
+    <t xml:space="preserve">7.16394519805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571619033813</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">7.10925769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93061590194702</t>
+    <t xml:space="preserve">6.93061542510986</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051246643066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14206981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707391738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
+    <t xml:space="preserve">7.14207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9670729637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634357452393</t>
   </si>
   <si>
     <t xml:space="preserve">7.00717639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96342849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800436019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2623815536499</t>
+    <t xml:space="preserve">6.96342802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238107681274</t>
   </si>
   <si>
     <t xml:space="preserve">7.40821170806885</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">7.39362955093384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43737697601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790140151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425455093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029443740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841905593872</t>
+    <t xml:space="preserve">7.43737840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.284255027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4300856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154005050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841857910156</t>
   </si>
   <si>
     <t xml:space="preserve">7.48112773895264</t>
@@ -134,64 +134,64 @@
     <t xml:space="preserve">7.3061318397522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61966753005981</t>
+    <t xml:space="preserve">7.61966562271118</t>
   </si>
   <si>
     <t xml:space="preserve">7.5467529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53216886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25509023666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34987878799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2988395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2477970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498584747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217604637146</t>
+    <t xml:space="preserve">7.53216743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34987926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29883766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873517990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175951004028</t>
   </si>
   <si>
     <t xml:space="preserve">6.99624061584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97801113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5248761177063</t>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487659454346</t>
   </si>
   <si>
     <t xml:space="preserve">7.47383594512939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20404863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633680343628</t>
+    <t xml:space="preserve">7.2040491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633728027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.50300216674805</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">7.5832085609436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7144570350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72903966903687</t>
+    <t xml:space="preserve">7.71445608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904014587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.87487268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778633117676</t>
+    <t xml:space="preserve">7.94778680801392</t>
   </si>
   <si>
     <t xml:space="preserve">8.03528594970703</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">8.12278366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98424339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18022155761719</t>
+    <t xml:space="preserve">7.98424482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1802225112915</t>
   </si>
   <si>
     <t xml:space="preserve">8.09774589538574</t>
@@ -239,91 +239,91 @@
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782772064209</t>
+    <t xml:space="preserve">7.88030576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782819747925</t>
   </si>
   <si>
     <t xml:space="preserve">7.61787843704224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68535900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64786958694458</t>
+    <t xml:space="preserve">7.68535852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787006378174</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.985276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276420593262</t>
+    <t xml:space="preserve">7.98527574539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530038833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276515960693</t>
   </si>
   <si>
     <t xml:space="preserve">8.0602560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68258285522461</t>
+    <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4398717880249</t>
+    <t xml:space="preserve">8.84003734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43986988067627</t>
   </si>
   <si>
     <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13245677947998</t>
+    <t xml:space="preserve">9.31240558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990337371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245582580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.982497215271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92251396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99749374389648</t>
+    <t xml:space="preserve">8.92251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9974946975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252185821533</t>
+    <t xml:space="preserve">8.89252376556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.66008758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69757747650146</t>
+    <t xml:space="preserve">8.69757843017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84753704071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8100471496582</t>
+    <t xml:space="preserve">8.84753608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81004619598389</t>
   </si>
   <si>
     <t xml:space="preserve">8.81754493713379</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">8.70507526397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79505062103271</t>
+    <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.64509105682373</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3676700592041</t>
+    <t xml:space="preserve">8.36767101287842</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266658782959</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">8.62259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61509990692139</t>
+    <t xml:space="preserve">8.6151008605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.5476188659668</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">8.32268238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73506641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87002944946289</t>
+    <t xml:space="preserve">8.73506546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87003040313721</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67508411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51762771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510780334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3601713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31518363952637</t>
+    <t xml:space="preserve">8.67508316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51762676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5101318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515995025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36017227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31518459320068</t>
   </si>
   <si>
     <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3001880645752</t>
+    <t xml:space="preserve">8.30018901824951</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727237701416</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">8.20271587371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45764446258545</t>
+    <t xml:space="preserve">8.45764541625977</t>
   </si>
   <si>
     <t xml:space="preserve">8.4201545715332</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11273956298828</t>
+    <t xml:space="preserve">8.1127405166626</t>
   </si>
   <si>
     <t xml:space="preserve">8.09024715423584</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">8.12773704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18771934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
+    <t xml:space="preserve">8.18772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277305603027</t>
   </si>
   <si>
     <t xml:space="preserve">7.97777843475342</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22521018981934</t>
+    <t xml:space="preserve">8.13523483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22520923614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.12023830413818</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">8.00777053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82781887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03775978088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93278980255127</t>
+    <t xml:space="preserve">7.76783561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82781934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8128228187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776264190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93278932571411</t>
   </si>
   <si>
     <t xml:space="preserve">7.88780307769775</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">7.91029644012451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76033973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531761169434</t>
+    <t xml:space="preserve">7.760338306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531665802002</t>
   </si>
   <si>
     <t xml:space="preserve">8.09667778015137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78823375701904</t>
+    <t xml:space="preserve">7.7882342338562</t>
   </si>
   <si>
     <t xml:space="preserve">7.69570016860962</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">7.74967813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390062332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86534452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523483276367</t>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90389966964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8653450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523387908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.21234512329102</t>
@@ -542,58 +542,58 @@
     <t xml:space="preserve">7.82678890228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71112203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485404968262</t>
+    <t xml:space="preserve">7.71112251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485500335693</t>
   </si>
   <si>
     <t xml:space="preserve">7.5568995475769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47978925704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3255672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41810083389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725471496582</t>
+    <t xml:space="preserve">7.51063299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5414776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4797887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41810035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725519180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.21760988235474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03254413604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303365707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845600128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507772445679</t>
+    <t xml:space="preserve">7.03254365921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845552444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507724761963</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17134428024292</t>
+    <t xml:space="preserve">7.1713433265686</t>
   </si>
   <si>
     <t xml:space="preserve">7.20218896865845</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">7.07881116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29472255706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0942325592041</t>
+    <t xml:space="preserve">7.29472160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423208236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.00169944763184</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">6.90916585922241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83205413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458772659302</t>
+    <t xml:space="preserve">6.83205461502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458820343018</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409915924072</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">6.86289834976196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01712131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578805923462</t>
+    <t xml:space="preserve">7.01712226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578853607178</t>
   </si>
   <si>
     <t xml:space="preserve">6.94001054763794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95543336868286</t>
+    <t xml:space="preserve">6.9554328918457</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627710342407</t>
@@ -656,43 +656,43 @@
     <t xml:space="preserve">6.67783212661743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7086763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47734260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192121505737</t>
+    <t xml:space="preserve">6.70867681503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6315655708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192073822021</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61614322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52361011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974231719971</t>
+    <t xml:space="preserve">6.61614370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52360963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974184036255</t>
   </si>
   <si>
     <t xml:space="preserve">6.23058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3231201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40023183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27685403823853</t>
+    <t xml:space="preserve">6.32312059402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40023136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2614312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27685451507568</t>
   </si>
   <si>
     <t xml:space="preserve">6.56987619400024</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5544548034668</t>
+    <t xml:space="preserve">6.41565370559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374303817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7703652381897</t>
+    <t xml:space="preserve">6.89374351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77036476135254</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720872879028</t>
+    <t xml:space="preserve">6.1072096824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889762878418</t>
@@ -731,37 +731,37 @@
     <t xml:space="preserve">6.09178733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30769872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99925327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24600887298584</t>
+    <t xml:space="preserve">6.30769824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99925374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
     <t xml:space="preserve">6.66240978240967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276542663574</t>
+    <t xml:space="preserve">6.49276447296143</t>
   </si>
   <si>
     <t xml:space="preserve">6.35396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44649791717529</t>
+    <t xml:space="preserve">6.44649839401245</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938762664795</t>
+    <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.75494432449341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87832164764404</t>
+    <t xml:space="preserve">6.87832117080688</t>
   </si>
   <si>
     <t xml:space="preserve">6.97085475921631</t>
@@ -770,31 +770,31 @@
     <t xml:space="preserve">7.04796695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15592241287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676567077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">7.15592193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338739395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.2011513710022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313108444214</t>
+    <t xml:space="preserve">7.15314340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00912094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913278579712</t>
+    <t xml:space="preserve">7.00912141799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913326263428</t>
   </si>
   <si>
     <t xml:space="preserve">7.12113761901855</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">6.88110017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8650975227356</t>
+    <t xml:space="preserve">6.86509799957275</t>
   </si>
   <si>
     <t xml:space="preserve">6.78508424758911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75307893753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73707675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72107410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4810357093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504585266113</t>
+    <t xml:space="preserve">6.75307941436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73707628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72107362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48103618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504632949829</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905647277832</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89710283279419</t>
+    <t xml:space="preserve">6.89710330963135</t>
   </si>
   <si>
     <t xml:space="preserve">6.81708955764771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56104850769043</t>
+    <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
     <t xml:space="preserve">6.65706396102905</t>
@@ -854,70 +854,70 @@
     <t xml:space="preserve">6.62505865097046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57705116271973</t>
+    <t xml:space="preserve">6.57705163955688</t>
   </si>
   <si>
     <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5130410194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102338790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33701276779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22499513626099</t>
+    <t xml:space="preserve">6.43302774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51304197311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702699661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33701372146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22499561309814</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0489673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06497001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697484970093</t>
+    <t xml:space="preserve">6.04896688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06496953964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.1609845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0009593963623</t>
+    <t xml:space="preserve">6.00095891952515</t>
   </si>
   <si>
     <t xml:space="preserve">5.95295190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0169620513916</t>
+    <t xml:space="preserve">6.01696157455444</t>
   </si>
   <si>
     <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92094707489014</t>
+    <t xml:space="preserve">5.92094612121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.76092100143433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74491786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68090772628784</t>
+    <t xml:space="preserve">5.74491882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.680908203125</t>
   </si>
   <si>
     <t xml:space="preserve">5.71291303634644</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">5.79292631149292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98495721817017</t>
+    <t xml:space="preserve">5.98495626449585</t>
   </si>
   <si>
     <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24099731445312</t>
+    <t xml:space="preserve">6.24099826812744</t>
   </si>
   <si>
     <t xml:space="preserve">6.32101106643677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27300262451172</t>
+    <t xml:space="preserve">6.27300310134888</t>
   </si>
   <si>
     <t xml:space="preserve">6.20899248123169</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12898015975952</t>
+    <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
     <t xml:space="preserve">6.1449818611145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25700092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500793457031</t>
+    <t xml:space="preserve">6.25699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500841140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.03296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887729644775</t>
+    <t xml:space="preserve">5.61689805984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55288791656494</t>
+    <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">5.60089540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36085605621338</t>
+    <t xml:space="preserve">5.36085653305054</t>
   </si>
   <si>
     <t xml:space="preserve">5.12081861495972</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">4.73675680160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6727466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871139526367</t>
+    <t xml:space="preserve">4.67274713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.24067783355713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92062616348267</t>
+    <t xml:space="preserve">3.92062640190125</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864692687988</t>
+    <t xml:space="preserve">4.04864740371704</t>
   </si>
   <si>
     <t xml:space="preserve">4.1606650352478</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">4.72075462341309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92878770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13682079315186</t>
+    <t xml:space="preserve">4.92878723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13682126998901</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">5.40886449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.32885217666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880002975464</t>
+    <t xml:space="preserve">5.18482828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882610321045</t>
@@ -1070,61 +1070,61 @@
     <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05680799484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47287464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093427658081</t>
+    <t xml:space="preserve">5.05680847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283672332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47287511825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69691038131714</t>
+    <t xml:space="preserve">5.77692270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6969108581543</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486715316772</t>
+    <t xml:space="preserve">5.58489274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486763000488</t>
   </si>
   <si>
     <t xml:space="preserve">5.56889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34485387802124</t>
+    <t xml:space="preserve">5.34485483169556</t>
   </si>
   <si>
     <t xml:space="preserve">5.44086980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24883937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45687246322632</t>
+    <t xml:space="preserve">5.37685966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24883890151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45687198638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.53688526153564</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">5.29684686660767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683359146118</t>
+    <t xml:space="preserve">5.21683311462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.35301542282104</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310453414917</t>
+    <t xml:space="preserve">6.67306709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310501098633</t>
   </si>
   <si>
     <t xml:space="preserve">7.24915885925293</t>
@@ -1160,40 +1160,40 @@
     <t xml:space="preserve">7.26516151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121583938599</t>
+    <t xml:space="preserve">7.28116464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6492223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.5212025642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53720474243164</t>
+    <t xml:space="preserve">7.5372052192688</t>
   </si>
   <si>
     <t xml:space="preserve">7.47319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44118976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40918493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315668106079</t>
+    <t xml:space="preserve">7.44118881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40918445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315620422363</t>
   </si>
   <si>
     <t xml:space="preserve">7.31316995620728</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">7.42518711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50520038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117744445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125232696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525110244751</t>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716634750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">7.90526390075684</t>
@@ -1232,55 +1232,55 @@
     <t xml:space="preserve">7.92126560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127792358398</t>
+    <t xml:space="preserve">7.93726778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0012788772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.87325811386108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95326948165894</t>
+    <t xml:space="preserve">7.95327043533325</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96927356719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134334564209</t>
+    <t xml:space="preserve">7.96927404403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28132343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134239196777</t>
   </si>
   <si>
     <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72139358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00143814086914</t>
+    <t xml:space="preserve">8.72139453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00144004821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12145900726318</t>
+    <t xml:space="preserve">9.12145709991455</t>
   </si>
   <si>
     <t xml:space="preserve">9.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96143341064453</t>
+    <t xml:space="preserve">8.96143245697021</t>
   </si>
   <si>
     <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48151588439941</t>
+    <t xml:space="preserve">9.48151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">10.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.121618270874</t>
+    <t xml:space="preserve">10.1216173171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.2816429138184</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">10.3216485977173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7217121124268</t>
+    <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
     <t xml:space="preserve">11.3218088150024</t>
@@ -1319,13 +1319,13 @@
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8417348861694</t>
+    <t xml:space="preserve">10.9617528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617851257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8417329788208</t>
   </si>
   <si>
     <t xml:space="preserve">10.881739616394</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.4818344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817708969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7617206573486</t>
+    <t xml:space="preserve">11.2417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7617197036743</t>
   </si>
   <si>
     <t xml:space="preserve">11.0017585754395</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">10.5216827392578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.60169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818040847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6965761184692</t>
+    <t xml:space="preserve">10.6016960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6965770721436</t>
   </si>
   <si>
     <t xml:space="preserve">11.1573715209961</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">10.7011213302612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4937362670898</t>
+    <t xml:space="preserve">10.4937353134155</t>
   </si>
   <si>
     <t xml:space="preserve">10.0374870300293</t>
@@ -1379,31 +1379,31 @@
     <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600982666016</t>
+    <t xml:space="preserve">9.99600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305541992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9545316696167</t>
+    <t xml:space="preserve">9.95453262329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278274536133</t>
+    <t xml:space="preserve">10.327826499939</t>
   </si>
   <si>
     <t xml:space="preserve">10.9914636611938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.742600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766906738281</t>
+    <t xml:space="preserve">10.7425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766916275024</t>
   </si>
   <si>
     <t xml:space="preserve">10.8670310974121</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">10.3693046569824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
     <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87157726287842</t>
+    <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522590637207</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">10.6596450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.323281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4891891479492</t>
+    <t xml:space="preserve">11.032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4891901016235</t>
   </si>
   <si>
     <t xml:space="preserve">11.240327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5721426010132</t>
+    <t xml:space="preserve">11.5721445083618</t>
   </si>
   <si>
     <t xml:space="preserve">11.5306663513184</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2772569656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3602123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6505517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261211395264</t>
+    <t xml:space="preserve">12.2772560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3602113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6505508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3187341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261201858521</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">12.816460609436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630521774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
+    <t xml:space="preserve">13.2727098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119144439697</t>
   </si>
   <si>
     <t xml:space="preserve">13.6460065841675</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5215721130371</t>
+    <t xml:space="preserve">13.5215730667114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141860961914</t>
@@ -1514,31 +1514,31 @@
     <t xml:space="preserve">14.0192985534668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6874809265137</t>
+    <t xml:space="preserve">13.894868850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874828338623</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1897554397583</t>
+    <t xml:space="preserve">13.1897563934326</t>
   </si>
   <si>
     <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6090745925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846420288086</t>
+    <t xml:space="preserve">12.609073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846429824829</t>
   </si>
   <si>
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647575378418</t>
+    <t xml:space="preserve">11.3647584915161</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062356948853</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">11.7380523681641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6641902923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
+    <t xml:space="preserve">9.78862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714756011963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624849319458</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">10.7177133560181</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9665765762329</t>
+    <t xml:space="preserve">10.9665784835815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7343034744263</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6347589492798</t>
+    <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679401397705</t>
@@ -1598,43 +1598,43 @@
     <t xml:space="preserve">10.8504409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9168033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8006677627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002122879028</t>
+    <t xml:space="preserve">10.9168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8006687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002132415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172578811646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.767484664917</t>
+    <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338499069214</t>
+    <t xml:space="preserve">10.8338489532471</t>
   </si>
   <si>
     <t xml:space="preserve">10.5849857330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4003810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4693689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3313913345337</t>
+    <t xml:space="preserve">11.4003820419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313932418823</t>
   </si>
   <si>
     <t xml:space="preserve">11.2279090881348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4866161346436</t>
+    <t xml:space="preserve">11.4866170883179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">12.193751335144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0212783813477</t>
+    <t xml:space="preserve">12.021279335022</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7794828414917</t>
+    <t xml:space="preserve">10.7794818878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6932468414307</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9522905349731</t>
+    <t xml:space="preserve">11.831561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3831338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9522895812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280778884888</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">11.8660545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2627401351929</t>
+    <t xml:space="preserve">12.2627391815186</t>
   </si>
   <si>
     <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177951812744</t>
+    <t xml:space="preserve">11.9177961349487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3144807815552</t>
+    <t xml:space="preserve">12.3144798278809</t>
   </si>
   <si>
     <t xml:space="preserve">12.3317279815674</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695377349854</t>
+    <t xml:space="preserve">11.9695386886597</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350433349609</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6590881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486385345459</t>
+    <t xml:space="preserve">11.6590890884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486394882202</t>
   </si>
   <si>
     <t xml:space="preserve">11.2451553344727</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">11.3658866882324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5900993347168</t>
+    <t xml:space="preserve">11.5211114883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5901002883911</t>
   </si>
   <si>
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
+    <t xml:space="preserve">11.4348754882812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0381898880005</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">11.107177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.020941734314</t>
+    <t xml:space="preserve">11.0209426879883</t>
   </si>
   <si>
     <t xml:space="preserve">11.1244249343872</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9692010879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8829641342163</t>
+    <t xml:space="preserve">10.969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415061950684</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">10.365550994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4172925949097</t>
+    <t xml:space="preserve">10.3655500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
     <t xml:space="preserve">10.3310556411743</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.831223487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383577346802</t>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
@@ -1865,22 +1865,22 @@
     <t xml:space="preserve">12.4007177352905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3662233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524583816528</t>
+    <t xml:space="preserve">12.3662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869527816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5731887817383</t>
+    <t xml:space="preserve">12.573187828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521448135376</t>
+    <t xml:space="preserve">12.5214471817017</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386943817139</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2799863815308</t>
+    <t xml:space="preserve">12.2799873352051</t>
   </si>
   <si>
     <t xml:space="preserve">12.4352111816406</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108297348022</t>
+    <t xml:space="preserve">11.7108306884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521217346191</t>
+    <t xml:space="preserve">11.4521226882935</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141450881958</t>
+    <t xml:space="preserve">11.3141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967290878296</t>
+    <t xml:space="preserve">11.0554361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347066879272</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">10.6070108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4345388412476</t>
+    <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">10.4517860412598</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4930410385132</t>
+    <t xml:space="preserve">10.4930419921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
+    <t xml:space="preserve">9.93509292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.89909648895264</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">9.80910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.421049118042</t>
+    <t xml:space="preserve">10.4210481643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">10.2950601577759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3670530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84510040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">10.3670539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79110622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111465454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">9.28715038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48513412475586</t>
+    <t xml:space="preserve">9.48513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35914516448975</t>
+    <t xml:space="preserve">9.35914421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.32314777374268</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">9.01717662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08917045593262</t>
+    <t xml:space="preserve">9.0891695022583</t>
   </si>
   <si>
     <t xml:space="preserve">9.05317306518555</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85519027709961</t>
+    <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.97218132019043</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">8.62121200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63921070098877</t>
+    <t xml:space="preserve">8.63921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.63021183013916</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9012770652771</t>
+    <t xml:space="preserve">8.20725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90127801895142</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
@@ -2153,28 +2153,28 @@
     <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05426406860352</t>
+    <t xml:space="preserve">8.05426502227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427249908447</t>
+    <t xml:space="preserve">7.96427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81128644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227914810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828353881836</t>
+    <t xml:space="preserve">7.81128692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">7.91927671432495</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79328775405884</t>
+    <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130235671997</t>
+    <t xml:space="preserve">7.63130283355713</t>
   </si>
   <si>
     <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19934225082397</t>
+    <t xml:space="preserve">7.19934272766113</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636463165283</t>
+    <t xml:space="preserve">6.95636415481567</t>
   </si>
   <si>
     <t xml:space="preserve">7.19034290313721</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10935068130493</t>
+    <t xml:space="preserve">7.10935115814209</t>
   </si>
   <si>
     <t xml:space="preserve">7.25333786010742</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">7.51431369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733203887939</t>
+    <t xml:space="preserve">7.49631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733251571655</t>
   </si>
   <si>
     <t xml:space="preserve">7.46931791305542</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136041641235</t>
+    <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.05535554885864</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">7.06435441970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68529796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99127006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9462742805481</t>
+    <t xml:space="preserve">7.68529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99127054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627475738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">8.27024459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37823486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821895599365</t>
+    <t xml:space="preserve">8.37823581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821800231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.75619983673096</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56721878051758</t>
+    <t xml:space="preserve">8.56721782684326</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19824981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11725902557373</t>
+    <t xml:space="preserve">8.19825077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11725997924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922660827637</t>
+    <t xml:space="preserve">8.45922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170127868652</t>
+    <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.9789972305298</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489728927612</t>
+    <t xml:space="preserve">11.2489719390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.1229829788208</t>
@@ -2408,43 +2408,43 @@
     <t xml:space="preserve">11.4829511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4649524688721</t>
+    <t xml:space="preserve">11.4649515151978</t>
   </si>
   <si>
     <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3389654159546</t>
+    <t xml:space="preserve">11.3389644622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749618530273</t>
+    <t xml:space="preserve">11.374960899353</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5009498596191</t>
+    <t xml:space="preserve">11.6089382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349281311035</t>
+    <t xml:space="preserve">11.9689073562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709245681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349271774292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">11.7529268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8069219589233</t>
+    <t xml:space="preserve">11.8429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6198072433472</t>
@@ -2529,9 +2529,6 @@
   </si>
   <si>
     <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.4139814376831</t>
@@ -59929,7 +59926,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59981,7 +59978,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60085,7 +60082,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60111,7 +60108,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60137,7 +60134,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60163,7 +60160,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60215,7 +60212,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60319,7 +60316,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60345,7 +60342,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60371,7 +60368,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60397,7 +60394,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60501,7 +60498,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60527,7 +60524,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60553,7 +60550,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60579,7 +60576,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60605,7 +60602,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60709,7 +60706,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60839,7 +60836,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60865,7 +60862,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60891,7 +60888,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60943,7 +60940,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60969,7 +60966,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61021,7 +61018,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61047,7 +61044,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61073,7 +61070,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61099,7 +61096,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61151,7 +61148,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61203,7 +61200,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61229,7 +61226,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61281,7 +61278,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61307,7 +61304,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61333,7 +61330,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61385,7 +61382,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61411,7 +61408,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61463,7 +61460,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61619,7 +61616,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61723,7 +61720,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61749,7 +61746,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61905,7 +61902,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61931,7 +61928,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61957,7 +61954,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61983,7 +61980,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62009,7 +62006,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62035,7 +62032,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62061,7 +62058,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62087,7 +62084,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62113,7 +62110,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62139,7 +62136,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62165,7 +62162,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62191,7 +62188,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62217,7 +62214,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62243,7 +62240,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62269,7 +62266,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62295,7 +62292,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62321,7 +62318,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62347,7 +62344,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62373,7 +62370,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62399,7 +62396,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62425,7 +62422,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62451,7 +62448,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62477,7 +62474,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62503,7 +62500,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62529,7 +62526,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62555,7 +62552,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62581,7 +62578,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62607,7 +62604,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62633,7 +62630,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62659,7 +62656,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62685,7 +62682,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62711,7 +62708,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62737,7 +62734,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62763,7 +62760,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62789,7 +62786,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62815,7 +62812,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62841,7 +62838,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62867,7 +62864,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62893,7 +62890,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62919,7 +62916,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62945,7 +62942,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62971,7 +62968,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62997,7 +62994,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63023,7 +63020,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63049,7 +63046,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63075,7 +63072,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63101,7 +63098,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63127,7 +63124,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63153,7 +63150,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63179,7 +63176,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63205,7 +63202,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63231,7 +63228,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63257,7 +63254,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63283,7 +63280,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63309,7 +63306,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63335,7 +63332,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63361,7 +63358,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63387,7 +63384,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63413,7 +63410,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63439,7 +63436,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63465,7 +63462,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63491,7 +63488,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63517,7 +63514,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63543,7 +63540,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63569,7 +63566,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63595,7 +63592,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63621,7 +63618,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63647,7 +63644,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63673,7 +63670,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63699,7 +63696,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63725,7 +63722,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63751,7 +63748,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63777,7 +63774,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63803,7 +63800,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63829,7 +63826,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63855,7 +63852,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63881,7 +63878,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63907,7 +63904,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63933,7 +63930,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63959,7 +63956,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63985,7 +63982,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64011,7 +64008,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64037,7 +64034,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64063,7 +64060,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64089,7 +64086,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64115,7 +64112,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64141,7 +64138,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64167,7 +64164,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64193,7 +64190,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64219,7 +64216,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64245,7 +64242,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64271,7 +64268,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64297,7 +64294,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64323,7 +64320,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64349,7 +64346,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64375,7 +64372,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64401,7 +64398,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64427,7 +64424,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64453,7 +64450,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64479,7 +64476,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64505,7 +64502,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64531,7 +64528,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64557,7 +64554,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64583,7 +64580,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64609,7 +64606,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64635,7 +64632,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64661,7 +64658,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64687,7 +64684,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64713,7 +64710,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64739,7 +64736,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64765,7 +64762,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64791,7 +64788,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64817,7 +64814,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64843,7 +64840,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64869,7 +64866,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64895,7 +64892,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64921,7 +64918,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64947,7 +64944,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64973,7 +64970,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64999,7 +64996,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65025,7 +65022,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65051,7 +65048,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65077,7 +65074,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65103,7 +65100,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65129,7 +65126,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65155,7 +65152,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65181,7 +65178,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65207,7 +65204,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65233,7 +65230,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65259,7 +65256,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65285,7 +65282,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65311,7 +65308,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65337,7 +65334,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65363,7 +65360,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65389,7 +65386,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65415,7 +65412,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65441,7 +65438,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65467,7 +65464,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65493,7 +65490,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65519,7 +65516,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65545,7 +65542,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65571,7 +65568,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65597,7 +65594,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65623,7 +65620,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65649,7 +65646,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65675,7 +65672,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65701,7 +65698,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65727,7 +65724,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65753,7 +65750,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65779,7 +65776,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65805,7 +65802,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65831,7 +65828,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65857,7 +65854,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65883,7 +65880,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65909,7 +65906,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65935,7 +65932,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65961,7 +65958,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65987,7 +65984,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66013,7 +66010,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66039,7 +66036,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66065,7 +66062,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66091,7 +66088,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66117,7 +66114,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66143,7 +66140,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66169,7 +66166,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66195,7 +66192,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66221,7 +66218,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66247,7 +66244,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66273,7 +66270,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66299,7 +66296,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66325,7 +66322,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66351,7 +66348,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66377,7 +66374,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66403,7 +66400,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66429,7 +66426,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66455,7 +66452,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66481,7 +66478,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66507,7 +66504,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66533,7 +66530,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66559,7 +66556,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66585,7 +66582,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66611,7 +66608,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66637,7 +66634,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66663,7 +66660,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66689,7 +66686,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66715,7 +66712,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66741,7 +66738,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66767,7 +66764,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66793,7 +66790,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66819,7 +66816,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66845,7 +66842,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66871,7 +66868,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66897,7 +66894,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66923,7 +66920,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66949,7 +66946,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66975,7 +66972,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67001,7 +66998,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67027,7 +67024,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67053,7 +67050,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67079,7 +67076,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67105,7 +67102,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67131,7 +67128,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67157,7 +67154,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67183,7 +67180,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67209,7 +67206,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67235,7 +67232,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67261,7 +67258,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67287,7 +67284,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67313,7 +67310,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67339,7 +67336,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67365,7 +67362,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67391,7 +67388,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67417,7 +67414,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67443,7 +67440,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67469,7 +67466,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67495,7 +67492,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67521,7 +67518,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67547,7 +67544,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67573,7 +67570,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67599,7 +67596,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67625,7 +67622,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67651,7 +67648,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67677,7 +67674,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67703,7 +67700,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67729,7 +67726,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67755,7 +67752,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67781,7 +67778,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67807,7 +67804,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67833,7 +67830,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67859,7 +67856,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67885,7 +67882,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67911,7 +67908,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67937,7 +67934,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67963,7 +67960,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67989,7 +67986,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68015,7 +68012,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68041,7 +68038,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68067,7 +68064,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68093,7 +68090,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68119,7 +68116,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68145,7 +68142,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68171,7 +68168,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68197,7 +68194,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2489" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68223,7 +68220,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2490" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68249,7 +68246,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2491" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68275,7 +68272,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2492" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68301,7 +68298,7 @@
         <v>17.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68327,7 +68324,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2494" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68353,7 +68350,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2495" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68379,7 +68376,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2496" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68405,7 +68402,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2497" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68431,7 +68428,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2498" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68457,7 +68454,7 @@
         <v>17</v>
       </c>
       <c r="G2499" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68483,7 +68480,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2500" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68509,7 +68506,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2501" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68535,7 +68532,7 @@
         <v>17</v>
       </c>
       <c r="G2502" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68561,7 +68558,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2503" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68587,7 +68584,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2504" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68613,7 +68610,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2505" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68639,7 +68636,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2506" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68665,7 +68662,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2507" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68691,7 +68688,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68717,7 +68714,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2509" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68743,7 +68740,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2510" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68769,7 +68766,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G2511" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68795,7 +68792,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2512" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68821,7 +68818,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G2513" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68829,7 +68826,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6910648148</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>53617</v>
@@ -68847,9 +68844,35 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6909722222</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>74884</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>15.5799999237061</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>14.8599996566772</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>15.4399995803833</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>985</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="1048">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,115 +44,115 @@
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394567489624</t>
+    <t xml:space="preserve">7.16394424438477</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571666717529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061637878418</t>
+    <t xml:space="preserve">7.0728006362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925912857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061542510986</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14207029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
+    <t xml:space="preserve">7.14207077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717782974243</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144290924072</t>
+    <t xml:space="preserve">7.25144338607788</t>
   </si>
   <si>
     <t xml:space="preserve">7.27696418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36446285247803</t>
+    <t xml:space="preserve">7.3644642829895</t>
   </si>
   <si>
     <t xml:space="preserve">7.29154682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32800579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238107681274</t>
+    <t xml:space="preserve">7.32800483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2623815536499</t>
   </si>
   <si>
     <t xml:space="preserve">7.40821218490601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39362859725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4373779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.284255027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029253005981</t>
+    <t xml:space="preserve">7.39362955093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029348373413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341686248779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154052734375</t>
+    <t xml:space="preserve">7.64154243469238</t>
   </si>
   <si>
     <t xml:space="preserve">7.48841953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48112821578979</t>
+    <t xml:space="preserve">7.48112726211548</t>
   </si>
   <si>
     <t xml:space="preserve">7.30613136291504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6196665763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34988117218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2988395690918</t>
+    <t xml:space="preserve">7.61966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5321683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25508832931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34988021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29884004592896</t>
   </si>
   <si>
     <t xml:space="preserve">7.25873517990112</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">7.2477970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21498727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769548416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99624061584473</t>
+    <t xml:space="preserve">7.21498775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99624013900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.97801113128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383546829224</t>
+    <t xml:space="preserve">7.52487659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383594512939</t>
   </si>
   <si>
     <t xml:space="preserve">7.20404863357544</t>
@@ -194,352 +194,352 @@
     <t xml:space="preserve">7.38633680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50300216674805</t>
+    <t xml:space="preserve">7.50300407409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.56133460998535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58320951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445655822754</t>
+    <t xml:space="preserve">7.58320808410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445560455322</t>
   </si>
   <si>
     <t xml:space="preserve">7.72904062271118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87487268447876</t>
+    <t xml:space="preserve">7.87487125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1802225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774494171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88030576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782724380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781240463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98527574539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530038833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06025505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4398717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990528106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9974946975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10996246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69757747650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59260749816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81004619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79505062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64509201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3676700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61509990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5476188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265773773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87002944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67508411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51762771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51013088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3601713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31518459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3001880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1727237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20271492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21021366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11273956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09024715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08274936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2252082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1202392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00777053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76783609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82782077789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16522598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93278932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529296875</t>
   </si>
   <si>
     <t xml:space="preserve">7.94778680801392</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03528594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424386978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273262023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18022155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88030576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782819747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787843704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64786958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98527574539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8953013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06025505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84003829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13245677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98249816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9974946975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10996246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69757843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59260749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81004524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72756862640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7950496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64509296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6900806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3676700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61510181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54761791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265678405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87003040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67508316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51762866973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5101318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3601713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31518268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766025543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30018901824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21021270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1127405166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09024620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08274745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1277379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777843475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22520923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12023830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00776958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82781934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780498504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.760338306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531761169434</t>
+    <t xml:space="preserve">7.87280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033926010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531713485718</t>
   </si>
   <si>
     <t xml:space="preserve">8.09667873382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78823375701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967908859253</t>
+    <t xml:space="preserve">7.78823328018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956992149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967813491821</t>
   </si>
   <si>
     <t xml:space="preserve">8.01956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98101139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90389966964722</t>
+    <t xml:space="preserve">7.98101186752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
   </si>
   <si>
     <t xml:space="preserve">7.86534452438354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21234512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678890228271</t>
+    <t xml:space="preserve">8.2123441696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678937911987</t>
   </si>
   <si>
     <t xml:space="preserve">7.71112203598022</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">7.51063299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147720336914</t>
+    <t xml:space="preserve">7.61858797073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147815704346</t>
   </si>
   <si>
     <t xml:space="preserve">7.47978830337524</t>
@@ -566,67 +566,67 @@
     <t xml:space="preserve">7.32556676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41809940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21760988235474</t>
+    <t xml:space="preserve">7.41809844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761035919189</t>
   </si>
   <si>
     <t xml:space="preserve">7.03254365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23303174972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845600128174</t>
+    <t xml:space="preserve">7.23303365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845552444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.26387786865234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12507724761963</t>
+    <t xml:space="preserve">7.12507677078247</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17134428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218896865845</t>
+    <t xml:space="preserve">7.17134475708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218849182129</t>
   </si>
   <si>
     <t xml:space="preserve">7.10965585708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14049863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07881164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.310142993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169992446899</t>
+    <t xml:space="preserve">7.14049911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472255706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169944763184</t>
   </si>
   <si>
     <t xml:space="preserve">6.90916538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83205366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458868026733</t>
+    <t xml:space="preserve">6.83205461502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458772659302</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409868240356</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0171217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578853607178</t>
+    <t xml:space="preserve">6.86289978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578805923462</t>
   </si>
   <si>
     <t xml:space="preserve">6.94001007080078</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">6.95543241500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98627662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67783260345459</t>
+    <t xml:space="preserve">6.98627710342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67783164978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086763381958</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">6.6315655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47734260559082</t>
+    <t xml:space="preserve">6.4773416519165</t>
   </si>
   <si>
     <t xml:space="preserve">6.46192073822021</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">6.61614274978638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974231719971</t>
+    <t xml:space="preserve">6.52361011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974279403687</t>
   </si>
   <si>
     <t xml:space="preserve">6.23058700561523</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">6.2614312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27685451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5698766708374</t>
+    <t xml:space="preserve">6.27685356140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56987714767456</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227542877197</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">6.41565370559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5544548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663274765015</t>
+    <t xml:space="preserve">6.55445432662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.89374303817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6469874382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036476135254</t>
+    <t xml:space="preserve">6.64698839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77036571502686</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720872879028</t>
+    <t xml:space="preserve">6.10720920562744</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889810562134</t>
@@ -731,85 +731,85 @@
     <t xml:space="preserve">6.09178686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30769872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99925374984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.246009349823</t>
+    <t xml:space="preserve">6.30769920349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99925327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24600982666016</t>
   </si>
   <si>
     <t xml:space="preserve">6.66240978240967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396528244019</t>
+    <t xml:space="preserve">6.49276542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396480560303</t>
   </si>
   <si>
     <t xml:space="preserve">6.44649791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21516466140747</t>
+    <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
     <t xml:space="preserve">6.36938762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085523605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796552658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592241287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">6.75494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
     <t xml:space="preserve">7.20115089416504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64106130599976</t>
+    <t xml:space="preserve">7.15314340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0731315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106178283691</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912046432495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913278579712</t>
+    <t xml:space="preserve">7.08913326263428</t>
   </si>
   <si>
     <t xml:space="preserve">7.12113809585571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83309173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508377075195</t>
+    <t xml:space="preserve">6.83309268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8650975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508472442627</t>
   </si>
   <si>
     <t xml:space="preserve">6.75307893753052</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4810357093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504632949829</t>
+    <t xml:space="preserve">6.48103618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504680633545</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905647277832</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710283279419</t>
+    <t xml:space="preserve">6.80108737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710235595703</t>
   </si>
   <si>
     <t xml:space="preserve">6.81709003448486</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59305429458618</t>
+    <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
     <t xml:space="preserve">6.62505912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57705116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51304149627686</t>
+    <t xml:space="preserve">6.57705211639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
     <t xml:space="preserve">6.44903087615967</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">6.40102338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33701276779175</t>
+    <t xml:space="preserve">6.33701372146606</t>
   </si>
   <si>
     <t xml:space="preserve">6.22499513626099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08097124099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04896640777588</t>
+    <t xml:space="preserve">6.08097219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0489673614502</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496953964233</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">6.09697484970093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1609845161438</t>
+    <t xml:space="preserve">6.16098499298096</t>
   </si>
   <si>
     <t xml:space="preserve">6.0009593963623</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">5.95295190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01696157455444</t>
+    <t xml:space="preserve">6.0169620513916</t>
   </si>
   <si>
     <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92094612121582</t>
+    <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.76092100143433</t>
@@ -923,40 +923,40 @@
     <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82493114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293863296509</t>
+    <t xml:space="preserve">5.82493162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494394302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293910980225</t>
   </si>
   <si>
     <t xml:space="preserve">5.79292583465576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98495674133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11297655105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24099779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32101106643677</t>
+    <t xml:space="preserve">5.98495626449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11297702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24099826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32101058959961</t>
   </si>
   <si>
     <t xml:space="preserve">6.27300310134888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20899248123169</t>
+    <t xml:space="preserve">6.20899295806885</t>
   </si>
   <si>
     <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38502025604248</t>
+    <t xml:space="preserve">6.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1449818611145</t>
+    <t xml:space="preserve">6.14498233795166</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30500793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93694925308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03296422958374</t>
+    <t xml:space="preserve">6.30500841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93694877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0329647064209</t>
   </si>
   <si>
     <t xml:space="preserve">5.61689805984497</t>
@@ -992,58 +992,58 @@
     <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50488042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36085653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081861495972</t>
+    <t xml:space="preserve">5.39286184310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3608570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081909179688</t>
   </si>
   <si>
     <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67274713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24067783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062711715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28868532180786</t>
+    <t xml:space="preserve">4.6727466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24067831039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9206268787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
     <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16066455841064</t>
+    <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40070295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72075462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92878818511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13682079315186</t>
+    <t xml:space="preserve">4.40070343017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72075414657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92878770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13682126998901</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
@@ -1052,46 +1052,46 @@
     <t xml:space="preserve">5.40886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3288516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3128490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18482828140259</t>
+    <t xml:space="preserve">5.32885217666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31284952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18482875823975</t>
   </si>
   <si>
     <t xml:space="preserve">5.00880098342896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16882610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28084421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05680799484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283672332764</t>
+    <t xml:space="preserve">5.16882658004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28084468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05680847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283624649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64890289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77692270278931</t>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64890241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77692317962646</t>
   </si>
   <si>
     <t xml:space="preserve">5.69691038131714</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489227294922</t>
+    <t xml:space="preserve">5.58489274978638</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486763000488</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">5.44086980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484107971191</t>
+    <t xml:space="preserve">5.37685966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484203338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24883937835693</t>
@@ -1133,121 +1133,121 @@
     <t xml:space="preserve">5.29684686660767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683359146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35301542282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49703884124756</t>
+    <t xml:space="preserve">5.21683406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3530158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28900623321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4970383644104</t>
   </si>
   <si>
     <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516199111938</t>
+    <t xml:space="preserve">6.67306709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915933609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516151428223</t>
   </si>
   <si>
     <t xml:space="preserve">7.28116416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64922285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121536254883</t>
+    <t xml:space="preserve">7.64922380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
     <t xml:space="preserve">7.5212025642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53720569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118976593018</t>
+    <t xml:space="preserve">7.5372052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319555282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44119024276733</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719194412231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40918350219727</t>
+    <t xml:space="preserve">7.40918445587158</t>
   </si>
   <si>
     <t xml:space="preserve">7.39318180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316804885864</t>
+    <t xml:space="preserve">7.23315668106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316995620728</t>
   </si>
   <si>
     <t xml:space="preserve">7.42518758773804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519847869873</t>
+    <t xml:space="preserve">7.50519990921021</t>
   </si>
   <si>
     <t xml:space="preserve">7.36117649078369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29716682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526390075684</t>
+    <t xml:space="preserve">7.2971658706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526342391968</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04128646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93726778030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8732590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327043533325</t>
+    <t xml:space="preserve">8.04128551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126607894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327138900757</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96927452087402</t>
+    <t xml:space="preserve">7.96927404403687</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132438659668</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">8.40134334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4413480758667</t>
+    <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.72139358520508</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141445159912</t>
+    <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
     <t xml:space="preserve">9.12145709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0414457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4815149307251</t>
+    <t xml:space="preserve">9.04144477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9614315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3216505050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3218097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2017908096313</t>
+    <t xml:space="preserve">10.3216495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217140197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3218088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.201789855957</t>
   </si>
   <si>
     <t xml:space="preserve">11.1217775344849</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8417339324951</t>
+    <t xml:space="preserve">11.1617841720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8417320251465</t>
   </si>
   <si>
     <t xml:space="preserve">10.881739616394</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417974472046</t>
+    <t xml:space="preserve">11.2417964935303</t>
   </si>
   <si>
     <t xml:space="preserve">11.0817718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7617206573486</t>
+    <t xml:space="preserve">10.76171875</t>
   </si>
   <si>
     <t xml:space="preserve">11.0017585754395</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6016941070557</t>
+    <t xml:space="preserve">10.60169506073</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6965761184692</t>
+    <t xml:space="preserve">11.6965751647949</t>
   </si>
   <si>
     <t xml:space="preserve">11.1573715209961</t>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374879837036</t>
+    <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.1204404830933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1619186401367</t>
+    <t xml:space="preserve">10.1619176864624</t>
   </si>
   <si>
     <t xml:space="preserve">10.0789632797241</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305541992188</t>
+    <t xml:space="preserve">9.99600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305637359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4107828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.327826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.742600440979</t>
+    <t xml:space="preserve">10.4107818603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3278274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7425994873047</t>
   </si>
   <si>
     <t xml:space="preserve">10.825553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5766897201538</t>
+    <t xml:space="preserve">10.5766906738281</t>
   </si>
   <si>
     <t xml:space="preserve">10.8670310974121</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">10.6181678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3693037033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
     <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87157726287842</t>
+    <t xml:space="preserve">9.87157917022705</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522590637207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9499864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840766906738</t>
+    <t xml:space="preserve">10.9499855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840757369995</t>
   </si>
   <si>
     <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085092544556</t>
+    <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">10.6596460342407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4891891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2403268814087</t>
+    <t xml:space="preserve">11.0329399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4891901016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2403249740601</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
@@ -1472,25 +1472,25 @@
     <t xml:space="preserve">12.2772569656372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3602113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3187351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261211395264</t>
+    <t xml:space="preserve">12.3602104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6505517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3187341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261201858521</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8164596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2727108001709</t>
+    <t xml:space="preserve">12.816460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
     <t xml:space="preserve">13.5630512237549</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">13.3141860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3556652069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0193004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.189754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8994140625</t>
+    <t xml:space="preserve">13.3556642532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0192995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1897554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846439361572</t>
+    <t xml:space="preserve">12.4846429824829</t>
   </si>
   <si>
     <t xml:space="preserve">12.0283937454224</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">11.4062347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8210077285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988496780396</t>
+    <t xml:space="preserve">11.8210067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988487243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">9.74714660644531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8624849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6136207580566</t>
+    <t xml:space="preserve">11.8624839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">11.0661220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177143096924</t>
+    <t xml:space="preserve">10.7177133560181</t>
   </si>
   <si>
     <t xml:space="preserve">10.9665765762329</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6347589492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504409790039</t>
+    <t xml:space="preserve">10.651349067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6347579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504390716553</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168043136597</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">10.9002141952515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8172588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7674856185913</t>
+    <t xml:space="preserve">10.8172578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.767484664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849857330322</t>
+    <t xml:space="preserve">10.8338489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3313932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866161346436</t>
+    <t xml:space="preserve">11.4693689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313913345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866170883179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2454919815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109975814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2282466888428</t>
+    <t xml:space="preserve">12.2454929351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109966278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2282457351685</t>
   </si>
   <si>
     <t xml:space="preserve">12.1592569351196</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7794818878174</t>
+    <t xml:space="preserve">10.7794828414917</t>
   </si>
   <si>
     <t xml:space="preserve">10.6932468414307</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">11.0036954879761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1589193344116</t>
+    <t xml:space="preserve">11.1589202880859</t>
   </si>
   <si>
     <t xml:space="preserve">11.7625713348389</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">11.3831338882446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9522886276245</t>
+    <t xml:space="preserve">11.9522905349731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280769348145</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453241348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.69358253479</t>
+    <t xml:space="preserve">11.7453231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6935834884644</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">11.8660545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2627391815186</t>
+    <t xml:space="preserve">12.2627401351929</t>
   </si>
   <si>
     <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177961349487</t>
+    <t xml:space="preserve">11.9177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3144798278809</t>
+    <t xml:space="preserve">12.3144807815552</t>
   </si>
   <si>
     <t xml:space="preserve">12.3317279815674</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695386886597</t>
+    <t xml:space="preserve">11.9695377349854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1075143814087</t>
+    <t xml:space="preserve">12.107515335083</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970657348633</t>
+    <t xml:space="preserve">11.7970666885376</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
@@ -1766,43 +1766,43 @@
     <t xml:space="preserve">11.607346534729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.245156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3658857345581</t>
+    <t xml:space="preserve">11.5556058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2451572418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3658876419067</t>
   </si>
   <si>
     <t xml:space="preserve">11.521110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5901002883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6418418884277</t>
+    <t xml:space="preserve">11.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6418409347534</t>
   </si>
   <si>
     <t xml:space="preserve">11.4348754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0381898880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.107177734375</t>
+    <t xml:space="preserve">11.0381908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1071786880493</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209426879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1244258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.141674041748</t>
+    <t xml:space="preserve">11.1244249343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3483028411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3655500411987</t>
+    <t xml:space="preserve">10.5207748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3483037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3310565948486</t>
+    <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
     <t xml:space="preserve">10.1930780410767</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">11.5383586883545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6245927810669</t>
+    <t xml:space="preserve">11.6245937347412</t>
   </si>
   <si>
     <t xml:space="preserve">11.4176273345947</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
+    <t xml:space="preserve">12.4007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">12.3662223815918</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869527816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.573187828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6421766281128</t>
+    <t xml:space="preserve">12.4869518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6421775817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5214471817017</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2799863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4352121353149</t>
+    <t xml:space="preserve">12.2799854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4352111816406</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798185348511</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2624044418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2796506881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141441345215</t>
+    <t xml:space="preserve">11.4521217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2624034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2796497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141450881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0899314880371</t>
+    <t xml:space="preserve">11.0899324417114</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554370880127</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657188415527</t>
+    <t xml:space="preserve">10.9347076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657178878784</t>
   </si>
   <si>
     <t xml:space="preserve">10.7622356414795</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4517860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4000453948975</t>
+    <t xml:space="preserve">10.4517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.469033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4000444412231</t>
   </si>
   <si>
     <t xml:space="preserve">10.277060508728</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">10.2590627670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3850517272949</t>
+    <t xml:space="preserve">10.3850507736206</t>
   </si>
   <si>
     <t xml:space="preserve">10.4930419921875</t>
@@ -1976,10 +1976,7 @@
     <t xml:space="preserve">10.6190299987793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3310556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.043083190918</t>
+    <t xml:space="preserve">10.0430822372437</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
@@ -1991,16 +1988,16 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89909648895264</t>
+    <t xml:space="preserve">9.93509292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.187068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89909553527832</t>
   </si>
   <si>
     <t xml:space="preserve">9.95309066772461</t>
@@ -2012,16 +2009,16 @@
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790786743164</t>
+    <t xml:space="preserve">10.0790796279907</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">10.1510725021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2033,16 +2030,16 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210472106934</t>
+    <t xml:space="preserve">10.4210481643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3130588531494</t>
+    <t xml:space="preserve">10.4030494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3130578994751</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950592041016</t>
@@ -2054,19 +2051,19 @@
     <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70111465454102</t>
+    <t xml:space="preserve">9.79110527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7011137008667</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41313934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17916202545166</t>
+    <t xml:space="preserve">9.41314029693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
@@ -2081,13 +2078,13 @@
     <t xml:space="preserve">9.53912830352783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37714385986328</t>
+    <t xml:space="preserve">9.37714290618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.35914516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32314777374268</t>
+    <t xml:space="preserve">9.32314872741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.25115489959717</t>
@@ -2105,13 +2102,13 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318897247314</t>
+    <t xml:space="preserve">8.87318992614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97218036651611</t>
+    <t xml:space="preserve">8.97218132019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2123,37 +2120,37 @@
     <t xml:space="preserve">8.47722625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62121200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63921165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63021087646484</t>
+    <t xml:space="preserve">8.62121295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63021183013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60321426391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123729705811</t>
+    <t xml:space="preserve">8.60321521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123634338379</t>
   </si>
   <si>
     <t xml:space="preserve">8.20725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90127801895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09925937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04526519775391</t>
+    <t xml:space="preserve">7.90127754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0992603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04526424407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.05426406860352</t>
@@ -2162,10 +2159,10 @@
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91027784347534</t>
+    <t xml:space="preserve">7.96427249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91027736663818</t>
   </si>
   <si>
     <t xml:space="preserve">7.81128692626953</t>
@@ -2174,31 +2171,31 @@
     <t xml:space="preserve">7.89227962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97327089309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828401565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927576065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428888320923</t>
+    <t xml:space="preserve">7.97327184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828449249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428840637207</t>
   </si>
   <si>
     <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64930152893066</t>
+    <t xml:space="preserve">7.64930200576782</t>
   </si>
   <si>
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533073425293</t>
+    <t xml:space="preserve">7.63130283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
     <t xml:space="preserve">7.19934272766113</t>
@@ -2219,7 +2216,7 @@
     <t xml:space="preserve">6.69538831710815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74038410186768</t>
+    <t xml:space="preserve">6.74038362503052</t>
   </si>
   <si>
     <t xml:space="preserve">6.77638101577759</t>
@@ -2231,37 +2228,37 @@
     <t xml:space="preserve">6.95636463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19034242630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16334581375122</t>
+    <t xml:space="preserve">7.19034290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16334533691406</t>
   </si>
   <si>
     <t xml:space="preserve">7.10935068130493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25333738327026</t>
+    <t xml:space="preserve">7.25333786010742</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42432165145874</t>
+    <t xml:space="preserve">7.4243221282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.5143141746521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46931838989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28933429718018</t>
+    <t xml:space="preserve">7.49631547927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733203887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46931791305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28933477401733</t>
   </si>
   <si>
     <t xml:space="preserve">7.28033494949341</t>
@@ -2279,7 +2276,7 @@
     <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05535554885864</t>
+    <t xml:space="preserve">7.0553560256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.06435441970825</t>
@@ -2288,7 +2285,7 @@
     <t xml:space="preserve">7.68529796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99127006530762</t>
+    <t xml:space="preserve">7.99126958847046</t>
   </si>
   <si>
     <t xml:space="preserve">7.92827606201172</t>
@@ -2303,19 +2300,19 @@
     <t xml:space="preserve">8.27024364471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37823581695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821800231934</t>
+    <t xml:space="preserve">8.37823486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821895599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.75619888305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66620826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74720191955566</t>
+    <t xml:space="preserve">8.66620922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.56721782684326</t>
@@ -2327,7 +2324,7 @@
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923503875732</t>
+    <t xml:space="preserve">8.36923599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
@@ -2336,10 +2333,10 @@
     <t xml:space="preserve">8.19825077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06326389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11725902557373</t>
+    <t xml:space="preserve">8.06326293945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11725997924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2348,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922660827637</t>
+    <t xml:space="preserve">8.45922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2366,16 +2363,16 @@
     <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9789962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8350105285645</t>
+    <t xml:space="preserve">10.9789972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8350114822388</t>
   </si>
   <si>
     <t xml:space="preserve">10.6370277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.90700340271</t>
+    <t xml:space="preserve">10.9070043563843</t>
   </si>
   <si>
     <t xml:space="preserve">10.6010313034058</t>
@@ -2390,16 +2387,16 @@
     <t xml:space="preserve">10.7990131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6730241775513</t>
+    <t xml:space="preserve">10.6730251312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1229839324951</t>
+    <t xml:space="preserve">11.2489728927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1229829788208</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2423,7 +2420,7 @@
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374960899353</t>
+    <t xml:space="preserve">11.3749618530273</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
@@ -2438,28 +2435,28 @@
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689073562622</t>
+    <t xml:space="preserve">11.9689064025879</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709245681763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249206542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349281311035</t>
+    <t xml:space="preserve">11.8249197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349290847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529277801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.806921005249</t>
+    <t xml:space="preserve">11.7529268264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429174423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8069219589233</t>
   </si>
   <si>
     <t xml:space="preserve">11.6198072433472</t>
@@ -2532,9 +2529,6 @@
   </si>
   <si>
     <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8069219589233</t>
   </si>
   <si>
     <t xml:space="preserve">11.4139804840088</t>
@@ -16804,7 +16798,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16830,7 +16824,7 @@
         <v>10.5</v>
       </c>
       <c r="G513" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16856,7 +16850,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G514" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16882,7 +16876,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G515" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16908,7 +16902,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G516" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16960,7 +16954,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G518" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17116,7 +17110,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G524" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17142,7 +17136,7 @@
         <v>10.5</v>
       </c>
       <c r="G525" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17168,7 +17162,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G526" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17766,7 +17760,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G549" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17896,7 +17890,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G554" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17922,7 +17916,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18000,7 +17994,7 @@
         <v>10.5</v>
       </c>
       <c r="G558" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18026,7 +18020,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18078,7 +18072,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18104,7 +18098,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G562" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18130,7 +18124,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G563" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18156,7 +18150,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G564" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18208,7 +18202,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G566" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18260,7 +18254,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18390,7 +18384,7 @@
         <v>10.5</v>
       </c>
       <c r="G573" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18442,7 +18436,7 @@
         <v>10.5</v>
       </c>
       <c r="G575" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18468,7 +18462,7 @@
         <v>10.5</v>
       </c>
       <c r="G576" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18494,7 +18488,7 @@
         <v>10.5</v>
       </c>
       <c r="G577" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19040,7 +19034,7 @@
         <v>10.5</v>
       </c>
       <c r="G598" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19066,7 +19060,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19092,7 +19086,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G600" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19118,7 +19112,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19144,7 +19138,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G602" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19170,7 +19164,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G603" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19196,7 +19190,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19222,7 +19216,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G605" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19248,7 +19242,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G606" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19274,7 +19268,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G607" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19300,7 +19294,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G608" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19326,7 +19320,7 @@
         <v>10.5</v>
       </c>
       <c r="G609" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19352,7 +19346,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19378,7 +19372,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G611" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19430,7 +19424,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19456,7 +19450,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G614" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19534,7 +19528,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19560,7 +19554,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19742,7 +19736,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19768,7 +19762,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19794,7 +19788,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G627" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19820,7 +19814,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G628" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19846,7 +19840,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20132,7 +20126,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G640" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20210,7 +20204,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -52398,7 +52392,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1881" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52424,7 +52418,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1882" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52450,7 +52444,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1883" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52476,7 +52470,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52528,7 +52522,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1886" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52554,7 +52548,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1887" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52580,7 +52574,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1888" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52606,7 +52600,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1889" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52632,7 +52626,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1890" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52658,7 +52652,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1891" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52684,7 +52678,7 @@
         <v>11</v>
       </c>
       <c r="G1892" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52710,7 +52704,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1893" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52736,7 +52730,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1894" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52762,7 +52756,7 @@
         <v>11</v>
       </c>
       <c r="G1895" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52788,7 +52782,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1896" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52814,7 +52808,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52840,7 +52834,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52866,7 +52860,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1899" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52892,7 +52886,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1900" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52918,7 +52912,7 @@
         <v>11</v>
       </c>
       <c r="G1901" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52944,7 +52938,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1902" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52970,7 +52964,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1903" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52996,7 +52990,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1904" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53022,7 +53016,7 @@
         <v>11.5</v>
       </c>
       <c r="G1905" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53048,7 +53042,7 @@
         <v>11.5</v>
       </c>
       <c r="G1906" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53074,7 +53068,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1907" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53126,7 +53120,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1909" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53152,7 +53146,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53178,7 +53172,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1911" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53204,7 +53198,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1912" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53230,7 +53224,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1913" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53256,7 +53250,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53282,7 +53276,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53308,7 +53302,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1916" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53360,7 +53354,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53386,7 +53380,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1919" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53412,7 +53406,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1920" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53438,7 +53432,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1921" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53464,7 +53458,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53490,7 +53484,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1923" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53516,7 +53510,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1924" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53542,7 +53536,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1925" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53568,7 +53562,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1926" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53594,7 +53588,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1927" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53620,7 +53614,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53646,7 +53640,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1929" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53672,7 +53666,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1930" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53698,7 +53692,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53724,7 +53718,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1932" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53750,7 +53744,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1933" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53776,7 +53770,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1934" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53802,7 +53796,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1935" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53828,7 +53822,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1936" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53854,7 +53848,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1937" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53880,7 +53874,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1938" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53906,7 +53900,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53932,7 +53926,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1940" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53958,7 +53952,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1941" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53984,7 +53978,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1942" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54010,7 +54004,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1943" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54036,7 +54030,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54062,7 +54056,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1945" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54088,7 +54082,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1946" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54114,7 +54108,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1947" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54140,7 +54134,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1948" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54166,7 +54160,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54192,7 +54186,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1950" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54218,7 +54212,7 @@
         <v>10</v>
       </c>
       <c r="G1951" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54244,7 +54238,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1952" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54270,7 +54264,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1953" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54296,7 +54290,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1954" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54322,7 +54316,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1955" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54348,7 +54342,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1956" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54374,7 +54368,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54400,7 +54394,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54426,7 +54420,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1959" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54452,7 +54446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1960" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54478,7 +54472,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1961" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54504,7 +54498,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1962" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54530,7 +54524,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54556,7 +54550,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1964" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54582,7 +54576,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1965" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54608,7 +54602,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1966" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54634,7 +54628,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1967" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54660,7 +54654,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54686,7 +54680,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54712,7 +54706,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54738,7 +54732,7 @@
         <v>9</v>
       </c>
       <c r="G1971" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54764,7 +54758,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1972" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54790,7 +54784,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54816,7 +54810,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1974" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54842,7 +54836,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1975" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54868,7 +54862,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54894,7 +54888,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1977" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54920,7 +54914,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1978" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54946,7 +54940,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1979" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54972,7 +54966,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54998,7 +54992,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1981" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55024,7 +55018,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1982" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55050,7 +55044,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55076,7 +55070,7 @@
         <v>8.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55102,7 +55096,7 @@
         <v>8.5</v>
       </c>
       <c r="G1985" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55128,7 +55122,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1986" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55154,7 +55148,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1987" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55180,7 +55174,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1988" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55206,7 +55200,7 @@
         <v>8</v>
       </c>
       <c r="G1989" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55232,7 +55226,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55258,7 +55252,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55284,7 +55278,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55310,7 +55304,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1993" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55336,7 +55330,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1994" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55362,7 +55356,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1995" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55388,7 +55382,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1996" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55414,7 +55408,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1997" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55440,7 +55434,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55466,7 +55460,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1999" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55492,7 +55486,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55518,7 +55512,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2001" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55544,7 +55538,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2002" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55570,7 +55564,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2003" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55596,7 +55590,7 @@
         <v>8.25</v>
       </c>
       <c r="G2004" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55622,7 +55616,7 @@
         <v>8.5</v>
       </c>
       <c r="G2005" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55648,7 +55642,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2006" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55674,7 +55668,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2007" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55700,7 +55694,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55726,7 +55720,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2009" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55752,7 +55746,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2010" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55778,7 +55772,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2011" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55804,7 +55798,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G2012" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55830,7 +55824,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2013" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55856,7 +55850,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55882,7 +55876,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2015" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55908,7 +55902,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2016" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55934,7 +55928,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2017" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55960,7 +55954,7 @@
         <v>8</v>
       </c>
       <c r="G2018" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55986,7 +55980,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2019" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56012,7 +56006,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2020" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56038,7 +56032,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2021" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56064,7 +56058,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2022" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56090,7 +56084,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2023" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56116,7 +56110,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56142,7 +56136,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2025" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56168,7 +56162,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56194,7 +56188,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56220,7 +56214,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2028" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56246,7 +56240,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2029" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56272,7 +56266,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56298,7 +56292,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2031" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56324,7 +56318,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2032" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56350,7 +56344,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2033" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56376,7 +56370,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2034" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56402,7 +56396,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2035" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56428,7 +56422,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2036" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56454,7 +56448,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2037" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56480,7 +56474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56506,7 +56500,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56532,7 +56526,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2040" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56558,7 +56552,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2041" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56584,7 +56578,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2042" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56610,7 +56604,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2043" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56636,7 +56630,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2044" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56662,7 +56656,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2045" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56688,7 +56682,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2046" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56714,7 +56708,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2047" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56740,7 +56734,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2048" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56766,7 +56760,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2049" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56792,7 +56786,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56818,7 +56812,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2051" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56844,7 +56838,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56870,7 +56864,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2053" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56896,7 +56890,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2054" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56922,7 +56916,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56948,7 +56942,7 @@
         <v>9</v>
       </c>
       <c r="G2056" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56974,7 +56968,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2057" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57000,7 +56994,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2058" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57026,7 +57020,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2059" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57052,7 +57046,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2060" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57078,7 +57072,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2061" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57104,7 +57098,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2062" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57130,7 +57124,7 @@
         <v>9.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57156,7 +57150,7 @@
         <v>9.5</v>
       </c>
       <c r="G2064" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57182,7 +57176,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2065" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57208,7 +57202,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2066" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57234,7 +57228,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2067" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57260,7 +57254,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57286,7 +57280,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2069" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57312,7 +57306,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2070" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57338,7 +57332,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2071" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57364,7 +57358,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2072" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57390,7 +57384,7 @@
         <v>11</v>
       </c>
       <c r="G2073" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57416,7 +57410,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2074" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57442,7 +57436,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2075" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57468,7 +57462,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2076" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57494,7 +57488,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2077" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57546,7 +57540,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2079" t="s">
-        <v>654</v>
+        <v>605</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57572,7 +57566,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2080" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57598,7 +57592,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2081" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57624,7 +57618,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2082" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57650,7 +57644,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2083" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57676,7 +57670,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57702,7 +57696,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2085" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57728,7 +57722,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57754,7 +57748,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57806,7 +57800,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2089" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57832,7 +57826,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57858,7 +57852,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2091" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57910,7 +57904,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2093" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57936,7 +57930,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57962,7 +57956,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2095" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58014,7 +58008,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2097" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58040,7 +58034,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2098" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58066,7 +58060,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2099" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58092,7 +58086,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2100" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58118,7 +58112,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2101" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58144,7 +58138,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2102" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58170,7 +58164,7 @@
         <v>12</v>
       </c>
       <c r="G2103" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58196,7 +58190,7 @@
         <v>12</v>
       </c>
       <c r="G2104" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58222,7 +58216,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2105" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58248,7 +58242,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2106" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58274,7 +58268,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2107" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58300,7 +58294,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2108" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58326,7 +58320,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2109" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58352,7 +58346,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2110" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58378,7 +58372,7 @@
         <v>12.5</v>
       </c>
       <c r="G2111" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58404,7 +58398,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2112" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58430,7 +58424,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58456,7 +58450,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58482,7 +58476,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58508,7 +58502,7 @@
         <v>12.5</v>
       </c>
       <c r="G2116" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58534,7 +58528,7 @@
         <v>12.5</v>
       </c>
       <c r="G2117" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58560,7 +58554,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2118" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58586,7 +58580,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2119" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58612,7 +58606,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2120" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58638,7 +58632,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2121" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58664,7 +58658,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58690,7 +58684,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2123" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58716,7 +58710,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2124" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58742,7 +58736,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2125" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58768,7 +58762,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2126" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58794,7 +58788,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58820,7 +58814,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G2128" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58846,7 +58840,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2129" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58872,7 +58866,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2130" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58898,7 +58892,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2131" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58924,7 +58918,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2132" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58950,7 +58944,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2133" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58976,7 +58970,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59002,7 +58996,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2135" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59028,7 +59022,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2136" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59054,7 +59048,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G2137" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59080,7 +59074,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2138" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59106,7 +59100,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2139" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59132,7 +59126,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59158,7 +59152,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2141" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59184,7 +59178,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2142" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59210,7 +59204,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59236,7 +59230,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2144" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59262,7 +59256,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2145" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59288,7 +59282,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2146" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59314,7 +59308,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2147" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59340,7 +59334,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2148" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59366,7 +59360,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2149" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59392,7 +59386,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2150" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59418,7 +59412,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59444,7 +59438,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59470,7 +59464,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2153" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59496,7 +59490,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59522,7 +59516,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2155" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59548,7 +59542,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2156" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59574,7 +59568,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2157" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59600,7 +59594,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2158" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59626,7 +59620,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2159" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59652,7 +59646,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2160" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59678,7 +59672,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59704,7 +59698,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2162" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59730,7 +59724,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2163" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59756,7 +59750,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2164" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59782,7 +59776,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2165" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59808,7 +59802,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2166" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59834,7 +59828,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2167" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59860,7 +59854,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2168" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59886,7 +59880,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2169" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59912,7 +59906,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2170" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59938,7 +59932,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59964,7 +59958,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2172" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59990,7 +59984,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60016,7 +60010,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2174" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60042,7 +60036,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2175" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60068,7 +60062,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60094,7 +60088,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60120,7 +60114,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60146,7 +60140,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60172,7 +60166,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60198,7 +60192,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2181" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60224,7 +60218,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60250,7 +60244,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2183" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60276,7 +60270,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2184" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60302,7 +60296,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2185" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60328,7 +60322,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60354,7 +60348,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60380,7 +60374,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60406,7 +60400,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60432,7 +60426,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2190" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60458,7 +60452,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2191" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60484,7 +60478,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2192" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60510,7 +60504,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60536,7 +60530,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60562,7 +60556,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60588,7 +60582,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60614,7 +60608,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60640,7 +60634,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2198" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60666,7 +60660,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2199" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60692,7 +60686,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2200" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60718,7 +60712,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60744,7 +60738,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2202" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60770,7 +60764,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60796,7 +60790,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2204" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60822,7 +60816,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2205" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60848,7 +60842,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60874,7 +60868,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60900,7 +60894,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60926,7 +60920,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2209" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60952,7 +60946,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60978,7 +60972,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61004,7 +60998,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2212" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61030,7 +61024,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61056,7 +61050,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61082,7 +61076,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61108,7 +61102,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61134,7 +61128,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61160,7 +61154,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61186,7 +61180,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61212,7 +61206,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61238,7 +61232,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61264,7 +61258,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61290,7 +61284,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61316,7 +61310,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61342,7 +61336,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61368,7 +61362,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2226" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61394,7 +61388,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61420,7 +61414,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61446,7 +61440,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2229" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61472,7 +61466,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61498,7 +61492,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2231" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61524,7 +61518,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2232" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61550,7 +61544,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2233" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61576,7 +61570,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2234" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61602,7 +61596,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2235" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61628,7 +61622,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61654,7 +61648,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2237" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61680,7 +61674,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2238" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61706,7 +61700,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2239" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61732,7 +61726,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61758,7 +61752,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61784,7 +61778,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2242" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61810,7 +61804,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2243" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61836,7 +61830,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2244" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61862,7 +61856,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2245" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61888,7 +61882,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2246" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61914,7 +61908,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61940,7 +61934,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61966,7 +61960,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61992,7 +61986,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62018,7 +62012,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62044,7 +62038,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62070,7 +62064,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62096,7 +62090,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62122,7 +62116,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62148,7 +62142,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62174,7 +62168,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62200,7 +62194,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62226,7 +62220,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62252,7 +62246,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62278,7 +62272,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62304,7 +62298,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62330,7 +62324,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62356,7 +62350,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62382,7 +62376,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62408,7 +62402,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62434,7 +62428,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62460,7 +62454,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62486,7 +62480,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62512,7 +62506,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62538,7 +62532,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62564,7 +62558,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62590,7 +62584,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62616,7 +62610,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62642,7 +62636,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62668,7 +62662,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62694,7 +62688,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62720,7 +62714,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62746,7 +62740,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62772,7 +62766,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62798,7 +62792,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62824,7 +62818,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62850,7 +62844,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62876,7 +62870,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62902,7 +62896,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62928,7 +62922,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62954,7 +62948,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62980,7 +62974,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63006,7 +63000,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63032,7 +63026,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63058,7 +63052,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63084,7 +63078,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63110,7 +63104,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63136,7 +63130,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63162,7 +63156,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63188,7 +63182,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63214,7 +63208,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63240,7 +63234,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63266,7 +63260,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63292,7 +63286,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63318,7 +63312,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63344,7 +63338,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63370,7 +63364,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63396,7 +63390,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63422,7 +63416,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63448,7 +63442,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63474,7 +63468,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63500,7 +63494,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63526,7 +63520,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63552,7 +63546,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63578,7 +63572,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63604,7 +63598,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63630,7 +63624,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63656,7 +63650,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63682,7 +63676,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63708,7 +63702,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63734,7 +63728,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63760,7 +63754,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63786,7 +63780,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63812,7 +63806,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63838,7 +63832,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63864,7 +63858,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63890,7 +63884,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63916,7 +63910,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63942,7 +63936,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63968,7 +63962,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63994,7 +63988,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64020,7 +64014,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64046,7 +64040,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64072,7 +64066,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64098,7 +64092,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64124,7 +64118,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64150,7 +64144,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64176,7 +64170,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64202,7 +64196,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64228,7 +64222,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64254,7 +64248,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64280,7 +64274,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64306,7 +64300,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64332,7 +64326,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64358,7 +64352,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64384,7 +64378,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64410,7 +64404,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64436,7 +64430,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64462,7 +64456,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64488,7 +64482,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64514,7 +64508,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64540,7 +64534,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64566,7 +64560,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64592,7 +64586,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64618,7 +64612,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64644,7 +64638,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64670,7 +64664,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64696,7 +64690,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64722,7 +64716,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64748,7 +64742,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64774,7 +64768,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64800,7 +64794,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64826,7 +64820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64852,7 +64846,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64878,7 +64872,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64904,7 +64898,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64930,7 +64924,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64956,7 +64950,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64982,7 +64976,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65008,7 +65002,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65034,7 +65028,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65060,7 +65054,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65086,7 +65080,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65112,7 +65106,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65138,7 +65132,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65164,7 +65158,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65190,7 +65184,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65216,7 +65210,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65242,7 +65236,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65268,7 +65262,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65294,7 +65288,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65320,7 +65314,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65346,7 +65340,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65372,7 +65366,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65398,7 +65392,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65424,7 +65418,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65450,7 +65444,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65476,7 +65470,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65502,7 +65496,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65528,7 +65522,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65554,7 +65548,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65580,7 +65574,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65606,7 +65600,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65632,7 +65626,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65658,7 +65652,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65684,7 +65678,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65710,7 +65704,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65736,7 +65730,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65762,7 +65756,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65788,7 +65782,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65814,7 +65808,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65840,7 +65834,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65866,7 +65860,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65892,7 +65886,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65918,7 +65912,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65944,7 +65938,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65970,7 +65964,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65996,7 +65990,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66022,7 +66016,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66048,7 +66042,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66074,7 +66068,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66100,7 +66094,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66126,7 +66120,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66152,7 +66146,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66178,7 +66172,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66204,7 +66198,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66230,7 +66224,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66256,7 +66250,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66282,7 +66276,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66308,7 +66302,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66334,7 +66328,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66360,7 +66354,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66386,7 +66380,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66412,7 +66406,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66438,7 +66432,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66464,7 +66458,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66490,7 +66484,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66516,7 +66510,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66542,7 +66536,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66568,7 +66562,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66594,7 +66588,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66620,7 +66614,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66646,7 +66640,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66672,7 +66666,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66698,7 +66692,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66724,7 +66718,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66750,7 +66744,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66776,7 +66770,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66802,7 +66796,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66828,7 +66822,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66854,7 +66848,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66880,7 +66874,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66906,7 +66900,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66932,7 +66926,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66958,7 +66952,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66984,7 +66978,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67010,7 +67004,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67036,7 +67030,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67062,7 +67056,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67088,7 +67082,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67114,7 +67108,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67140,7 +67134,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67166,7 +67160,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67192,7 +67186,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67218,7 +67212,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67244,7 +67238,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67270,7 +67264,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67296,7 +67290,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67322,7 +67316,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67348,7 +67342,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67374,7 +67368,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67400,7 +67394,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67426,7 +67420,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67452,7 +67446,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67478,7 +67472,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67504,7 +67498,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67530,7 +67524,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67556,7 +67550,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67582,7 +67576,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67608,7 +67602,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67634,7 +67628,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67660,7 +67654,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67686,7 +67680,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67712,7 +67706,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67738,7 +67732,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67764,7 +67758,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67790,7 +67784,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67816,7 +67810,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67842,7 +67836,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67868,7 +67862,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67894,7 +67888,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67920,7 +67914,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67946,7 +67940,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67972,7 +67966,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67998,7 +67992,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68024,7 +68018,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68050,7 +68044,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68076,7 +68070,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68102,7 +68096,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68128,7 +68122,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68154,7 +68148,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68180,7 +68174,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68206,7 +68200,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2489" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68232,7 +68226,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2490" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68258,7 +68252,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2491" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68284,7 +68278,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2492" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68310,7 +68304,7 @@
         <v>17.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68336,7 +68330,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2494" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68362,7 +68356,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2495" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68388,7 +68382,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2496" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68414,7 +68408,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2497" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68440,7 +68434,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2498" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68466,7 +68460,7 @@
         <v>17</v>
       </c>
       <c r="G2499" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68492,7 +68486,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2500" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68518,7 +68512,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2501" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68544,7 +68538,7 @@
         <v>17</v>
       </c>
       <c r="G2502" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68570,7 +68564,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2503" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68596,7 +68590,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2504" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68622,7 +68616,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2505" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68648,7 +68642,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2506" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68674,7 +68668,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2507" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68700,7 +68694,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68726,7 +68720,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2509" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68752,7 +68746,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2510" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68778,7 +68772,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G2511" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68804,7 +68798,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2512" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68830,7 +68824,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G2513" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68856,7 +68850,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68882,7 +68876,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2515" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68908,7 +68902,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2516" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68934,7 +68928,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2517" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68960,7 +68954,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2518" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68968,7 +68962,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6910416667</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>121433</v>
@@ -68986,9 +68980,35 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2519" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6911574074</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>71567</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>16.6399993896484</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="1050">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217515945435</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394424438477</t>
+    <t xml:space="preserve">7.16394472122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571666717529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07280111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1092586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051198959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634309768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717687606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96342706680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696371078491</t>
+    <t xml:space="preserve">7.0728006362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051294326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717782974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96342754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696418762207</t>
   </si>
   <si>
     <t xml:space="preserve">7.36446380615234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29154682159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863174438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2623815536499</t>
+    <t xml:space="preserve">7.29154872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800626754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238203048706</t>
   </si>
   <si>
     <t xml:space="preserve">7.40821170806885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39362955093384</t>
+    <t xml:space="preserve">7.393630027771</t>
   </si>
   <si>
     <t xml:space="preserve">7.43737888336182</t>
@@ -110,76 +110,76 @@
     <t xml:space="preserve">7.28790092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28425598144531</t>
+    <t xml:space="preserve">7.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341686248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154005050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112916946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61966800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216934204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25509023666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3498797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29883909225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873517990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24779796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2076940536499</t>
+    <t xml:space="preserve">7.51029443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154195785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112773895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30613231658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6196665763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5321683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34987831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2988395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873613357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779891967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498584747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769453048706</t>
   </si>
   <si>
     <t xml:space="preserve">6.99988555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02176141738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9780101776123</t>
+    <t xml:space="preserve">7.02175998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623918533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801065444946</t>
   </si>
   <si>
     <t xml:space="preserve">7.52487707138062</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">7.47383642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20404863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3863377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133508682251</t>
+    <t xml:space="preserve">7.20404815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133460998535</t>
   </si>
   <si>
     <t xml:space="preserve">7.58320903778076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71445751190186</t>
+    <t xml:space="preserve">7.7144570350647</t>
   </si>
   <si>
     <t xml:space="preserve">7.72904014587402</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">7.87487125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278461456299</t>
+    <t xml:space="preserve">7.94778680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0352840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
   </si>
   <si>
     <t xml:space="preserve">7.98424530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14273357391357</t>
+    <t xml:space="preserve">8.14273262023926</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770355224609</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09774494171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525157928467</t>
+    <t xml:space="preserve">8.09774398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">7.88030576705933</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">7.61787796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68535995483398</t>
+    <t xml:space="preserve">7.68535947799683</t>
   </si>
   <si>
     <t xml:space="preserve">7.6478705406189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.985276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89530181884766</t>
+    <t xml:space="preserve">7.85781192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98527669906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530038833618</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276515960693</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">8.06025505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68258190155029</t>
+    <t xml:space="preserve">8.68258285522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003925323486</t>
+    <t xml:space="preserve">8.84003829956055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43987083435059</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">9.25992012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240653991699</t>
+    <t xml:space="preserve">9.31240558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13245582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.982497215271</t>
+    <t xml:space="preserve">9.13245677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249816894531</t>
   </si>
   <si>
     <t xml:space="preserve">8.92251491546631</t>
@@ -311,28 +311,28 @@
     <t xml:space="preserve">8.66008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69757843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59260654449463</t>
+    <t xml:space="preserve">8.69757747650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.84753704071045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77255630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754398345947</t>
+    <t xml:space="preserve">8.77255725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81004810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754493713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.72756958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507526397705</t>
+    <t xml:space="preserve">8.70507621765137</t>
   </si>
   <si>
     <t xml:space="preserve">8.79505062103271</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69008159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36766910552979</t>
+    <t xml:space="preserve">8.72007083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.38266658782959</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">8.6151008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54761981964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519344329834</t>
+    <t xml:space="preserve">8.5476188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265773773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519248962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.32268333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73506832122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87002944946289</t>
+    <t xml:space="preserve">8.73506736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87003135681152</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002250671387</t>
@@ -389,46 +389,46 @@
     <t xml:space="preserve">8.51762866973877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58510971069336</t>
+    <t xml:space="preserve">8.58510875701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.51012992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40515899658203</t>
+    <t xml:space="preserve">8.40515995025635</t>
   </si>
   <si>
     <t xml:space="preserve">8.36017036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.315185546875</t>
+    <t xml:space="preserve">8.31518459320068</t>
   </si>
   <si>
     <t xml:space="preserve">8.39766025543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30018901824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764446258545</t>
+    <t xml:space="preserve">8.30018997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17272472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20271492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764350891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21021461486816</t>
+    <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.1127405166626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09024715423584</t>
+    <t xml:space="preserve">8.09024810791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.06775379180908</t>
@@ -440,49 +440,49 @@
     <t xml:space="preserve">8.12773609161377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18771839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777843475342</t>
+    <t xml:space="preserve">8.18772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777891159058</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22520923614502</t>
+    <t xml:space="preserve">8.13523578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24020576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22521018981934</t>
   </si>
   <si>
     <t xml:space="preserve">8.12023830413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00776958465576</t>
+    <t xml:space="preserve">8.00777149200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.76783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282377243042</t>
+    <t xml:space="preserve">7.82781887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282520294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528364181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776264190674</t>
+    <t xml:space="preserve">7.95528507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776359558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522598266602</t>
@@ -491,40 +491,40 @@
     <t xml:space="preserve">7.93279123306274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88780355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280750274658</t>
+    <t xml:space="preserve">7.88780450820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529249191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8728084564209</t>
   </si>
   <si>
     <t xml:space="preserve">7.91029739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76033926010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531904220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09667873382568</t>
+    <t xml:space="preserve">7.76033973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0966796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.7882342338562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6956992149353</t>
+    <t xml:space="preserve">7.69570064544678</t>
   </si>
   <si>
     <t xml:space="preserve">7.74967813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01956844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101282119751</t>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101329803467</t>
   </si>
   <si>
     <t xml:space="preserve">7.90390110015869</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">8.21234512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82678890228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55690002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858892440796</t>
+    <t xml:space="preserve">7.82678842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690097808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6185884475708</t>
   </si>
   <si>
     <t xml:space="preserve">7.54147815704346</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">7.4797887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32556629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809940338135</t>
+    <t xml:space="preserve">7.32556581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41809988021851</t>
   </si>
   <si>
     <t xml:space="preserve">7.38725566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21760988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254413604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2330322265625</t>
+    <t xml:space="preserve">7.21761035919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254365921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303318023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.24845504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2638783454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929925918579</t>
+    <t xml:space="preserve">7.26387786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507772445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929973602295</t>
   </si>
   <si>
     <t xml:space="preserve">7.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20218849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965538024902</t>
+    <t xml:space="preserve">7.20218801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965490341187</t>
   </si>
   <si>
     <t xml:space="preserve">7.14050006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07881164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472160339355</t>
+    <t xml:space="preserve">7.0788106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472255706787</t>
   </si>
   <si>
     <t xml:space="preserve">7.31014394760132</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">7.09423303604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00169897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205509185791</t>
+    <t xml:space="preserve">7.00169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205461502075</t>
   </si>
   <si>
     <t xml:space="preserve">6.92458772659302</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578805923462</t>
+    <t xml:space="preserve">6.86289834976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0171217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578758239746</t>
   </si>
   <si>
     <t xml:space="preserve">6.94001007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95543384552002</t>
+    <t xml:space="preserve">6.95543241500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627758026123</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">6.63156604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47734260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192073822021</t>
+    <t xml:space="preserve">6.47734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192121505737</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903150558472</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">6.61614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52361011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3231201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40023231506348</t>
+    <t xml:space="preserve">6.52360963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058652877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32311964035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40023136138916</t>
   </si>
   <si>
     <t xml:space="preserve">6.26143169403076</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56987619400024</t>
+    <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227590560913</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">6.81663274765015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374351501465</t>
+    <t xml:space="preserve">6.89374303817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.6469874382019</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">6.43107652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720872879028</t>
+    <t xml:space="preserve">6.10720920562744</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889810562134</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99925327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66240978240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4927659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396528244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649791717529</t>
+    <t xml:space="preserve">5.99925374984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.246009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66241025924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276494979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649839401245</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516466140747</t>
@@ -755,79 +755,79 @@
     <t xml:space="preserve">6.36938762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494289398193</t>
+    <t xml:space="preserve">6.75494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">6.87832069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97085475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796695709229</t>
+    <t xml:space="preserve">6.97085523605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796600341797</t>
   </si>
   <si>
     <t xml:space="preserve">7.155921459198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18676519393921</t>
+    <t xml:space="preserve">7.18676567077637</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338787078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20115041732788</t>
+    <t xml:space="preserve">7.20115089416504</t>
   </si>
   <si>
     <t xml:space="preserve">7.15314292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07313060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64106178283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00912046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913373947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
+    <t xml:space="preserve">7.07313108444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106130599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00912094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913326263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113809585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309268951416</t>
   </si>
   <si>
     <t xml:space="preserve">6.88110017776489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8650975227356</t>
+    <t xml:space="preserve">6.86509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">6.78508424758911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75307893753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73707723617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72107410430908</t>
+    <t xml:space="preserve">6.75307941436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73707675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72107362747192</t>
   </si>
   <si>
     <t xml:space="preserve">6.48103618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54504632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76908254623413</t>
+    <t xml:space="preserve">6.54504680633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
     <t xml:space="preserve">6.80108737945557</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">6.81709003448486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56104850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65706396102905</t>
+    <t xml:space="preserve">6.56104803085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65706443786621</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
+    <t xml:space="preserve">6.62505865097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.57705163955688</t>
@@ -857,25 +857,25 @@
     <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302869796753</t>
+    <t xml:space="preserve">6.43302822113037</t>
   </si>
   <si>
     <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102338790894</t>
+    <t xml:space="preserve">6.44903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
     <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22499561309814</t>
+    <t xml:space="preserve">6.22499513626099</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097171783447</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">6.04896688461304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09697484970093</t>
+    <t xml:space="preserve">6.06496953964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
     <t xml:space="preserve">6.1609845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00095987319946</t>
+    <t xml:space="preserve">6.0009593963623</t>
   </si>
   <si>
     <t xml:space="preserve">5.95295190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01696157455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895360946655</t>
+    <t xml:space="preserve">6.0169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76092100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74491786956787</t>
+    <t xml:space="preserve">5.76092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74491834640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.68090772628784</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90494394302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87293815612793</t>
+    <t xml:space="preserve">5.90494346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87293910980225</t>
   </si>
   <si>
     <t xml:space="preserve">5.79292583465576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98495674133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11297655105591</t>
+    <t xml:space="preserve">5.98495578765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.24099779129028</t>
@@ -950,43 +950,43 @@
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1769871711731</t>
+    <t xml:space="preserve">6.17698764801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.38502073287964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19298982620239</t>
+    <t xml:space="preserve">6.19298934936523</t>
   </si>
   <si>
     <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14498233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25699996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93694877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0329647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61689805984497</t>
+    <t xml:space="preserve">6.1449818611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25700044631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93694925308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03296422958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61689758300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.48887729644775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63290023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55288743972778</t>
+    <t xml:space="preserve">5.63290071487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55288696289062</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">5.50487995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60089540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3608570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081861495972</t>
+    <t xml:space="preserve">5.60089492797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36085653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081813812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.73675727844238</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">4.67274713516235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24067783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28868579864502</t>
+    <t xml:space="preserve">4.44871187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24067831039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062711715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28868627548218</t>
   </si>
   <si>
     <t xml:space="preserve">4.04864692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1606650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08065271377563</t>
+    <t xml:space="preserve">4.16066551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">4.40070343017578</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13682126998901</t>
+    <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3288516998291</t>
+    <t xml:space="preserve">5.40886497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32885122299194</t>
   </si>
   <si>
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1848292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880002975464</t>
+    <t xml:space="preserve">5.18482828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28084373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05680799484253</t>
+    <t xml:space="preserve">5.28084421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.23283624649048</t>
@@ -1076,34 +1076,34 @@
     <t xml:space="preserve">5.47287464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894128799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64890241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69691038131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85693645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58489274978638</t>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64890289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77692270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6969108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85693597793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58489322662354</t>
   </si>
   <si>
     <t xml:space="preserve">5.42486715316772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56889009475708</t>
+    <t xml:space="preserve">5.56888961791992</t>
   </si>
   <si>
     <t xml:space="preserve">5.34485387802124</t>
@@ -1112,55 +1112,55 @@
     <t xml:space="preserve">5.44086933135986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484155654907</t>
+    <t xml:space="preserve">5.37685966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484107971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.24883842468262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45687198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688478469849</t>
+    <t xml:space="preserve">5.45687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688526153564</t>
   </si>
   <si>
     <t xml:space="preserve">5.29684638977051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683359146118</t>
+    <t xml:space="preserve">5.21683406829834</t>
   </si>
   <si>
     <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28900527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70507144927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67306709289551</t>
+    <t xml:space="preserve">6.28900575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49703884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70507192611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67306661605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.91310548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24915885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922380447388</t>
+    <t xml:space="preserve">7.24915981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922285079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5212025642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5372052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118928909302</t>
+    <t xml:space="preserve">7.52120208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53720474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44119024276733</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719146728516</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">7.40918493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39318132400513</t>
+    <t xml:space="preserve">7.39318227767944</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315668106079</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">7.42518711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50519943237305</t>
+    <t xml:space="preserve">7.50519990921021</t>
   </si>
   <si>
     <t xml:space="preserve">7.36117696762085</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">7.29716634750366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125328063965</t>
+    <t xml:space="preserve">7.74523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">7.82525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90526390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0812931060791</t>
+    <t xml:space="preserve">7.90526342391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08129215240479</t>
   </si>
   <si>
     <t xml:space="preserve">8.04128551483154</t>
@@ -1232,37 +1232,37 @@
     <t xml:space="preserve">7.93726873397827</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00127792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87325811386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327138900757</t>
+    <t xml:space="preserve">8.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325859069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327091217041</t>
   </si>
   <si>
     <t xml:space="preserve">8.12129783630371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96927404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132438659668</t>
+    <t xml:space="preserve">7.96927452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.281325340271</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44134998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139358520508</t>
+    <t xml:space="preserve">8.44135093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139453887939</t>
   </si>
   <si>
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141445159912</t>
+    <t xml:space="preserve">8.84141254425049</t>
   </si>
   <si>
     <t xml:space="preserve">9.12145805358887</t>
@@ -1271,55 +1271,55 @@
     <t xml:space="preserve">9.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96143245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152252197266</t>
+    <t xml:space="preserve">8.9614315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.48151588439941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72155380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84157180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1616249084473</t>
+    <t xml:space="preserve">9.72155284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84157276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1616239547729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.121618270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2816429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216485977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217140197754</t>
+    <t xml:space="preserve">10.1216173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2816438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216505050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
     <t xml:space="preserve">11.3218088150024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2017908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217775344849</t>
+    <t xml:space="preserve">11.201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617841720581</t>
+    <t xml:space="preserve">10.9617509841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8417329788208</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">10.8817386627197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4818353652954</t>
+    <t xml:space="preserve">11.4818363189697</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417964935303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.76171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216808319092</t>
+    <t xml:space="preserve">11.0817708969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7617206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
     <t xml:space="preserve">10.60169506073</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">11.6965761184692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1573705673218</t>
+    <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.7011222839355</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1204404830933</t>
+    <t xml:space="preserve">10.1204414367676</t>
   </si>
   <si>
     <t xml:space="preserve">10.1619176864624</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">10.0789632797241</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95453071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4107828140259</t>
+    <t xml:space="preserve">9.99600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305541992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95453262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
     <t xml:space="preserve">10.327826499939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9914636611938</t>
+    <t xml:space="preserve">10.9914627075195</t>
   </si>
   <si>
     <t xml:space="preserve">10.7425994873047</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">10.825553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5766897201538</t>
+    <t xml:space="preserve">10.5766906738281</t>
   </si>
   <si>
     <t xml:space="preserve">10.8670310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693037033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244873046875</t>
+    <t xml:space="preserve">10.6181688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2448740005493</t>
   </si>
   <si>
     <t xml:space="preserve">10.2033958435059</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522581100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9499845504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7840766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115894317627</t>
+    <t xml:space="preserve">10.4522590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9499855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7840776443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1158933639526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535213470459</t>
+    <t xml:space="preserve">10.5352125167847</t>
   </si>
   <si>
     <t xml:space="preserve">10.6596450805664</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">11.3232803344727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4891901016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2403268814087</t>
+    <t xml:space="preserve">11.4891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2403259277344</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">12.2772569656372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3602104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6505517959595</t>
+    <t xml:space="preserve">12.3602113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6505527496338</t>
   </si>
   <si>
     <t xml:space="preserve">12.3187341690063</t>
@@ -1484,28 +1484,28 @@
     <t xml:space="preserve">12.5675973892212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8164596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630502700806</t>
+    <t xml:space="preserve">12.816460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2727098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">13.8119125366211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6460046768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215730667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3141860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3556652069092</t>
+    <t xml:space="preserve">13.6460056304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3141870498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3556642532349</t>
   </si>
   <si>
     <t xml:space="preserve">14.0192995071411</t>
@@ -1514,49 +1514,49 @@
     <t xml:space="preserve">13.8948669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6874828338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312326431274</t>
+    <t xml:space="preserve">13.687481880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312316894531</t>
   </si>
   <si>
     <t xml:space="preserve">13.1897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8994150161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.609073638916</t>
+    <t xml:space="preserve">12.8994159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846429824829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0283937454224</t>
+    <t xml:space="preserve">12.028392791748</t>
   </si>
   <si>
     <t xml:space="preserve">11.3647575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062356948853</t>
+    <t xml:space="preserve">11.4062347412109</t>
   </si>
   <si>
     <t xml:space="preserve">11.8210077285767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988496780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4477119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7380523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419219970703</t>
+    <t xml:space="preserve">11.1988477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4477128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7380514144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419124603271</t>
   </si>
   <si>
     <t xml:space="preserve">9.74714660644531</t>
@@ -1565,25 +1565,25 @@
     <t xml:space="preserve">11.8624839782715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.613621711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4808940887451</t>
+    <t xml:space="preserve">11.6136207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4808950424194</t>
   </si>
   <si>
     <t xml:space="preserve">11.0661220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177124023438</t>
+    <t xml:space="preserve">10.7177133560181</t>
   </si>
   <si>
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.651349067688</t>
+    <t xml:space="preserve">10.7343044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6347589492798</t>
@@ -1592,25 +1592,25 @@
     <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8504409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8006677627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002122879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8172578811646</t>
+    <t xml:space="preserve">10.8504390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8006687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8172588348389</t>
   </si>
   <si>
     <t xml:space="preserve">10.7674856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9997577667236</t>
+    <t xml:space="preserve">10.9997587203979</t>
   </si>
   <si>
     <t xml:space="preserve">10.8338489532471</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">10.5849857330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4003801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4693689346313</t>
+    <t xml:space="preserve">11.4003810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693698883057</t>
   </si>
   <si>
     <t xml:space="preserve">11.331392288208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2279100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866161346436</t>
+    <t xml:space="preserve">11.2279090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866151809692</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">12.2282457351685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4179630279541</t>
+    <t xml:space="preserve">12.1592569351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.1937503814697</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">12.021279335022</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1420097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8833017349243</t>
+    <t xml:space="preserve">12.1420087814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
     <t xml:space="preserve">11.5038642883301</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">11.2106618881226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5035285949707</t>
+    <t xml:space="preserve">10.5035276412964</t>
   </si>
   <si>
     <t xml:space="preserve">10.7794828414917</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">10.6242570877075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0036954879761</t>
+    <t xml:space="preserve">11.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.1589202880859</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">11.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3831338882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9522895812988</t>
+    <t xml:space="preserve">11.3831329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9522905349731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280769348145</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453241348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.69358253479</t>
+    <t xml:space="preserve">11.7453231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6935834884644</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660545349121</t>
+    <t xml:space="preserve">11.8660554885864</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627401351929</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1765041351318</t>
+    <t xml:space="preserve">11.9177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1765031814575</t>
   </si>
   <si>
     <t xml:space="preserve">12.3144807815552</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350442886353</t>
+    <t xml:space="preserve">11.9695377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">12.1075143814087</t>
@@ -1754,34 +1754,34 @@
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3486394882202</t>
+    <t xml:space="preserve">11.7970666885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3486385345459</t>
   </si>
   <si>
     <t xml:space="preserve">11.245156288147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3658857345581</t>
+    <t xml:space="preserve">11.3658866882324</t>
   </si>
   <si>
     <t xml:space="preserve">11.521110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5901002883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6418418884277</t>
+    <t xml:space="preserve">11.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6418409347534</t>
   </si>
   <si>
     <t xml:space="preserve">11.4348754882812</t>
@@ -1790,28 +1790,28 @@
     <t xml:space="preserve">11.0381898880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209426879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1244268417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.141674041748</t>
+    <t xml:space="preserve">11.1071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.020941734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1244249343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8829660415649</t>
+    <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
     <t xml:space="preserve">10.641505241394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1758327484131</t>
+    <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5207738876343</t>
@@ -1820,193 +1820,196 @@
     <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3655500411987</t>
+    <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
+    <t xml:space="preserve">10.3310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1930780410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5383586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245937347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4176273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8143119812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0557727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697065353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2972345352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4869527816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6421775817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5214471817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386934280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5041999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2799854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4352111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7798185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7108297348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2968978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2624034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2796497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9519529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0899314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9347076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657178878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5725164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6070108413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4517860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.469033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380229949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4000444412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2770614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2590627670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4930410385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5830335617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6190299987793</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1930780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5383586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4176273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8143119812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0557727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.469705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2972345352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4869518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.573187828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6421775817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5214471817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386943817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5041999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2799873352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4352121353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7798175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7108297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2968978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2624034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2796506881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9519538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0899314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9347066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657188415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5725164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6070108413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4517860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4000453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.277060508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2590627670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3850507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4930419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5830335617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6190309524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.043083190918</t>
+    <t xml:space="preserve">10.0430822372437</t>
   </si>
   <si>
     <t xml:space="preserve">9.88109683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1150760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93509197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89909553527832</t>
+    <t xml:space="preserve">10.1690721511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1150751113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93509292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.187068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
     <t xml:space="preserve">9.95309066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0250835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98908710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0790796279907</t>
+    <t xml:space="preserve">10.0250844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98908805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0790786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
@@ -2015,10 +2018,10 @@
     <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73711109161377</t>
+    <t xml:space="preserve">9.80910301208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73711013793945</t>
   </si>
   <si>
     <t xml:space="preserve">9.77310752868652</t>
@@ -2027,16 +2030,16 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5290384292603</t>
+    <t xml:space="preserve">10.421049118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5290374755859</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130578994751</t>
+    <t xml:space="preserve">10.3130588531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950592041016</t>
@@ -2048,10 +2051,10 @@
     <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70111465454102</t>
+    <t xml:space="preserve">9.79110527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111274719238</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
@@ -2063,10 +2066,10 @@
     <t xml:space="preserve">9.17916107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19715976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28715133666992</t>
+    <t xml:space="preserve">9.1971607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28715038299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.48513412475586</t>
@@ -2099,94 +2102,94 @@
     <t xml:space="preserve">8.99917793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318992614746</t>
+    <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97218036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79219627380371</t>
+    <t xml:space="preserve">8.97218132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79219722747803</t>
   </si>
   <si>
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47722625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62121200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63921165466309</t>
+    <t xml:space="preserve">8.4772253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62121295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63921070098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.63021183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72920227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60321521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35123729705811</t>
+    <t xml:space="preserve">8.7292013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60321426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35123634338379</t>
   </si>
   <si>
     <t xml:space="preserve">8.20725059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90127754211426</t>
+    <t xml:space="preserve">7.9012770652771</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04526424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0542631149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00926685333252</t>
+    <t xml:space="preserve">8.04526519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05426406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
     <t xml:space="preserve">7.96427249908447</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91027736663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81128692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327089309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78428936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.793288230896</t>
+    <t xml:space="preserve">7.91027784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81128740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227914810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828449249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91927671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78428792953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79328870773315</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72129440307617</t>
+    <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.63130235671997</t>
@@ -2195,10 +2198,10 @@
     <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19934272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1813440322876</t>
+    <t xml:space="preserve">7.19934225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18134355545044</t>
   </si>
   <si>
     <t xml:space="preserve">7.01035976409912</t>
@@ -2207,7 +2210,7 @@
     <t xml:space="preserve">6.76738166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65039253234863</t>
+    <t xml:space="preserve">6.65039205551147</t>
   </si>
   <si>
     <t xml:space="preserve">6.69538831710815</t>
@@ -2222,7 +2225,7 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636415481567</t>
+    <t xml:space="preserve">6.95636463165283</t>
   </si>
   <si>
     <t xml:space="preserve">7.19034290313721</t>
@@ -2240,7 +2243,7 @@
     <t xml:space="preserve">7.24433851242065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4243221282959</t>
+    <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
     <t xml:space="preserve">7.5143141746521</t>
@@ -2249,22 +2252,22 @@
     <t xml:space="preserve">7.49631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30733251571655</t>
+    <t xml:space="preserve">7.30733203887939</t>
   </si>
   <si>
     <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28033494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0283579826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15434598922729</t>
+    <t xml:space="preserve">7.28933429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28033542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02835750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15434646606445</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
@@ -2282,13 +2285,13 @@
     <t xml:space="preserve">7.68529796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99127054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627380371094</t>
+    <t xml:space="preserve">7.99127006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9462742805481</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
@@ -2306,28 +2309,28 @@
     <t xml:space="preserve">8.75619888305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66620826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74720191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56721878051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61221313476562</t>
+    <t xml:space="preserve">8.66620922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74720096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56721782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61221218109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.42323017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36923503875732</t>
+    <t xml:space="preserve">8.36923599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19825077056885</t>
+    <t xml:space="preserve">8.19824981689453</t>
   </si>
   <si>
     <t xml:space="preserve">8.06326293945312</t>
@@ -2336,19 +2339,19 @@
     <t xml:space="preserve">8.11725902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.414231300354</t>
+    <t xml:space="preserve">8.41423225402832</t>
   </si>
   <si>
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922756195068</t>
+    <t xml:space="preserve">8.45922660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2230663299561</t>
+    <t xml:space="preserve">10.2230653762817</t>
   </si>
   <si>
     <t xml:space="preserve">10.133074760437</t>
@@ -2357,13 +2360,13 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170118331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9789962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8350105285645</t>
+    <t xml:space="preserve">10.8170127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9789972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8350114822388</t>
   </si>
   <si>
     <t xml:space="preserve">10.6370277404785</t>
@@ -2372,7 +2375,7 @@
     <t xml:space="preserve">10.90700340271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6010313034058</t>
+    <t xml:space="preserve">10.6010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">10.7270202636719</t>
@@ -2381,10 +2384,10 @@
     <t xml:space="preserve">10.6550273895264</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7990131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6730241775513</t>
+    <t xml:space="preserve">10.7990140914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6730251312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.0509901046753</t>
@@ -2399,16 +2402,16 @@
     <t xml:space="preserve">11.0329923629761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1589794158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4829511642456</t>
+    <t xml:space="preserve">11.1589803695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4829521179199</t>
   </si>
   <si>
     <t xml:space="preserve">11.4649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2669715881348</t>
+    <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
     <t xml:space="preserve">11.3389644622803</t>
@@ -2417,13 +2420,13 @@
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374960899353</t>
+    <t xml:space="preserve">11.3749618530273</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089401245117</t>
+    <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
     <t xml:space="preserve">11.5009489059448</t>
@@ -2432,7 +2435,7 @@
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
+    <t xml:space="preserve">11.9689073562622</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709245681763</t>
@@ -2450,7 +2453,7 @@
     <t xml:space="preserve">11.7529268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429183959961</t>
+    <t xml:space="preserve">11.8429174423218</t>
   </si>
   <si>
     <t xml:space="preserve">11.806921005249</t>
@@ -2474,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578481674194</t>
+    <t xml:space="preserve">11.3578472137451</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514045715332</t>
+    <t xml:space="preserve">11.4514036178589</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.208155632019</t>
+    <t xml:space="preserve">11.2081546783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2495,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
+    <t xml:space="preserve">11.8443441390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688810348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2507,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940366744995</t>
+    <t xml:space="preserve">11.9940357208252</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133655548096</t>
+    <t xml:space="preserve">11.7133646011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2528,10 +2531,7 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4139804840088</t>
+    <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823850631714</t>
+    <t xml:space="preserve">11.5823841094971</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624393463135</t>
+    <t xml:space="preserve">12.1624383926392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191904067993</t>
+    <t xml:space="preserve">11.919189453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.544960975647</t>
+    <t xml:space="preserve">11.5449619293213</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0584630966187</t>
+    <t xml:space="preserve">11.058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771760940552</t>
+    <t xml:space="preserve">11.0771751403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842346191406</t>
+    <t xml:space="preserve">10.6842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2612,22 +2612,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222745895386</t>
+    <t xml:space="preserve">10.4784097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222755432129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287172317505</t>
+    <t xml:space="preserve">10.3287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977367401123</t>
+    <t xml:space="preserve">10.1977376937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3159,6 +3159,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.7399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1200008392334</t>
   </si>
 </sst>
 </file>
@@ -52395,7 +52398,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1881" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52421,7 +52424,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1882" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52447,7 +52450,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1883" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52473,7 +52476,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52525,7 +52528,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1886" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52551,7 +52554,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1887" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52577,7 +52580,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1888" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52603,7 +52606,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1889" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52629,7 +52632,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1890" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52655,7 +52658,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1891" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52681,7 +52684,7 @@
         <v>11</v>
       </c>
       <c r="G1892" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52707,7 +52710,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1893" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52733,7 +52736,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1894" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52759,7 +52762,7 @@
         <v>11</v>
       </c>
       <c r="G1895" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52785,7 +52788,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1896" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52811,7 +52814,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52837,7 +52840,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52863,7 +52866,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1899" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52889,7 +52892,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1900" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52915,7 +52918,7 @@
         <v>11</v>
       </c>
       <c r="G1901" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52941,7 +52944,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1902" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52967,7 +52970,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1903" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52993,7 +52996,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1904" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53019,7 +53022,7 @@
         <v>11.5</v>
       </c>
       <c r="G1905" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53045,7 +53048,7 @@
         <v>11.5</v>
       </c>
       <c r="G1906" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53071,7 +53074,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1907" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53123,7 +53126,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1909" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53149,7 +53152,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53175,7 +53178,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1911" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53201,7 +53204,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1912" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53227,7 +53230,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1913" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53253,7 +53256,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53279,7 +53282,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53305,7 +53308,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1916" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53357,7 +53360,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53383,7 +53386,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1919" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53409,7 +53412,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1920" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53435,7 +53438,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1921" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53461,7 +53464,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53487,7 +53490,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1923" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53513,7 +53516,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1924" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53539,7 +53542,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1925" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53565,7 +53568,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1926" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53591,7 +53594,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1927" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53617,7 +53620,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53643,7 +53646,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1929" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53669,7 +53672,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1930" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53695,7 +53698,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53721,7 +53724,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1932" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53747,7 +53750,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1933" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53773,7 +53776,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1934" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53799,7 +53802,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1935" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53825,7 +53828,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1936" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53851,7 +53854,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1937" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53877,7 +53880,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1938" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53903,7 +53906,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53929,7 +53932,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1940" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53955,7 +53958,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1941" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53981,7 +53984,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1942" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54007,7 +54010,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1943" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54033,7 +54036,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54059,7 +54062,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1945" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54085,7 +54088,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1946" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54111,7 +54114,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1947" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54137,7 +54140,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1948" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54163,7 +54166,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54189,7 +54192,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1950" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54215,7 +54218,7 @@
         <v>10</v>
       </c>
       <c r="G1951" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54241,7 +54244,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1952" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54267,7 +54270,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1953" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54293,7 +54296,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1954" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54319,7 +54322,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1955" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54345,7 +54348,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1956" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54371,7 +54374,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54397,7 +54400,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54423,7 +54426,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1959" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54449,7 +54452,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1960" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54475,7 +54478,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1961" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54501,7 +54504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1962" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54527,7 +54530,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54553,7 +54556,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1964" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54579,7 +54582,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1965" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54605,7 +54608,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1966" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54631,7 +54634,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1967" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54657,7 +54660,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54683,7 +54686,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54709,7 +54712,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54735,7 +54738,7 @@
         <v>9</v>
       </c>
       <c r="G1971" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54761,7 +54764,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1972" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54787,7 +54790,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54813,7 +54816,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1974" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54839,7 +54842,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1975" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54865,7 +54868,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54891,7 +54894,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1977" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54917,7 +54920,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1978" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54943,7 +54946,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1979" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54969,7 +54972,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54995,7 +54998,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1981" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55021,7 +55024,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1982" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55047,7 +55050,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55073,7 +55076,7 @@
         <v>8.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55099,7 +55102,7 @@
         <v>8.5</v>
       </c>
       <c r="G1985" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55125,7 +55128,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1986" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55151,7 +55154,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1987" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55177,7 +55180,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1988" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55203,7 +55206,7 @@
         <v>8</v>
       </c>
       <c r="G1989" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55229,7 +55232,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55255,7 +55258,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55281,7 +55284,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55307,7 +55310,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1993" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55333,7 +55336,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1994" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55359,7 +55362,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1995" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55385,7 +55388,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1996" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55411,7 +55414,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1997" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55437,7 +55440,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55463,7 +55466,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1999" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55489,7 +55492,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55515,7 +55518,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2001" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55541,7 +55544,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2002" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55567,7 +55570,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2003" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55593,7 +55596,7 @@
         <v>8.25</v>
       </c>
       <c r="G2004" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55619,7 +55622,7 @@
         <v>8.5</v>
       </c>
       <c r="G2005" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55645,7 +55648,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2006" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55671,7 +55674,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2007" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55697,7 +55700,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55723,7 +55726,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2009" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55749,7 +55752,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2010" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55775,7 +55778,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2011" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55801,7 +55804,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G2012" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55827,7 +55830,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2013" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55853,7 +55856,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55879,7 +55882,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2015" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55905,7 +55908,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2016" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55931,7 +55934,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2017" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55957,7 +55960,7 @@
         <v>8</v>
       </c>
       <c r="G2018" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55983,7 +55986,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2019" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56009,7 +56012,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2020" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56035,7 +56038,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2021" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56061,7 +56064,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2022" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56087,7 +56090,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2023" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56113,7 +56116,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56139,7 +56142,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2025" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56165,7 +56168,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56191,7 +56194,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2027" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56217,7 +56220,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2028" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56243,7 +56246,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2029" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56269,7 +56272,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2030" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56295,7 +56298,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2031" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56321,7 +56324,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2032" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56347,7 +56350,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2033" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56373,7 +56376,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2034" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56399,7 +56402,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2035" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56425,7 +56428,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2036" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56451,7 +56454,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2037" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56477,7 +56480,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56503,7 +56506,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56529,7 +56532,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2040" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56555,7 +56558,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2041" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56581,7 +56584,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2042" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56607,7 +56610,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2043" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56633,7 +56636,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2044" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56659,7 +56662,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2045" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56685,7 +56688,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2046" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56711,7 +56714,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2047" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56737,7 +56740,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2048" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56763,7 +56766,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2049" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56789,7 +56792,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56815,7 +56818,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2051" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56841,7 +56844,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56867,7 +56870,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2053" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56893,7 +56896,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2054" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56919,7 +56922,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56945,7 +56948,7 @@
         <v>9</v>
       </c>
       <c r="G2056" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56971,7 +56974,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2057" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56997,7 +57000,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2058" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57023,7 +57026,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2059" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57049,7 +57052,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2060" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57075,7 +57078,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2061" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57101,7 +57104,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2062" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57127,7 +57130,7 @@
         <v>9.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57153,7 +57156,7 @@
         <v>9.5</v>
       </c>
       <c r="G2064" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57179,7 +57182,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2065" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57205,7 +57208,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2066" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57231,7 +57234,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2067" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57257,7 +57260,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57283,7 +57286,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2069" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57309,7 +57312,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2070" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57335,7 +57338,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2071" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57361,7 +57364,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2072" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57387,7 +57390,7 @@
         <v>11</v>
       </c>
       <c r="G2073" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57413,7 +57416,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2074" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57439,7 +57442,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2075" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57465,7 +57468,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2076" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57491,7 +57494,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2077" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57543,7 +57546,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2079" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57569,7 +57572,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2080" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57595,7 +57598,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2081" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57621,7 +57624,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2082" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57647,7 +57650,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2083" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57673,7 +57676,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57699,7 +57702,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2085" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57725,7 +57728,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57751,7 +57754,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57803,7 +57806,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2089" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57829,7 +57832,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57855,7 +57858,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2091" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57907,7 +57910,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2093" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57933,7 +57936,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57959,7 +57962,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2095" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58011,7 +58014,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2097" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58037,7 +58040,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2098" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58063,7 +58066,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2099" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58089,7 +58092,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2100" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58115,7 +58118,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2101" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58141,7 +58144,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2102" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58167,7 +58170,7 @@
         <v>12</v>
       </c>
       <c r="G2103" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58193,7 +58196,7 @@
         <v>12</v>
       </c>
       <c r="G2104" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58219,7 +58222,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2105" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58245,7 +58248,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2106" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58271,7 +58274,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2107" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58297,7 +58300,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2108" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58323,7 +58326,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2109" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58349,7 +58352,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2110" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58375,7 +58378,7 @@
         <v>12.5</v>
       </c>
       <c r="G2111" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58401,7 +58404,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2112" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58427,7 +58430,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58453,7 +58456,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58479,7 +58482,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58505,7 +58508,7 @@
         <v>12.5</v>
       </c>
       <c r="G2116" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58531,7 +58534,7 @@
         <v>12.5</v>
       </c>
       <c r="G2117" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58557,7 +58560,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2118" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58583,7 +58586,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2119" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58609,7 +58612,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2120" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58635,7 +58638,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2121" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58661,7 +58664,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58687,7 +58690,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2123" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58713,7 +58716,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2124" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58739,7 +58742,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2125" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58765,7 +58768,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2126" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58791,7 +58794,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58817,7 +58820,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G2128" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58843,7 +58846,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2129" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58869,7 +58872,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2130" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58895,7 +58898,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2131" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58921,7 +58924,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2132" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58947,7 +58950,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2133" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58973,7 +58976,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58999,7 +59002,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2135" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59025,7 +59028,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2136" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59051,7 +59054,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G2137" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59077,7 +59080,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2138" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59103,7 +59106,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2139" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59129,7 +59132,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59155,7 +59158,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2141" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59181,7 +59184,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2142" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59207,7 +59210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59233,7 +59236,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2144" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59259,7 +59262,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2145" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59285,7 +59288,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2146" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59311,7 +59314,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2147" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59337,7 +59340,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2148" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59363,7 +59366,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2149" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59389,7 +59392,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2150" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59415,7 +59418,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59441,7 +59444,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59467,7 +59470,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2153" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59493,7 +59496,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59519,7 +59522,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2155" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59545,7 +59548,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2156" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59571,7 +59574,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2157" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59597,7 +59600,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2158" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59623,7 +59626,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2159" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59649,7 +59652,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2160" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59675,7 +59678,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59701,7 +59704,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2162" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59727,7 +59730,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2163" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59753,7 +59756,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2164" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59779,7 +59782,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2165" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59805,7 +59808,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2166" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59831,7 +59834,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2167" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59857,7 +59860,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2168" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59883,7 +59886,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2169" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59909,7 +59912,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2170" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59935,7 +59938,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>838</v>
+        <v>814</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59961,7 +59964,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2172" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60013,7 +60016,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2174" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60039,7 +60042,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2175" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60065,7 +60068,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60195,7 +60198,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2181" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60247,7 +60250,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2183" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60273,7 +60276,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2184" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60299,7 +60302,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2185" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60429,7 +60432,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2190" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60455,7 +60458,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2191" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60481,7 +60484,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2192" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60637,7 +60640,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2198" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60663,7 +60666,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2199" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60689,7 +60692,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2200" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60741,7 +60744,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2202" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60767,7 +60770,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60793,7 +60796,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2204" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60819,7 +60822,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2205" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60923,7 +60926,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2209" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61001,7 +61004,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2212" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61131,7 +61134,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61183,7 +61186,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61261,7 +61264,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61313,7 +61316,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>838</v>
+        <v>814</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61365,7 +61368,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2226" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61443,7 +61446,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2229" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61495,7 +61498,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2231" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61521,7 +61524,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2232" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61547,7 +61550,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2233" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61573,7 +61576,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2234" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61599,7 +61602,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2235" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61651,7 +61654,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2237" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61677,7 +61680,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2238" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61703,7 +61706,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2239" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61781,7 +61784,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2242" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61807,7 +61810,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2243" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61833,7 +61836,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2244" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61859,7 +61862,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2245" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61885,7 +61888,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2246" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -69121,7 +69124,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6911805556</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>63416</v>
@@ -69142,6 +69145,32 @@
         <v>1048</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6913078704</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>108878</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>17.1599998474121</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>16.7199993133545</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>16.7600002288818</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>17.1200008392334</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217372894287</t>
+    <t xml:space="preserve">7.18217515945435</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07280111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10925722122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061637878418</t>
+    <t xml:space="preserve">7.1639461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0728006362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10925817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061590194702</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051198959351</t>
@@ -65,88 +65,88 @@
     <t xml:space="preserve">7.14207077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9670729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96342754364014</t>
+    <t xml:space="preserve">6.96707344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634357452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96342802047729</t>
   </si>
   <si>
     <t xml:space="preserve">7.25144243240356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863174438477</t>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446332931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2915472984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863222122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.26238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40821170806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790187835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4300856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029300689697</t>
+    <t xml:space="preserve">7.40821123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39363050460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008756637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029396057129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112726211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613088607788</t>
+    <t xml:space="preserve">7.64154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48842000961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3061318397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.6196665763855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54675245285034</t>
+    <t xml:space="preserve">7.54675197601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.5321683883667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2550892829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529615402222</t>
+    <t xml:space="preserve">7.25509023666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
   </si>
   <si>
     <t xml:space="preserve">7.3498797416687</t>
@@ -158,82 +158,82 @@
     <t xml:space="preserve">7.25873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24779748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2149863243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050760269165</t>
+    <t xml:space="preserve">7.2477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21498727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050664901733</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769453048706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99988508224487</t>
+    <t xml:space="preserve">6.99988555908203</t>
   </si>
   <si>
     <t xml:space="preserve">7.0217604637146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99623966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2040491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300264358521</t>
+    <t xml:space="preserve">6.99624013900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97800922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5248761177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3863377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.56133460998535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58320903778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7144570350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87487173080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9477858543396</t>
+    <t xml:space="preserve">7.5832085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8748722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778537750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.03528594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18022155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774494171143</t>
+    <t xml:space="preserve">8.12278270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424386978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18022060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774589538574</t>
   </si>
   <si>
     <t xml:space="preserve">8.07525157928467</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">7.79782772064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61787796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64787006378174</t>
+    <t xml:space="preserve">7.61787748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787101745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89530038833618</t>
+    <t xml:space="preserve">7.985276222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530086517334</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0602560043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258285522461</t>
+    <t xml:space="preserve">8.06025505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">8.84003639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990528106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1324577331543</t>
+    <t xml:space="preserve">9.4398717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13245677947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.982497215271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92251491546631</t>
+    <t xml:space="preserve">8.92251586914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.9974946975708</t>
@@ -308,46 +308,46 @@
     <t xml:space="preserve">8.89252281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66008758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69757843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59260845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753704071045</t>
+    <t xml:space="preserve">8.66008853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69757747650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59260654449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753513336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81754493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507526397705</t>
+    <t xml:space="preserve">8.8100471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81754398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507431030273</t>
   </si>
   <si>
     <t xml:space="preserve">8.79505062103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64509201049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72007083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010433197021</t>
+    <t xml:space="preserve">8.64509296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72007274627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010528564453</t>
   </si>
   <si>
     <t xml:space="preserve">8.3676700592041</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">8.38266563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6151008605957</t>
+    <t xml:space="preserve">8.62259864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61509990692139</t>
   </si>
   <si>
     <t xml:space="preserve">8.5476188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41265773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519248962402</t>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519153594971</t>
   </si>
   <si>
     <t xml:space="preserve">8.32268142700195</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">8.87002944946289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67508220672607</t>
+    <t xml:space="preserve">8.90002155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.51762771606445</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">8.58510875701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012992858887</t>
+    <t xml:space="preserve">8.5101318359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36017036437988</t>
+    <t xml:space="preserve">8.3601713180542</t>
   </si>
   <si>
     <t xml:space="preserve">8.31518363952637</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">8.17272281646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271492004395</t>
+    <t xml:space="preserve">8.20271587371826</t>
   </si>
   <si>
     <t xml:space="preserve">8.45764446258545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42015361785889</t>
+    <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11273860931396</t>
+    <t xml:space="preserve">8.1127405166626</t>
   </si>
   <si>
     <t xml:space="preserve">8.09024620056152</t>
@@ -434,154 +434,154 @@
     <t xml:space="preserve">8.06775379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08274936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777843475342</t>
+    <t xml:space="preserve">8.08274841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18771839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777891159058</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13523483276367</t>
+    <t xml:space="preserve">8.13523387908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.24020481109619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22521018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12023735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00777053833008</t>
+    <t xml:space="preserve">8.2252082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1202392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00776958465576</t>
   </si>
   <si>
     <t xml:space="preserve">7.76783561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282424926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0302619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776073455811</t>
+    <t xml:space="preserve">7.82781934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93279075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280750274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029596328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033926010132</t>
+    <t xml:space="preserve">7.93278932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780355453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529344558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033878326416</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531713485718</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09667873382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69569969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967908859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390157699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2123441696167</t>
+    <t xml:space="preserve">8.09667778015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823518753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69570016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21234512329102</t>
   </si>
   <si>
     <t xml:space="preserve">7.82678890228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71112203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5568995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6185884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47978925704956</t>
+    <t xml:space="preserve">7.71112251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5414776802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47978830337524</t>
   </si>
   <si>
     <t xml:space="preserve">7.32556629180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41809892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725614547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845457077026</t>
+    <t xml:space="preserve">7.41809940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761083602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254413604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303270339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845552444458</t>
   </si>
   <si>
     <t xml:space="preserve">7.26387691497803</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">7.12507724761963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27929973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17134428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218896865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14050054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07881116867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29472208023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0942325592041</t>
+    <t xml:space="preserve">7.27929925918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17134380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965490341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14049911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07881164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014442443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423208236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.00169897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90916538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952150344849</t>
+    <t xml:space="preserve">6.90916585922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">6.86289882659912</t>
@@ -641,58 +641,58 @@
     <t xml:space="preserve">7.0171217918396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78578758239746</t>
+    <t xml:space="preserve">6.78578853607178</t>
   </si>
   <si>
     <t xml:space="preserve">6.94001054763794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95543336868286</t>
+    <t xml:space="preserve">6.95543241500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627758026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783212661743</t>
+    <t xml:space="preserve">6.67783164978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.70867681503296</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63156509399414</t>
+    <t xml:space="preserve">6.6315655708313</t>
   </si>
   <si>
     <t xml:space="preserve">6.47734212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46192073822021</t>
+    <t xml:space="preserve">6.46192121505737</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61614370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32312059402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40023183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2614312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27685451507568</t>
+    <t xml:space="preserve">6.61614322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3231201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.400230884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26143169403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.56987619400024</t>
@@ -701,25 +701,25 @@
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565370559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55445384979248</t>
+    <t xml:space="preserve">6.41565418243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374351501465</t>
+    <t xml:space="preserve">6.89374303817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.6469874382019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77036619186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107604980469</t>
+    <t xml:space="preserve">6.7703652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107557296753</t>
   </si>
   <si>
     <t xml:space="preserve">6.10720872879028</t>
@@ -737,49 +737,49 @@
     <t xml:space="preserve">5.99925327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24600982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66240930557251</t>
+    <t xml:space="preserve">6.246009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66241073608398</t>
   </si>
   <si>
     <t xml:space="preserve">6.49276494979858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35396480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649744033813</t>
+    <t xml:space="preserve">6.35396432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649696350098</t>
   </si>
   <si>
     <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36938762664795</t>
+    <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.75494337081909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87832164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085428237915</t>
+    <t xml:space="preserve">6.8783221244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085523605347</t>
   </si>
   <si>
     <t xml:space="preserve">7.04796648025513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115041732788</t>
+    <t xml:space="preserve">7.155921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676662445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338834762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2011513710022</t>
   </si>
   <si>
     <t xml:space="preserve">7.15314292907715</t>
@@ -788,88 +788,88 @@
     <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64106130599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00912094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913230895996</t>
+    <t xml:space="preserve">6.6410608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00912046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913373947144</t>
   </si>
   <si>
     <t xml:space="preserve">7.12113809585571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83309268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509704589844</t>
+    <t xml:space="preserve">6.83309173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
     <t xml:space="preserve">6.78508424758911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75307941436768</t>
+    <t xml:space="preserve">6.75307893753052</t>
   </si>
   <si>
     <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72107458114624</t>
+    <t xml:space="preserve">6.72107362747192</t>
   </si>
   <si>
     <t xml:space="preserve">6.48103618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54504632949829</t>
+    <t xml:space="preserve">6.54504680633545</t>
   </si>
   <si>
     <t xml:space="preserve">6.60905647277832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76908206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108690261841</t>
+    <t xml:space="preserve">6.76908159255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
     <t xml:space="preserve">6.89710235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81709051132202</t>
+    <t xml:space="preserve">6.81708955764771</t>
   </si>
   <si>
     <t xml:space="preserve">6.56104850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59305381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705163955688</t>
+    <t xml:space="preserve">6.65706443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59305334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705211639404</t>
   </si>
   <si>
     <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5130410194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702556610107</t>
+    <t xml:space="preserve">6.43302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51304149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44903135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702651977539</t>
   </si>
   <si>
     <t xml:space="preserve">6.40102338790894</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2249960899353</t>
+    <t xml:space="preserve">6.22499513626099</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04896640777588</t>
+    <t xml:space="preserve">6.04896688461304</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496953964233</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">5.95295143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96895456314087</t>
+    <t xml:space="preserve">6.01696109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96895360946655</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094659805298</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">5.680908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71291303634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8249306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90494394302368</t>
+    <t xml:space="preserve">5.71291351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90494441986084</t>
   </si>
   <si>
     <t xml:space="preserve">5.87293863296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79292631149292</t>
+    <t xml:space="preserve">5.79292583465576</t>
   </si>
   <si>
     <t xml:space="preserve">5.98495674133301</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">6.24099731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101011276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27300262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20899295806885</t>
+    <t xml:space="preserve">6.32101058959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27300310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38502073287964</t>
+    <t xml:space="preserve">6.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298982620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14498233795166</t>
+    <t xml:space="preserve">6.12897920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1449818611145</t>
   </si>
   <si>
     <t xml:space="preserve">6.25699996948242</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">5.61689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48887729644775</t>
+    <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55288791656494</t>
+    <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50487995147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089492797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3608570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12081909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73675775527954</t>
+    <t xml:space="preserve">5.50487947463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089540481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36085653305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12081861495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.67274761199951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871044158936</t>
+    <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.24067783355713</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">3.92062664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28868532180786</t>
+    <t xml:space="preserve">4.28868579864502</t>
   </si>
   <si>
     <t xml:space="preserve">4.04864692687988</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40070343017578</t>
+    <t xml:space="preserve">4.08065271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40070390701294</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075462341309</t>
@@ -1043,49 +1043,49 @@
     <t xml:space="preserve">4.92878770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13682079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52088212966919</t>
+    <t xml:space="preserve">5.13682126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32885217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3128490447998</t>
+    <t xml:space="preserve">5.3288516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31284856796265</t>
   </si>
   <si>
     <t xml:space="preserve">5.18482875823975</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0088005065918</t>
+    <t xml:space="preserve">5.00880098342896</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28084421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05680847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283624649048</t>
+    <t xml:space="preserve">5.28084373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05680894851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283672332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093379974365</t>
+    <t xml:space="preserve">5.72891569137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093427658081</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">5.69691038131714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85693645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58489322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486715316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56888961791992</t>
+    <t xml:space="preserve">5.85693693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58489227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889009475708</t>
   </si>
   <si>
     <t xml:space="preserve">5.3448543548584</t>
@@ -1115,25 +1115,25 @@
     <t xml:space="preserve">5.44086980819702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37685966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484155654907</t>
+    <t xml:space="preserve">5.37685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484107971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.24883890151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45687198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688526153564</t>
+    <t xml:space="preserve">5.45687246322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688478469849</t>
   </si>
   <si>
     <t xml:space="preserve">5.29684638977051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683359146118</t>
+    <t xml:space="preserve">5.21683406829834</t>
   </si>
   <si>
     <t xml:space="preserve">6.3530158996582</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">6.49703884124756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70507192611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915885925293</t>
+    <t xml:space="preserve">6.7050724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67306613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915933609009</t>
   </si>
   <si>
     <t xml:space="preserve">7.26516103744507</t>
@@ -1166,16 +1166,16 @@
     <t xml:space="preserve">7.64922285079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58521175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60121536254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52120208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5372052192688</t>
+    <t xml:space="preserve">7.58521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60121488571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5212025642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53720426559448</t>
   </si>
   <si>
     <t xml:space="preserve">7.47319555282593</t>
@@ -1184,34 +1184,34 @@
     <t xml:space="preserve">7.44118928909302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45719194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40918445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318132400513</t>
+    <t xml:space="preserve">7.45719242095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40918397903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318180084229</t>
   </si>
   <si>
     <t xml:space="preserve">7.23315668106079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3131685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518758773804</t>
+    <t xml:space="preserve">7.31316947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518663406372</t>
   </si>
   <si>
     <t xml:space="preserve">7.50519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36117696762085</t>
+    <t xml:space="preserve">7.36117601394653</t>
   </si>
   <si>
     <t xml:space="preserve">7.29716682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7452392578125</t>
+    <t xml:space="preserve">7.74523830413818</t>
   </si>
   <si>
     <t xml:space="preserve">7.84125328063965</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">7.90526390075684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08129119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04128646850586</t>
+    <t xml:space="preserve">8.0812931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04128551483154</t>
   </si>
   <si>
     <t xml:space="preserve">7.92126655578613</t>
@@ -1238,49 +1238,49 @@
     <t xml:space="preserve">8.0012788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8732590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327138900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132343292236</t>
+    <t xml:space="preserve">7.87325811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327043533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129783630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927309036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">8.40134239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44134998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00143909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8414134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145805358887</t>
+    <t xml:space="preserve">8.44134902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00143814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145709991455</t>
   </si>
   <si>
     <t xml:space="preserve">9.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9614315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48151588439941</t>
+    <t xml:space="preserve">8.96143245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1298,34 +1298,34 @@
     <t xml:space="preserve">10.1216173171997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2816438674927</t>
+    <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
     <t xml:space="preserve">10.3216495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7217140197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3218107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.201789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0417642593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9617509841919</t>
+    <t xml:space="preserve">10.7217130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3218097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2017908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217775344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8417320251465</t>
+    <t xml:space="preserve">10.8417329788208</t>
   </si>
   <si>
     <t xml:space="preserve">10.881739616394</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817708969116</t>
+    <t xml:space="preserve">11.2417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817728042603</t>
   </si>
   <si>
     <t xml:space="preserve">10.7617197036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0017585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6016960144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818031311035</t>
+    <t xml:space="preserve">11.0017576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.60169506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818040847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.6965761184692</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">11.1573705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7011222839355</t>
+    <t xml:space="preserve">10.7011213302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204414367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.161919593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0789642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99600887298584</t>
+    <t xml:space="preserve">10.037486076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1619186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0789632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99600982666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305637359619</t>
@@ -1391,43 +1391,43 @@
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.327826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914636611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8670301437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
+    <t xml:space="preserve">10.3278274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7425985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766897201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
   </si>
   <si>
     <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2033958435059</t>
+    <t xml:space="preserve">10.2033948898315</t>
   </si>
   <si>
     <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522590637207</t>
+    <t xml:space="preserve">10.452260017395</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
@@ -1439,40 +1439,37 @@
     <t xml:space="preserve">11.115894317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085073471069</t>
+    <t xml:space="preserve">10.9085083007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.032940864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.323281288147</t>
+    <t xml:space="preserve">10.6596441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0329399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232803344727</t>
   </si>
   <si>
     <t xml:space="preserve">11.4891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818040847778</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.2403259277344</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5306673049927</t>
+    <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
     <t xml:space="preserve">11.7795295715332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2772569656372</t>
+    <t xml:space="preserve">12.2772579193115</t>
   </si>
   <si>
     <t xml:space="preserve">12.3602104187012</t>
@@ -1481,28 +1478,28 @@
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5675973892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.816460609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2727098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630502700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460046768188</t>
+    <t xml:space="preserve">12.3187351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261201858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5675964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8164615631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2727108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119134902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460056304932</t>
   </si>
   <si>
     <t xml:space="preserve">13.5215730667114</t>
@@ -1514,13 +1511,13 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0192995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6874828338623</t>
+    <t xml:space="preserve">14.0193004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.687481880188</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312316894531</t>
@@ -1541,25 +1538,25 @@
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647575378418</t>
+    <t xml:space="preserve">11.3647584915161</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062356948853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8210067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988496780396</t>
+    <t xml:space="preserve">11.8210077285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988477706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862380981445</t>
+    <t xml:space="preserve">11.7380523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862476348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.66419124603271</t>
@@ -1580,25 +1577,25 @@
     <t xml:space="preserve">11.0661220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177133560181</t>
+    <t xml:space="preserve">10.7177124023438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6347589492798</t>
+    <t xml:space="preserve">10.7343034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.651349067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6347579956055</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8504400253296</t>
+    <t xml:space="preserve">10.8504409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168043136597</t>
@@ -1619,19 +1616,19 @@
     <t xml:space="preserve">10.9997577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4003810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.46937084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3313932418823</t>
+    <t xml:space="preserve">10.8338499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4003820419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.331392288208</t>
   </si>
   <si>
     <t xml:space="preserve">11.2279100418091</t>
@@ -1664,28 +1661,28 @@
     <t xml:space="preserve">12.0212783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1420087814331</t>
+    <t xml:space="preserve">12.1420078277588</t>
   </si>
   <si>
     <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5038642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0730199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2106628417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035276412964</t>
+    <t xml:space="preserve">11.5038633346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0730209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2106618881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
     <t xml:space="preserve">10.7794828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6932468414307</t>
+    <t xml:space="preserve">10.6932458877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6242570877075</t>
@@ -1694,7 +1691,7 @@
     <t xml:space="preserve">11.0036964416504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1589202880859</t>
+    <t xml:space="preserve">11.1589193344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.7625713348389</t>
@@ -1706,7 +1703,7 @@
     <t xml:space="preserve">11.3831329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9522905349731</t>
+    <t xml:space="preserve">11.9522895812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280778884888</t>
@@ -1715,10 +1712,10 @@
     <t xml:space="preserve">11.5728530883789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.69358253479</t>
+    <t xml:space="preserve">11.7453241348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6935834884644</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
@@ -1727,13 +1724,13 @@
     <t xml:space="preserve">11.8660554885864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2627401351929</t>
+    <t xml:space="preserve">12.2627391815186</t>
   </si>
   <si>
     <t xml:space="preserve">11.9867849349976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9177951812744</t>
+    <t xml:space="preserve">11.9177961349487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765031814575</t>
@@ -1742,25 +1739,25 @@
     <t xml:space="preserve">12.3144798278809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3317279815674</t>
+    <t xml:space="preserve">12.3317289352417</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">11.9695377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970666885376</t>
+    <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
@@ -1790,7 +1787,7 @@
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
+    <t xml:space="preserve">11.4348754882812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0381908416748</t>
@@ -1805,7 +1802,7 @@
     <t xml:space="preserve">11.1244249343872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1416730880737</t>
+    <t xml:space="preserve">11.141674041748</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
@@ -1814,16 +1811,16 @@
     <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.641505241394</t>
+    <t xml:space="preserve">10.6415061950684</t>
   </si>
   <si>
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3483028411865</t>
+    <t xml:space="preserve">10.5207738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3483037948608</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
@@ -1874,7 +1871,7 @@
     <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869527816772</t>
+    <t xml:space="preserve">12.4869518280029</t>
   </si>
   <si>
     <t xml:space="preserve">12.573187828064</t>
@@ -1895,16 +1892,16 @@
     <t xml:space="preserve">12.2799863815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4352121353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7798175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7108297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2968969345093</t>
+    <t xml:space="preserve">12.4352111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7798185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7108287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521217346191</t>
@@ -1913,10 +1910,10 @@
     <t xml:space="preserve">11.2624034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3141450881958</t>
+    <t xml:space="preserve">11.2796506881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
@@ -1928,25 +1925,25 @@
     <t xml:space="preserve">11.0554370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7967290878296</t>
+    <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347076416016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8657188415527</t>
+    <t xml:space="preserve">10.8657178878784</t>
   </si>
   <si>
     <t xml:space="preserve">10.7622346878052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5725173950195</t>
+    <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
     <t xml:space="preserve">10.6070108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4345397949219</t>
+    <t xml:space="preserve">10.4345388412476</t>
   </si>
   <si>
     <t xml:space="preserve">10.4517860412598</t>
@@ -1961,7 +1958,7 @@
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2770614624023</t>
+    <t xml:space="preserve">10.277060508728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
@@ -1991,7 +1988,7 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509292602539</t>
+    <t xml:space="preserve">9.93509197235107</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870698928833</t>
@@ -2003,25 +2000,25 @@
     <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250844955444</t>
+    <t xml:space="preserve">9.95309066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790796279907</t>
+    <t xml:space="preserve">10.0790786743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910396575928</t>
+    <t xml:space="preserve">10.1510715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910301208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2033,7 +2030,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210481643677</t>
+    <t xml:space="preserve">10.4210472106934</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2042,16 +2039,16 @@
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130578994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950601577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3670539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84510135650635</t>
+    <t xml:space="preserve">10.3130588531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3670530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84510040283203</t>
   </si>
   <si>
     <t xml:space="preserve">9.79110622406006</t>
@@ -2066,13 +2063,13 @@
     <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17916107177734</t>
+    <t xml:space="preserve">9.17916202545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715038299561</t>
+    <t xml:space="preserve">9.28715133666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.48513317108154</t>
@@ -2084,7 +2081,7 @@
     <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35914421081543</t>
+    <t xml:space="preserve">9.35914516448975</t>
   </si>
   <si>
     <t xml:space="preserve">9.32314777374268</t>
@@ -2096,7 +2093,7 @@
     <t xml:space="preserve">9.01717662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0891695022583</t>
+    <t xml:space="preserve">9.08917045593262</t>
   </si>
   <si>
     <t xml:space="preserve">9.05317306518555</t>
@@ -2111,7 +2108,7 @@
     <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97218132019043</t>
+    <t xml:space="preserve">8.97218036651611</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2120,7 +2117,7 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4772253036499</t>
+    <t xml:space="preserve">8.47722625732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.62121200561523</t>
@@ -2129,7 +2126,7 @@
     <t xml:space="preserve">8.63921165466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63021183013916</t>
+    <t xml:space="preserve">8.63021087646484</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
@@ -2150,13 +2147,13 @@
     <t xml:space="preserve">7.90127801895142</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0992603302002</t>
+    <t xml:space="preserve">8.09925937652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05426502227783</t>
+    <t xml:space="preserve">8.05426406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.00926780700684</t>
@@ -2174,13 +2171,13 @@
     <t xml:space="preserve">7.89227962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97327184677124</t>
+    <t xml:space="preserve">7.97327089309692</t>
   </si>
   <si>
     <t xml:space="preserve">7.83828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91927671432495</t>
+    <t xml:space="preserve">7.91927576065063</t>
   </si>
   <si>
     <t xml:space="preserve">7.78428888320923</t>
@@ -2195,10 +2192,10 @@
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533121109009</t>
+    <t xml:space="preserve">7.63130235671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32533073425293</t>
   </si>
   <si>
     <t xml:space="preserve">7.19934272766113</t>
@@ -2228,19 +2225,19 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19034290313721</t>
+    <t xml:space="preserve">6.95636463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19034242630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10935115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25333786010742</t>
+    <t xml:space="preserve">7.10935068130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25333738327026</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
@@ -2249,7 +2246,7 @@
     <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51431369781494</t>
+    <t xml:space="preserve">7.5143141746521</t>
   </si>
   <si>
     <t xml:space="preserve">7.49631500244141</t>
@@ -2258,19 +2255,19 @@
     <t xml:space="preserve">7.30733251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46931791305542</t>
+    <t xml:space="preserve">7.46931838989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.28933429718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28033542633057</t>
+    <t xml:space="preserve">7.28033494949341</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434646606445</t>
+    <t xml:space="preserve">7.15434598922729</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
@@ -2285,22 +2282,22 @@
     <t xml:space="preserve">7.06435441970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68529748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99127054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627475738525</t>
+    <t xml:space="preserve">7.68529796600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99127006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627380371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024459838867</t>
+    <t xml:space="preserve">8.27024364471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.37823581695557</t>
@@ -2309,13 +2306,13 @@
     <t xml:space="preserve">8.55821800231934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75619983673096</t>
+    <t xml:space="preserve">8.75619888305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74720096588135</t>
+    <t xml:space="preserve">8.74720191955566</t>
   </si>
   <si>
     <t xml:space="preserve">8.56721782684326</t>
@@ -2339,7 +2336,7 @@
     <t xml:space="preserve">8.06326389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11725997924805</t>
+    <t xml:space="preserve">8.11725902557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2348,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922756195068</t>
+    <t xml:space="preserve">8.45922660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2366,13 +2363,13 @@
     <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9789972305298</t>
+    <t xml:space="preserve">10.9789962768555</t>
   </si>
   <si>
     <t xml:space="preserve">10.8350105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6370286941528</t>
+    <t xml:space="preserve">10.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.90700340271</t>
@@ -2384,7 +2381,7 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550264358521</t>
+    <t xml:space="preserve">10.6550273895264</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
@@ -2399,7 +2396,7 @@
     <t xml:space="preserve">11.2489719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1229829788208</t>
+    <t xml:space="preserve">11.1229839324951</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2411,10 +2408,10 @@
     <t xml:space="preserve">11.4829511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4649515151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2669706344604</t>
+    <t xml:space="preserve">11.4649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2669715881348</t>
   </si>
   <si>
     <t xml:space="preserve">11.3389644622803</t>
@@ -2429,7 +2426,7 @@
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089382171631</t>
+    <t xml:space="preserve">11.6089391708374</t>
   </si>
   <si>
     <t xml:space="preserve">11.5009489059448</t>
@@ -2447,13 +2444,13 @@
     <t xml:space="preserve">11.8249206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349271774292</t>
+    <t xml:space="preserve">11.7349281311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529268264771</t>
+    <t xml:space="preserve">11.7529277801514</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429183959961</t>
@@ -2480,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578472137451</t>
+    <t xml:space="preserve">11.3578481674194</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514036178589</t>
+    <t xml:space="preserve">11.4514045715332</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2081546783447</t>
+    <t xml:space="preserve">11.208155632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2501,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443441390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688810348511</t>
+    <t xml:space="preserve">11.8443450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688819885254</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2513,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940357208252</t>
+    <t xml:space="preserve">11.9940366744995</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133646011353</t>
+    <t xml:space="preserve">11.7133655548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2534,7 +2531,10 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4139814376831</t>
+    <t xml:space="preserve">11.8069219589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4139804840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823841094971</t>
+    <t xml:space="preserve">11.5823850631714</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624383926392</t>
+    <t xml:space="preserve">12.1624393463135</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.919189453125</t>
+    <t xml:space="preserve">11.9191904067993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5449619293213</t>
+    <t xml:space="preserve">11.544960975647</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.058464050293</t>
+    <t xml:space="preserve">11.0584630966187</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771751403809</t>
+    <t xml:space="preserve">11.0771760940552</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842355728149</t>
+    <t xml:space="preserve">10.6842346191406</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222755432129</t>
+    <t xml:space="preserve">10.4784088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222745895386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287181854248</t>
+    <t xml:space="preserve">10.3287172317505</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977376937866</t>
+    <t xml:space="preserve">10.1977367401123</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -42680,7 +42680,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -42732,7 +42732,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1509" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -42758,7 +42758,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1510" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -42784,7 +42784,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42810,7 +42810,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1512" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42836,7 +42836,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42862,7 +42862,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1514" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42888,7 +42888,7 @@
         <v>15.25</v>
       </c>
       <c r="G1515" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42914,7 +42914,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1516" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42940,7 +42940,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1517" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42966,7 +42966,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1518" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42992,7 +42992,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43018,7 +43018,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1520" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43044,7 +43044,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1521" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43070,7 +43070,7 @@
         <v>16</v>
       </c>
       <c r="G1522" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43096,7 +43096,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1523" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43122,7 +43122,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43148,7 +43148,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1525" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43174,7 +43174,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43200,7 +43200,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43226,7 +43226,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1528" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43252,7 +43252,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43278,7 +43278,7 @@
         <v>16.75</v>
       </c>
       <c r="G1530" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43304,7 +43304,7 @@
         <v>16.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43330,7 +43330,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1532" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43356,7 +43356,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43382,7 +43382,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1534" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43408,7 +43408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43434,7 +43434,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1536" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43460,7 +43460,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43486,7 +43486,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1538" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43512,7 +43512,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43538,7 +43538,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1540" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43564,7 +43564,7 @@
         <v>14.5</v>
       </c>
       <c r="G1541" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43590,7 +43590,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1542" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43616,7 +43616,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1543" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43642,7 +43642,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1544" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -43668,7 +43668,7 @@
         <v>13.75</v>
       </c>
       <c r="G1545" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -43694,7 +43694,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1546" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -43720,7 +43720,7 @@
         <v>14.25</v>
       </c>
       <c r="G1547" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43746,7 +43746,7 @@
         <v>14.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43772,7 +43772,7 @@
         <v>14.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43824,7 +43824,7 @@
         <v>13.75</v>
       </c>
       <c r="G1551" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43850,7 +43850,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1552" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43902,7 +43902,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1554" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43954,7 +43954,7 @@
         <v>13.5</v>
       </c>
       <c r="G1556" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44006,7 +44006,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1558" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44032,7 +44032,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1559" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44058,7 +44058,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1560" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44136,7 +44136,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1563" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44162,7 +44162,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1564" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44214,7 +44214,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1566" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44240,7 +44240,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44344,7 +44344,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1571" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44370,7 +44370,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1572" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44396,7 +44396,7 @@
         <v>11.75</v>
       </c>
       <c r="G1573" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44682,7 +44682,7 @@
         <v>13.5</v>
       </c>
       <c r="G1584" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -44786,7 +44786,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1588" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44812,7 +44812,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1589" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44838,7 +44838,7 @@
         <v>14</v>
       </c>
       <c r="G1590" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44864,7 +44864,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1591" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44890,7 +44890,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1592" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44942,7 +44942,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1594" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44994,7 +44994,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1596" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45020,7 +45020,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1597" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45046,7 +45046,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1598" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45072,7 +45072,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1599" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45098,7 +45098,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1600" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45124,7 +45124,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1601" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45150,7 +45150,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1602" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45202,7 +45202,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1604" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45228,7 +45228,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1605" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45254,7 +45254,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1606" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45306,7 +45306,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1608" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45410,7 +45410,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1612" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45436,7 +45436,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1613" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45488,7 +45488,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1615" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45514,7 +45514,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1616" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45540,7 +45540,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1617" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45566,7 +45566,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1618" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45592,7 +45592,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1619" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45618,7 +45618,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1620" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45644,7 +45644,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1621" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -45670,7 +45670,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1622" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45696,7 +45696,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1623" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45722,7 +45722,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1624" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45748,7 +45748,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45774,7 +45774,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1626" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45800,7 +45800,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1627" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45826,7 +45826,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1628" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45852,7 +45852,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1629" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45878,7 +45878,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45904,7 +45904,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1631" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45930,7 +45930,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1632" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45956,7 +45956,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1633" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45982,7 +45982,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1634" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46008,7 +46008,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46034,7 +46034,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1636" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46060,7 +46060,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1637" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46086,7 +46086,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1638" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46112,7 +46112,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1639" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46138,7 +46138,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1640" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46164,7 +46164,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1641" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46190,7 +46190,7 @@
         <v>14</v>
       </c>
       <c r="G1642" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46216,7 +46216,7 @@
         <v>13</v>
       </c>
       <c r="G1643" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46242,7 +46242,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1644" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46268,7 +46268,7 @@
         <v>12.5</v>
       </c>
       <c r="G1645" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46294,7 +46294,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46320,7 +46320,7 @@
         <v>13</v>
       </c>
       <c r="G1647" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46346,7 +46346,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1648" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46372,7 +46372,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1649" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46398,7 +46398,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1650" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46424,7 +46424,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1651" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46450,7 +46450,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1652" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46476,7 +46476,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1653" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46502,7 +46502,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1654" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46528,7 +46528,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1655" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46554,7 +46554,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1656" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46580,7 +46580,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1657" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46606,7 +46606,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1658" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46632,7 +46632,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1659" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46658,7 +46658,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1660" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46684,7 +46684,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1661" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46710,7 +46710,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1662" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46736,7 +46736,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1663" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46762,7 +46762,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1664" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46788,7 +46788,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1665" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46814,7 +46814,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1666" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46840,7 +46840,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1667" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46866,7 +46866,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1668" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46892,7 +46892,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46918,7 +46918,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1670" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46944,7 +46944,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1671" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46970,7 +46970,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1672" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46996,7 +46996,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1673" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47022,7 +47022,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1674" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47048,7 +47048,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1675" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47074,7 +47074,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1676" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47100,7 +47100,7 @@
         <v>14</v>
       </c>
       <c r="G1677" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47126,7 +47126,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1678" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47152,7 +47152,7 @@
         <v>14</v>
       </c>
       <c r="G1679" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47178,7 +47178,7 @@
         <v>14</v>
       </c>
       <c r="G1680" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47204,7 +47204,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1681" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47230,7 +47230,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1682" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47256,7 +47256,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1683" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47282,7 +47282,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1684" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47308,7 +47308,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1685" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47334,7 +47334,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1686" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47360,7 +47360,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1687" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47386,7 +47386,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47412,7 +47412,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1689" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47438,7 +47438,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1690" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47464,7 +47464,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1691" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47490,7 +47490,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1692" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47516,7 +47516,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1693" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47542,7 +47542,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1694" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47568,7 +47568,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1695" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47594,7 +47594,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1696" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47620,7 +47620,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47646,7 +47646,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1698" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47672,7 +47672,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1699" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47698,7 +47698,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1700" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47724,7 +47724,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1701" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47750,7 +47750,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1702" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47776,7 +47776,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1703" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47802,7 +47802,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1704" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47828,7 +47828,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1705" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47854,7 +47854,7 @@
         <v>13.5</v>
       </c>
       <c r="G1706" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47880,7 +47880,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1707" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47906,7 +47906,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1708" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47932,7 +47932,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1709" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47958,7 +47958,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1710" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47984,7 +47984,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1711" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48010,7 +48010,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1712" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48036,7 +48036,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1713" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48062,7 +48062,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1714" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48088,7 +48088,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1715" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48114,7 +48114,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1716" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48140,7 +48140,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1717" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48166,7 +48166,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48192,7 +48192,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1719" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48218,7 +48218,7 @@
         <v>13</v>
       </c>
       <c r="G1720" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48244,7 +48244,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1721" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48270,7 +48270,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1722" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48296,7 +48296,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1723" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48322,7 +48322,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1724" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48348,7 +48348,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1725" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48374,7 +48374,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48400,7 +48400,7 @@
         <v>12</v>
       </c>
       <c r="G1727" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48426,7 +48426,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1728" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48452,7 +48452,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1729" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48478,7 +48478,7 @@
         <v>12.5</v>
       </c>
       <c r="G1730" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48504,7 +48504,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1731" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48530,7 +48530,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1732" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48556,7 +48556,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1733" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48582,7 +48582,7 @@
         <v>12</v>
       </c>
       <c r="G1734" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48608,7 +48608,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1735" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48634,7 +48634,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1736" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48660,7 +48660,7 @@
         <v>12.5</v>
       </c>
       <c r="G1737" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48686,7 +48686,7 @@
         <v>13</v>
       </c>
       <c r="G1738" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48712,7 +48712,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1739" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48738,7 +48738,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48764,7 +48764,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1741" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48790,7 +48790,7 @@
         <v>13.5</v>
       </c>
       <c r="G1742" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48816,7 +48816,7 @@
         <v>13.5</v>
       </c>
       <c r="G1743" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48842,7 +48842,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1744" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48868,7 +48868,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1745" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48894,7 +48894,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48920,7 +48920,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1747" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48946,7 +48946,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1748" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48972,7 +48972,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1749" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48998,7 +48998,7 @@
         <v>13.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49024,7 +49024,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1751" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49050,7 +49050,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1752" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49076,7 +49076,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1753" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49102,7 +49102,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1754" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49128,7 +49128,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1755" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49154,7 +49154,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1756" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49180,7 +49180,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49206,7 +49206,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1758" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49232,7 +49232,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1759" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49258,7 +49258,7 @@
         <v>13.5</v>
       </c>
       <c r="G1760" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49284,7 +49284,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1761" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49310,7 +49310,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1762" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49336,7 +49336,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1763" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49362,7 +49362,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1764" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49388,7 +49388,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1765" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49414,7 +49414,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49440,7 +49440,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1767" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49466,7 +49466,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1768" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49492,7 +49492,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1769" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49518,7 +49518,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1770" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49544,7 +49544,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1771" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49570,7 +49570,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1772" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49596,7 +49596,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1773" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49622,7 +49622,7 @@
         <v>13.5</v>
       </c>
       <c r="G1774" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49648,7 +49648,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1775" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49674,7 +49674,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1776" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49700,7 +49700,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1777" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49726,7 +49726,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1778" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49752,7 +49752,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49778,7 +49778,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1780" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49804,7 +49804,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1781" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49830,7 +49830,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1782" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49856,7 +49856,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1783" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49882,7 +49882,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1784" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49908,7 +49908,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1785" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49934,7 +49934,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1786" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49960,7 +49960,7 @@
         <v>14</v>
       </c>
       <c r="G1787" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49986,7 +49986,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50012,7 +50012,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1789" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50038,7 +50038,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1790" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50064,7 +50064,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1791" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50090,7 +50090,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1792" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50116,7 +50116,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1793" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50142,7 +50142,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50168,7 +50168,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1795" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50194,7 +50194,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1796" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50220,7 +50220,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1797" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50246,7 +50246,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1798" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50272,7 +50272,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1799" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50298,7 +50298,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1800" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50324,7 +50324,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1801" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50350,7 +50350,7 @@
         <v>14.5</v>
       </c>
       <c r="G1802" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50376,7 +50376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1803" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50402,7 +50402,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1804" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50428,7 +50428,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1805" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50454,7 +50454,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1806" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50480,7 +50480,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1807" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50506,7 +50506,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1808" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50532,7 +50532,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1809" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50558,7 +50558,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1810" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50584,7 +50584,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1811" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50610,7 +50610,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1812" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50636,7 +50636,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1813" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -50662,7 +50662,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50688,7 +50688,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1815" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50714,7 +50714,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1816" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50740,7 +50740,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1817" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50766,7 +50766,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1818" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50792,7 +50792,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1819" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50818,7 +50818,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1820" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50844,7 +50844,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1821" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50870,7 +50870,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1822" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50896,7 +50896,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1823" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50922,7 +50922,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1824" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50948,7 +50948,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1825" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50974,7 +50974,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1826" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51000,7 +51000,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1827" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51026,7 +51026,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1828" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51052,7 +51052,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1829" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51078,7 +51078,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1830" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51104,7 +51104,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1831" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51130,7 +51130,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51156,7 +51156,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1833" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51182,7 +51182,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1834" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51208,7 +51208,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1835" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51234,7 +51234,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1836" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51260,7 +51260,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51286,7 +51286,7 @@
         <v>13</v>
       </c>
       <c r="G1838" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51312,7 +51312,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1839" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51338,7 +51338,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1840" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51364,7 +51364,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1841" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51390,7 +51390,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1842" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51416,7 +51416,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1843" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51442,7 +51442,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1844" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51468,7 +51468,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1845" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51494,7 +51494,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51520,7 +51520,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1847" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51546,7 +51546,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1848" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51572,7 +51572,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1849" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51598,7 +51598,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1850" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51624,7 +51624,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1851" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51650,7 +51650,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -51676,7 +51676,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1853" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51702,7 +51702,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1854" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51728,7 +51728,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1855" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51754,7 +51754,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1856" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51780,7 +51780,7 @@
         <v>12.5</v>
       </c>
       <c r="G1857" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51806,7 +51806,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1858" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51832,7 +51832,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1859" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51858,7 +51858,7 @@
         <v>12.5</v>
       </c>
       <c r="G1860" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51884,7 +51884,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1861" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51910,7 +51910,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1862" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51936,7 +51936,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51962,7 +51962,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51988,7 +51988,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1865" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52014,7 +52014,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1866" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52040,7 +52040,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1867" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52066,7 +52066,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1868" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52092,7 +52092,7 @@
         <v>12</v>
       </c>
       <c r="G1869" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52118,7 +52118,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1870" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52144,7 +52144,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1871" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52170,7 +52170,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1872" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52196,7 +52196,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1873" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52222,7 +52222,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1874" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52248,7 +52248,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1875" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52274,7 +52274,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1876" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52300,7 +52300,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1877" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52326,7 +52326,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1878" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52352,7 +52352,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1879" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52378,7 +52378,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52404,7 +52404,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1881" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52430,7 +52430,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1882" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52456,7 +52456,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1883" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52482,7 +52482,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52508,7 +52508,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1885" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52534,7 +52534,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1886" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52560,7 +52560,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1887" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52586,7 +52586,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1888" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52612,7 +52612,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1889" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52638,7 +52638,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1890" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52664,7 +52664,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1891" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52690,7 +52690,7 @@
         <v>11</v>
       </c>
       <c r="G1892" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52716,7 +52716,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1893" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52742,7 +52742,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1894" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52768,7 +52768,7 @@
         <v>11</v>
       </c>
       <c r="G1895" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52794,7 +52794,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1896" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52820,7 +52820,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1897" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52846,7 +52846,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52872,7 +52872,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1899" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52898,7 +52898,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1900" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52924,7 +52924,7 @@
         <v>11</v>
       </c>
       <c r="G1901" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52950,7 +52950,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1902" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52976,7 +52976,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1903" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53002,7 +53002,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1904" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53028,7 +53028,7 @@
         <v>11.5</v>
       </c>
       <c r="G1905" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53054,7 +53054,7 @@
         <v>11.5</v>
       </c>
       <c r="G1906" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53080,7 +53080,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1907" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53106,7 +53106,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1908" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53132,7 +53132,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1909" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53158,7 +53158,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53184,7 +53184,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1911" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53210,7 +53210,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1912" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53236,7 +53236,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1913" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53262,7 +53262,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53288,7 +53288,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53314,7 +53314,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1916" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53340,7 +53340,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53366,7 +53366,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1918" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53392,7 +53392,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1919" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53418,7 +53418,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1920" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53444,7 +53444,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1921" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53470,7 +53470,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1922" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53496,7 +53496,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1923" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53522,7 +53522,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1924" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53548,7 +53548,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1925" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53574,7 +53574,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1926" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53600,7 +53600,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1927" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53626,7 +53626,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53652,7 +53652,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1929" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53678,7 +53678,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1930" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53704,7 +53704,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1931" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53730,7 +53730,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1932" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53756,7 +53756,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1933" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53782,7 +53782,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1934" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53808,7 +53808,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1935" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53834,7 +53834,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1936" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53860,7 +53860,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1937" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53886,7 +53886,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1938" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53912,7 +53912,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53938,7 +53938,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1940" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53964,7 +53964,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1941" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53990,7 +53990,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1942" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54016,7 +54016,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1943" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54042,7 +54042,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54068,7 +54068,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1945" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54094,7 +54094,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G1946" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54120,7 +54120,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1947" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54146,7 +54146,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1948" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54172,7 +54172,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54198,7 +54198,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G1950" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54224,7 +54224,7 @@
         <v>10</v>
       </c>
       <c r="G1951" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54250,7 +54250,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1952" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54276,7 +54276,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1953" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54302,7 +54302,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1954" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54328,7 +54328,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1955" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54354,7 +54354,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1956" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54380,7 +54380,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54406,7 +54406,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54432,7 +54432,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1959" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54458,7 +54458,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1960" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54484,7 +54484,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1961" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54510,7 +54510,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1962" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54536,7 +54536,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54562,7 +54562,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1964" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54588,7 +54588,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1965" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54614,7 +54614,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1966" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54640,7 +54640,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1967" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54666,7 +54666,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54692,7 +54692,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54718,7 +54718,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54744,7 +54744,7 @@
         <v>9</v>
       </c>
       <c r="G1971" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54770,7 +54770,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1972" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54796,7 +54796,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54822,7 +54822,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1974" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54848,7 +54848,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1975" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54874,7 +54874,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54900,7 +54900,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1977" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54926,7 +54926,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G1978" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54952,7 +54952,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1979" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54978,7 +54978,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G1980" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55004,7 +55004,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1981" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55030,7 +55030,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1982" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55056,7 +55056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55082,7 +55082,7 @@
         <v>8.5</v>
       </c>
       <c r="G1984" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55108,7 +55108,7 @@
         <v>8.5</v>
       </c>
       <c r="G1985" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55134,7 +55134,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1986" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55160,7 +55160,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1987" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55186,7 +55186,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1988" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55212,7 +55212,7 @@
         <v>8</v>
       </c>
       <c r="G1989" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55238,7 +55238,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55264,7 +55264,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1991" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55290,7 +55290,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1992" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55316,7 +55316,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1993" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55342,7 +55342,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1994" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55368,7 +55368,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1995" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55394,7 +55394,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1996" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55420,7 +55420,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1997" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55446,7 +55446,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55472,7 +55472,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1999" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55498,7 +55498,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55524,7 +55524,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2001" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55550,7 +55550,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2002" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55576,7 +55576,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2003" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55602,7 +55602,7 @@
         <v>8.25</v>
       </c>
       <c r="G2004" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55628,7 +55628,7 @@
         <v>8.5</v>
       </c>
       <c r="G2005" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55654,7 +55654,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2006" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55680,7 +55680,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G2007" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55706,7 +55706,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2008" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55732,7 +55732,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2009" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55758,7 +55758,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2010" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55784,7 +55784,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2011" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55810,7 +55810,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G2012" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55836,7 +55836,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2013" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55862,7 +55862,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55888,7 +55888,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2015" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55914,7 +55914,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2016" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55940,7 +55940,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2017" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55966,7 +55966,7 @@
         <v>8</v>
       </c>
       <c r="G2018" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55992,7 +55992,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2019" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56018,7 +56018,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G2020" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56044,7 +56044,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2021" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56070,7 +56070,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2022" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56096,7 +56096,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2023" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56122,7 +56122,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56148,7 +56148,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2025" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56174,7 +56174,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56200,7 +56200,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56226,7 +56226,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2028" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56252,7 +56252,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2029" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56278,7 +56278,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56304,7 +56304,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2031" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56330,7 +56330,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G2032" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56356,7 +56356,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2033" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56382,7 +56382,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2034" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56408,7 +56408,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G2035" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56434,7 +56434,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G2036" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56460,7 +56460,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2037" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56486,7 +56486,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2038" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56512,7 +56512,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G2039" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56538,7 +56538,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2040" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56564,7 +56564,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2041" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56590,7 +56590,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G2042" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56616,7 +56616,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2043" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56642,7 +56642,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2044" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56668,7 +56668,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2045" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56694,7 +56694,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2046" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56720,7 +56720,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2047" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56746,7 +56746,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G2048" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56772,7 +56772,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2049" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56798,7 +56798,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G2050" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56824,7 +56824,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2051" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56850,7 +56850,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2052" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56876,7 +56876,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2053" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56902,7 +56902,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2054" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56928,7 +56928,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2055" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56954,7 +56954,7 @@
         <v>9</v>
       </c>
       <c r="G2056" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56980,7 +56980,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2057" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57006,7 +57006,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2058" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57032,7 +57032,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G2059" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57058,7 +57058,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2060" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57084,7 +57084,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G2061" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57110,7 +57110,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G2062" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57136,7 +57136,7 @@
         <v>9.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57162,7 +57162,7 @@
         <v>9.5</v>
       </c>
       <c r="G2064" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57188,7 +57188,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G2065" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57214,7 +57214,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2066" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57240,7 +57240,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2067" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57266,7 +57266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2068" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57292,7 +57292,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2069" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57318,7 +57318,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G2070" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57344,7 +57344,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2071" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57370,7 +57370,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2072" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57396,7 +57396,7 @@
         <v>11</v>
       </c>
       <c r="G2073" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57422,7 +57422,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2074" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57448,7 +57448,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2075" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57474,7 +57474,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2076" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57500,7 +57500,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G2077" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57526,7 +57526,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57552,7 +57552,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2079" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57578,7 +57578,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2080" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57604,7 +57604,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2081" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57630,7 +57630,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2082" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57656,7 +57656,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2083" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57682,7 +57682,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57708,7 +57708,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G2085" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57734,7 +57734,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2086" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57760,7 +57760,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57786,7 +57786,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2088" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57812,7 +57812,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2089" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57838,7 +57838,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2090" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57864,7 +57864,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2091" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57890,7 +57890,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2092" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57916,7 +57916,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2093" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57942,7 +57942,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2094" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57968,7 +57968,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2095" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57994,7 +57994,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2096" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58020,7 +58020,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2097" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58046,7 +58046,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2098" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58072,7 +58072,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2099" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58098,7 +58098,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2100" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58124,7 +58124,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2101" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58150,7 +58150,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2102" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58176,7 +58176,7 @@
         <v>12</v>
       </c>
       <c r="G2103" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58202,7 +58202,7 @@
         <v>12</v>
       </c>
       <c r="G2104" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58228,7 +58228,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2105" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58254,7 +58254,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2106" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58280,7 +58280,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2107" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58306,7 +58306,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2108" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58332,7 +58332,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2109" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58358,7 +58358,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2110" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58384,7 +58384,7 @@
         <v>12.5</v>
       </c>
       <c r="G2111" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58410,7 +58410,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2112" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58436,7 +58436,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58462,7 +58462,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2114" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58488,7 +58488,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2115" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58514,7 +58514,7 @@
         <v>12.5</v>
       </c>
       <c r="G2116" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58540,7 +58540,7 @@
         <v>12.5</v>
       </c>
       <c r="G2117" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58566,7 +58566,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2118" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58592,7 +58592,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2119" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58618,7 +58618,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2120" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58644,7 +58644,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2121" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58670,7 +58670,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58696,7 +58696,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2123" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58722,7 +58722,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G2124" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58748,7 +58748,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2125" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58774,7 +58774,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2126" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58800,7 +58800,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58826,7 +58826,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G2128" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58852,7 +58852,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2129" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58878,7 +58878,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2130" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58904,7 +58904,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G2131" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58930,7 +58930,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2132" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58956,7 +58956,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2133" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58982,7 +58982,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2134" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59008,7 +59008,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2135" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59034,7 +59034,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2136" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59060,7 +59060,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G2137" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59086,7 +59086,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2138" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59112,7 +59112,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2139" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59138,7 +59138,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2140" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59164,7 +59164,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2141" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59190,7 +59190,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2142" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59216,7 +59216,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2143" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59242,7 +59242,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2144" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59268,7 +59268,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2145" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59294,7 +59294,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2146" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59320,7 +59320,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2147" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59346,7 +59346,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2148" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59372,7 +59372,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2149" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59398,7 +59398,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2150" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59424,7 +59424,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2151" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59450,7 +59450,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59476,7 +59476,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2153" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59502,7 +59502,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2154" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59528,7 +59528,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2155" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59554,7 +59554,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2156" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59580,7 +59580,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2157" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59606,7 +59606,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2158" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59632,7 +59632,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G2159" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59658,7 +59658,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2160" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59684,7 +59684,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59710,7 +59710,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2162" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59736,7 +59736,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2163" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59762,7 +59762,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2164" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59788,7 +59788,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2165" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59814,7 +59814,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2166" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59840,7 +59840,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2167" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59866,7 +59866,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2168" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59892,7 +59892,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2169" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59918,7 +59918,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2170" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59944,7 +59944,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59970,7 +59970,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2172" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60022,7 +60022,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2174" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60048,7 +60048,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2175" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60074,7 +60074,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2176" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60204,7 +60204,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2181" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60256,7 +60256,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2183" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60282,7 +60282,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2184" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60308,7 +60308,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2185" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60438,7 +60438,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2190" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60464,7 +60464,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2191" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60490,7 +60490,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2192" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60646,7 +60646,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2198" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60672,7 +60672,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2199" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60698,7 +60698,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2200" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60750,7 +60750,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2202" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60776,7 +60776,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60802,7 +60802,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2204" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60828,7 +60828,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2205" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60932,7 +60932,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2209" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61010,7 +61010,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2212" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61140,7 +61140,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61192,7 +61192,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2219" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61270,7 +61270,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2222" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61322,7 +61322,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61374,7 +61374,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2226" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61452,7 +61452,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2229" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61504,7 +61504,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2231" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61530,7 +61530,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2232" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61556,7 +61556,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2233" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61582,7 +61582,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2234" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61608,7 +61608,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G2235" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61660,7 +61660,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2237" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61686,7 +61686,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2238" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61712,7 +61712,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2239" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61790,7 +61790,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2242" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61816,7 +61816,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2243" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61842,7 +61842,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2244" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61868,7 +61868,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2245" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61894,7 +61894,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2246" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -69182,7 +69182,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6910763889</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>83465</v>
@@ -69203,6 +69203,32 @@
         <v>1051</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6910416667</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>30097</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>17.0200004577637</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>16.6800003051758</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>17.0200004577637</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217515945435</t>
+    <t xml:space="preserve">7.18217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1639461517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0728006362915</t>
+    <t xml:space="preserve">7.16394424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07280111312866</t>
   </si>
   <si>
     <t xml:space="preserve">7.10925817489624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93061590194702</t>
+    <t xml:space="preserve">6.93061542510986</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051198959351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14207077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717639923096</t>
+    <t xml:space="preserve">7.14207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707391738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634309768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717687606812</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144243240356</t>
+    <t xml:space="preserve">7.2514443397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.27696371078491</t>
@@ -86,85 +86,85 @@
     <t xml:space="preserve">7.36446332931519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39363050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737888336182</t>
+    <t xml:space="preserve">7.29154634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800531387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737745285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.28790092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28425598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008756637573</t>
+    <t xml:space="preserve">7.28425550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008661270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.51029396057129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66341590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48842000961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112821578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3061318397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6196665763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675197601318</t>
+    <t xml:space="preserve">7.66341638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30613136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675102233887</t>
   </si>
   <si>
     <t xml:space="preserve">7.5321683883667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25509023666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3498797416687</t>
+    <t xml:space="preserve">7.25508975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529615402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34988069534302</t>
   </si>
   <si>
     <t xml:space="preserve">7.2988395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25873565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2477970123291</t>
+    <t xml:space="preserve">7.25873517990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779796600342</t>
   </si>
   <si>
     <t xml:space="preserve">7.21498727798462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24050664901733</t>
+    <t xml:space="preserve">7.24050712585449</t>
   </si>
   <si>
     <t xml:space="preserve">7.20769453048706</t>
@@ -179,88 +179,88 @@
     <t xml:space="preserve">6.99624013900757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97800922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5248761177063</t>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487659454346</t>
   </si>
   <si>
     <t xml:space="preserve">7.47383642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20404863357544</t>
+    <t xml:space="preserve">7.20404958724976</t>
   </si>
   <si>
     <t xml:space="preserve">7.3863377571106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50300216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445608139038</t>
+    <t xml:space="preserve">7.50300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133508682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320999145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
   </si>
   <si>
     <t xml:space="preserve">7.72904109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8748722076416</t>
+    <t xml:space="preserve">7.87487030029297</t>
   </si>
   <si>
     <t xml:space="preserve">7.94778537750244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03528594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278270721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424386978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273071289062</t>
+    <t xml:space="preserve">8.03528690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273166656494</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770355224609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18022060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88030481338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787748336792</t>
+    <t xml:space="preserve">8.18022155761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88030529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782915115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787939071655</t>
   </si>
   <si>
     <t xml:space="preserve">7.68535995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64787101745605</t>
+    <t xml:space="preserve">7.64786911010742</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.985276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89530086517334</t>
+    <t xml:space="preserve">7.98527526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530181884766</t>
   </si>
   <si>
     <t xml:space="preserve">8.02276515960693</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4398717880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25992012023926</t>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240653991699</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">9.31990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13245677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.982497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251586914062</t>
+    <t xml:space="preserve">9.1324577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251396179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.9974946975708</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008853912354</t>
+    <t xml:space="preserve">8.89252376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008758544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.69757747650146</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">8.59260654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84753513336182</t>
+    <t xml:space="preserve">8.84753608703613</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255725860596</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">8.72756862640381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70507431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79505062103271</t>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7950496673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.64509296417236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72007274627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6900806427002</t>
+    <t xml:space="preserve">8.72007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69007968902588</t>
   </si>
   <si>
     <t xml:space="preserve">8.60010528564453</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">8.38266563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61509990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5476188659668</t>
+    <t xml:space="preserve">8.62259769439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6151008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54761791229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.41265678405762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28519153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506736755371</t>
+    <t xml:space="preserve">8.28519248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506641387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.87002944946289</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51762771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58510875701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5101318359375</t>
+    <t xml:space="preserve">8.51762676239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58510971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51012992858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.40515899658203</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">8.31518363952637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39766120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30018901824951</t>
+    <t xml:space="preserve">8.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30018711090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.17272281646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764446258545</t>
+    <t xml:space="preserve">8.20271396636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764350891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.4201545715332</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">8.09024620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08274841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18771839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777891159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526737213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13523387908936</t>
+    <t xml:space="preserve">8.06775283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08274936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.24020481109619</t>
@@ -461,52 +461,52 @@
     <t xml:space="preserve">8.2252082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1202392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00776958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76783561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82781934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282520294189</t>
+    <t xml:space="preserve">8.12023830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00777053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76783752441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282377243042</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026390075684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776168823242</t>
+    <t xml:space="preserve">7.95528364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776264190674</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93278932571411</t>
+    <t xml:space="preserve">7.93279075622559</t>
   </si>
   <si>
     <t xml:space="preserve">7.88780355453491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92529344558716</t>
+    <t xml:space="preserve">7.92529296875</t>
   </si>
   <si>
     <t xml:space="preserve">7.94778728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033878326416</t>
+    <t xml:space="preserve">7.87280750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.760338306427</t>
   </si>
   <si>
     <t xml:space="preserve">7.83531713485718</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">8.09667778015137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78823518753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570016860962</t>
+    <t xml:space="preserve">7.7882342338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956992149353</t>
   </si>
   <si>
     <t xml:space="preserve">7.74967813491821</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">8.01956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98101234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390062332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86534595489502</t>
+    <t xml:space="preserve">7.98101186752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">8.21234512329102</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">7.82678890228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71112251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55690002441406</t>
+    <t xml:space="preserve">7.71112203598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690097808838</t>
   </si>
   <si>
     <t xml:space="preserve">7.51063251495361</t>
@@ -560,46 +560,46 @@
     <t xml:space="preserve">7.5414776802063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47978830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32556629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21761083602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254413604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23303270339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507724761963</t>
+    <t xml:space="preserve">7.4797887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32556676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41809892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21760988235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23303365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2638783454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507677078247</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17134380340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20218944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10965490341187</t>
+    <t xml:space="preserve">7.17134475708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20218849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10965585708618</t>
   </si>
   <si>
     <t xml:space="preserve">7.14049911499023</t>
@@ -608,55 +608,55 @@
     <t xml:space="preserve">7.07881164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29472160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31014442443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72409868240356</t>
+    <t xml:space="preserve">7.29472208023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31014394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205461502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72409820556641</t>
   </si>
   <si>
     <t xml:space="preserve">6.73952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0171217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95543241500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98627758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67783164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70867681503296</t>
+    <t xml:space="preserve">6.86289930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94000959396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543336868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98627805709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67783212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7086763381958</t>
   </si>
   <si>
     <t xml:space="preserve">6.6315655708313</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">6.47734212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46192121505737</t>
+    <t xml:space="preserve">6.46192073822021</t>
   </si>
   <si>
     <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61614322662354</t>
+    <t xml:space="preserve">6.61614274978638</t>
   </si>
   <si>
     <t xml:space="preserve">6.52360916137695</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">6.23058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3231201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.400230884552</t>
+    <t xml:space="preserve">6.32312059402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40023183822632</t>
   </si>
   <si>
     <t xml:space="preserve">6.26143169403076</t>
@@ -695,109 +695,109 @@
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56987619400024</t>
+    <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565418243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55445432662964</t>
+    <t xml:space="preserve">6.41565370559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5544548034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374303817749</t>
+    <t xml:space="preserve">6.89374351501465</t>
   </si>
   <si>
     <t xml:space="preserve">6.6469874382019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7703652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107557296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16889810562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09178686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30769872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99925327301025</t>
+    <t xml:space="preserve">6.77036571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16889762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09178638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30769824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99925374984741</t>
   </si>
   <si>
     <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66241073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21516513824463</t>
+    <t xml:space="preserve">6.66240930557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649839401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21516466140747</t>
   </si>
   <si>
     <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8783221244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085523605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676662445068</t>
+    <t xml:space="preserve">6.75494289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676567077637</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2011513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314292907715</t>
+    <t xml:space="preserve">7.20115089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314340591431</t>
   </si>
   <si>
     <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6410608291626</t>
+    <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912046432495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913373947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113809585571</t>
+    <t xml:space="preserve">7.08913326263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113761901855</t>
   </si>
   <si>
     <t xml:space="preserve">6.83309173583984</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">6.8650975227356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78508424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75307893753052</t>
+    <t xml:space="preserve">6.78508377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75307941436768</t>
   </si>
   <si>
     <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72107362747192</t>
+    <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
     <t xml:space="preserve">6.48103618621826</t>
@@ -830,22 +830,22 @@
     <t xml:space="preserve">6.60905647277832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76908159255981</t>
+    <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
     <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89710235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81708955764771</t>
+    <t xml:space="preserve">6.89710283279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81709003448486</t>
   </si>
   <si>
     <t xml:space="preserve">6.56104850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65706443786621</t>
+    <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.59305334091187</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">6.62505912780762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57705211639404</t>
+    <t xml:space="preserve">6.57705163955688</t>
   </si>
   <si>
     <t xml:space="preserve">6.52904367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43302822113037</t>
+    <t xml:space="preserve">6.43302774429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.51304149627686</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">6.41702651977539</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40102338790894</t>
+    <t xml:space="preserve">6.40102291107178</t>
   </si>
   <si>
     <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22499513626099</t>
+    <t xml:space="preserve">6.22499561309814</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097171783447</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">6.06496953964233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09697437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1609845161438</t>
+    <t xml:space="preserve">6.09697484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16098499298096</t>
   </si>
   <si>
     <t xml:space="preserve">6.0009593963623</t>
@@ -905,34 +905,34 @@
     <t xml:space="preserve">6.01696109771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96895360946655</t>
+    <t xml:space="preserve">5.96895408630371</t>
   </si>
   <si>
     <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76092100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74491786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.680908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71291351318359</t>
+    <t xml:space="preserve">5.76092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74491882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68090772628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71291303634644</t>
   </si>
   <si>
     <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90494441986084</t>
+    <t xml:space="preserve">5.90494394302368</t>
   </si>
   <si>
     <t xml:space="preserve">5.87293863296509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79292583465576</t>
+    <t xml:space="preserve">5.79292631149292</t>
   </si>
   <si>
     <t xml:space="preserve">5.98495674133301</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">6.11297702789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24099731445312</t>
+    <t xml:space="preserve">6.24099779129028</t>
   </si>
   <si>
     <t xml:space="preserve">6.32101058959961</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">6.20899248123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1769871711731</t>
+    <t xml:space="preserve">6.17698764801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.38502025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19298982620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12897920608521</t>
+    <t xml:space="preserve">6.19298934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
     <t xml:space="preserve">6.1449818611145</t>
@@ -971,34 +971,34 @@
     <t xml:space="preserve">6.25699996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30500745773315</t>
+    <t xml:space="preserve">6.30500793457031</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03296422958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290023803711</t>
+    <t xml:space="preserve">6.0329647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61689805984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887729644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63289976119995</t>
   </si>
   <si>
     <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286184310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50487947463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089540481567</t>
+    <t xml:space="preserve">5.39286136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089492797852</t>
   </si>
   <si>
     <t xml:space="preserve">5.36085653305054</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">4.73675727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67274761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44871091842651</t>
+    <t xml:space="preserve">4.67274713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44871044158936</t>
   </si>
   <si>
     <t xml:space="preserve">4.24067783355713</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">3.92062664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28868579864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04864692687988</t>
+    <t xml:space="preserve">4.28868627548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04864740371704</t>
   </si>
   <si>
     <t xml:space="preserve">4.1606650352478</t>
@@ -1034,55 +1034,55 @@
     <t xml:space="preserve">4.08065271377563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40070390701294</t>
+    <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
     <t xml:space="preserve">4.72075462341309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92878770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13682126998901</t>
+    <t xml:space="preserve">4.92878723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13682079315186</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886497497559</t>
+    <t xml:space="preserve">5.40886449813843</t>
   </si>
   <si>
     <t xml:space="preserve">5.3288516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31284856796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880098342896</t>
+    <t xml:space="preserve">5.3128490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18482828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0088005065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.16882610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28084373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05680894851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23283672332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47287511825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894128799438</t>
+    <t xml:space="preserve">5.28084421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05680847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23283624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47287559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894176483154</t>
   </si>
   <si>
     <t xml:space="preserve">5.84093427658081</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69691038131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85693693161011</t>
+    <t xml:space="preserve">5.77692270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6969108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
     <t xml:space="preserve">5.58489227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42486667633057</t>
+    <t xml:space="preserve">5.42486715316772</t>
   </si>
   <si>
     <t xml:space="preserve">5.56889009475708</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">5.26484107971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24883890151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45687246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29684638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21683406829834</t>
+    <t xml:space="preserve">5.24883842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45687198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29684686660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683359146118</t>
   </si>
   <si>
     <t xml:space="preserve">6.3530158996582</t>
@@ -1142,49 +1142,49 @@
     <t xml:space="preserve">6.28900527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49703884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7050724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67306613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91310596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521270751953</t>
+    <t xml:space="preserve">6.4970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70507192611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67306709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91310548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521175384521</t>
   </si>
   <si>
     <t xml:space="preserve">7.60121488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5212025642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53720426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319555282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719242095947</t>
+    <t xml:space="preserve">7.52120351791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5372052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719194412231</t>
   </si>
   <si>
     <t xml:space="preserve">7.40918397903442</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">7.39318180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23315668106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518663406372</t>
+    <t xml:space="preserve">7.23315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3131685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518615722656</t>
   </si>
   <si>
     <t xml:space="preserve">7.50519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36117601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29716682434082</t>
+    <t xml:space="preserve">7.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716634750366</t>
   </si>
   <si>
     <t xml:space="preserve">7.74523830413818</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">7.82525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90526390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0812931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04128551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93726825714111</t>
+    <t xml:space="preserve">7.90526485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08129215240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93726873397827</t>
   </si>
   <si>
     <t xml:space="preserve">8.0012788772583</t>
@@ -1241,34 +1241,34 @@
     <t xml:space="preserve">7.87325811386108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95327043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927309036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40134239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44134902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72139263153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00143814086914</t>
+    <t xml:space="preserve">7.95327138900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927404403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28132343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40134334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44135093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72139453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00144004821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.84141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12145709991455</t>
+    <t xml:space="preserve">9.12145805358887</t>
   </si>
   <si>
     <t xml:space="preserve">9.0414457321167</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">8.96143245697021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52152347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48151683807373</t>
+    <t xml:space="preserve">9.52152156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3216495513916</t>
+    <t xml:space="preserve">10.3216485977173</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2017908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217775344849</t>
+    <t xml:space="preserve">11.3218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217784881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">10.9617519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1617832183838</t>
+    <t xml:space="preserve">11.1617841720581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8417329788208</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417984008789</t>
+    <t xml:space="preserve">11.241795539856</t>
   </si>
   <si>
     <t xml:space="preserve">11.0817728042603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7617197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0017576217651</t>
+    <t xml:space="preserve">10.76171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0017585754395</t>
   </si>
   <si>
     <t xml:space="preserve">10.5216817855835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.60169506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818040847778</t>
+    <t xml:space="preserve">10.6016941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818031311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.6965761184692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1573705673218</t>
+    <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.7011213302612</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.037486076355</t>
+    <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.1204404830933</t>
@@ -1376,34 +1376,34 @@
     <t xml:space="preserve">10.1619186401367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0789632797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99600982666016</t>
+    <t xml:space="preserve">10.0789642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.91305637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95453262329102</t>
+    <t xml:space="preserve">9.9545316696167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278274536133</t>
+    <t xml:space="preserve">10.327826499939</t>
   </si>
   <si>
     <t xml:space="preserve">10.9914627075195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7425985336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766897201538</t>
+    <t xml:space="preserve">10.7425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.825553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766916275024</t>
   </si>
   <si>
     <t xml:space="preserve">10.8670310974121</t>
@@ -1421,43 +1421,43 @@
     <t xml:space="preserve">10.244873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2033948898315</t>
+    <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.87157821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.452260017395</t>
+    <t xml:space="preserve">10.4522581100464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7840776443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085083007812</t>
+    <t xml:space="preserve">10.7840766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1158933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085073471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6596441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3232803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4891891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2403259277344</t>
+    <t xml:space="preserve">10.6596450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.032940864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3232793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4891901016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2403268814087</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7795295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3602104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6505517959595</t>
+    <t xml:space="preserve">11.7795286178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772569656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3602113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6505508422852</t>
   </si>
   <si>
     <t xml:space="preserve">12.3187351226807</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">12.5261201858521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5675964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8164615631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215730667114</t>
+    <t xml:space="preserve">12.5675973892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.816460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2727098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215721130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141860961914</t>
@@ -1511,25 +1511,25 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0193004608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8994159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6090745925903</t>
+    <t xml:space="preserve">14.0192995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1897563934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8994150161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.609073638916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4846429824829</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3647584915161</t>
+    <t xml:space="preserve">11.3647575378418</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062356948853</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">11.8210077285767</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4477119445801</t>
+    <t xml:space="preserve">11.1988487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
     <t xml:space="preserve">11.7380523681641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
+    <t xml:space="preserve">9.78862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714756011963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624849319458</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">10.7177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9665765762329</t>
+    <t xml:space="preserve">10.9665775299072</t>
   </si>
   <si>
     <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.651349067688</t>
+    <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6347579956055</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">10.9168043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8006677627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002132415771</t>
+    <t xml:space="preserve">10.8006687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002122879028</t>
   </si>
   <si>
     <t xml:space="preserve">10.8172578811646</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">10.9997577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338499069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849857330322</t>
+    <t xml:space="preserve">10.8338489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003820419312</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">11.4693698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279100418091</t>
+    <t xml:space="preserve">11.3313932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279090881348</t>
   </si>
   <si>
     <t xml:space="preserve">11.4866170883179</t>
@@ -1655,40 +1655,40 @@
     <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1937503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0212783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1420078277588</t>
+    <t xml:space="preserve">12.193751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.021279335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1420087814331</t>
   </si>
   <si>
     <t xml:space="preserve">11.88330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5038633346558</t>
+    <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
     <t xml:space="preserve">12.0730209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2106618881226</t>
+    <t xml:space="preserve">11.2106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7794828414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6932458877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6242570877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0036964416504</t>
+    <t xml:space="preserve">10.7794818878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6242580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0036954879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.1589193344116</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">11.831561088562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3831329345703</t>
+    <t xml:space="preserve">11.3831338882446</t>
   </si>
   <si>
     <t xml:space="preserve">11.9522895812988</t>
@@ -1709,43 +1709,43 @@
     <t xml:space="preserve">11.7280778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5728530883789</t>
+    <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
     <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6935834884644</t>
+    <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8660554885864</t>
+    <t xml:space="preserve">11.8660545349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9867849349976</t>
+    <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
     <t xml:space="preserve">11.9177961349487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1765031814575</t>
+    <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
     <t xml:space="preserve">12.3144798278809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3317289352417</t>
+    <t xml:space="preserve">12.3317279815674</t>
   </si>
   <si>
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695377349854</t>
+    <t xml:space="preserve">11.9695386886597</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350433349609</t>
@@ -1766,22 +1766,22 @@
     <t xml:space="preserve">11.6073474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5556039810181</t>
+    <t xml:space="preserve">11.5556049346924</t>
   </si>
   <si>
     <t xml:space="preserve">11.3486394882202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.245156288147</t>
+    <t xml:space="preserve">11.2451553344727</t>
   </si>
   <si>
     <t xml:space="preserve">11.3658866882324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5900993347168</t>
+    <t xml:space="preserve">11.5211114883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5901002883911</t>
   </si>
   <si>
     <t xml:space="preserve">11.6418418884277</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">11.4348754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071796417236</t>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.107177734375</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209426879883</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">11.1244249343872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.141674041748</t>
+    <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
     <t xml:space="preserve">10.969202041626</t>
@@ -1817,13 +1817,13 @@
     <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3483037948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.365550994873</t>
+    <t xml:space="preserve">10.5207748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3483028411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3655500411987</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1930780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862794876099</t>
+    <t xml:space="preserve">10.193078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312244415283</t>
@@ -1847,31 +1847,31 @@
     <t xml:space="preserve">11.6245937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4176273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8143119812012</t>
+    <t xml:space="preserve">11.417628288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8143129348755</t>
   </si>
   <si>
     <t xml:space="preserve">12.0557727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4697065353394</t>
+    <t xml:space="preserve">12.469705581665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662233352661</t>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662223815918</t>
   </si>
   <si>
     <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4869518280029</t>
+    <t xml:space="preserve">12.4869527816772</t>
   </si>
   <si>
     <t xml:space="preserve">12.573187828064</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">12.5214471817017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386934280396</t>
+    <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2799863815308</t>
+    <t xml:space="preserve">12.2799873352051</t>
   </si>
   <si>
     <t xml:space="preserve">12.4352111816406</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108287811279</t>
+    <t xml:space="preserve">11.7108306884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521217346191</t>
+    <t xml:space="preserve">11.4521226882935</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554370880127</t>
+    <t xml:space="preserve">11.0554361343384</t>
   </si>
   <si>
     <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9347076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8657178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7622346878052</t>
+    <t xml:space="preserve">10.9347066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8657188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">10.6070108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4345388412476</t>
+    <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">10.4517860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5380220413208</t>
+    <t xml:space="preserve">10.469033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.277060508728</t>
+    <t xml:space="preserve">10.2770614624023</t>
   </si>
   <si>
     <t xml:space="preserve">10.2590627670288</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509197235107</t>
+    <t xml:space="preserve">9.93509292602539</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870698928833</t>
@@ -2000,25 +2000,25 @@
     <t xml:space="preserve">9.89909648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95309066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250835418701</t>
+    <t xml:space="preserve">9.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250844955444</t>
   </si>
   <si>
     <t xml:space="preserve">9.98908805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0790786743164</t>
+    <t xml:space="preserve">10.0790796279907</t>
   </si>
   <si>
     <t xml:space="preserve">10.0070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1510715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">10.1510725021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4210472106934</t>
+    <t xml:space="preserve">10.4210481643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">10.4030504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3130588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3670530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84510040283203</t>
+    <t xml:space="preserve">10.3130578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950601577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3670539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84510135650635</t>
   </si>
   <si>
     <t xml:space="preserve">9.79110622406006</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">9.41313934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17916202545166</t>
+    <t xml:space="preserve">9.17916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">9.19715976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28715133666992</t>
+    <t xml:space="preserve">9.28715038299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.48513317108154</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35914516448975</t>
+    <t xml:space="preserve">9.35914421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.32314777374268</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">9.01717662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08917045593262</t>
+    <t xml:space="preserve">9.0891695022583</t>
   </si>
   <si>
     <t xml:space="preserve">9.05317306518555</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97218036651611</t>
+    <t xml:space="preserve">8.97218132019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.79219722747803</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">8.46822643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47722625732422</t>
+    <t xml:space="preserve">8.4772253036499</t>
   </si>
   <si>
     <t xml:space="preserve">8.62121200561523</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">8.63921165466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63021087646484</t>
+    <t xml:space="preserve">8.63021183013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.72920227050781</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">7.90127801895142</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09925937652588</t>
+    <t xml:space="preserve">8.0992603302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05426406860352</t>
+    <t xml:space="preserve">8.05426502227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.00926780700684</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">7.89227962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97327089309692</t>
+    <t xml:space="preserve">7.97327184677124</t>
   </si>
   <si>
     <t xml:space="preserve">7.83828401565552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91927576065063</t>
+    <t xml:space="preserve">7.91927671432495</t>
   </si>
   <si>
     <t xml:space="preserve">7.78428888320923</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130235671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533073425293</t>
+    <t xml:space="preserve">7.63130283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
     <t xml:space="preserve">7.19934272766113</t>
@@ -2225,19 +2225,19 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19034242630005</t>
+    <t xml:space="preserve">6.95636415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19034290313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10935068130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25333738327026</t>
+    <t xml:space="preserve">7.10935115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25333786010742</t>
   </si>
   <si>
     <t xml:space="preserve">7.24433851242065</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">7.42432165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5143141746521</t>
+    <t xml:space="preserve">7.51431369781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.49631500244141</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">7.30733251571655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46931838989258</t>
+    <t xml:space="preserve">7.46931791305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.28933429718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28033494949341</t>
+    <t xml:space="preserve">7.28033542633057</t>
   </si>
   <si>
     <t xml:space="preserve">7.0283579826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15434598922729</t>
+    <t xml:space="preserve">7.15434646606445</t>
   </si>
   <si>
     <t xml:space="preserve">7.07335424423218</t>
@@ -2282,22 +2282,22 @@
     <t xml:space="preserve">7.06435441970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68529796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99127006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94627380371094</t>
+    <t xml:space="preserve">7.68529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99127054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627475738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27024364471436</t>
+    <t xml:space="preserve">8.27024459838867</t>
   </si>
   <si>
     <t xml:space="preserve">8.37823581695557</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">8.55821800231934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75619888305664</t>
+    <t xml:space="preserve">8.75619983673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.66620826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74720191955566</t>
+    <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.56721782684326</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">8.06326389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11725902557373</t>
+    <t xml:space="preserve">8.11725997924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922660827637</t>
+    <t xml:space="preserve">8.45922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9789962768555</t>
+    <t xml:space="preserve">10.9789972305298</t>
   </si>
   <si>
     <t xml:space="preserve">10.8350105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6370277404785</t>
+    <t xml:space="preserve">10.6370286941528</t>
   </si>
   <si>
     <t xml:space="preserve">10.90700340271</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">10.7270202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6550273895264</t>
+    <t xml:space="preserve">10.6550264358521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7990131378174</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">11.2489719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1229839324951</t>
+    <t xml:space="preserve">11.1229829788208</t>
   </si>
   <si>
     <t xml:space="preserve">11.0329923629761</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">11.4829511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4649524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2669715881348</t>
+    <t xml:space="preserve">11.4649515151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
     <t xml:space="preserve">11.3389644622803</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089391708374</t>
+    <t xml:space="preserve">11.6089382171631</t>
   </si>
   <si>
     <t xml:space="preserve">11.5009489059448</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">11.8249206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7349281311035</t>
+    <t xml:space="preserve">11.7349271774292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7529277801514</t>
+    <t xml:space="preserve">11.7529268264771</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429183959961</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">11.3391351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3578481674194</t>
+    <t xml:space="preserve">11.3578472137451</t>
   </si>
   <si>
     <t xml:space="preserve">11.4326934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4514045715332</t>
+    <t xml:space="preserve">11.4514036178589</t>
   </si>
   <si>
     <t xml:space="preserve">11.4701156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.208155632019</t>
+    <t xml:space="preserve">11.2081546783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.601095199585</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">11.8256330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688819885254</t>
+    <t xml:space="preserve">11.8443441390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688810348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.0314588546753</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">11.9753246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9940366744995</t>
+    <t xml:space="preserve">11.9940357208252</t>
   </si>
   <si>
     <t xml:space="preserve">12.0501699447632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7133655548096</t>
+    <t xml:space="preserve">11.7133646011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.7507877349854</t>
@@ -2531,10 +2531,7 @@
     <t xml:space="preserve">11.3952703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4139804840088</t>
+    <t xml:space="preserve">11.4139814376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3017129898071</t>
@@ -2552,7 +2549,7 @@
     <t xml:space="preserve">11.376558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823850631714</t>
+    <t xml:space="preserve">11.5823841094971</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268667221069</t>
@@ -2564,13 +2561,13 @@
     <t xml:space="preserve">11.8817672729492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1624393463135</t>
+    <t xml:space="preserve">12.1624383926392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1437273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191904067993</t>
+    <t xml:space="preserve">11.919189453125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004793167114</t>
@@ -2579,7 +2576,7 @@
     <t xml:space="preserve">11.6385183334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.544960975647</t>
+    <t xml:space="preserve">11.5449619293213</t>
   </si>
   <si>
     <t xml:space="preserve">11.114598274231</t>
@@ -2588,7 +2585,7 @@
     <t xml:space="preserve">11.2455787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0584630966187</t>
+    <t xml:space="preserve">11.058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.0958862304688</t>
@@ -2597,7 +2594,7 @@
     <t xml:space="preserve">11.1333093643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0771760940552</t>
+    <t xml:space="preserve">11.0771751403809</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397529602051</t>
@@ -2606,7 +2603,7 @@
     <t xml:space="preserve">10.8526382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6842346191406</t>
+    <t xml:space="preserve">10.6842355728149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7590808868408</t>
@@ -2615,22 +2612,22 @@
     <t xml:space="preserve">10.5158319473267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4784088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222745895386</t>
+    <t xml:space="preserve">10.4784097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222755432129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4971208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287172317505</t>
+    <t xml:space="preserve">10.3287181854248</t>
   </si>
   <si>
     <t xml:space="preserve">10.3661403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977367401123</t>
+    <t xml:space="preserve">10.1977376937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912950515747</t>
@@ -3168,6 +3165,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.9400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -59944,7 +59944,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59996,7 +59996,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60100,7 +60100,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60126,7 +60126,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60152,7 +60152,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60178,7 +60178,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60230,7 +60230,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60334,7 +60334,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60360,7 +60360,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60386,7 +60386,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60412,7 +60412,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60516,7 +60516,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60542,7 +60542,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60568,7 +60568,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60594,7 +60594,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60620,7 +60620,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60724,7 +60724,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60854,7 +60854,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60880,7 +60880,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60906,7 +60906,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60958,7 +60958,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60984,7 +60984,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61036,7 +61036,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61062,7 +61062,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61088,7 +61088,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61114,7 +61114,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61166,7 +61166,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61218,7 +61218,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61244,7 +61244,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61296,7 +61296,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61322,7 +61322,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61348,7 +61348,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61400,7 +61400,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61426,7 +61426,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61478,7 +61478,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61634,7 +61634,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61738,7 +61738,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61764,7 +61764,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61920,7 +61920,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61946,7 +61946,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61972,7 +61972,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61998,7 +61998,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62024,7 +62024,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62050,7 +62050,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62076,7 +62076,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62102,7 +62102,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62128,7 +62128,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62154,7 +62154,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62180,7 +62180,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62206,7 +62206,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62232,7 +62232,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62258,7 +62258,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62284,7 +62284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62310,7 +62310,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62336,7 +62336,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62362,7 +62362,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62388,7 +62388,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62414,7 +62414,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62440,7 +62440,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62466,7 +62466,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62492,7 +62492,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62518,7 +62518,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62544,7 +62544,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62570,7 +62570,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62596,7 +62596,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62622,7 +62622,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62648,7 +62648,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62674,7 +62674,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62700,7 +62700,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62726,7 +62726,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62752,7 +62752,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62778,7 +62778,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62804,7 +62804,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62830,7 +62830,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62856,7 +62856,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62882,7 +62882,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62908,7 +62908,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62934,7 +62934,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62960,7 +62960,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62986,7 +62986,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63012,7 +63012,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63038,7 +63038,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63064,7 +63064,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63090,7 +63090,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63116,7 +63116,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63142,7 +63142,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63168,7 +63168,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63194,7 +63194,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63220,7 +63220,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63246,7 +63246,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63272,7 +63272,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63298,7 +63298,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63324,7 +63324,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63350,7 +63350,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63376,7 +63376,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63402,7 +63402,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63428,7 +63428,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63454,7 +63454,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63480,7 +63480,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63506,7 +63506,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63532,7 +63532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63558,7 +63558,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63584,7 +63584,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63610,7 +63610,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63636,7 +63636,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63662,7 +63662,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63688,7 +63688,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63714,7 +63714,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63740,7 +63740,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63766,7 +63766,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63792,7 +63792,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63818,7 +63818,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63844,7 +63844,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63870,7 +63870,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63896,7 +63896,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63922,7 +63922,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63948,7 +63948,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63974,7 +63974,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64000,7 +64000,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64026,7 +64026,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64052,7 +64052,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64078,7 +64078,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64104,7 +64104,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64130,7 +64130,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64156,7 +64156,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64182,7 +64182,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64208,7 +64208,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64234,7 +64234,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64260,7 +64260,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64286,7 +64286,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64312,7 +64312,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64338,7 +64338,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64364,7 +64364,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64390,7 +64390,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64416,7 +64416,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64442,7 +64442,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64468,7 +64468,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64494,7 +64494,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64520,7 +64520,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64546,7 +64546,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64572,7 +64572,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64598,7 +64598,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64624,7 +64624,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64650,7 +64650,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64676,7 +64676,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64702,7 +64702,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64728,7 +64728,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64754,7 +64754,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64780,7 +64780,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64806,7 +64806,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64832,7 +64832,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64858,7 +64858,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64884,7 +64884,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64910,7 +64910,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64936,7 +64936,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64962,7 +64962,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64988,7 +64988,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65014,7 +65014,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65040,7 +65040,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65066,7 +65066,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65092,7 +65092,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65118,7 +65118,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65144,7 +65144,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65170,7 +65170,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65196,7 +65196,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65222,7 +65222,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65248,7 +65248,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65274,7 +65274,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65300,7 +65300,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65326,7 +65326,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65352,7 +65352,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65378,7 +65378,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65404,7 +65404,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65430,7 +65430,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65456,7 +65456,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65482,7 +65482,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65508,7 +65508,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65534,7 +65534,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65560,7 +65560,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65586,7 +65586,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65612,7 +65612,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65638,7 +65638,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65664,7 +65664,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65690,7 +65690,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65716,7 +65716,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65742,7 +65742,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65768,7 +65768,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65794,7 +65794,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65820,7 +65820,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65846,7 +65846,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65872,7 +65872,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65898,7 +65898,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65924,7 +65924,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65950,7 +65950,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65976,7 +65976,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66002,7 +66002,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66028,7 +66028,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66054,7 +66054,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66080,7 +66080,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66106,7 +66106,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66132,7 +66132,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66158,7 +66158,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66184,7 +66184,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66210,7 +66210,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66236,7 +66236,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66262,7 +66262,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66288,7 +66288,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66314,7 +66314,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66340,7 +66340,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66366,7 +66366,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66392,7 +66392,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66418,7 +66418,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66444,7 +66444,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66470,7 +66470,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66496,7 +66496,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66522,7 +66522,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66548,7 +66548,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66574,7 +66574,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66600,7 +66600,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66626,7 +66626,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66652,7 +66652,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66678,7 +66678,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66704,7 +66704,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66730,7 +66730,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66756,7 +66756,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66782,7 +66782,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66808,7 +66808,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66834,7 +66834,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66860,7 +66860,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66886,7 +66886,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66912,7 +66912,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66938,7 +66938,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66964,7 +66964,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66990,7 +66990,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67016,7 +67016,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67042,7 +67042,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67068,7 +67068,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67094,7 +67094,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67120,7 +67120,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67146,7 +67146,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67172,7 +67172,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67198,7 +67198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67224,7 +67224,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67250,7 +67250,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67276,7 +67276,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67302,7 +67302,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67328,7 +67328,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67354,7 +67354,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67380,7 +67380,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67406,7 +67406,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67432,7 +67432,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67458,7 +67458,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67484,7 +67484,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67510,7 +67510,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67536,7 +67536,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67562,7 +67562,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67588,7 +67588,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67614,7 +67614,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67640,7 +67640,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67666,7 +67666,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67692,7 +67692,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67718,7 +67718,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67744,7 +67744,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67770,7 +67770,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67796,7 +67796,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67822,7 +67822,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67848,7 +67848,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67874,7 +67874,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67900,7 +67900,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67926,7 +67926,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67952,7 +67952,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67978,7 +67978,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68004,7 +68004,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68030,7 +68030,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68056,7 +68056,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68082,7 +68082,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68108,7 +68108,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68134,7 +68134,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68160,7 +68160,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68186,7 +68186,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68212,7 +68212,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2489" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68238,7 +68238,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2490" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68264,7 +68264,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2491" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68290,7 +68290,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2492" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68316,7 +68316,7 @@
         <v>17.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68342,7 +68342,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2494" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68368,7 +68368,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2495" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68394,7 +68394,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2496" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68420,7 +68420,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2497" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68446,7 +68446,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2498" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68472,7 +68472,7 @@
         <v>17</v>
       </c>
       <c r="G2499" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68498,7 +68498,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2500" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68524,7 +68524,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2501" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68550,7 +68550,7 @@
         <v>17</v>
       </c>
       <c r="G2502" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68576,7 +68576,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2503" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68602,7 +68602,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2504" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68628,7 +68628,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2505" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68654,7 +68654,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2506" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68680,7 +68680,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2507" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68706,7 +68706,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68732,7 +68732,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2509" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68758,7 +68758,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2510" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68784,7 +68784,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G2511" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68810,7 +68810,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2512" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68836,7 +68836,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G2513" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68862,7 +68862,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68888,7 +68888,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2515" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68914,7 +68914,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2516" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68940,7 +68940,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2517" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68966,7 +68966,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2518" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68992,7 +68992,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2519" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -69018,7 +69018,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2520" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -69044,7 +69044,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2521" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -69070,7 +69070,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2522" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -69096,7 +69096,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2523" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -69122,7 +69122,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2524" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -69148,7 +69148,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2525" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69174,7 +69174,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2526" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69200,7 +69200,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G2527" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69208,7 +69208,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6910416667</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>30097</v>
@@ -69226,9 +69226,35 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2528" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6911921296</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>23088</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>17.0400009155273</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -47,223 +47,223 @@
     <t xml:space="preserve">7.16394519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14571666717529</t>
+    <t xml:space="preserve">7.14571619033813</t>
   </si>
   <si>
     <t xml:space="preserve">7.07280015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10925674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061542510986</t>
+    <t xml:space="preserve">7.10925769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061494827271</t>
   </si>
   <si>
     <t xml:space="preserve">6.89051198959351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14207077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707391738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96342802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446332931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154682159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863174438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2623815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821170806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790044784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.284255027771</t>
+    <t xml:space="preserve">7.14207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717687606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96342754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25144386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821218490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737745285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28425550460815</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008708953857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341686248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154195785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4884181022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613136291504</t>
+    <t xml:space="preserve">7.51029348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3061318397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.61966705322266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54675149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5321683883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34987926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2988395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24779796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21498680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99624013900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9780101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2040491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3863377571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300168991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832085609436</t>
+    <t xml:space="preserve">7.54675197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34988021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29883766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873470306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24779748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2149863243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623966217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404863357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133508682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320903778076</t>
   </si>
   <si>
     <t xml:space="preserve">7.7144570350647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72903966903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8748722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9477858543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278461456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1802225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09774589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88030576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782724380493</t>
+    <t xml:space="preserve">7.72904062271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87487077713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778680801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424386978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273262023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24770450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18022155761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09774494171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07525157928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88030481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782819747925</t>
   </si>
   <si>
     <t xml:space="preserve">7.61787843704224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68535995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6478705406189</t>
+    <t xml:space="preserve">7.68535947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64786863327026</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98527479171753</t>
+    <t xml:space="preserve">7.98527574539185</t>
   </si>
   <si>
     <t xml:space="preserve">7.89530038833618</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02276515960693</t>
+    <t xml:space="preserve">8.02276420593262</t>
   </si>
   <si>
     <t xml:space="preserve">8.06025505065918</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003639221191</t>
+    <t xml:space="preserve">8.84003734588623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43987083435059</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240558624268</t>
+    <t xml:space="preserve">9.31240749359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.31990432739258</t>
@@ -293,91 +293,91 @@
     <t xml:space="preserve">9.13245582580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98249816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92251396179199</t>
+    <t xml:space="preserve">8.982497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92251491546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.99749374389648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89252376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66008949279785</t>
+    <t xml:space="preserve">9.10996246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89252281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008853912354</t>
   </si>
   <si>
     <t xml:space="preserve">8.69757747650146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59260559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84753799438477</t>
+    <t xml:space="preserve">8.59260654449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84753608703613</t>
   </si>
   <si>
     <t xml:space="preserve">8.77255630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81004619598389</t>
+    <t xml:space="preserve">8.8100471496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.81754398345947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79505062103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64509201049805</t>
+    <t xml:space="preserve">8.72756862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7950496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64509105682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.72007179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69008159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60010528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36766910552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38266563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54761791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268142700195</t>
+    <t xml:space="preserve">8.69007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60010433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3676700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61510181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5476188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268238067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.73506736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87002849578857</t>
+    <t xml:space="preserve">8.87003040313721</t>
   </si>
   <si>
     <t xml:space="preserve">8.90002059936523</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">8.51012992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40515804290771</t>
+    <t xml:space="preserve">8.40515899658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.36017036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31518268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3001880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17272281646729</t>
+    <t xml:space="preserve">8.31518459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766025543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30018711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1727237701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.20271587371826</t>
@@ -419,43 +419,43 @@
     <t xml:space="preserve">8.45764446258545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4201545715332</t>
+    <t xml:space="preserve">8.42015552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11273956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09024524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775379180908</t>
+    <t xml:space="preserve">8.1127405166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09024715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775188446045</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
+    <t xml:space="preserve">8.12773704528809</t>
   </si>
   <si>
     <t xml:space="preserve">8.18772029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99277353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777891159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526737213135</t>
+    <t xml:space="preserve">7.99277400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9777774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526641845703</t>
   </si>
   <si>
     <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24020481109619</t>
+    <t xml:space="preserve">8.24020576477051</t>
   </si>
   <si>
     <t xml:space="preserve">8.22521018981934</t>
@@ -470,109 +470,109 @@
     <t xml:space="preserve">7.76783561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82781982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0302619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95528411865234</t>
+    <t xml:space="preserve">7.82781934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528507232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529249191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94778680801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8728084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91029834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76033782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531713485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01956558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98101139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90390014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86534595489502</t>
+    <t xml:space="preserve">8.16522598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93279123306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94778776168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91029739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76033926010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09667873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69570016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967908859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98101234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90390062332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86534357070923</t>
   </si>
   <si>
     <t xml:space="preserve">8.21234512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82678937911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112155914307</t>
+    <t xml:space="preserve">7.82678890228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71112298965454</t>
   </si>
   <si>
     <t xml:space="preserve">7.66485500335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55690097808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6185884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147815704346</t>
+    <t xml:space="preserve">7.5568995475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858892440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147672653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.47978782653809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32556581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21760988235474</t>
+    <t xml:space="preserve">7.3255672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41809988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">7.03254413604736</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">7.24845504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26387786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507677078247</t>
+    <t xml:space="preserve">7.26387691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507724761963</t>
   </si>
   <si>
     <t xml:space="preserve">7.27929973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17134380340576</t>
+    <t xml:space="preserve">7.1713433265686</t>
   </si>
   <si>
     <t xml:space="preserve">7.20218849182129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10965490341187</t>
+    <t xml:space="preserve">7.10965442657471</t>
   </si>
   <si>
     <t xml:space="preserve">7.14049959182739</t>
@@ -611,79 +611,79 @@
     <t xml:space="preserve">7.29472208023071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31014347076416</t>
+    <t xml:space="preserve">7.31014442443848</t>
   </si>
   <si>
     <t xml:space="preserve">7.0942325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00169897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205461502075</t>
+    <t xml:space="preserve">7.00169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205366134644</t>
   </si>
   <si>
     <t xml:space="preserve">6.92458820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73952102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86289882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0171217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98627710342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67783164978027</t>
+    <t xml:space="preserve">6.72409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73952150344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8628978729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78578758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9400110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543336868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98627758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67783212661743</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086763381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63156461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47734212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3231201171875</t>
+    <t xml:space="preserve">6.63156604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52361011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974279403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058652877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32312059402466</t>
   </si>
   <si>
     <t xml:space="preserve">6.40023183822632</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">6.2614312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27685451507568</t>
+    <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.56987619400024</t>
@@ -701,31 +701,31 @@
     <t xml:space="preserve">6.29227590560913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41565322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5544548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81663227081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89374303817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43107604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10720872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16889810562134</t>
+    <t xml:space="preserve">6.41565370559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55445432662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81663274765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89374208450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6469874382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77036476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43107652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10720825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16889762878418</t>
   </si>
   <si>
     <t xml:space="preserve">6.09178686141968</t>
@@ -740,79 +740,79 @@
     <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66241073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44649744033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21516466140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36938762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75494289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87832164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97085523605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.155921459198</t>
+    <t xml:space="preserve">6.66240978240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44649791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21516513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36938714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87832069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97085475921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592098236084</t>
   </si>
   <si>
     <t xml:space="preserve">7.18676471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6410608291626</t>
+    <t xml:space="preserve">7.06338787078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20115184783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314197540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313108444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106130599976</t>
   </si>
   <si>
     <t xml:space="preserve">7.00912094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08913326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113809585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88109970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78508424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75307941436768</t>
+    <t xml:space="preserve">7.08913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1211371421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8650975227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78508377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75307893753052</t>
   </si>
   <si>
     <t xml:space="preserve">6.73707675933838</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48103666305542</t>
+    <t xml:space="preserve">6.48103618621826</t>
   </si>
   <si>
     <t xml:space="preserve">6.54504632949829</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">6.60905647277832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76908254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108785629272</t>
+    <t xml:space="preserve">6.76908206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108737945557</t>
   </si>
   <si>
     <t xml:space="preserve">6.89710283279419</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">6.81708955764771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56104850769043</t>
+    <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
     <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59305381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904367446899</t>
+    <t xml:space="preserve">6.59305334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904415130615</t>
   </si>
   <si>
     <t xml:space="preserve">6.43302822113037</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102243423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33701229095459</t>
+    <t xml:space="preserve">6.44903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33701276779175</t>
   </si>
   <si>
     <t xml:space="preserve">6.22499513626099</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">6.08097171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04896688461304</t>
+    <t xml:space="preserve">6.04896640777588</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496953964233</t>
@@ -893,22 +893,22 @@
     <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1609845161438</t>
+    <t xml:space="preserve">6.16098499298096</t>
   </si>
   <si>
     <t xml:space="preserve">6.0009593963623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95295190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01696157455444</t>
+    <t xml:space="preserve">5.95295143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0169620513916</t>
   </si>
   <si>
     <t xml:space="preserve">5.96895360946655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92094612121582</t>
+    <t xml:space="preserve">5.92094659805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.76092052459717</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">5.68090772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71291351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82493114471436</t>
+    <t xml:space="preserve">5.71291255950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493162155151</t>
   </si>
   <si>
     <t xml:space="preserve">5.90494394302368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87293910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7929253578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98495626449585</t>
+    <t xml:space="preserve">5.87293863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79292631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98495721817017</t>
   </si>
   <si>
     <t xml:space="preserve">6.11297702789307</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">6.27300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20899200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17698764801025</t>
+    <t xml:space="preserve">6.20899248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1769871711731</t>
   </si>
   <si>
     <t xml:space="preserve">6.38502073287964</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">6.12897968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1449818611145</t>
+    <t xml:space="preserve">6.14498138427734</t>
   </si>
   <si>
     <t xml:space="preserve">6.25700044631958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30500745773315</t>
+    <t xml:space="preserve">6.30500793457031</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">6.03296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61689758300781</t>
+    <t xml:space="preserve">5.61689805984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.48887777328491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63290023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55288743972778</t>
+    <t xml:space="preserve">5.63290071487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">5.39286184310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50487995147705</t>
+    <t xml:space="preserve">5.50487947463989</t>
   </si>
   <si>
     <t xml:space="preserve">5.60089492797852</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">4.6727466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44871139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24067831039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062711715698</t>
+    <t xml:space="preserve">4.44871091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24067783355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062664031982</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868532180786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04864692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1606650352478</t>
+    <t xml:space="preserve">4.04864740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16066551208496</t>
   </si>
   <si>
     <t xml:space="preserve">4.08065176010132</t>
@@ -1037,91 +1037,91 @@
     <t xml:space="preserve">4.40070343017578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72075462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92878818511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13682079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52088308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40886449813843</t>
+    <t xml:space="preserve">4.72075510025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92878770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13682126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52088260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40886402130127</t>
   </si>
   <si>
     <t xml:space="preserve">5.3288516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31284856796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880098342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28084373474121</t>
+    <t xml:space="preserve">5.3128490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1848292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880002975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
     <t xml:space="preserve">5.05680847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23283672332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47287511825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72891521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894128799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093427658081</t>
+    <t xml:space="preserve">5.23283624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47287464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72891569137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69691038131714</t>
+    <t xml:space="preserve">5.77692270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6969108581543</t>
   </si>
   <si>
     <t xml:space="preserve">5.85693645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58489227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56888961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34485387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44086980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24883890151978</t>
+    <t xml:space="preserve">5.58489274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3448543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44087028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24883985519409</t>
   </si>
   <si>
     <t xml:space="preserve">5.45687246322632</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">5.29684686660767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21683406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3530158996582</t>
+    <t xml:space="preserve">5.21683359146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
     <t xml:space="preserve">6.28900527954102</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">6.70507192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67306661605835</t>
+    <t xml:space="preserve">6.67306709289551</t>
   </si>
   <si>
     <t xml:space="preserve">6.91310501098633</t>
@@ -1157,70 +1157,70 @@
     <t xml:space="preserve">7.24915933609009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26516151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922332763672</t>
+    <t xml:space="preserve">7.26516199111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922285079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.58521223068237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60121536254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52120208740234</t>
+    <t xml:space="preserve">7.60121583938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52120161056519</t>
   </si>
   <si>
     <t xml:space="preserve">7.5372052192688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47319507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45719194412231</t>
+    <t xml:space="preserve">7.47319412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45719146728516</t>
   </si>
   <si>
     <t xml:space="preserve">7.40918445587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39318227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519895553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2971658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523830413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82525062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90526437759399</t>
+    <t xml:space="preserve">7.39318132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316995620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74523782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125328063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82525014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90526390075684</t>
   </si>
   <si>
     <t xml:space="preserve">8.08129215240479</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">7.92126655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93726873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00127792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87325954437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129783630371</t>
+    <t xml:space="preserve">7.93726968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0012788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87325811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327043533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129688262939</t>
   </si>
   <si>
     <t xml:space="preserve">7.96927356719971</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">8.44134902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72139358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00143909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84141254425049</t>
+    <t xml:space="preserve">8.72139453887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00143814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8414134979248</t>
   </si>
   <si>
     <t xml:space="preserve">9.12145805358887</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">9.52152156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48151588439941</t>
+    <t xml:space="preserve">9.4815149307251</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">10.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1216173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2816438674927</t>
+    <t xml:space="preserve">10.121618270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2816429138184</t>
   </si>
   <si>
     <t xml:space="preserve">10.3216495513916</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218097686768</t>
+    <t xml:space="preserve">11.3218107223511</t>
   </si>
   <si>
     <t xml:space="preserve">11.201789855957</t>
@@ -1316,40 +1316,40 @@
     <t xml:space="preserve">11.1217775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.041766166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9617509841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617822647095</t>
+    <t xml:space="preserve">11.0417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9617519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617832183838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8417339324951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.881739616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818363189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2417974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817718505859</t>
+    <t xml:space="preserve">10.8817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817708969116</t>
   </si>
   <si>
     <t xml:space="preserve">10.7617197036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0017595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.60169506073</t>
+    <t xml:space="preserve">11.0017585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6016941070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818040847778</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">11.1573715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7011222839355</t>
+    <t xml:space="preserve">10.7011213302612</t>
   </si>
   <si>
     <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0374879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1204423904419</t>
+    <t xml:space="preserve">10.0374870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1204414367676</t>
   </si>
   <si>
     <t xml:space="preserve">10.1619186401367</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">10.0789642333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99600887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91305637359619</t>
+    <t xml:space="preserve">9.99600982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91305541992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
@@ -1391,97 +1391,97 @@
     <t xml:space="preserve">10.4107818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.327826499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255548477173</t>
+    <t xml:space="preserve">10.3278274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9914636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.742600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255558013916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5766906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8670301437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693056106567</t>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
   </si>
   <si>
     <t xml:space="preserve">10.2863502502441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.244873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033948898315</t>
+    <t xml:space="preserve">10.2448740005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033958435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.87157726287842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.452260017395</t>
+    <t xml:space="preserve">10.4522590637207</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7840776443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085073471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5352125167847</t>
+    <t xml:space="preserve">10.7840757369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1158933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085092544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.535213470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.6596450805664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.032940864563</t>
+    <t xml:space="preserve">11.0329399108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.323281288147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4891901016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5721435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5306673049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7795305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3602104187012</t>
+    <t xml:space="preserve">11.4891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.240327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5721426010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5306663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7795295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772569656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3602123260498</t>
   </si>
   <si>
     <t xml:space="preserve">12.6505517959595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3187341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5261201858521</t>
+    <t xml:space="preserve">12.318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5261211395264</t>
   </si>
   <si>
     <t xml:space="preserve">12.5675973892212</t>
@@ -1490,34 +1490,34 @@
     <t xml:space="preserve">12.816460609436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2727098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5630512237549</t>
+    <t xml:space="preserve">13.2727108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5630521774292</t>
   </si>
   <si>
     <t xml:space="preserve">13.8119134902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6460056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215730667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3141870498657</t>
+    <t xml:space="preserve">13.6460065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3141860961914</t>
   </si>
   <si>
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0192995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
+    <t xml:space="preserve">14.0192985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874809265137</t>
   </si>
   <si>
     <t xml:space="preserve">13.2312326431274</t>
@@ -1526,49 +1526,49 @@
     <t xml:space="preserve">13.1897554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8994159698486</t>
+    <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
     <t xml:space="preserve">12.6090745925903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4846429824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.028392791748</t>
+    <t xml:space="preserve">12.4846420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0283937454224</t>
   </si>
   <si>
     <t xml:space="preserve">11.3647575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062347412109</t>
+    <t xml:space="preserve">11.4062356948853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8210067749023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1988487243652</t>
+    <t xml:space="preserve">11.1988496780396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74714660644531</t>
+    <t xml:space="preserve">11.7380523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6641902923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.747145652771</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6136198043823</t>
+    <t xml:space="preserve">11.613621711731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4808940887451</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">10.9665765762329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7343044281006</t>
+    <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6513500213623</t>
@@ -1595,46 +1595,46 @@
     <t xml:space="preserve">10.6679401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8504400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8006687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9002132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8172588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7674856185913</t>
+    <t xml:space="preserve">10.8504409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8006677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9002122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8172578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.767484664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.9997577667236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8338489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5849866867065</t>
+    <t xml:space="preserve">10.8338499069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5849857330322</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4866170883179</t>
+    <t xml:space="preserve">11.4693689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3313913345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4866161346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.9005489349365</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1937503814697</t>
+    <t xml:space="preserve">12.193751335144</t>
   </si>
   <si>
     <t xml:space="preserve">12.0212783813477</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0730199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2106618881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035276412964</t>
+    <t xml:space="preserve">12.0730209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035285949707</t>
   </si>
   <si>
     <t xml:space="preserve">10.7794828414917</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">10.6932468414307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6242570877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0036964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1589202880859</t>
+    <t xml:space="preserve">10.6242580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1589193344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.7625713348389</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453231811523</t>
+    <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
     <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6763362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8660554885864</t>
+    <t xml:space="preserve">11.6763353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8660545349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.2627401351929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9867849349976</t>
+    <t xml:space="preserve">11.9867839813232</t>
   </si>
   <si>
     <t xml:space="preserve">11.9177951812744</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">11.9695377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">11.9350433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970666885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590890884399</t>
+    <t xml:space="preserve">11.7970657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590881347656</t>
   </si>
   <si>
     <t xml:space="preserve">11.607346534729</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">11.5556039810181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3486394882202</t>
+    <t xml:space="preserve">11.3486385345459</t>
   </si>
   <si>
     <t xml:space="preserve">11.2451553344727</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">11.4348745346069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209426879883</t>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.020941734314</t>
   </si>
   <si>
     <t xml:space="preserve">11.1244249343872</t>
@@ -1808,40 +1808,40 @@
     <t xml:space="preserve">10.9692010879517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8829650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.641505241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1758308410645</t>
+    <t xml:space="preserve">10.8829641342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5207748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3483018875122</t>
+    <t xml:space="preserve">10.3483028411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.365550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172916412354</t>
+    <t xml:space="preserve">10.4172925949097</t>
   </si>
   <si>
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1930780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862794876099</t>
+    <t xml:space="preserve">10.193078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862804412842</t>
   </si>
   <si>
     <t xml:space="preserve">10.831223487854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5383586883545</t>
+    <t xml:space="preserve">11.5383577346802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245937347412</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
+    <t xml:space="preserve">12.4007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">12.3662233352661</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">12.6421766281128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5214471817017</t>
+    <t xml:space="preserve">12.521448135376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5041990280151</t>
+    <t xml:space="preserve">12.5041999816895</t>
   </si>
   <si>
     <t xml:space="preserve">12.2799863815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4352121353149</t>
+    <t xml:space="preserve">12.4352111816406</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798185348511</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">11.7108297348022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2968969345093</t>
+    <t xml:space="preserve">11.2968978881836</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521217346191</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">10.8657188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7622346878052</t>
+    <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6070098876953</t>
+    <t xml:space="preserve">10.6070108413696</t>
   </si>
   <si>
     <t xml:space="preserve">10.4345388412476</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">10.469033241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5380220413208</t>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
@@ -69408,7 +69408,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6911574074</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>42497</v>
@@ -69429,6 +69429,32 @@
         <v>1057</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6910069444</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>21611</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>992</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="1057">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217420578003</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394472122192</t>
+    <t xml:space="preserve">7.16394519805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.14571666717529</t>
@@ -53,70 +53,70 @@
     <t xml:space="preserve">7.07280111312866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10925722122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93061685562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051198959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96707344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03634357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0071759223938</t>
+    <t xml:space="preserve">7.1092586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93061637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96707439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03634309768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717639923096</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25144338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27696323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446332931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29154634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39362955093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43737888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28790092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28425550460815</t>
+    <t xml:space="preserve">7.25144386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154682159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238107681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821170806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43737840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28790187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.284255027771</t>
   </si>
   <si>
     <t xml:space="preserve">7.43008756637573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51029348373413</t>
+    <t xml:space="preserve">7.51029396057129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66341686248779</t>
@@ -125,118 +125,118 @@
     <t xml:space="preserve">7.64154148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48841953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30613088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61966562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675245285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53216886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2550892829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33529758453369</t>
+    <t xml:space="preserve">7.48841905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48112726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30612993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966753005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5321683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25508880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33529663085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.34988021850586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29883813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25873470306396</t>
+    <t xml:space="preserve">7.29883909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25873613357544</t>
   </si>
   <si>
     <t xml:space="preserve">7.24779796600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21498489379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02176141738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97801113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5248761177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404767990112</t>
+    <t xml:space="preserve">7.2149863243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99623870849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9780101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20404958724976</t>
   </si>
   <si>
     <t xml:space="preserve">7.38633728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50300121307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133413314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904109954834</t>
+    <t xml:space="preserve">7.50300264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133317947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58320903778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71445751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72904014587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.87487125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778680801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03528499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98424339294434</t>
+    <t xml:space="preserve">7.94778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03528594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12278461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98424530029297</t>
   </si>
   <si>
     <t xml:space="preserve">8.14273166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24770259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18022346496582</t>
+    <t xml:space="preserve">8.24770355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18022060394287</t>
   </si>
   <si>
     <t xml:space="preserve">8.09774494171143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07525062561035</t>
+    <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
     <t xml:space="preserve">7.88030576705933</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">7.79782819747925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61787891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6478705406189</t>
+    <t xml:space="preserve">7.61787796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64787101745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.85781192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98527574539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8953013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276515960693</t>
+    <t xml:space="preserve">7.98527669906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89530181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276611328125</t>
   </si>
   <si>
     <t xml:space="preserve">8.06025505065918</t>
@@ -275,40 +275,40 @@
     <t xml:space="preserve">8.47264099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43987083435059</t>
+    <t xml:space="preserve">8.84003829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43986988067627</t>
   </si>
   <si>
     <t xml:space="preserve">9.25992107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240653991699</t>
+    <t xml:space="preserve">9.31240558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.31990528106689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13245677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.982497215271</t>
+    <t xml:space="preserve">9.13245582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98249912261963</t>
   </si>
   <si>
     <t xml:space="preserve">8.92251491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99749565124512</t>
+    <t xml:space="preserve">8.99749374389648</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6600866317749</t>
+    <t xml:space="preserve">8.89252376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66008758544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.69757843017578</t>
@@ -317,28 +317,28 @@
     <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84753608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255725860596</t>
+    <t xml:space="preserve">8.84753704071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255821228027</t>
   </si>
   <si>
     <t xml:space="preserve">8.8100471496582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81754493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72756958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70507621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79505062103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64509105682373</t>
+    <t xml:space="preserve">8.81754398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72756862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70507526397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7950496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64509296417236</t>
   </si>
   <si>
     <t xml:space="preserve">8.72007179260254</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">8.6900806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60010528564453</t>
+    <t xml:space="preserve">8.60010623931885</t>
   </si>
   <si>
     <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38266658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.38266563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259864807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.6151008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54761695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41265773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87002849578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67508411407471</t>
+    <t xml:space="preserve">8.54761791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41265678405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28519439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268333435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87003040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.51762771606445</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">8.58510971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36017036437988</t>
+    <t xml:space="preserve">8.51013088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40516090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3601713180542</t>
   </si>
   <si>
     <t xml:space="preserve">8.31518459320068</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">8.39766120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30018901824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17272281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45764350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4201545715332</t>
+    <t xml:space="preserve">8.3001880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1727237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20271492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45764446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42015361785889</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11273956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09024810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06775283813477</t>
+    <t xml:space="preserve">8.1127405166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09024620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06775379180908</t>
   </si>
   <si>
     <t xml:space="preserve">8.08274936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773609161377</t>
+    <t xml:space="preserve">8.12773704528809</t>
   </si>
   <si>
     <t xml:space="preserve">8.18772029876709</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">7.99277448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97777795791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526641845703</t>
+    <t xml:space="preserve">7.97777938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526737213135</t>
   </si>
   <si>
     <t xml:space="preserve">8.13523483276367</t>
@@ -458,73 +458,73 @@
     <t xml:space="preserve">8.24020481109619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2252082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12023735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00777053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76783561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82781982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81282424926758</t>
+    <t xml:space="preserve">8.22521018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12023830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00776958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76783657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82781887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81282377243042</t>
   </si>
   <si>
     <t xml:space="preserve">8.03026294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95528411865234</t>
+    <t xml:space="preserve">7.9552845954895</t>
   </si>
   <si>
     <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529249191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87280559539795</t>
+    <t xml:space="preserve">8.16522693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93279075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780450820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87280750274658</t>
   </si>
   <si>
     <t xml:space="preserve">7.91029739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76033878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83531808853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78823328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69570016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74967956542969</t>
+    <t xml:space="preserve">7.76033926010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83531618118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09667873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78823518753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6956992149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74967908859253</t>
   </si>
   <si>
     <t xml:space="preserve">8.01956653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98101139068604</t>
+    <t xml:space="preserve">7.98101186752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.90390014648438</t>
@@ -533,97 +533,97 @@
     <t xml:space="preserve">7.8653450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21234512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82678842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71112203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55690097808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147815704346</t>
+    <t xml:space="preserve">8.21234703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7111234664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55690002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54147863388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.4797887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3255672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809988021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21760988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03254318237305</t>
+    <t xml:space="preserve">7.32556772232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41809892654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725519180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21761131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03254365921021</t>
   </si>
   <si>
     <t xml:space="preserve">7.23303318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24845504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12507629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27929782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17134428024292</t>
+    <t xml:space="preserve">7.24845409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387739181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12507724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27929878234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17134380340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.20218849182129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10965490341187</t>
+    <t xml:space="preserve">7.10965538024902</t>
   </si>
   <si>
     <t xml:space="preserve">7.14049959182739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07881116867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2947211265564</t>
+    <t xml:space="preserve">7.0788106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29472255706787</t>
   </si>
   <si>
     <t xml:space="preserve">7.31014394760132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92458820343018</t>
+    <t xml:space="preserve">7.09423208236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169897079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205461502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92458772659302</t>
   </si>
   <si>
     <t xml:space="preserve">6.72409915924072</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">6.73952054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01712131500244</t>
+    <t xml:space="preserve">6.86289930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0171217918396</t>
   </si>
   <si>
     <t xml:space="preserve">6.78578805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94001007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9554328918457</t>
+    <t xml:space="preserve">6.94001054763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543336868286</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627758026123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783212661743</t>
+    <t xml:space="preserve">6.67783164978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086763381958</t>
@@ -659,34 +659,34 @@
     <t xml:space="preserve">6.6315655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47734308242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61614322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52360963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058652877808</t>
+    <t xml:space="preserve">6.47734212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61614274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974279403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058700561523</t>
   </si>
   <si>
     <t xml:space="preserve">6.32312059402466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40023136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2614312171936</t>
+    <t xml:space="preserve">6.40023183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26143169403076</t>
   </si>
   <si>
     <t xml:space="preserve">6.27685403823853</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">6.5698766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29227590560913</t>
+    <t xml:space="preserve">6.29227638244629</t>
   </si>
   <si>
     <t xml:space="preserve">6.41565370559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55445384979248</t>
+    <t xml:space="preserve">6.55445432662964</t>
   </si>
   <si>
     <t xml:space="preserve">6.81663227081299</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">6.89374303817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64698791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7703652381897</t>
+    <t xml:space="preserve">6.6469874382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77036571502686</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107652664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10720920562744</t>
+    <t xml:space="preserve">6.10720872879028</t>
   </si>
   <si>
     <t xml:space="preserve">6.16889762878418</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">6.09178686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30769824981689</t>
+    <t xml:space="preserve">6.30769872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.99925374984741</t>
@@ -737,64 +737,64 @@
     <t xml:space="preserve">6.246009349823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66240978240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35396432876587</t>
+    <t xml:space="preserve">6.66241025924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49276542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35396528244019</t>
   </si>
   <si>
     <t xml:space="preserve">6.44649839401245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21516466140747</t>
+    <t xml:space="preserve">6.21516513824463</t>
   </si>
   <si>
     <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494384765625</t>
+    <t xml:space="preserve">6.75494289398193</t>
   </si>
   <si>
     <t xml:space="preserve">6.87832117080688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97085428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20115089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313108444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64106130599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00912141799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12113809585571</t>
+    <t xml:space="preserve">6.97085475921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15592050552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676662445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338739395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2011513710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314245223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313013076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64106178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00912046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08913326263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12113857269287</t>
   </si>
   <si>
     <t xml:space="preserve">6.833092212677</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">6.72107410430908</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48103666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54504632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60905694961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76908254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80108690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81708955764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56104850769043</t>
+    <t xml:space="preserve">6.48103618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54504680633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60905647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76908206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80108737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81709003448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56104898452759</t>
   </si>
   <si>
     <t xml:space="preserve">6.65706396102905</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">6.59305381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62505912780762</t>
+    <t xml:space="preserve">6.62505865097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.57705116271973</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">6.51304149627686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41702604293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40102243423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33701276779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22499513626099</t>
+    <t xml:space="preserve">6.44903135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41702651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40102291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33701324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22499561309814</t>
   </si>
   <si>
     <t xml:space="preserve">6.08097219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04896640777588</t>
+    <t xml:space="preserve">6.04896688461304</t>
   </si>
   <si>
     <t xml:space="preserve">6.06496906280518</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">6.09697437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16098403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0009593963623</t>
+    <t xml:space="preserve">6.16098499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00095891952515</t>
   </si>
   <si>
     <t xml:space="preserve">5.95295143127441</t>
@@ -902,37 +902,37 @@
     <t xml:space="preserve">6.01696157455444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96895456314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92094564437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76092052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74491786956787</t>
+    <t xml:space="preserve">5.96895408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92094659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76092100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74491882324219</t>
   </si>
   <si>
     <t xml:space="preserve">5.68090772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71291303634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82493162155151</t>
+    <t xml:space="preserve">5.71291351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82493114471436</t>
   </si>
   <si>
     <t xml:space="preserve">5.90494394302368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87293910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79292583465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98495626449585</t>
+    <t xml:space="preserve">5.87293863296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79292631149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98495674133301</t>
   </si>
   <si>
     <t xml:space="preserve">6.11297702789307</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">6.24099779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32101058959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27300262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20899295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1769871711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3850212097168</t>
+    <t xml:space="preserve">6.32101011276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27300310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20899248123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17698764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38502073287964</t>
   </si>
   <si>
     <t xml:space="preserve">6.19298934936523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12897968292236</t>
+    <t xml:space="preserve">6.12898015975952</t>
   </si>
   <si>
     <t xml:space="preserve">6.1449818611145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25700044631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30500745773315</t>
+    <t xml:space="preserve">6.25699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30500841140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.93694925308228</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">6.0329647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48887777328491</t>
+    <t xml:space="preserve">5.61689805984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290023803711</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">5.55288743972778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39286184310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50487947463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60089492797852</t>
+    <t xml:space="preserve">5.39286136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50487995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60089540481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.36085653305054</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">4.73675680160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6727466583252</t>
+    <t xml:space="preserve">4.67274713516235</t>
   </si>
   <si>
     <t xml:space="preserve">4.44871091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24067783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92062711715698</t>
+    <t xml:space="preserve">4.24067831039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92062664031982</t>
   </si>
   <si>
     <t xml:space="preserve">4.28868579864502</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">4.1606650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08065176010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40070390701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72075414657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92878770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13682079315186</t>
+    <t xml:space="preserve">4.08065271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40070343017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72075510025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92878675460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13682126998901</t>
   </si>
   <si>
     <t xml:space="preserve">5.52088260650635</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">5.3128490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0088005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16882658004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28084373474121</t>
+    <t xml:space="preserve">5.18482828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880098342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16882562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28084421157837</t>
   </si>
   <si>
     <t xml:space="preserve">5.05680847167969</t>
@@ -1076,64 +1076,64 @@
     <t xml:space="preserve">5.47287511825562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72891569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88894128799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84093427658081</t>
+    <t xml:space="preserve">5.72891521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88894176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84093379974365</t>
   </si>
   <si>
     <t xml:space="preserve">5.64890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6969108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85693597793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58489322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42486763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56888961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3448543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44086980819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37685871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26484107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24883890151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45687246322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53688478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29684734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21683359146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3530158996582</t>
+    <t xml:space="preserve">5.77692270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69691038131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85693645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58489227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42486715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34485387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44086933135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37685966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26484155654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24883842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45687198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53688526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29684591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21683311462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35301542282104</t>
   </si>
   <si>
     <t xml:space="preserve">6.28900527954102</t>
@@ -1148,37 +1148,37 @@
     <t xml:space="preserve">6.67306709289551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91310501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24915933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26516199111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28116369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64922285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58521223068237</t>
+    <t xml:space="preserve">6.91310548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24915885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26516056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28116464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64922332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58521270751953</t>
   </si>
   <si>
     <t xml:space="preserve">7.60121536254883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52120208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53720617294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47319459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44118976593018</t>
+    <t xml:space="preserve">7.52120161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5372052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47319507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44118881225586</t>
   </si>
   <si>
     <t xml:space="preserve">7.45719194412231</t>
@@ -1187,46 +1187,46 @@
     <t xml:space="preserve">7.40918445587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39318132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42518663406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50519943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36117696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2971658706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74523782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84125423431396</t>
+    <t xml:space="preserve">7.39318180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31316995620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42518711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50519990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36117601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29716634750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7452392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84125328063965</t>
   </si>
   <si>
     <t xml:space="preserve">7.82525062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90526342391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08129119873047</t>
+    <t xml:space="preserve">7.90526390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08129215240479</t>
   </si>
   <si>
     <t xml:space="preserve">8.04128646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92126655578613</t>
+    <t xml:space="preserve">7.92126560211182</t>
   </si>
   <si>
     <t xml:space="preserve">7.93726873397827</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">8.0012788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87325763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95327043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12129783630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96927356719971</t>
+    <t xml:space="preserve">7.8732590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95327138900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12129878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96927499771118</t>
   </si>
   <si>
     <t xml:space="preserve">8.28132343292236</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">9.00143909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12145900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96143054962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52152061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48151588439941</t>
+    <t xml:space="preserve">8.8414134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12145709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96143245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52152156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.72155380249023</t>
@@ -1286,70 +1286,70 @@
     <t xml:space="preserve">9.84157371520996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1616249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0816125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1216173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2816438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3216495513916</t>
+    <t xml:space="preserve">10.1616239547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0816106796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.121618270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2816429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3216485977173</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3218107223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.201789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1217784881592</t>
+    <t xml:space="preserve">11.3218088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2017908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1217775344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.0417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9617509841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1617822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8417339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.881739616394</t>
+    <t xml:space="preserve">10.9617519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1617841720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8417329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8817386627197</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0817708969116</t>
+    <t xml:space="preserve">11.241795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0817718505859</t>
   </si>
   <si>
     <t xml:space="preserve">10.7617197036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0017595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5216817855835</t>
+    <t xml:space="preserve">11.0017585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5216808319092</t>
   </si>
   <si>
     <t xml:space="preserve">10.60169506073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818040847778</t>
+    <t xml:space="preserve">11.2818031311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.6965761184692</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">10.7011213302612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4937353134155</t>
+    <t xml:space="preserve">10.4937362670898</t>
   </si>
   <si>
     <t xml:space="preserve">10.0374870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1204423904419</t>
+    <t xml:space="preserve">10.1204404830933</t>
   </si>
   <si>
     <t xml:space="preserve">10.1619186401367</t>
@@ -1397,46 +1397,46 @@
     <t xml:space="preserve">10.7425994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8255548477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5766906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8670301437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3693056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2448740005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2033948898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87157726287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.452260017395</t>
+    <t xml:space="preserve">10.825553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5766916275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8670310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3693046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863492965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.244873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2033958435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87157821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522581100464</t>
   </si>
   <si>
     <t xml:space="preserve">10.9499855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7840776443481</t>
+    <t xml:space="preserve">10.7840766906738</t>
   </si>
   <si>
     <t xml:space="preserve">11.1158933639526</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085083007812</t>
+    <t xml:space="preserve">10.9085073471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.535213470459</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">11.032940864563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.323281288147</t>
+    <t xml:space="preserve">11.3232793807983</t>
   </si>
   <si>
     <t xml:space="preserve">11.4891901016235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2403259277344</t>
+    <t xml:space="preserve">11.2403268814087</t>
   </si>
   <si>
     <t xml:space="preserve">11.5721435546875</t>
@@ -1463,19 +1463,19 @@
     <t xml:space="preserve">11.5306663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7795305252075</t>
+    <t xml:space="preserve">11.7795286178589</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772569656372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3602104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6505527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3187341690063</t>
+    <t xml:space="preserve">12.3602113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6505508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3187351226807</t>
   </si>
   <si>
     <t xml:space="preserve">12.5261201858521</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">13.2727098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5630521774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8119134902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6460056304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5215730667114</t>
+    <t xml:space="preserve">13.5630502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8119125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6460065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5215721130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3141860961914</t>
@@ -1508,61 +1508,61 @@
     <t xml:space="preserve">13.3556652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0192985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.894868850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.687481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2312316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1897554397583</t>
+    <t xml:space="preserve">14.0192995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8948669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6874828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2312326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1897563934326</t>
   </si>
   <si>
     <t xml:space="preserve">12.8994150161743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6090745925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4846420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.028392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3647584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062337875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8210067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1988496780396</t>
+    <t xml:space="preserve">12.609073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4846429824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0283937454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3647575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062356948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8210077285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1988487243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.4477128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7380533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78862285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66419124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.747145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624839782715</t>
+    <t xml:space="preserve">11.7380523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66419219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74714756011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624849319458</t>
   </si>
   <si>
     <t xml:space="preserve">11.6136207580566</t>
@@ -1571,28 +1571,28 @@
     <t xml:space="preserve">11.4808940887451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.066123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9665765762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7343044281006</t>
+    <t xml:space="preserve">11.0661220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9665775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7343034744263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6347589492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679410934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8504400253296</t>
+    <t xml:space="preserve">10.6347579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8504409790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9168043136597</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">10.8006687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9002132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8172588348389</t>
+    <t xml:space="preserve">10.9002122879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8172578811646</t>
   </si>
   <si>
     <t xml:space="preserve">10.7674856185913</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">10.5849866867065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4003810882568</t>
+    <t xml:space="preserve">11.4003820419312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4693698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.331392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2279100418091</t>
+    <t xml:space="preserve">11.3313932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2279090881348</t>
   </si>
   <si>
     <t xml:space="preserve">11.4866170883179</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">12.4179639816284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1937503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0212783813477</t>
+    <t xml:space="preserve">12.193751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.021279335022</t>
   </si>
   <si>
     <t xml:space="preserve">12.1420087814331</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">11.5038642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0730199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2106618881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7794828414917</t>
+    <t xml:space="preserve">12.0730209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7794818878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6932468414307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6242570877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0036964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1589202880859</t>
+    <t xml:space="preserve">10.6242580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0036954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1589193344116</t>
   </si>
   <si>
     <t xml:space="preserve">11.7625713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9522905349731</t>
+    <t xml:space="preserve">11.831561088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3831338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9522895812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7280778884888</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">11.5728521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7453231811523</t>
+    <t xml:space="preserve">11.7453241348267</t>
   </si>
   <si>
     <t xml:space="preserve">11.69358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6763362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8660554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2627401351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9867849349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9177951812744</t>
+    <t xml:space="preserve">11.6763353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8660545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2627391815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9867839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9177961349487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1765041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3144807815552</t>
+    <t xml:space="preserve">12.3144798278809</t>
   </si>
   <si>
     <t xml:space="preserve">12.3317279815674</t>
@@ -1742,28 +1742,28 @@
     <t xml:space="preserve">12.1247625350952</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107515335083</t>
+    <t xml:space="preserve">11.9695386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075143814087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0902681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7970666885376</t>
+    <t xml:space="preserve">11.7970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">11.6590890884399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5556039810181</t>
+    <t xml:space="preserve">11.6073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5556049346924</t>
   </si>
   <si>
     <t xml:space="preserve">11.3486394882202</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">11.3658866882324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.521110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5900993347168</t>
+    <t xml:space="preserve">11.5211114883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5901002883911</t>
   </si>
   <si>
     <t xml:space="preserve">11.6418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4348745346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0381908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1071786880493</t>
+    <t xml:space="preserve">11.4348754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0381898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.107177734375</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209426879883</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">11.1416730880737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9692010879517</t>
+    <t xml:space="preserve">10.969202041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.8829650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.641505241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1758308410645</t>
+    <t xml:space="preserve">10.6415061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1758317947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5207748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3483018875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.365550994873</t>
+    <t xml:space="preserve">10.3483028411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3655500411987</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">10.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1930780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4862794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.831223487854</t>
+    <t xml:space="preserve">10.193078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4862804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312244415283</t>
   </si>
   <si>
     <t xml:space="preserve">11.5383586883545</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">12.2972345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4007167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3662233352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4524583816528</t>
+    <t xml:space="preserve">12.4007177352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3662223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4524574279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.4869527816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5731887817383</t>
+    <t xml:space="preserve">12.573187828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.6421766281128</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">12.5386943817139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5041990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2799863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4352121353149</t>
+    <t xml:space="preserve">12.5041999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2799873352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4352111816406</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7108297348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2968969345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521217346191</t>
+    <t xml:space="preserve">11.7108306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2968978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521226882935</t>
   </si>
   <si>
     <t xml:space="preserve">11.2624034881592</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">11.2796506881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3141450881958</t>
+    <t xml:space="preserve">11.3141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9519538879395</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">11.0899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7967290878296</t>
+    <t xml:space="preserve">11.0554361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7967300415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.9347066879272</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">10.8657188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7622346878052</t>
+    <t xml:space="preserve">10.7622356414795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5725164413452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6070098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345388412476</t>
+    <t xml:space="preserve">10.6070108413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">10.4517860412598</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">10.469033241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5380220413208</t>
+    <t xml:space="preserve">10.5380229949951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4000453948975</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">10.3850517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4930410385132</t>
+    <t xml:space="preserve">10.4930419921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830335617065</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">10.1150760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93509197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97108840942383</t>
+    <t xml:space="preserve">9.93509292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97108936309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.89909648895264</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">10.1510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80910301208496</t>
+    <t xml:space="preserve">9.80910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.73711013793945</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">10.3490543365479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.421049118042</t>
+    <t xml:space="preserve">10.4210481643677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5290384292603</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">10.2950601577759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3670530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84510040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7011137008667</t>
+    <t xml:space="preserve">10.3670539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79110622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70111465454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.64711952209473</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">9.28715038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48513412475586</t>
+    <t xml:space="preserve">9.48513317108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.53912830352783</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">9.37714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35914516448975</t>
+    <t xml:space="preserve">9.35914421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.32314777374268</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">9.01717662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08917045593262</t>
+    <t xml:space="preserve">9.0891695022583</t>
   </si>
   <si>
     <t xml:space="preserve">9.05317306518555</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">8.87318897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85519027709961</t>
+    <t xml:space="preserve">8.85519123077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.97218132019043</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">8.62121200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63921070098877</t>
+    <t xml:space="preserve">8.63921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.63021183013916</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">8.35123729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20724964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9012770652771</t>
+    <t xml:space="preserve">8.20725059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90127801895142</t>
   </si>
   <si>
     <t xml:space="preserve">8.0992603302002</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">8.04526519775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05426406860352</t>
+    <t xml:space="preserve">8.05426502227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.00926780700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96427249908447</t>
+    <t xml:space="preserve">7.96427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">7.91027784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81128644943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89227914810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97327136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83828353881836</t>
+    <t xml:space="preserve">7.81128692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89227962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97327184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83828401565552</t>
   </si>
   <si>
     <t xml:space="preserve">7.91927671432495</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">7.78428888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79328775405884</t>
+    <t xml:space="preserve">7.793288230896</t>
   </si>
   <si>
     <t xml:space="preserve">7.64930152893066</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">7.72129487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63130235671997</t>
+    <t xml:space="preserve">7.63130283355713</t>
   </si>
   <si>
     <t xml:space="preserve">7.32533121109009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19934225082397</t>
+    <t xml:space="preserve">7.19934272766113</t>
   </si>
   <si>
     <t xml:space="preserve">7.1813440322876</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">6.75838279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95636463165283</t>
+    <t xml:space="preserve">6.95636415481567</t>
   </si>
   <si>
     <t xml:space="preserve">7.19034290313721</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">7.16334581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10935068130493</t>
+    <t xml:space="preserve">7.10935115814209</t>
   </si>
   <si>
     <t xml:space="preserve">7.25333786010742</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">7.51431369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30733203887939</t>
+    <t xml:space="preserve">7.49631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30733251571655</t>
   </si>
   <si>
     <t xml:space="preserve">7.46931791305542</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">7.07335424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00136041641235</t>
+    <t xml:space="preserve">7.00136089324951</t>
   </si>
   <si>
     <t xml:space="preserve">7.05535554885864</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">7.06435441970825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68529796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99127006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92827653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9462742805481</t>
+    <t xml:space="preserve">7.68529748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99127054214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92827701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94627475738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.16225433349609</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">8.27024459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37823486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55821895599365</t>
+    <t xml:space="preserve">8.37823581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55821800231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.75619983673096</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">8.74720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56721878051758</t>
+    <t xml:space="preserve">8.56721782684326</t>
   </si>
   <si>
     <t xml:space="preserve">8.61221313476562</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">8.30624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19824981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06326293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11725902557373</t>
+    <t xml:space="preserve">8.19825077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06326389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11725997924805</t>
   </si>
   <si>
     <t xml:space="preserve">8.414231300354</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">8.54921913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45922660827637</t>
+    <t xml:space="preserve">8.45922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.67520809173584</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">10.4390468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8170127868652</t>
+    <t xml:space="preserve">10.8170118331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.9789972305298</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">11.0509901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2489728927612</t>
+    <t xml:space="preserve">11.2489719390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.1229829788208</t>
@@ -2405,43 +2405,43 @@
     <t xml:space="preserve">11.4829511642456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4649524688721</t>
+    <t xml:space="preserve">11.4649515151978</t>
   </si>
   <si>
     <t xml:space="preserve">11.2669706344604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3389654159546</t>
+    <t xml:space="preserve">11.3389644622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.3029680252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3749618530273</t>
+    <t xml:space="preserve">11.374960899353</t>
   </si>
   <si>
     <t xml:space="preserve">11.4469547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6089391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5009498596191</t>
+    <t xml:space="preserve">11.6089382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5009489059448</t>
   </si>
   <si>
     <t xml:space="preserve">11.5729427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9689064025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7349281311035</t>
+    <t xml:space="preserve">11.9689073562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709245681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7349271774292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7889232635498</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">11.7529268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429174423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8069219589233</t>
+    <t xml:space="preserve">11.8429183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.6198072433472</t>
@@ -2526,9 +2526,6 @@
   </si>
   <si>
     <t xml:space="preserve">11.3952703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.806921005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.4139814376831</t>
@@ -59962,7 +59959,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2171" t="s">
-        <v>838</v>
+        <v>813</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60014,7 +60011,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60118,7 +60115,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2177" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60144,7 +60141,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2178" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60170,7 +60167,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2179" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60196,7 +60193,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2180" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60248,7 +60245,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2182" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60352,7 +60349,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2186" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60378,7 +60375,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2187" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60404,7 +60401,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2188" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60430,7 +60427,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2189" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60534,7 +60531,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2193" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60560,7 +60557,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2194" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60586,7 +60583,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2195" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60612,7 +60609,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2196" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60638,7 +60635,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60742,7 +60739,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2201" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60872,7 +60869,7 @@
         <v>12</v>
       </c>
       <c r="G2206" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60898,7 +60895,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2207" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60924,7 +60921,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2208" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60976,7 +60973,7 @@
         <v>12</v>
       </c>
       <c r="G2210" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61002,7 +60999,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2211" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61054,7 +61051,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2213" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61080,7 +61077,7 @@
         <v>13</v>
       </c>
       <c r="G2214" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61106,7 +61103,7 @@
         <v>13</v>
       </c>
       <c r="G2215" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61132,7 +61129,7 @@
         <v>13</v>
       </c>
       <c r="G2216" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61184,7 +61181,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2218" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61236,7 +61233,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2220" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61262,7 +61259,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2221" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61314,7 +61311,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2223" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61340,7 +61337,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2224" t="s">
-        <v>838</v>
+        <v>813</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61366,7 +61363,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2225" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61418,7 +61415,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61444,7 +61441,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2228" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61496,7 +61493,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2230" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61652,7 +61649,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2236" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61756,7 +61753,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2240" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61782,7 +61779,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2241" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61938,7 +61935,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2247" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61964,7 +61961,7 @@
         <v>12</v>
       </c>
       <c r="G2248" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61990,7 +61987,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2249" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62016,7 +62013,7 @@
         <v>12</v>
       </c>
       <c r="G2250" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62042,7 +62039,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2251" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62068,7 +62065,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2252" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62094,7 +62091,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2253" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62120,7 +62117,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2254" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62146,7 +62143,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G2255" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62172,7 +62169,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2256" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62198,7 +62195,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2257" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62224,7 +62221,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2258" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62250,7 +62247,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G2259" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62276,7 +62273,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2260" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62302,7 +62299,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62328,7 +62325,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62354,7 +62351,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62380,7 +62377,7 @@
         <v>11.5</v>
       </c>
       <c r="G2264" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62406,7 +62403,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2265" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62432,7 +62429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2266" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62458,7 +62455,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2267" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62484,7 +62481,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2268" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62510,7 +62507,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2269" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62536,7 +62533,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G2270" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62562,7 +62559,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G2271" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62588,7 +62585,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2272" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62614,7 +62611,7 @@
         <v>11</v>
       </c>
       <c r="G2273" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62640,7 +62637,7 @@
         <v>11</v>
       </c>
       <c r="G2274" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62666,7 +62663,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2275" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62692,7 +62689,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G2276" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62718,7 +62715,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G2277" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62744,7 +62741,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2278" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62770,7 +62767,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2279" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62796,7 +62793,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2280" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62822,7 +62819,7 @@
         <v>10.5</v>
       </c>
       <c r="G2281" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62848,7 +62845,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G2282" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62874,7 +62871,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2283" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62900,7 +62897,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2284" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62926,7 +62923,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2285" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62952,7 +62949,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G2286" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62978,7 +62975,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G2287" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63004,7 +63001,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G2288" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63030,7 +63027,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2289" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63056,7 +63053,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2290" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63082,7 +63079,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2291" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63108,7 +63105,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2292" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63134,7 +63131,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2293" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63160,7 +63157,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2294" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63186,7 +63183,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2295" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63212,7 +63209,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2296" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63238,7 +63235,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63264,7 +63261,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2298" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63290,7 +63287,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2299" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63316,7 +63313,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2300" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63342,7 +63339,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2301" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63368,7 +63365,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G2302" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63394,7 +63391,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2303" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63420,7 +63417,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2304" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63446,7 +63443,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2305" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63472,7 +63469,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G2306" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63498,7 +63495,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2307" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63524,7 +63521,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2308" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63550,7 +63547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G2309" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63576,7 +63573,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G2310" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63602,7 +63599,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2311" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63628,7 +63625,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G2312" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63654,7 +63651,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2313" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63680,7 +63677,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G2314" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63706,7 +63703,7 @@
         <v>9.5</v>
       </c>
       <c r="G2315" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63732,7 +63729,7 @@
         <v>9.5</v>
       </c>
       <c r="G2316" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63758,7 +63755,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G2317" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63784,7 +63781,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2318" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63810,7 +63807,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2319" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63836,7 +63833,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G2320" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63862,7 +63859,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2321" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63888,7 +63885,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2322" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63914,7 +63911,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2323" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63940,7 +63937,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2324" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63966,7 +63963,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G2325" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63992,7 +63989,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G2326" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64018,7 +64015,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2327" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64044,7 +64041,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G2328" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64070,7 +64067,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G2329" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64096,7 +64093,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2330" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64122,7 +64119,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2331" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64148,7 +64145,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2332" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64174,7 +64171,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2333" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64200,7 +64197,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G2334" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64226,7 +64223,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2335" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64252,7 +64249,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2336" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64278,7 +64275,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G2337" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64304,7 +64301,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G2338" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64330,7 +64327,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2339" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64356,7 +64353,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2340" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64382,7 +64379,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2341" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64408,7 +64405,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2342" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64434,7 +64431,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2343" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64460,7 +64457,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2344" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64486,7 +64483,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2345" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64512,7 +64509,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64538,7 +64535,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2347" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64564,7 +64561,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G2348" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64590,7 +64587,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2349" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64616,7 +64613,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64642,7 +64639,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2351" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64668,7 +64665,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2352" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64694,7 +64691,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G2353" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64720,7 +64717,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2354" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64746,7 +64743,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2355" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64772,7 +64769,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2356" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64798,7 +64795,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G2357" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64824,7 +64821,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64850,7 +64847,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2359" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64876,7 +64873,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G2360" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64902,7 +64899,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G2361" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64928,7 +64925,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G2362" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64954,7 +64951,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2363" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64980,7 +64977,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2364" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65006,7 +65003,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2365" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65032,7 +65029,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G2366" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65058,7 +65055,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2367" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65084,7 +65081,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G2368" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65110,7 +65107,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65136,7 +65133,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65162,7 +65159,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2371" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65188,7 +65185,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2372" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65214,7 +65211,7 @@
         <v>9.5</v>
       </c>
       <c r="G2373" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65240,7 +65237,7 @@
         <v>9.75</v>
       </c>
       <c r="G2374" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65266,7 +65263,7 @@
         <v>9.75</v>
       </c>
       <c r="G2375" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65292,7 +65289,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2376" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65318,7 +65315,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G2377" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65344,7 +65341,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G2378" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65370,7 +65367,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G2379" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65396,7 +65393,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G2380" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65422,7 +65419,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65448,7 +65445,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G2382" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65474,7 +65471,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G2383" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65500,7 +65497,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G2384" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65526,7 +65523,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G2385" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65552,7 +65549,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G2386" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65578,7 +65575,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2387" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65604,7 +65601,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G2388" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65630,7 +65627,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2389" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65656,7 +65653,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G2390" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65682,7 +65679,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G2391" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65708,7 +65705,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G2392" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65734,7 +65731,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2393" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65760,7 +65757,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G2394" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65786,7 +65783,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2395" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65812,7 +65809,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2396" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65838,7 +65835,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2397" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65864,7 +65861,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2398" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65890,7 +65887,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2399" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65916,7 +65913,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2400" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65942,7 +65939,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G2401" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65968,7 +65965,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2402" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65994,7 +65991,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G2403" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66020,7 +66017,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66046,7 +66043,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66072,7 +66069,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G2406" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66098,7 +66095,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G2407" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66124,7 +66121,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2408" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66150,7 +66147,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G2409" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66176,7 +66173,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2410" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66202,7 +66199,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2411" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66228,7 +66225,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2412" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66254,7 +66251,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2413" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66280,7 +66277,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2414" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66306,7 +66303,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G2415" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66332,7 +66329,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2416" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66358,7 +66355,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2417" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66384,7 +66381,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66410,7 +66407,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2419" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66436,7 +66433,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G2420" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66462,7 +66459,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2421" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66488,7 +66485,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2422" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66514,7 +66511,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2423" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66540,7 +66537,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2424" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66566,7 +66563,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G2425" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66592,7 +66589,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2426" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66618,7 +66615,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G2427" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66644,7 +66641,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2428" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66670,7 +66667,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2429" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66696,7 +66693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2430" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66722,7 +66719,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G2431" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66748,7 +66745,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G2432" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66774,7 +66771,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2433" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66800,7 +66797,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G2434" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66826,7 +66823,7 @@
         <v>15.5</v>
       </c>
       <c r="G2435" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66852,7 +66849,7 @@
         <v>15.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66878,7 +66875,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G2437" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66904,7 +66901,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G2438" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66930,7 +66927,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G2439" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66956,7 +66953,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66982,7 +66979,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G2441" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67008,7 +67005,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G2442" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67034,7 +67031,7 @@
         <v>16</v>
       </c>
       <c r="G2443" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67060,7 +67057,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G2444" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67086,7 +67083,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2445" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67112,7 +67109,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67138,7 +67135,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G2447" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67164,7 +67161,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2448" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67190,7 +67187,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67216,7 +67213,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G2450" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67242,7 +67239,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G2451" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67268,7 +67265,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2452" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67294,7 +67291,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G2453" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67320,7 +67317,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2454" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67346,7 +67343,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67372,7 +67369,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G2456" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67398,7 +67395,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2457" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67424,7 +67421,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G2458" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67450,7 +67447,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67476,7 +67473,7 @@
         <v>17.5</v>
       </c>
       <c r="G2460" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67502,7 +67499,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G2461" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67528,7 +67525,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2462" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67554,7 +67551,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G2463" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67580,7 +67577,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67606,7 +67603,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67632,7 +67629,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2466" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67658,7 +67655,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67684,7 +67681,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67710,7 +67707,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G2469" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67736,7 +67733,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G2470" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67762,7 +67759,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2471" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67788,7 +67785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2472" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67814,7 +67811,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G2473" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67840,7 +67837,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67866,7 +67863,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67892,7 +67889,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G2476" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67918,7 +67915,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G2477" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67944,7 +67941,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G2478" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67970,7 +67967,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G2479" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67996,7 +67993,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G2480" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68022,7 +68019,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2481" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68048,7 +68045,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G2482" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68074,7 +68071,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2483" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68100,7 +68097,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68126,7 +68123,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2485" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68152,7 +68149,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G2486" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68178,7 +68175,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G2487" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68204,7 +68201,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68230,7 +68227,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G2489" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68256,7 +68253,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G2490" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68282,7 +68279,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G2491" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68308,7 +68305,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2492" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68334,7 +68331,7 @@
         <v>17.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68360,7 +68357,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G2494" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68386,7 +68383,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G2495" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68412,7 +68409,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G2496" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68438,7 +68435,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G2497" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68464,7 +68461,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G2498" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68490,7 +68487,7 @@
         <v>17</v>
       </c>
       <c r="G2499" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68516,7 +68513,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G2500" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68542,7 +68539,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G2501" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68568,7 +68565,7 @@
         <v>17</v>
       </c>
       <c r="G2502" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68594,7 +68591,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G2503" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68620,7 +68617,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2504" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68646,7 +68643,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2505" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68672,7 +68669,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2506" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68698,7 +68695,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G2507" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68724,7 +68721,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G2508" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68750,7 +68747,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G2509" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68776,7 +68773,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G2510" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68802,7 +68799,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G2511" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68828,7 +68825,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2512" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68854,7 +68851,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G2513" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68880,7 +68877,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68906,7 +68903,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G2515" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68932,7 +68929,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2516" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68958,7 +68955,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2517" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68984,7 +68981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G2518" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -69010,7 +69007,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2519" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -69036,7 +69033,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2520" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -69062,7 +69059,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G2521" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -69088,7 +69085,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2522" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -69114,7 +69111,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G2523" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -69140,7 +69137,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G2524" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -69166,7 +69163,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2525" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69192,7 +69189,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G2526" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69218,7 +69215,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G2527" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69244,7 +69241,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G2528" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -69270,7 +69267,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G2529" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -69296,7 +69293,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G2530" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -69322,7 +69319,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2531" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -69348,7 +69345,7 @@
         <v>16.5</v>
       </c>
       <c r="G2532" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -69374,7 +69371,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G2533" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -69400,7 +69397,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G2534" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -69426,7 +69423,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G2535" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -69452,7 +69449,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2536" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -69460,7 +69457,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6912268518</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>12029</v>
@@ -69478,9 +69475,35 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G2537" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.69125</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>51151</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>16.3999996185303</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>990</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GPI.MI.xlsx
+++ b/data/GPI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="1059">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18217468261719</t>
+    <t xml:space="preserve">7.18217372894287</t>
   </si>
   <si>
     <t xml:space="preserve">GPI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16394472122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0728006362915</t>
+    <t xml:space="preserve">7.16394519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14571666717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07280111312866</t>
   </si>
   <si>
     <t xml:space="preserve">7.10925817489624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93061590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89051294326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14206981658936</t>
+    <t xml:space="preserve">6.93061542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89051198959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14207029342651</t>
   </si>
   <si>
     <t xml:space="preserve">6.96707344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00717735290527</t>
+    <t xml:space="preserve">7.03634309768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00717639923096</t>
   </si>
   <si>
     <t xml:space="preserve">6.96342802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2514443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2769627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36446380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2915472984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32800579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21863126754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26238203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40821170806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.393630027771</t>
+    <t xml:space="preserve">7.25144338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27696371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36446475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29154777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32800483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21863079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40821218490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39362955093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.43737840652466</t>
@@ -110,46 +110,46 @@
     <t xml:space="preserve">7.28790187835693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28425550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43008756637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51029348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66341733932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64154100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48841953277588</t>
+    <t xml:space="preserve">7.28425598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43008613586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51029443740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66341638565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64154195785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48841905593872</t>
   </si>
   <si>
     <t xml:space="preserve">7.48112726211548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30613088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6196665763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54675102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5321683883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25509071350098</t>
+    <t xml:space="preserve">7.30613136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61966562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54675149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53216743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2550892829895</t>
   </si>
   <si>
     <t xml:space="preserve">7.33529710769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34988021850586</t>
+    <t xml:space="preserve">7.34988069534302</t>
   </si>
   <si>
     <t xml:space="preserve">7.2988395690918</t>
@@ -161,58 +161,58 @@
     <t xml:space="preserve">7.24779748916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21498727798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24050664901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02175998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99623966217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9780101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52487754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47383594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20404863357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38633632659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50300264358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56133508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58320951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71445655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72904109954834</t>
+    <t xml:space="preserve">7.2149863243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24050569534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99988555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99624013900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97801065444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52487659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2040491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38633728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50300121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56133270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72903919219971</t>
   </si>
   <si>
     <t xml:space="preserve">7.87487077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94778728485107</t>
+    <t xml:space="preserve">7.94778633117676</t>
   </si>
   <si>
     <t xml:space="preserve">8.03528594970703</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">8.12278270721436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98424386978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14273071289062</t>
+    <t xml:space="preserve">7.98424482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14273166656494</t>
   </si>
   <si>
     <t xml:space="preserve">8.24770259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18022060394287</t>
+    <t xml:space="preserve">8.18022155761719</t>
   </si>
   <si>
     <t xml:space="preserve">8.09774398803711</t>
@@ -239,37 +239,37 @@
     <t xml:space="preserve">8.07525157928467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88030672073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79782772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61787796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68535947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64787006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85781097412109</t>
+    <t xml:space="preserve">7.88030481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79782676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61787843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68535995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6478705406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85781002044678</t>
   </si>
   <si>
     <t xml:space="preserve">7.98527669906616</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8953013420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02276611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0602560043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68258285522461</t>
+    <t xml:space="preserve">7.89530229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02276420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06025505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68258190155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.47264099121094</t>
@@ -281,52 +281,52 @@
     <t xml:space="preserve">9.43987083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25992107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13245582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98249816894531</t>
+    <t xml:space="preserve">9.25992012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31990528106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1324577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98250007629395</t>
   </si>
   <si>
     <t xml:space="preserve">8.92251586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99749279022217</t>
+    <t xml:space="preserve">8.9974946975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89252281188965</t>
+    <t xml:space="preserve">8.89252376556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.66008853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6975793838501</t>
+    <t xml:space="preserve">8.69757747650146</t>
   </si>
   <si>
     <t xml:space="preserve">8.59260749816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84753799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77255821228027</t>
+    <t xml:space="preserve">8.84753513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77255725860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.8100471496582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81754493713379</t>
+    <t xml:space="preserve">8.81754398345947</t>
   </si>
   <si>
     <t xml:space="preserve">8.72756958007812</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">8.70507526397705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7950496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64509296417236</t>
+    <t xml:space="preserve">8.79504871368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64509201049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72007179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69007968902588</t>
+    <t xml:space="preserve">8.6900806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.60010528564453</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">8.3676700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.38266563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259864807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.61509990692139</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">8.41265773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73506832122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87003040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67508411407471</t>
+    <t xml:space="preserve">8.28519248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32268142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73506641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87002944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90002155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67508316040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.51762771606445</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">8.58510875701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51012992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40515899658203</t>
+    <t xml:space="preserve">8.51013088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40515804290771</t>
   </si>
   <si>
     <t xml:space="preserve">8.3601713180542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31518459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30018901824951</t>
+    <t xml:space="preserve">8.31518363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39766120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727237701416</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">8.45764446258545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42015361785889</t>
+    <t xml:space="preserve">8.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.21021270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1127405166626</t>
+    <t xml:space="preserve">8.11273956298828</t>
   </si>
   <si>
     <t xml:space="preserve">8.09024715423584</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">8.06775283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08274936676025</t>
+    <t xml:space="preserve">8.08274841308594</t>
   </si>
   <si>
     <t xml:space="preserve">8.12773609161377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99277448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97777938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526737213135</t>
+    <t xml:space="preserve">8.18771934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99277353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526832580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.13523483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24020481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22521018981934</t>
+    <t xml:space="preserve">8.24020385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22520923614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.1202392578125</t>
@@ -467,34 +467,34 @@
     <t xml:space="preserve">8.00776958465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76783657073975</t>
+    <t xml:space="preserve">7.76783561706543</t>
   </si>
   <si>
     <t xml:space="preserve">7.82781887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81282520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9552845954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03776073455811</t>
+    <t xml:space="preserve">7.81282424926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95528554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.16522598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93279027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88780307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92529201507568</t>
+    <t xml:space="preserve">7.93279075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88780212402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92529344558716</t>
   </si>
   <si>
     <t xml:space="preserve">7.87280750274658</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">7.760338306427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83531713485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0966796875</t>
+    <t xml:space="preserve">7.83531808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09667873382568</t>
   </si>
   <si>
     <t xml:space="preserve">7.7882342338562</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">7.69569969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74967908859253</t>
+    <t xml:space="preserve">7.7496771812439</t>
   </si>
   <si>
     <t xml:space="preserve">8.01956653594971</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">7.98101234436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90390062332153</t>
+    <t xml:space="preserve">7.90390157699585</t>
   </si>
   <si>
     <t xml:space="preserve">7.8653450012207</t>
@@ -536,37 +536,37 @@
     <t xml:space="preserve">8.21234607696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82678985595703</t>
+    <t xml:space="preserve">7.82678890228271</t>
   </si>
   <si>
     <t xml:space="preserve">7.7111234664917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66485595703125</t>
+    <t xml:space="preserve">7.66485548019409</t>
   </si>
   <si>
     <t xml:space="preserve">7.55690050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858892440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54147815704346</t>
+    <t xml:space="preserve">7.51063346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5414776802063</t>
   </si>
   <si>
     <t xml:space="preserve">7.4797887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32556772232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41809892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38725519180298</t>
+    <t xml:space="preserve">7.32556676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41810083389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38725566864014</t>
   </si>
   <si>
     <t xml:space="preserve">7.21761131286621</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">7.03254365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23303318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24845409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26387691497803</t>
+    <t xml:space="preserve">7.23303365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24845552444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26387739181519</t>
   </si>
   <si>
     <t xml:space="preserve">7.12507677078247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27929878234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17134380340576</t>
+    <t xml:space="preserve">7.27930021286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">7.20218849182129</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">7.10965538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14050006866455</t>
+    <t xml:space="preserve">7.14049959182739</t>
   </si>
   <si>
     <t xml:space="preserve">7.0788106918335</t>
@@ -608,79 +608,79 @@
     <t xml:space="preserve">7.29472303390503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31014394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09423208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00169897079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90916633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83205461502075</t>
+    <t xml:space="preserve">7.310142993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09423303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00169849395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90916538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83205413818359</t>
   </si>
   <si>
     <t xml:space="preserve">6.92458772659302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72409915924072</t>
+    <t xml:space="preserve">6.72409868240356</t>
   </si>
   <si>
     <t xml:space="preserve">6.73952054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86289930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0171217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78578758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95543336868286</t>
+    <t xml:space="preserve">6.86289739608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01712131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7857871055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95543241500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.98627710342407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67783164978027</t>
+    <t xml:space="preserve">6.67783117294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.7086763381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63156509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47734212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53903198242188</t>
+    <t xml:space="preserve">6.63156604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47734260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46192073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53903150558472</t>
   </si>
   <si>
     <t xml:space="preserve">6.61614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52360916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19974279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23058652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32312059402466</t>
+    <t xml:space="preserve">6.52360963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19974184036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23058748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3231201171875</t>
   </si>
   <si>
     <t xml:space="preserve">6.40023136138916</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">6.27685403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5698766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29227590560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41565370559692</t>
+    <t xml:space="preserve">6.56987619400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29227542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41565322875977</t>
   </si>
   <si>
     <t xml:space="preserve">6.55445384979248</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">6.81663227081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89374256134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6469874382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77036571502686</t>
+    <t xml:space="preserve">6.89374303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64698696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7703652381897</t>
   </si>
   <si>
     <t xml:space="preserve">6.43107652664185</t>
@@ -728,61 +728,61 @@
     <t xml:space="preserve">6.09178686141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30769920349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99925327301025</t>
+    <t xml:space="preserve">6.30769824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9992527961731</t>
   </si>
   <si>
     <t xml:space="preserve">6.24600982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66241025924683</t>
+    <t xml:space="preserve">6.66240978240967</t>
   </si>
   <si>
     <t xml:space="preserve">6.49276494979858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35396528244019</t>
+    <t xml:space="preserve">6.35396432876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.44649839401245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21516513824463</t>
+    <t xml:space="preserve">6.21516466140747</t>
   </si>
   <si>
     <t xml:space="preserve">6.36938714981079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75494289398193</t>
+    <t xml:space="preserve">6.75494241714478</t>
   </si>
   <si>
     <t xml:space="preserve">6.87832164764404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97085475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04796648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15592050552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18676614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2011513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15314245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07313013076782</t>
+    <t xml:space="preserve">6.97085380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.155921459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18676662445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338834762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20115089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15314340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">6.64106178283691</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">7.08913326263428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12113857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.833092212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88110017776489</t>
+    <t xml:space="preserve">7.12113761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83309268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88110065460205</t>
   </si>
   <si>
     <t xml:space="preserve">6.86509704589844</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">6.78508472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75307893753052</t>
+    <t xml:space="preserve">6.75307941436768</t>
   </si>
   <si>
     <t xml:space="preserve">6.73707675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72107410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48103618621826</t>
+    <t xml:space="preserve">6.72107458114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48103666305542</t>
   </si>
   <si>
     <t xml:space="preserve">6.54504680633545</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">6.76908206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80108737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89710187911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81709003448486</t>
+    <t xml:space="preserve">6.80108785629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89710235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81708955764771</t>
   </si>
   <si>
     <t xml:space="preserve">6.56104850769043</t>
@@ -845,31 +845,31 @@
     <t xml:space="preserve">6.65706396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59305381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62505865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57705163955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52904367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43302822113037</t>
+    <t xml:space="preserve">6.59305334091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62505912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57705211639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52904415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43302774429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.5130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44903135299683</t>
+    <t xml:space="preserve">6.44903182983398</t>
   </si>